--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\study\개인 공부\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1116DB6A-FF97-4CA0-A80E-1FA2B19E73EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8730336-3879-4B3B-901D-BB1AB8045717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="126">
   <si>
     <t>팀명</t>
   </si>
@@ -402,29 +402,13 @@
   </si>
   <si>
     <t>주요기능 개발 단계</t>
-  </si>
-  <si>
-    <t>10일</t>
-    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>메인 페이지 프로토타입 구현</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>2일</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>김석현, 이재빈, 정윤성</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>3일</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>6일</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -973,6 +957,9 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1005,9 +992,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,31 +1224,31 @@
       <c r="B1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48" t="s">
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -1328,7 +1312,7 @@
       <c r="F2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="50" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -1516,7 +1500,7 @@
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="21">
         <v>45951</v>
       </c>
@@ -1696,7 +1680,7 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="52" t="s">
         <v>73</v>
       </c>
       <c r="B4" s="25" t="s">
@@ -1705,8 +1689,9 @@
       <c r="C4" s="26">
         <v>1</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>15</v>
+      <c r="D4" s="27">
+        <f>IF(AND(F4&lt;&gt;"", E4&lt;&gt;""), F4-E4+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E4" s="28">
         <v>45951</v>
@@ -1778,15 +1763,16 @@
       <c r="BN4" s="31"/>
     </row>
     <row r="5" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="52"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="25" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="26">
         <v>1</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>15</v>
+      <c r="D5" s="27">
+        <f>IF(AND(F5&lt;&gt;"", E5&lt;&gt;""), F5-E5+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E5" s="28">
         <v>45951</v>
@@ -1858,15 +1844,16 @@
       <c r="BN5" s="31"/>
     </row>
     <row r="6" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="52"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="25" t="s">
         <v>76</v>
       </c>
       <c r="C6" s="26">
         <v>1</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>15</v>
+      <c r="D6" s="27">
+        <f>IF(AND(F6&lt;&gt;"", E6&lt;&gt;""), F6-E6+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E6" s="28">
         <v>45951</v>
@@ -1938,15 +1925,16 @@
       <c r="BN6" s="31"/>
     </row>
     <row r="7" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="52"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="34" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="26">
         <v>0.5</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>24</v>
+      <c r="D7" s="27">
+        <f>IF(AND(F7&lt;&gt;"", E7&lt;&gt;""), F7-E7+1, "")</f>
+        <v>11</v>
       </c>
       <c r="E7" s="28">
         <v>45951</v>
@@ -2018,15 +2006,16 @@
       <c r="BN7" s="31"/>
     </row>
     <row r="8" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="52"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="35" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>26</v>
+      <c r="D8" s="27">
+        <f>IF(AND(F8&lt;&gt;"", E8&lt;&gt;""), F8-E8+1, "")</f>
+        <v>13</v>
       </c>
       <c r="E8" s="28">
         <v>45954</v>
@@ -2098,15 +2087,16 @@
       <c r="BN8" s="31"/>
     </row>
     <row r="9" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="52"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="36" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="26">
         <v>0</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>14</v>
+      <c r="D9" s="27">
+        <f>IF(AND(F9&lt;&gt;"", E9&lt;&gt;""), F9-E9+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E9" s="28">
         <v>45962</v>
@@ -2178,15 +2168,16 @@
       <c r="BN9" s="31"/>
     </row>
     <row r="10" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="34" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="26">
         <v>0</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>23</v>
+      <c r="D10" s="27">
+        <f>IF(AND(F10&lt;&gt;"", E10&lt;&gt;""), F10-E10+1, "")</f>
+        <v>10</v>
       </c>
       <c r="E10" s="28">
         <v>45952</v>
@@ -2258,15 +2249,16 @@
       <c r="BN10" s="31"/>
     </row>
     <row r="11" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="37" t="s">
         <v>81</v>
       </c>
       <c r="C11" s="26">
         <v>0</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>15</v>
+      <c r="D11" s="27">
+        <f>IF(AND(F11&lt;&gt;"", E11&lt;&gt;""), F11-E11+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E11" s="28">
         <v>45957</v>
@@ -2338,7 +2330,7 @@
       <c r="BN11" s="31"/>
     </row>
     <row r="12" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="44" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -2347,8 +2339,9 @@
       <c r="C12" s="26">
         <v>0</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>14</v>
+      <c r="D12" s="27">
+        <f>IF(AND(F12&lt;&gt;"", E12&lt;&gt;""), F12-E12+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E12" s="28">
         <v>45959</v>
@@ -2418,15 +2411,16 @@
       <c r="BN12" s="31"/>
     </row>
     <row r="13" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="44"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="26">
         <v>0</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>14</v>
+      <c r="D13" s="27">
+        <f>IF(AND(F13&lt;&gt;"", E13&lt;&gt;""), F13-E13+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E13" s="28">
         <v>45959</v>
@@ -2498,15 +2492,16 @@
       <c r="BN13" s="31"/>
     </row>
     <row r="14" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="44"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="25" t="s">
         <v>85</v>
       </c>
       <c r="C14" s="26">
         <v>0</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>14</v>
+      <c r="D14" s="27">
+        <f>IF(AND(F14&lt;&gt;"", E14&lt;&gt;""), F14-E14+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E14" s="28">
         <v>45959</v>
@@ -2578,15 +2573,16 @@
       <c r="BN14" s="31"/>
     </row>
     <row r="15" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="44"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="38" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="26">
         <v>0</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>31</v>
+      <c r="D15" s="27">
+        <f>IF(AND(F15&lt;&gt;"", E15&lt;&gt;""), F15-E15+1, "")</f>
+        <v>18</v>
       </c>
       <c r="E15" s="28">
         <v>45964</v>
@@ -2656,15 +2652,16 @@
       <c r="BN15" s="31"/>
     </row>
     <row r="16" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="44"/>
+      <c r="A16" s="45"/>
       <c r="B16" s="41" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="26">
         <v>0</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>14</v>
+      <c r="D16" s="27">
+        <f>IF(AND(F16&lt;&gt;"", E16&lt;&gt;""), F16-E16+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E16" s="28">
         <v>45966</v>
@@ -2736,15 +2733,16 @@
       <c r="BN16" s="31"/>
     </row>
     <row r="17" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="44"/>
-      <c r="B17" s="54" t="s">
-        <v>124</v>
+      <c r="A17" s="45"/>
+      <c r="B17" s="43" t="s">
+        <v>123</v>
       </c>
       <c r="C17" s="26">
         <v>0</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>125</v>
+      <c r="D17" s="27">
+        <f>IF(AND(F17&lt;&gt;"", E17&lt;&gt;""), F17-E17+1, "")</f>
+        <v>3</v>
       </c>
       <c r="E17" s="28">
         <v>45966</v>
@@ -2753,7 +2751,7 @@
         <v>45968</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -2816,15 +2814,16 @@
       <c r="BN17" s="31"/>
     </row>
     <row r="18" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="44"/>
+      <c r="A18" s="45"/>
       <c r="B18" s="41" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="26">
         <v>0</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>127</v>
+      <c r="D18" s="27">
+        <f>IF(AND(F18&lt;&gt;"", E18&lt;&gt;""), F18-E18+1, "")</f>
+        <v>4</v>
       </c>
       <c r="E18" s="28">
         <v>45968</v>
@@ -2896,15 +2895,16 @@
       <c r="BN18" s="31"/>
     </row>
     <row r="19" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="44"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="41" t="s">
         <v>114</v>
       </c>
       <c r="C19" s="26">
         <v>0</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>127</v>
+      <c r="D19" s="27">
+        <f>IF(AND(F19&lt;&gt;"", E19&lt;&gt;""), F19-E19+1, "")</f>
+        <v>4</v>
       </c>
       <c r="E19" s="28">
         <v>45968</v>
@@ -2976,15 +2976,16 @@
       <c r="BN19" s="31"/>
     </row>
     <row r="20" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="44"/>
+      <c r="A20" s="45"/>
       <c r="B20" s="41" t="s">
         <v>116</v>
       </c>
       <c r="C20" s="26">
         <v>0</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>127</v>
+      <c r="D20" s="27">
+        <f>IF(AND(F20&lt;&gt;"", E20&lt;&gt;""), F20-E20+1, "")</f>
+        <v>4</v>
       </c>
       <c r="E20" s="28">
         <v>45968</v>
@@ -3056,15 +3057,16 @@
       <c r="BN20" s="31"/>
     </row>
     <row r="21" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="44"/>
+      <c r="A21" s="45"/>
       <c r="B21" s="41" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="26">
         <v>0</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>128</v>
+      <c r="D21" s="27">
+        <f>IF(AND(F21&lt;&gt;"", E21&lt;&gt;""), F21-E21+1, "")</f>
+        <v>6</v>
       </c>
       <c r="E21" s="28">
         <v>45972</v>
@@ -3136,15 +3138,16 @@
       <c r="BN21" s="31"/>
     </row>
     <row r="22" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="44"/>
+      <c r="A22" s="45"/>
       <c r="B22" s="41" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="26">
         <v>0</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>128</v>
+      <c r="D22" s="27">
+        <f>IF(AND(F22&lt;&gt;"", E22&lt;&gt;""), F22-E22+1, "")</f>
+        <v>6</v>
       </c>
       <c r="E22" s="28">
         <v>45972</v>
@@ -3216,15 +3219,16 @@
       <c r="BN22" s="31"/>
     </row>
     <row r="23" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="44"/>
+      <c r="A23" s="45"/>
       <c r="B23" s="41" t="s">
         <v>89</v>
       </c>
       <c r="C23" s="26">
         <v>0</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>128</v>
+      <c r="D23" s="27">
+        <f>IF(AND(F23&lt;&gt;"", E23&lt;&gt;""), F23-E23+1, "")</f>
+        <v>6</v>
       </c>
       <c r="E23" s="28">
         <v>45972</v>
@@ -3296,15 +3300,16 @@
       <c r="BN23" s="31"/>
     </row>
     <row r="24" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="44"/>
+      <c r="A24" s="45"/>
       <c r="B24" s="37" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="26">
         <v>0</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>125</v>
+      <c r="D24" s="27">
+        <f>IF(AND(F24&lt;&gt;"", E24&lt;&gt;""), F24-E24+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E24" s="28">
         <v>45964</v>
@@ -3313,7 +3318,7 @@
         <v>45965</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="31"/>
@@ -3376,15 +3381,16 @@
       <c r="BN24" s="31"/>
     </row>
     <row r="25" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="44"/>
+      <c r="A25" s="45"/>
       <c r="B25" s="37" t="s">
         <v>91</v>
       </c>
       <c r="C25" s="26">
         <v>0</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>21</v>
+      <c r="D25" s="27">
+        <f>IF(AND(F25&lt;&gt;"", E25&lt;&gt;""), F25-E25+1, "")</f>
+        <v>7</v>
       </c>
       <c r="E25" s="28">
         <v>45965</v>
@@ -3456,15 +3462,16 @@
       <c r="BN25" s="31"/>
     </row>
     <row r="26" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="44"/>
+      <c r="A26" s="45"/>
       <c r="B26" s="37" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="26">
         <v>0</v>
       </c>
-      <c r="D26" s="27" t="s">
-        <v>21</v>
+      <c r="D26" s="27">
+        <f>IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26-E26+1, "")</f>
+        <v>7</v>
       </c>
       <c r="E26" s="28">
         <v>45965</v>
@@ -3536,15 +3543,16 @@
       <c r="BN26" s="31"/>
     </row>
     <row r="27" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="44"/>
+      <c r="A27" s="45"/>
       <c r="B27" s="42" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="26">
         <v>0</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>20</v>
+      <c r="D27" s="27">
+        <f>IF(AND(F27&lt;&gt;"", E27&lt;&gt;""), F27-E27+1, "")</f>
+        <v>6</v>
       </c>
       <c r="E27" s="28">
         <v>45965</v>
@@ -3616,15 +3624,16 @@
       <c r="BN27" s="31"/>
     </row>
     <row r="28" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="44"/>
+      <c r="A28" s="45"/>
       <c r="B28" s="37" t="s">
         <v>93</v>
       </c>
       <c r="C28" s="26">
         <v>0</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>17</v>
+      <c r="D28" s="27">
+        <f>IF(AND(F28&lt;&gt;"", E28&lt;&gt;""), F28-E28+1, "")</f>
+        <v>3</v>
       </c>
       <c r="E28" s="28">
         <v>45965</v>
@@ -3696,15 +3705,16 @@
       <c r="BN28" s="31"/>
     </row>
     <row r="29" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="44"/>
+      <c r="A29" s="45"/>
       <c r="B29" s="37" t="s">
         <v>94</v>
       </c>
       <c r="C29" s="26">
         <v>0</v>
       </c>
-      <c r="D29" s="27" t="s">
-        <v>17</v>
+      <c r="D29" s="27">
+        <f>IF(AND(F29&lt;&gt;"", E29&lt;&gt;""), F29-E29+1, "")</f>
+        <v>4</v>
       </c>
       <c r="E29" s="28">
         <v>45968</v>
@@ -3776,15 +3786,16 @@
       <c r="BN29" s="31"/>
     </row>
     <row r="30" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="44"/>
+      <c r="A30" s="45"/>
       <c r="B30" s="37" t="s">
         <v>89</v>
       </c>
       <c r="C30" s="26">
         <v>0</v>
       </c>
-      <c r="D30" s="27" t="s">
-        <v>23</v>
+      <c r="D30" s="27">
+        <f>IF(AND(F30&lt;&gt;"", E30&lt;&gt;""), F30-E30+1, "")</f>
+        <v>10</v>
       </c>
       <c r="E30" s="28">
         <v>45972</v>
@@ -3856,15 +3867,16 @@
       <c r="BN30" s="31"/>
     </row>
     <row r="31" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A31" s="44"/>
+      <c r="A31" s="45"/>
       <c r="B31" s="38" t="s">
         <v>122</v>
       </c>
       <c r="C31" s="26">
         <v>0</v>
       </c>
-      <c r="D31" s="27" t="s">
-        <v>48</v>
+      <c r="D31" s="27">
+        <f>IF(AND(F31&lt;&gt;"", E31&lt;&gt;""), F31-E31+1, "")</f>
+        <v>35</v>
       </c>
       <c r="E31" s="28">
         <v>45964</v>
@@ -3934,15 +3946,16 @@
       <c r="BN31" s="31"/>
     </row>
     <row r="32" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A32" s="44"/>
+      <c r="A32" s="45"/>
       <c r="B32" s="41" t="s">
         <v>95</v>
       </c>
       <c r="C32" s="26">
         <v>0</v>
       </c>
-      <c r="D32" s="27" t="s">
-        <v>27</v>
+      <c r="D32" s="27">
+        <f>IF(AND(F32&lt;&gt;"", E32&lt;&gt;""), F32-E32+1, "")</f>
+        <v>14</v>
       </c>
       <c r="E32" s="28">
         <v>45978</v>
@@ -4014,15 +4027,16 @@
       <c r="BN32" s="31"/>
     </row>
     <row r="33" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="44"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="41" t="s">
         <v>96</v>
       </c>
       <c r="C33" s="26">
         <v>0</v>
       </c>
-      <c r="D33" s="27" t="s">
-        <v>27</v>
+      <c r="D33" s="27">
+        <f>IF(AND(F33&lt;&gt;"", E33&lt;&gt;""), F33-E33+1, "")</f>
+        <v>14</v>
       </c>
       <c r="E33" s="28">
         <v>45978</v>
@@ -4094,15 +4108,16 @@
       <c r="BN33" s="31"/>
     </row>
     <row r="34" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="44"/>
+      <c r="A34" s="45"/>
       <c r="B34" s="41" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="26">
         <v>0</v>
       </c>
-      <c r="D34" s="27" t="s">
-        <v>27</v>
+      <c r="D34" s="27">
+        <f>IF(AND(F34&lt;&gt;"", E34&lt;&gt;""), F34-E34+1, "")</f>
+        <v>14</v>
       </c>
       <c r="E34" s="28">
         <v>45978</v>
@@ -4174,15 +4189,16 @@
       <c r="BN34" s="31"/>
     </row>
     <row r="35" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="44"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C35" s="26">
         <v>0</v>
       </c>
-      <c r="D35" s="27" t="s">
-        <v>20</v>
+      <c r="D35" s="27">
+        <f>IF(AND(F35&lt;&gt;"", E35&lt;&gt;""), F35-E35+1, "")</f>
+        <v>7</v>
       </c>
       <c r="E35" s="28">
         <v>45992</v>
@@ -4254,15 +4270,16 @@
       <c r="BN35" s="31"/>
     </row>
     <row r="36" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="44"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="41" t="s">
         <v>99</v>
       </c>
       <c r="C36" s="26">
         <v>0</v>
       </c>
-      <c r="D36" s="27" t="s">
-        <v>20</v>
+      <c r="D36" s="27">
+        <f>IF(AND(F36&lt;&gt;"", E36&lt;&gt;""), F36-E36+1, "")</f>
+        <v>7</v>
       </c>
       <c r="E36" s="28">
         <v>45992</v>
@@ -4334,15 +4351,16 @@
       <c r="BN36" s="31"/>
     </row>
     <row r="37" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A37" s="44"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="26">
         <v>0</v>
       </c>
-      <c r="D37" s="27" t="s">
-        <v>45</v>
+      <c r="D37" s="27">
+        <f>IF(AND(F37&lt;&gt;"", E37&lt;&gt;""), F37-E37+1, "")</f>
+        <v>32</v>
       </c>
       <c r="E37" s="28">
         <v>45964</v>
@@ -4414,15 +4432,16 @@
       <c r="BN37" s="31"/>
     </row>
     <row r="38" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A38" s="44"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="42" t="s">
         <v>100</v>
       </c>
       <c r="C38" s="26">
         <v>0</v>
       </c>
-      <c r="D38" s="27" t="s">
-        <v>14</v>
+      <c r="D38" s="27">
+        <f>IF(AND(F38&lt;&gt;"", E38&lt;&gt;""), F38-E38+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E38" s="28">
         <v>45996</v>
@@ -4494,15 +4513,16 @@
       <c r="BN38" s="31"/>
     </row>
     <row r="39" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A39" s="45"/>
+      <c r="A39" s="46"/>
       <c r="B39" s="42" t="s">
         <v>101</v>
       </c>
       <c r="C39" s="26">
         <v>0</v>
       </c>
-      <c r="D39" s="27" t="s">
-        <v>15</v>
+      <c r="D39" s="27">
+        <f>IF(AND(F39&lt;&gt;"", E39&lt;&gt;""), F39-E39+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E39" s="28">
         <v>45997</v>
@@ -4574,7 +4594,7 @@
       <c r="BN39" s="31"/>
     </row>
     <row r="40" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="44" t="s">
         <v>102</v>
       </c>
       <c r="B40" s="38" t="s">
@@ -4583,8 +4603,9 @@
       <c r="C40" s="26">
         <v>0</v>
       </c>
-      <c r="D40" s="27" t="s">
-        <v>25</v>
+      <c r="D40" s="27">
+        <f>IF(AND(F40&lt;&gt;"", E40&lt;&gt;""), F40-E40+1, "")</f>
+        <v>12</v>
       </c>
       <c r="E40" s="28">
         <v>45999</v>
@@ -4654,15 +4675,16 @@
       <c r="BN40" s="40"/>
     </row>
     <row r="41" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A41" s="44"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C41" s="26">
         <v>0</v>
       </c>
-      <c r="D41" s="27" t="s">
-        <v>23</v>
+      <c r="D41" s="27">
+        <f>IF(AND(F41&lt;&gt;"", E41&lt;&gt;""), F41-E41+1, "")</f>
+        <v>10</v>
       </c>
       <c r="E41" s="28">
         <v>45999</v>
@@ -4734,15 +4756,16 @@
       <c r="BN41" s="31"/>
     </row>
     <row r="42" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A42" s="44"/>
+      <c r="A42" s="45"/>
       <c r="B42" s="25" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="26">
         <v>0</v>
       </c>
-      <c r="D42" s="27" t="s">
-        <v>123</v>
+      <c r="D42" s="27">
+        <f>IF(AND(F42&lt;&gt;"", E42&lt;&gt;""), F42-E42+1, "")</f>
+        <v>10</v>
       </c>
       <c r="E42" s="28">
         <v>45999</v>
@@ -4814,15 +4837,16 @@
       <c r="BN42" s="31"/>
     </row>
     <row r="43" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A43" s="44"/>
+      <c r="A43" s="45"/>
       <c r="B43" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="26">
         <v>0</v>
       </c>
-      <c r="D43" s="27" t="s">
-        <v>14</v>
+      <c r="D43" s="27">
+        <f>IF(AND(F43&lt;&gt;"", E43&lt;&gt;""), F43-E43+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E43" s="28">
         <v>46010</v>
@@ -4894,15 +4918,16 @@
       <c r="BN43" s="31"/>
     </row>
     <row r="44" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="45"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="25" t="s">
         <v>105</v>
       </c>
       <c r="C44" s="26">
         <v>0</v>
       </c>
-      <c r="D44" s="27" t="s">
-        <v>14</v>
+      <c r="D44" s="27">
+        <f>IF(AND(F44&lt;&gt;"", E44&lt;&gt;""), F44-E44+1, "")</f>
+        <v>1</v>
       </c>
       <c r="E44" s="28">
         <v>46010</v>
@@ -5068,5 +5093,6 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\study\개인 공부\Re_View_Doc\2. WBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8730336-3879-4B3B-901D-BB1AB8045717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DCC612-50F1-40C5-9DBF-4A15F14B9C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="130">
   <si>
     <t>팀명</t>
   </si>
@@ -41,12 +41,6 @@
     <t>구분</t>
   </si>
   <si>
-    <t>회원가입 및 로그인 구현</t>
-  </si>
-  <si>
-    <t>상품 목록 및 상세보기 구현</t>
-  </si>
-  <si>
     <t>UI/UX 개선 및 디자인 보완</t>
   </si>
   <si>
@@ -296,12 +290,6 @@
     <t>필수 기능 개발 단계</t>
   </si>
   <si>
-    <t>데이터 DB에 반영</t>
-  </si>
-  <si>
-    <t>제품 결제 및 배송</t>
-  </si>
-  <si>
     <t>리뷰 작성 조회 삭제 CRUD</t>
   </si>
   <si>
@@ -311,30 +299,12 @@
     <t>관리자 페이지 ui</t>
   </si>
   <si>
-    <t>메인페이지, 마이페이지 UI</t>
-  </si>
-  <si>
     <t>검색 페이지 UI</t>
   </si>
   <si>
     <t>상세페이지 UI</t>
   </si>
   <si>
-    <t>보상 체계 관련( 혜택 시스템 )</t>
-  </si>
-  <si>
-    <t>리뷰 커뮤니티 시스템 강화(추천, 비추천, 신고, 태그, 별점, 댓글)</t>
-  </si>
-  <si>
-    <t>리뷰 검색,정렬 기능</t>
-  </si>
-  <si>
-    <t>구매 기록 기반 상품 리뷰 추천</t>
-  </si>
-  <si>
-    <t>회원의 타입과 비슷한 고객들이 구매한 상품 리뷰 추천</t>
-  </si>
-  <si>
     <t>프론트 엔드 기능 고도화(상세 ui 반응 개선)</t>
   </si>
   <si>
@@ -377,18 +347,6 @@
     <t>이재빈</t>
   </si>
   <si>
-    <t>마이 페이지 구현</t>
-  </si>
-  <si>
-    <t>김석현</t>
-  </si>
-  <si>
-    <t>메인페이지 및 관리 페이지 구현</t>
-  </si>
-  <si>
-    <t>정윤성</t>
-  </si>
-  <si>
     <t>오승환</t>
   </si>
   <si>
@@ -402,10 +360,6 @@
   </si>
   <si>
     <t>주요기능 개발 단계</t>
-  </si>
-  <si>
-    <t>메인 페이지 프로토타입 구현</t>
-    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>김석현, 이재빈, 정윤성</t>
@@ -413,6 +367,917 @@
   </si>
   <si>
     <t>오승환, 김시연, 박진성</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기본적인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> header, body, footer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원의 피부 타입에 추천되는 상품 추천 알고리즘</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알고리즘</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>정렬, 검색 기능(리뷰, 상품 등)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커뮤니티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비추천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>태그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>댓글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자 페이지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">관리자 페이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및 비즈니스 로직 구현</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 상세보기 및 목록 조회 API 및 비즈니스 로직 구현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원 정보 조회, 수정 API 및 비즈니스 로직 구현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매내역 조회 및 상풍 확인(배송중 등) 조회 API 및 비즈니스 로직 구현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>리뷰 내역 조회 및 찜목록 조회 API 및 비즈니스 로직 구현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반영</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 상품 API, 검색API 및 비즈니스 로직 API 및 비즈니스 로직 구현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로그인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로직 구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비즈니스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비즈니스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 페이지 및 상품 페이지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>마이페이지 및 로그인페이지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관련</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혜택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인페이지 프로토타입 구현</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -423,7 +1288,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,8 +1459,28 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,8 +1565,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -825,11 +1716,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -951,9 +1879,6 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -992,6 +1917,42 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1211,10 +2172,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BN66"/>
+  <dimension ref="A1:BN71"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="38.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="16.5" thickBot="1">
@@ -1222,33 +2184,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -1298,199 +2260,199 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="I2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="O2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="P2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="Q2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="R2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="S2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="T2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="U2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="V2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="W2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="X2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="Y2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="Z2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="AA2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="16" t="s">
+      <c r="AB2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="17" t="s">
+      <c r="AC2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AD2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AE2" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AF2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AG2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="15" t="s">
+      <c r="AH2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="16" t="s">
+      <c r="AI2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AJ2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AK2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AL2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AM2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AN2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AM2" s="15" t="s">
+      <c r="AO2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="AN2" s="16" t="s">
+      <c r="AP2" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AO2" s="17" t="s">
+      <c r="AQ2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AR2" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AS2" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AT2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AU2" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AV2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="AU2" s="16" t="s">
+      <c r="AW2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="AV2" s="17" t="s">
+      <c r="AX2" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AW2" s="15" t="s">
+      <c r="AY2" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="AX2" s="15" t="s">
+      <c r="AZ2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AY2" s="15" t="s">
+      <c r="BA2" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AZ2" s="15" t="s">
+      <c r="BB2" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="BA2" s="15" t="s">
+      <c r="BC2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="BB2" s="16" t="s">
+      <c r="BD2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="BC2" s="17" t="s">
+      <c r="BE2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="BD2" s="15" t="s">
+      <c r="BF2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="BE2" s="15" t="s">
+      <c r="BG2" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="BF2" s="15" t="s">
+      <c r="BH2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="BG2" s="15" t="s">
+      <c r="BI2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="BH2" s="15" t="s">
+      <c r="BJ2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="BI2" s="16" t="s">
+      <c r="BK2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="BJ2" s="18" t="s">
+      <c r="BL2" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="BK2" s="15" t="s">
+      <c r="BM2" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="BL2" s="15" t="s">
+      <c r="BN2" s="15" t="s">
         <v>70</v>
-      </c>
-      <c r="BM2" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="BN2" s="15" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:66" ht="15" customHeight="1" thickBot="1">
@@ -1500,7 +2462,7 @@
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="51"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="21">
         <v>45951</v>
       </c>
@@ -1680,17 +2642,18 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="52" t="s">
-        <v>73</v>
+      <c r="A4" s="51" t="s">
+        <v>71</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="26">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="C4" s="26" t="str">
+        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F4) - E4) / (F4 - E4) * 100, 1) &amp; "%"</f>
+        <v>100%</v>
       </c>
       <c r="D4" s="27">
-        <f>IF(AND(F4&lt;&gt;"", E4&lt;&gt;""), F4-E4+1, "")</f>
+        <f t="shared" ref="D4:D49" si="0">IF(AND(F4&lt;&gt;"", E4&lt;&gt;""), F4-E4+1, "")</f>
         <v>2</v>
       </c>
       <c r="E4" s="28">
@@ -1700,7 +2663,7 @@
         <v>45952</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H4" s="30"/>
       <c r="I4" s="30"/>
@@ -1763,15 +2726,16 @@
       <c r="BN4" s="31"/>
     </row>
     <row r="5" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="53"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="26">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="C5" s="26" t="str">
+        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F5) - E5) / (F5 - E5) * 100, 1) &amp; "%"</f>
+        <v>100%</v>
       </c>
       <c r="D5" s="27">
-        <f>IF(AND(F5&lt;&gt;"", E5&lt;&gt;""), F5-E5+1, "")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E5" s="28">
@@ -1781,7 +2745,7 @@
         <v>45952</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H5" s="30"/>
       <c r="I5" s="30"/>
@@ -1844,15 +2808,16 @@
       <c r="BN5" s="31"/>
     </row>
     <row r="6" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="26">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="C6" s="26" t="str">
+        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F6) - E6) / (F6 - E6) * 100, 1) &amp; "%"</f>
+        <v>100%</v>
       </c>
       <c r="D6" s="27">
-        <f>IF(AND(F6&lt;&gt;"", E6&lt;&gt;""), F6-E6+1, "")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E6" s="28">
@@ -1862,7 +2827,7 @@
         <v>45952</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -1925,15 +2890,16 @@
       <c r="BN6" s="31"/>
     </row>
     <row r="7" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="53"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="26">
-        <v>0.5</v>
+        <v>75</v>
+      </c>
+      <c r="C7" s="26" t="str">
+        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F7) - E7) / (F7 - E7) * 100, 1) &amp; "%"</f>
+        <v>100%</v>
       </c>
       <c r="D7" s="27">
-        <f>IF(AND(F7&lt;&gt;"", E7&lt;&gt;""), F7-E7+1, "")</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E7" s="28">
@@ -1943,7 +2909,7 @@
         <v>45961</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
@@ -2006,15 +2972,16 @@
       <c r="BN7" s="31"/>
     </row>
     <row r="8" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="53"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="26">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="C8" s="26" t="str">
+        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F8) - E8) / (F8 - E8) * 100, 1) &amp; "%"</f>
+        <v>100%</v>
       </c>
       <c r="D8" s="27">
-        <f>IF(AND(F8&lt;&gt;"", E8&lt;&gt;""), F8-E8+1, "")</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="E8" s="28">
@@ -2024,7 +2991,7 @@
         <v>45966</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
@@ -2087,15 +3054,16 @@
       <c r="BN8" s="31"/>
     </row>
     <row r="9" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="53"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="26">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="C9" s="26" t="e">
+        <f>B17+B21,B28,B33</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D9" s="27">
-        <f>IF(AND(F9&lt;&gt;"", E9&lt;&gt;""), F9-E9+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E9" s="28">
@@ -2105,7 +3073,7 @@
         <v>45962</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
@@ -2168,15 +3136,16 @@
       <c r="BN9" s="31"/>
     </row>
     <row r="10" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="26">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="C10" s="26" t="str">
+        <f ca="1">IF(F10=E10, IF(TODAY()&gt;F10, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F10) - E10) / (F10 - E10) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D10" s="27">
-        <f>IF(AND(F10&lt;&gt;"", E10&lt;&gt;""), F10-E10+1, "")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E10" s="28">
@@ -2186,7 +3155,7 @@
         <v>45961</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="30"/>
@@ -2249,15 +3218,16 @@
       <c r="BN10" s="31"/>
     </row>
     <row r="11" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="54"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="26">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="C11" s="26" t="str">
+        <f ca="1">IF(F11=E11, IF(TODAY()&gt;F11, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F11) - E11) / (F11 - E11) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D11" s="27">
-        <f>IF(AND(F11&lt;&gt;"", E11&lt;&gt;""), F11-E11+1, "")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E11" s="28">
@@ -2267,7 +3237,7 @@
         <v>45958</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
@@ -2330,17 +3300,18 @@
       <c r="BN11" s="31"/>
     </row>
     <row r="12" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="44" t="s">
-        <v>82</v>
+      <c r="A12" s="63" t="s">
+        <v>80</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="26">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="C12" s="26" t="str">
+        <f ca="1">IF(F12=E12, IF(TODAY()&gt;F12, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F12) - E12) / (F12 - E12) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D12" s="27">
-        <f>IF(AND(F12&lt;&gt;"", E12&lt;&gt;""), F12-E12+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E12" s="28">
@@ -2411,15 +3382,16 @@
       <c r="BN12" s="31"/>
     </row>
     <row r="13" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="45"/>
+      <c r="A13" s="64"/>
       <c r="B13" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="26">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="C13" s="26" t="str">
+        <f ca="1">IF(F13=E13, IF(TODAY()&gt;F13, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F13) - E13) / (F13 - E13) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D13" s="27">
-        <f>IF(AND(F13&lt;&gt;"", E13&lt;&gt;""), F13-E13+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E13" s="28">
@@ -2429,7 +3401,7 @@
         <v>45959</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="31"/>
@@ -2492,15 +3464,16 @@
       <c r="BN13" s="31"/>
     </row>
     <row r="14" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="45"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="26">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="C14" s="26" t="str">
+        <f ca="1">IF(F14=E14, IF(TODAY()&gt;F14, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F14) - E14) / (F14 - E14) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D14" s="27">
-        <f>IF(AND(F14&lt;&gt;"", E14&lt;&gt;""), F14-E14+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E14" s="28">
@@ -2510,7 +3483,7 @@
         <v>45959</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
@@ -2573,15 +3546,16 @@
       <c r="BN14" s="31"/>
     </row>
     <row r="15" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="45"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="26">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="C15" s="26" t="str">
+        <f ca="1">IF(F15=E15, IF(TODAY()&gt;F15, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F15) - E15) / (F15 - E15) * 100, 1) &amp; "%")</f>
+        <v>11.8%</v>
       </c>
       <c r="D15" s="27">
-        <f>IF(AND(F15&lt;&gt;"", E15&lt;&gt;""), F15-E15+1, "")</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="E15" s="28">
@@ -2652,15 +3626,16 @@
       <c r="BN15" s="31"/>
     </row>
     <row r="16" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="26">
-        <v>0</v>
+      <c r="A16" s="64"/>
+      <c r="B16" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="26" t="str">
+        <f ca="1">IF(F16=E16, IF(TODAY()&gt;F16, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F16) - E16) / (F16 - E16) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D16" s="27">
-        <f>IF(AND(F16&lt;&gt;"", E16&lt;&gt;""), F16-E16+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E16" s="28">
@@ -2670,7 +3645,7 @@
         <v>45966</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
@@ -2733,26 +3708,15 @@
       <c r="BN16" s="31"/>
     </row>
     <row r="17" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="45"/>
-      <c r="B17" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="26">
-        <v>0</v>
-      </c>
-      <c r="D17" s="27">
-        <f>IF(AND(F17&lt;&gt;"", E17&lt;&gt;""), F17-E17+1, "")</f>
-        <v>3</v>
-      </c>
-      <c r="E17" s="28">
-        <v>45966</v>
-      </c>
-      <c r="F17" s="28">
-        <v>45968</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>124</v>
-      </c>
+      <c r="A17" s="64"/>
+      <c r="B17" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="59"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
@@ -2814,25 +3778,26 @@
       <c r="BN17" s="31"/>
     </row>
     <row r="18" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="45"/>
-      <c r="B18" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="26">
-        <v>0</v>
+      <c r="A18" s="64"/>
+      <c r="B18" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="26" t="str">
+        <f ca="1">IF(F18=E18, IF(TODAY()&gt;F18, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F18) - E18) / (F18 - E18) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
       </c>
       <c r="D18" s="27">
         <f>IF(AND(F18&lt;&gt;"", E18&lt;&gt;""), F18-E18+1, "")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="28">
-        <v>45968</v>
+        <v>45964</v>
       </c>
       <c r="F18" s="28">
-        <v>45971</v>
+        <v>45965</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="31"/>
@@ -2847,14 +3812,14 @@
       <c r="R18" s="31"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
       <c r="W18" s="30"/>
       <c r="X18" s="30"/>
       <c r="Y18" s="30"/>
       <c r="Z18" s="30"/>
       <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="AB18" s="31"/>
       <c r="AC18" s="31"/>
       <c r="AD18" s="31"/>
       <c r="AE18" s="31"/>
@@ -2895,25 +3860,26 @@
       <c r="BN18" s="31"/>
     </row>
     <row r="19" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="26">
-        <v>0</v>
+      <c r="A19" s="64"/>
+      <c r="B19" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="26" t="str">
+        <f ca="1">IF(F19=E19, IF(TODAY()&gt;F19, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F19) - E19) / (F19 - E19) * 100, 1) &amp; "%")</f>
+        <v>50%</v>
       </c>
       <c r="D19" s="27">
         <f>IF(AND(F19&lt;&gt;"", E19&lt;&gt;""), F19-E19+1, "")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="28">
-        <v>45968</v>
+        <v>45965</v>
       </c>
       <c r="F19" s="28">
-        <v>45971</v>
+        <v>45967</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
@@ -2928,14 +3894,14 @@
       <c r="R19" s="31"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
       <c r="W19" s="30"/>
       <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="31"/>
       <c r="AC19" s="31"/>
       <c r="AD19" s="31"/>
       <c r="AE19" s="31"/>
@@ -2976,25 +3942,26 @@
       <c r="BN19" s="31"/>
     </row>
     <row r="20" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="26">
-        <v>0</v>
+      <c r="A20" s="64"/>
+      <c r="B20" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="26" t="str">
+        <f ca="1">IF(F20=E20, IF(TODAY()&gt;F20, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F20) - E20) / (F20 - E20) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D20" s="27">
-        <f>IF(AND(F20&lt;&gt;"", E20&lt;&gt;""), F20-E20+1, "")</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E20" s="28">
-        <v>45968</v>
+        <v>45966</v>
       </c>
       <c r="F20" s="28">
-        <v>45971</v>
+        <v>45967</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="31"/>
@@ -3012,11 +3979,11 @@
       <c r="U20" s="31"/>
       <c r="V20" s="31"/>
       <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="31"/>
       <c r="AC20" s="31"/>
       <c r="AD20" s="31"/>
       <c r="AE20" s="31"/>
@@ -3057,26 +4024,15 @@
       <c r="BN20" s="31"/>
     </row>
     <row r="21" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="45"/>
-      <c r="B21" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="26">
-        <v>0</v>
-      </c>
-      <c r="D21" s="27">
-        <f>IF(AND(F21&lt;&gt;"", E21&lt;&gt;""), F21-E21+1, "")</f>
-        <v>6</v>
-      </c>
-      <c r="E21" s="28">
-        <v>45972</v>
-      </c>
-      <c r="F21" s="28">
-        <v>45977</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>115</v>
-      </c>
+      <c r="A21" s="64"/>
+      <c r="B21" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
@@ -3092,18 +4048,18 @@
       <c r="T21" s="33"/>
       <c r="U21" s="31"/>
       <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="33"/>
-      <c r="AB21" s="31"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="30"/>
       <c r="AC21" s="31"/>
-      <c r="AD21" s="30"/>
-      <c r="AE21" s="30"/>
-      <c r="AF21" s="30"/>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="30"/>
+      <c r="AD21" s="31"/>
+      <c r="AE21" s="31"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="33"/>
       <c r="AI21" s="31"/>
       <c r="AJ21" s="31"/>
       <c r="AK21" s="31"/>
@@ -3138,26 +4094,25 @@
       <c r="BN21" s="31"/>
     </row>
     <row r="22" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="45"/>
-      <c r="B22" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="26">
-        <v>0</v>
+      <c r="A22" s="64"/>
+      <c r="B22" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="26" t="str">
+        <f ca="1">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D22" s="27">
         <f>IF(AND(F22&lt;&gt;"", E22&lt;&gt;""), F22-E22+1, "")</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22" s="28">
-        <v>45972</v>
+        <v>45968</v>
       </c>
       <c r="F22" s="28">
-        <v>45977</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>117</v>
-      </c>
+        <v>45969</v>
+      </c>
+      <c r="G22" s="29"/>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -3173,18 +4128,18 @@
       <c r="T22" s="33"/>
       <c r="U22" s="31"/>
       <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="31"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30"/>
       <c r="AC22" s="31"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="33"/>
       <c r="AI22" s="31"/>
       <c r="AJ22" s="31"/>
       <c r="AK22" s="31"/>
@@ -3219,25 +4174,26 @@
       <c r="BN22" s="31"/>
     </row>
     <row r="23" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="45"/>
+      <c r="A23" s="64"/>
       <c r="B23" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="26">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="C23" s="26" t="str">
+        <f ca="1">IF(F23=E23, IF(TODAY()&gt;F23, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F23) - E23) / (F23 - E23) * 100, 1) &amp; "%")</f>
+        <v>20%</v>
       </c>
       <c r="D23" s="27">
         <f>IF(AND(F23&lt;&gt;"", E23&lt;&gt;""), F23-E23+1, "")</f>
         <v>6</v>
       </c>
       <c r="E23" s="28">
-        <v>45972</v>
+        <v>45965</v>
       </c>
       <c r="F23" s="28">
-        <v>45977</v>
+        <v>45970</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="31"/>
@@ -3252,7 +4208,7 @@
       <c r="R23" s="31"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
-      <c r="U23" s="31"/>
+      <c r="U23" s="30"/>
       <c r="V23" s="31"/>
       <c r="W23" s="31"/>
       <c r="X23" s="31"/>
@@ -3261,11 +4217,11 @@
       <c r="AA23" s="33"/>
       <c r="AB23" s="31"/>
       <c r="AC23" s="31"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="33"/>
       <c r="AI23" s="31"/>
       <c r="AJ23" s="31"/>
       <c r="AK23" s="31"/>
@@ -3300,25 +4256,26 @@
       <c r="BN23" s="31"/>
     </row>
     <row r="24" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="45"/>
+      <c r="A24" s="64"/>
       <c r="B24" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="26">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="C24" s="26" t="str">
+        <f ca="1">IF(F24=E24, IF(TODAY()&gt;F24, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F24) - E24) / (F24 - E24) * 100, 1) &amp; "%")</f>
+        <v>16.7%</v>
       </c>
       <c r="D24" s="27">
         <f>IF(AND(F24&lt;&gt;"", E24&lt;&gt;""), F24-E24+1, "")</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E24" s="28">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="F24" s="28">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="31"/>
@@ -3340,7 +4297,7 @@
       <c r="Y24" s="30"/>
       <c r="Z24" s="30"/>
       <c r="AA24" s="30"/>
-      <c r="AB24" s="31"/>
+      <c r="AB24" s="30"/>
       <c r="AC24" s="31"/>
       <c r="AD24" s="31"/>
       <c r="AE24" s="31"/>
@@ -3381,26 +4338,25 @@
       <c r="BN24" s="31"/>
     </row>
     <row r="25" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="26">
-        <v>0</v>
+      <c r="A25" s="64"/>
+      <c r="B25" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="26" t="str">
+        <f ca="1">IF(F25=E25, IF(TODAY()&gt;F25, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F25) - E25) / (F25 - E25) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D25" s="27">
-        <f>IF(AND(F25&lt;&gt;"", E25&lt;&gt;""), F25-E25+1, "")</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E25" s="28">
-        <v>45965</v>
+        <v>45968</v>
       </c>
       <c r="F25" s="28">
-        <v>45971</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>119</v>
-      </c>
+        <v>45969</v>
+      </c>
+      <c r="G25" s="29"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
@@ -3414,8 +4370,8 @@
       <c r="R25" s="31"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
       <c r="W25" s="30"/>
       <c r="X25" s="30"/>
       <c r="Y25" s="30"/>
@@ -3462,26 +4418,25 @@
       <c r="BN25" s="31"/>
     </row>
     <row r="26" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="45"/>
-      <c r="B26" s="37" t="s">
+      <c r="A26" s="64"/>
+      <c r="B26" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="26">
-        <v>0</v>
+      <c r="C26" s="26" t="str">
+        <f ca="1">IF(F26=E26, IF(TODAY()&gt;F26, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F26) - E26) / (F26 - E26) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D26" s="27">
-        <f>IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26-E26+1, "")</f>
-        <v>7</v>
+        <f t="shared" ref="D26:D27" si="1">IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26-E26+1, "")</f>
+        <v>2</v>
       </c>
       <c r="E26" s="28">
-        <v>45965</v>
+        <v>45968</v>
       </c>
       <c r="F26" s="28">
-        <v>45971</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>119</v>
-      </c>
+        <v>45969</v>
+      </c>
+      <c r="G26" s="29"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
@@ -3495,8 +4450,8 @@
       <c r="R26" s="31"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
       <c r="W26" s="30"/>
       <c r="X26" s="30"/>
       <c r="Y26" s="30"/>
@@ -3543,26 +4498,25 @@
       <c r="BN26" s="31"/>
     </row>
     <row r="27" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="45"/>
+      <c r="A27" s="64"/>
       <c r="B27" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="26">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="C27" s="26" t="str">
+        <f ca="1">IF(F27=E27, IF(TODAY()&gt;F27, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F27) - E27) / (F27 - E27) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D27" s="27">
-        <f>IF(AND(F27&lt;&gt;"", E27&lt;&gt;""), F27-E27+1, "")</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="E27" s="28">
-        <v>45965</v>
+        <v>45968</v>
       </c>
       <c r="F27" s="28">
-        <v>45970</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>118</v>
-      </c>
+        <v>45969</v>
+      </c>
+      <c r="G27" s="29"/>
       <c r="H27" s="31"/>
       <c r="I27" s="31"/>
       <c r="J27" s="31"/>
@@ -3576,14 +4530,14 @@
       <c r="R27" s="31"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
-      <c r="U27" s="30"/>
+      <c r="U27" s="31"/>
       <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="31"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
       <c r="AC27" s="31"/>
       <c r="AD27" s="31"/>
       <c r="AE27" s="31"/>
@@ -3624,26 +4578,15 @@
       <c r="BN27" s="31"/>
     </row>
     <row r="28" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="45"/>
-      <c r="B28" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="26">
-        <v>0</v>
-      </c>
-      <c r="D28" s="27">
-        <f>IF(AND(F28&lt;&gt;"", E28&lt;&gt;""), F28-E28+1, "")</f>
-        <v>3</v>
-      </c>
-      <c r="E28" s="28">
-        <v>45965</v>
-      </c>
-      <c r="F28" s="28">
-        <v>45967</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>121</v>
-      </c>
+      <c r="A28" s="64"/>
+      <c r="B28" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="62"/>
       <c r="H28" s="31"/>
       <c r="I28" s="31"/>
       <c r="J28" s="31"/>
@@ -3657,14 +4600,14 @@
       <c r="R28" s="31"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
       <c r="W28" s="30"/>
       <c r="X28" s="30"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="31"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
       <c r="AC28" s="31"/>
       <c r="AD28" s="31"/>
       <c r="AE28" s="31"/>
@@ -3705,26 +4648,25 @@
       <c r="BN28" s="31"/>
     </row>
     <row r="29" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="45"/>
-      <c r="B29" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="26">
-        <v>0</v>
+      <c r="A29" s="64"/>
+      <c r="B29" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="26" t="str">
+        <f ca="1">IF(F29=E29, IF(TODAY()&gt;F29, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F29) - E29) / (F29 - E29) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D29" s="27">
-        <f>IF(AND(F29&lt;&gt;"", E29&lt;&gt;""), F29-E29+1, "")</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="E29" s="28">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="F29" s="28">
-        <v>45971</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>121</v>
-      </c>
+        <v>45977</v>
+      </c>
+      <c r="G29" s="29"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="J29" s="31"/>
@@ -3742,16 +4684,16 @@
       <c r="V29" s="31"/>
       <c r="W29" s="31"/>
       <c r="X29" s="31"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="31"/>
       <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="33"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
       <c r="AI29" s="31"/>
       <c r="AJ29" s="31"/>
       <c r="AK29" s="31"/>
@@ -3786,26 +4728,25 @@
       <c r="BN29" s="31"/>
     </row>
     <row r="30" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="45"/>
-      <c r="B30" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="26">
-        <v>0</v>
+      <c r="A30" s="64"/>
+      <c r="B30" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="26" t="str">
+        <f ca="1">IF(F30=E30, IF(TODAY()&gt;F30, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F30) - E30) / (F30 - E30) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D30" s="27">
-        <f>IF(AND(F30&lt;&gt;"", E30&lt;&gt;""), F30-E30+1, "")</f>
-        <v>10</v>
+        <f t="shared" ref="D30" si="2">IF(AND(F30&lt;&gt;"", E30&lt;&gt;""), F30-E30+1, "")</f>
+        <v>6</v>
       </c>
       <c r="E30" s="28">
         <v>45972</v>
       </c>
       <c r="F30" s="28">
-        <v>45981</v>
-      </c>
-      <c r="G30" s="29" t="s">
-        <v>121</v>
-      </c>
+        <v>45977</v>
+      </c>
+      <c r="G30" s="29"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="J30" s="31"/>
@@ -3827,16 +4768,16 @@
       <c r="Z30" s="32"/>
       <c r="AA30" s="33"/>
       <c r="AB30" s="31"/>
-      <c r="AC30" s="30"/>
+      <c r="AC30" s="31"/>
       <c r="AD30" s="30"/>
       <c r="AE30" s="30"/>
       <c r="AF30" s="30"/>
       <c r="AG30" s="30"/>
       <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="30"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="31"/>
+      <c r="AK30" s="31"/>
+      <c r="AL30" s="31"/>
       <c r="AM30" s="31"/>
       <c r="AN30" s="32"/>
       <c r="AO30" s="33"/>
@@ -3866,25 +4807,28 @@
       <c r="BM30" s="31"/>
       <c r="BN30" s="31"/>
     </row>
-    <row r="31" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A31" s="45"/>
-      <c r="B31" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" s="26">
-        <v>0</v>
+    <row r="31" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A31" s="64"/>
+      <c r="B31" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="26" t="str">
+        <f ca="1">IF(F31=E31, IF(TODAY()&gt;F31, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F31) - E31) / (F31 - E31) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D31" s="27">
         <f>IF(AND(F31&lt;&gt;"", E31&lt;&gt;""), F31-E31+1, "")</f>
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E31" s="28">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="F31" s="28">
-        <v>45998</v>
-      </c>
-      <c r="G31" s="39"/>
+        <v>45971</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>107</v>
+      </c>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="J31" s="31"/>
@@ -3898,41 +4842,41 @@
       <c r="R31" s="31"/>
       <c r="S31" s="32"/>
       <c r="T31" s="33"/>
-      <c r="U31" s="40"/>
-      <c r="V31" s="40"/>
-      <c r="W31" s="40"/>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="40"/>
-      <c r="AA31" s="40"/>
-      <c r="AB31" s="40"/>
-      <c r="AC31" s="40"/>
-      <c r="AD31" s="40"/>
-      <c r="AE31" s="40"/>
-      <c r="AF31" s="40"/>
-      <c r="AG31" s="40"/>
-      <c r="AH31" s="40"/>
-      <c r="AI31" s="40"/>
-      <c r="AJ31" s="40"/>
-      <c r="AK31" s="40"/>
-      <c r="AL31" s="40"/>
-      <c r="AM31" s="40"/>
-      <c r="AN31" s="40"/>
-      <c r="AO31" s="40"/>
-      <c r="AP31" s="40"/>
-      <c r="AQ31" s="40"/>
-      <c r="AR31" s="40"/>
-      <c r="AS31" s="40"/>
-      <c r="AT31" s="40"/>
-      <c r="AU31" s="40"/>
-      <c r="AV31" s="40"/>
-      <c r="AW31" s="40"/>
-      <c r="AX31" s="40"/>
-      <c r="AY31" s="40"/>
-      <c r="AZ31" s="40"/>
-      <c r="BA31" s="40"/>
-      <c r="BB31" s="40"/>
-      <c r="BC31" s="40"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="32"/>
+      <c r="AH31" s="33"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="31"/>
+      <c r="AK31" s="31"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="31"/>
+      <c r="AN31" s="32"/>
+      <c r="AO31" s="33"/>
+      <c r="AP31" s="31"/>
+      <c r="AQ31" s="31"/>
+      <c r="AR31" s="31"/>
+      <c r="AS31" s="31"/>
+      <c r="AT31" s="31"/>
+      <c r="AU31" s="32"/>
+      <c r="AV31" s="33"/>
+      <c r="AW31" s="31"/>
+      <c r="AX31" s="31"/>
+      <c r="AY31" s="31"/>
+      <c r="AZ31" s="31"/>
+      <c r="BA31" s="31"/>
+      <c r="BB31" s="32"/>
+      <c r="BC31" s="33"/>
       <c r="BD31" s="31"/>
       <c r="BE31" s="31"/>
       <c r="BF31" s="31"/>
@@ -3945,26 +4889,27 @@
       <c r="BM31" s="31"/>
       <c r="BN31" s="31"/>
     </row>
-    <row r="32" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A32" s="45"/>
-      <c r="B32" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="26">
-        <v>0</v>
+    <row r="32" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A32" s="64"/>
+      <c r="B32" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="26" t="str">
+        <f ca="1">IF(F32=E32, IF(TODAY()&gt;F32, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F32) - E32) / (F32 - E32) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D32" s="27">
         <f>IF(AND(F32&lt;&gt;"", E32&lt;&gt;""), F32-E32+1, "")</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E32" s="28">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="F32" s="28">
-        <v>45991</v>
+        <v>45981</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
@@ -3987,26 +4932,26 @@
       <c r="Z32" s="32"/>
       <c r="AA32" s="33"/>
       <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="33"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
       <c r="AK32" s="30"/>
       <c r="AL32" s="30"/>
-      <c r="AM32" s="30"/>
-      <c r="AN32" s="30"/>
-      <c r="AO32" s="30"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-      <c r="AR32" s="30"/>
-      <c r="AS32" s="30"/>
-      <c r="AT32" s="30"/>
-      <c r="AU32" s="30"/>
-      <c r="AV32" s="30"/>
+      <c r="AM32" s="31"/>
+      <c r="AN32" s="32"/>
+      <c r="AO32" s="33"/>
+      <c r="AP32" s="31"/>
+      <c r="AQ32" s="31"/>
+      <c r="AR32" s="31"/>
+      <c r="AS32" s="31"/>
+      <c r="AT32" s="31"/>
+      <c r="AU32" s="32"/>
+      <c r="AV32" s="33"/>
       <c r="AW32" s="31"/>
       <c r="AX32" s="31"/>
       <c r="AY32" s="31"/>
@@ -4027,26 +4972,15 @@
       <c r="BN32" s="31"/>
     </row>
     <row r="33" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="45"/>
-      <c r="B33" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="26">
-        <v>0</v>
-      </c>
-      <c r="D33" s="27">
-        <f>IF(AND(F33&lt;&gt;"", E33&lt;&gt;""), F33-E33+1, "")</f>
-        <v>14</v>
-      </c>
-      <c r="E33" s="28">
-        <v>45978</v>
-      </c>
-      <c r="F33" s="28">
-        <v>45991</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>111</v>
-      </c>
+      <c r="A33" s="64"/>
+      <c r="B33" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="62"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
@@ -4069,25 +5003,25 @@
       <c r="AA33" s="33"/>
       <c r="AB33" s="31"/>
       <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="32"/>
-      <c r="AH33" s="33"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="30"/>
-      <c r="AM33" s="30"/>
-      <c r="AN33" s="30"/>
-      <c r="AO33" s="30"/>
-      <c r="AP33" s="30"/>
-      <c r="AQ33" s="30"/>
-      <c r="AR33" s="30"/>
-      <c r="AS33" s="30"/>
-      <c r="AT33" s="30"/>
-      <c r="AU33" s="30"/>
-      <c r="AV33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="31"/>
+      <c r="AK33" s="31"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="31"/>
+      <c r="AN33" s="32"/>
+      <c r="AO33" s="33"/>
+      <c r="AP33" s="31"/>
+      <c r="AQ33" s="31"/>
+      <c r="AR33" s="31"/>
+      <c r="AS33" s="31"/>
+      <c r="AT33" s="31"/>
+      <c r="AU33" s="32"/>
+      <c r="AV33" s="33"/>
       <c r="AW33" s="31"/>
       <c r="AX33" s="31"/>
       <c r="AY33" s="31"/>
@@ -4108,25 +5042,26 @@
       <c r="BN33" s="31"/>
     </row>
     <row r="34" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="26">
-        <v>0</v>
+      <c r="A34" s="64"/>
+      <c r="B34" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="26" t="str">
+        <f ca="1">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D34" s="27">
-        <f>IF(AND(F34&lt;&gt;"", E34&lt;&gt;""), F34-E34+1, "")</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="E34" s="28">
-        <v>45978</v>
+        <v>45972</v>
       </c>
       <c r="F34" s="28">
-        <v>45991</v>
+        <v>45977</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
@@ -4150,25 +5085,25 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="31"/>
       <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="32"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-      <c r="AR34" s="30"/>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="30"/>
-      <c r="AU34" s="30"/>
-      <c r="AV34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
+      <c r="AK34" s="31"/>
+      <c r="AL34" s="31"/>
+      <c r="AM34" s="31"/>
+      <c r="AN34" s="32"/>
+      <c r="AO34" s="33"/>
+      <c r="AP34" s="31"/>
+      <c r="AQ34" s="31"/>
+      <c r="AR34" s="31"/>
+      <c r="AS34" s="31"/>
+      <c r="AT34" s="31"/>
+      <c r="AU34" s="32"/>
+      <c r="AV34" s="33"/>
       <c r="AW34" s="31"/>
       <c r="AX34" s="31"/>
       <c r="AY34" s="31"/>
@@ -4189,25 +5124,26 @@
       <c r="BN34" s="31"/>
     </row>
     <row r="35" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="45"/>
-      <c r="B35" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="26">
-        <v>0</v>
+      <c r="A35" s="64"/>
+      <c r="B35" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="26" t="str">
+        <f ca="1">IF(F35=E35, IF(TODAY()&gt;F35, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F35) - E35) / (F35 - E35) * 100, 1) &amp; "%")</f>
+        <v>16.7%</v>
       </c>
       <c r="D35" s="27">
-        <f>IF(AND(F35&lt;&gt;"", E35&lt;&gt;""), F35-E35+1, "")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="E35" s="28">
-        <v>45992</v>
+        <v>45965</v>
       </c>
       <c r="F35" s="28">
-        <v>45998</v>
+        <v>45971</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
@@ -4222,14 +5158,14 @@
       <c r="R35" s="31"/>
       <c r="S35" s="32"/>
       <c r="T35" s="33"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="31"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
       <c r="AC35" s="31"/>
       <c r="AD35" s="31"/>
       <c r="AE35" s="31"/>
@@ -4250,13 +5186,13 @@
       <c r="AT35" s="31"/>
       <c r="AU35" s="32"/>
       <c r="AV35" s="33"/>
-      <c r="AW35" s="30"/>
-      <c r="AX35" s="30"/>
-      <c r="AY35" s="30"/>
-      <c r="AZ35" s="30"/>
-      <c r="BA35" s="30"/>
-      <c r="BB35" s="30"/>
-      <c r="BC35" s="30"/>
+      <c r="AW35" s="31"/>
+      <c r="AX35" s="31"/>
+      <c r="AY35" s="31"/>
+      <c r="AZ35" s="31"/>
+      <c r="BA35" s="31"/>
+      <c r="BB35" s="32"/>
+      <c r="BC35" s="33"/>
       <c r="BD35" s="31"/>
       <c r="BE35" s="31"/>
       <c r="BF35" s="31"/>
@@ -4269,27 +5205,26 @@
       <c r="BM35" s="31"/>
       <c r="BN35" s="31"/>
     </row>
-    <row r="36" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="45"/>
-      <c r="B36" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="26">
-        <v>0</v>
+    <row r="36" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A36" s="64"/>
+      <c r="B36" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="26" t="str">
+        <f ca="1">IF(F36=E36, IF(TODAY()&gt;F36, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F36) - E36) / (F36 - E36) * 100, 1) &amp; "%")</f>
+        <v>5.9%</v>
       </c>
       <c r="D36" s="27">
-        <f>IF(AND(F36&lt;&gt;"", E36&lt;&gt;""), F36-E36+1, "")</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="E36" s="28">
-        <v>45992</v>
+        <v>45964</v>
       </c>
       <c r="F36" s="28">
         <v>45998</v>
       </c>
-      <c r="G36" s="29" t="s">
-        <v>111</v>
-      </c>
+      <c r="G36" s="39"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="J36" s="31"/>
@@ -4303,41 +5238,41 @@
       <c r="R36" s="31"/>
       <c r="S36" s="32"/>
       <c r="T36" s="33"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="32"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
-      <c r="AG36" s="32"/>
-      <c r="AH36" s="33"/>
-      <c r="AI36" s="31"/>
-      <c r="AJ36" s="31"/>
-      <c r="AK36" s="31"/>
-      <c r="AL36" s="31"/>
-      <c r="AM36" s="31"/>
-      <c r="AN36" s="32"/>
-      <c r="AO36" s="33"/>
-      <c r="AP36" s="31"/>
-      <c r="AQ36" s="31"/>
-      <c r="AR36" s="31"/>
-      <c r="AS36" s="31"/>
-      <c r="AT36" s="31"/>
-      <c r="AU36" s="32"/>
-      <c r="AV36" s="33"/>
-      <c r="AW36" s="30"/>
-      <c r="AX36" s="30"/>
-      <c r="AY36" s="30"/>
-      <c r="AZ36" s="30"/>
-      <c r="BA36" s="30"/>
-      <c r="BB36" s="30"/>
-      <c r="BC36" s="30"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="40"/>
+      <c r="AD36" s="40"/>
+      <c r="AE36" s="40"/>
+      <c r="AF36" s="40"/>
+      <c r="AG36" s="40"/>
+      <c r="AH36" s="40"/>
+      <c r="AI36" s="40"/>
+      <c r="AJ36" s="40"/>
+      <c r="AK36" s="40"/>
+      <c r="AL36" s="40"/>
+      <c r="AM36" s="40"/>
+      <c r="AN36" s="40"/>
+      <c r="AO36" s="40"/>
+      <c r="AP36" s="40"/>
+      <c r="AQ36" s="40"/>
+      <c r="AR36" s="40"/>
+      <c r="AS36" s="40"/>
+      <c r="AT36" s="40"/>
+      <c r="AU36" s="40"/>
+      <c r="AV36" s="40"/>
+      <c r="AW36" s="40"/>
+      <c r="AX36" s="40"/>
+      <c r="AY36" s="40"/>
+      <c r="AZ36" s="40"/>
+      <c r="BA36" s="40"/>
+      <c r="BB36" s="40"/>
+      <c r="BC36" s="40"/>
       <c r="BD36" s="31"/>
       <c r="BE36" s="31"/>
       <c r="BF36" s="31"/>
@@ -4350,26 +5285,27 @@
       <c r="BM36" s="31"/>
       <c r="BN36" s="31"/>
     </row>
-    <row r="37" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A37" s="45"/>
-      <c r="B37" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="26">
-        <v>0</v>
+    <row r="37" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A37" s="64"/>
+      <c r="B37" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="26" t="str">
+        <f ca="1">IF(F37=E37, IF(TODAY()&gt;F37, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F37) - E37) / (F37 - E37) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D37" s="27">
-        <f>IF(AND(F37&lt;&gt;"", E37&lt;&gt;""), F37-E37+1, "")</f>
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="E37" s="28">
-        <v>45964</v>
+        <v>45978</v>
       </c>
       <c r="F37" s="28">
-        <v>45995</v>
+        <v>45991</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H37" s="31"/>
       <c r="I37" s="31"/>
@@ -4384,20 +5320,20 @@
       <c r="R37" s="31"/>
       <c r="S37" s="32"/>
       <c r="T37" s="33"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="32"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="32"/>
+      <c r="AH37" s="33"/>
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
       <c r="AK37" s="30"/>
@@ -4412,10 +5348,10 @@
       <c r="AT37" s="30"/>
       <c r="AU37" s="30"/>
       <c r="AV37" s="30"/>
-      <c r="AW37" s="30"/>
-      <c r="AX37" s="30"/>
-      <c r="AY37" s="30"/>
-      <c r="AZ37" s="30"/>
+      <c r="AW37" s="31"/>
+      <c r="AX37" s="31"/>
+      <c r="AY37" s="31"/>
+      <c r="AZ37" s="31"/>
       <c r="BA37" s="31"/>
       <c r="BB37" s="32"/>
       <c r="BC37" s="33"/>
@@ -4431,26 +5367,27 @@
       <c r="BM37" s="31"/>
       <c r="BN37" s="31"/>
     </row>
-    <row r="38" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A38" s="45"/>
-      <c r="B38" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="26">
-        <v>0</v>
+    <row r="38" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A38" s="64"/>
+      <c r="B38" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="26" t="str">
+        <f ca="1">IF(F38=E38, IF(TODAY()&gt;F38, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F38) - E38) / (F38 - E38) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D38" s="27">
-        <f>IF(AND(F38&lt;&gt;"", E38&lt;&gt;""), F38-E38+1, "")</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="E38" s="28">
-        <v>45996</v>
+        <v>45978</v>
       </c>
       <c r="F38" s="28">
-        <v>45996</v>
+        <v>45991</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H38" s="31"/>
       <c r="I38" s="31"/>
@@ -4479,25 +5416,25 @@
       <c r="AF38" s="31"/>
       <c r="AG38" s="32"/>
       <c r="AH38" s="33"/>
-      <c r="AI38" s="31"/>
-      <c r="AJ38" s="31"/>
-      <c r="AK38" s="31"/>
-      <c r="AL38" s="31"/>
-      <c r="AM38" s="31"/>
-      <c r="AN38" s="32"/>
-      <c r="AO38" s="33"/>
-      <c r="AP38" s="31"/>
-      <c r="AQ38" s="31"/>
-      <c r="AR38" s="31"/>
-      <c r="AS38" s="31"/>
-      <c r="AT38" s="31"/>
-      <c r="AU38" s="32"/>
-      <c r="AV38" s="33"/>
+      <c r="AI38" s="30"/>
+      <c r="AJ38" s="30"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="30"/>
+      <c r="AM38" s="30"/>
+      <c r="AN38" s="30"/>
+      <c r="AO38" s="30"/>
+      <c r="AP38" s="30"/>
+      <c r="AQ38" s="30"/>
+      <c r="AR38" s="30"/>
+      <c r="AS38" s="30"/>
+      <c r="AT38" s="30"/>
+      <c r="AU38" s="30"/>
+      <c r="AV38" s="30"/>
       <c r="AW38" s="31"/>
       <c r="AX38" s="31"/>
       <c r="AY38" s="31"/>
       <c r="AZ38" s="31"/>
-      <c r="BA38" s="30"/>
+      <c r="BA38" s="31"/>
       <c r="BB38" s="32"/>
       <c r="BC38" s="33"/>
       <c r="BD38" s="31"/>
@@ -4512,26 +5449,27 @@
       <c r="BM38" s="31"/>
       <c r="BN38" s="31"/>
     </row>
-    <row r="39" spans="1:66" ht="24.75" thickBot="1">
-      <c r="A39" s="46"/>
-      <c r="B39" s="42" t="s">
+    <row r="39" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A39" s="64"/>
+      <c r="B39" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="26" t="str">
+        <f ca="1">IF(F39=E39, IF(TODAY()&gt;F39, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F39) - E39) / (F39 - E39) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D39" s="27">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E39" s="28">
+        <v>45978</v>
+      </c>
+      <c r="F39" s="28">
+        <v>45991</v>
+      </c>
+      <c r="G39" s="29" t="s">
         <v>101</v>
-      </c>
-      <c r="C39" s="26">
-        <v>0</v>
-      </c>
-      <c r="D39" s="27">
-        <f>IF(AND(F39&lt;&gt;"", E39&lt;&gt;""), F39-E39+1, "")</f>
-        <v>2</v>
-      </c>
-      <c r="E39" s="28">
-        <v>45997</v>
-      </c>
-      <c r="F39" s="28">
-        <v>45998</v>
-      </c>
-      <c r="G39" s="29" t="s">
-        <v>112</v>
       </c>
       <c r="H39" s="31"/>
       <c r="I39" s="31"/>
@@ -4560,27 +5498,27 @@
       <c r="AF39" s="31"/>
       <c r="AG39" s="32"/>
       <c r="AH39" s="33"/>
-      <c r="AI39" s="31"/>
-      <c r="AJ39" s="31"/>
-      <c r="AK39" s="31"/>
-      <c r="AL39" s="31"/>
-      <c r="AM39" s="31"/>
-      <c r="AN39" s="32"/>
-      <c r="AO39" s="33"/>
-      <c r="AP39" s="31"/>
-      <c r="AQ39" s="31"/>
-      <c r="AR39" s="31"/>
-      <c r="AS39" s="31"/>
-      <c r="AT39" s="31"/>
-      <c r="AU39" s="32"/>
-      <c r="AV39" s="33"/>
+      <c r="AI39" s="30"/>
+      <c r="AJ39" s="30"/>
+      <c r="AK39" s="30"/>
+      <c r="AL39" s="30"/>
+      <c r="AM39" s="30"/>
+      <c r="AN39" s="30"/>
+      <c r="AO39" s="30"/>
+      <c r="AP39" s="30"/>
+      <c r="AQ39" s="30"/>
+      <c r="AR39" s="30"/>
+      <c r="AS39" s="30"/>
+      <c r="AT39" s="30"/>
+      <c r="AU39" s="30"/>
+      <c r="AV39" s="30"/>
       <c r="AW39" s="31"/>
       <c r="AX39" s="31"/>
       <c r="AY39" s="31"/>
       <c r="AZ39" s="31"/>
       <c r="BA39" s="31"/>
-      <c r="BB39" s="30"/>
-      <c r="BC39" s="30"/>
+      <c r="BB39" s="32"/>
+      <c r="BC39" s="33"/>
       <c r="BD39" s="31"/>
       <c r="BE39" s="31"/>
       <c r="BF39" s="31"/>
@@ -4593,27 +5531,28 @@
       <c r="BM39" s="31"/>
       <c r="BN39" s="31"/>
     </row>
-    <row r="40" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A40" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="26">
-        <v>0</v>
+    <row r="40" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A40" s="64"/>
+      <c r="B40" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="26" t="str">
+        <f ca="1">IF(F40=E40, IF(TODAY()&gt;F40, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F40) - E40) / (F40 - E40) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D40" s="27">
-        <f>IF(AND(F40&lt;&gt;"", E40&lt;&gt;""), F40-E40+1, "")</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="E40" s="28">
-        <v>45999</v>
+        <v>45992</v>
       </c>
       <c r="F40" s="28">
-        <v>46010</v>
-      </c>
-      <c r="G40" s="39"/>
+        <v>45998</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>101</v>
+      </c>
       <c r="H40" s="31"/>
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
@@ -4655,45 +5594,46 @@
       <c r="AT40" s="31"/>
       <c r="AU40" s="32"/>
       <c r="AV40" s="33"/>
-      <c r="AW40" s="31"/>
-      <c r="AX40" s="31"/>
-      <c r="AY40" s="31"/>
-      <c r="AZ40" s="31"/>
-      <c r="BA40" s="31"/>
-      <c r="BB40" s="32"/>
-      <c r="BC40" s="33"/>
-      <c r="BD40" s="40"/>
-      <c r="BE40" s="40"/>
-      <c r="BF40" s="40"/>
-      <c r="BG40" s="40"/>
-      <c r="BH40" s="40"/>
-      <c r="BI40" s="40"/>
-      <c r="BJ40" s="40"/>
-      <c r="BK40" s="40"/>
-      <c r="BL40" s="40"/>
-      <c r="BM40" s="40"/>
-      <c r="BN40" s="40"/>
-    </row>
-    <row r="41" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A41" s="45"/>
-      <c r="B41" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="26">
-        <v>0</v>
+      <c r="AW40" s="30"/>
+      <c r="AX40" s="30"/>
+      <c r="AY40" s="30"/>
+      <c r="AZ40" s="30"/>
+      <c r="BA40" s="30"/>
+      <c r="BB40" s="30"/>
+      <c r="BC40" s="30"/>
+      <c r="BD40" s="31"/>
+      <c r="BE40" s="31"/>
+      <c r="BF40" s="31"/>
+      <c r="BG40" s="31"/>
+      <c r="BH40" s="31"/>
+      <c r="BI40" s="31"/>
+      <c r="BJ40" s="31"/>
+      <c r="BK40" s="31"/>
+      <c r="BL40" s="31"/>
+      <c r="BM40" s="31"/>
+      <c r="BN40" s="31"/>
+    </row>
+    <row r="41" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A41" s="64"/>
+      <c r="B41" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="26" t="str">
+        <f ca="1">IF(F41=E41, IF(TODAY()&gt;F41, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F41) - E41) / (F41 - E41) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D41" s="27">
-        <f>IF(AND(F41&lt;&gt;"", E41&lt;&gt;""), F41-E41+1, "")</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="E41" s="28">
-        <v>45999</v>
+        <v>45992</v>
       </c>
       <c r="F41" s="28">
-        <v>46008</v>
+        <v>45998</v>
       </c>
       <c r="G41" s="29" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="31"/>
@@ -4736,45 +5676,46 @@
       <c r="AT41" s="31"/>
       <c r="AU41" s="32"/>
       <c r="AV41" s="33"/>
-      <c r="AW41" s="31"/>
-      <c r="AX41" s="31"/>
-      <c r="AY41" s="31"/>
-      <c r="AZ41" s="31"/>
-      <c r="BA41" s="31"/>
-      <c r="BB41" s="32"/>
-      <c r="BC41" s="33"/>
-      <c r="BD41" s="30"/>
-      <c r="BE41" s="30"/>
-      <c r="BF41" s="30"/>
-      <c r="BG41" s="30"/>
-      <c r="BH41" s="30"/>
-      <c r="BI41" s="30"/>
-      <c r="BJ41" s="30"/>
-      <c r="BK41" s="30"/>
-      <c r="BL41" s="30"/>
-      <c r="BM41" s="30"/>
+      <c r="AW41" s="30"/>
+      <c r="AX41" s="30"/>
+      <c r="AY41" s="30"/>
+      <c r="AZ41" s="30"/>
+      <c r="BA41" s="30"/>
+      <c r="BB41" s="30"/>
+      <c r="BC41" s="30"/>
+      <c r="BD41" s="31"/>
+      <c r="BE41" s="31"/>
+      <c r="BF41" s="31"/>
+      <c r="BG41" s="31"/>
+      <c r="BH41" s="31"/>
+      <c r="BI41" s="31"/>
+      <c r="BJ41" s="31"/>
+      <c r="BK41" s="31"/>
+      <c r="BL41" s="31"/>
+      <c r="BM41" s="31"/>
       <c r="BN41" s="31"/>
     </row>
     <row r="42" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A42" s="45"/>
-      <c r="B42" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="26">
-        <v>0</v>
+      <c r="A42" s="64"/>
+      <c r="B42" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="26" t="str">
+        <f ca="1">IF(F42=E42, IF(TODAY()&gt;F42, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F42) - E42) / (F42 - E42) * 100, 1) &amp; "%")</f>
+        <v>6.5%</v>
       </c>
       <c r="D42" s="27">
-        <f>IF(AND(F42&lt;&gt;"", E42&lt;&gt;""), F42-E42+1, "")</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="E42" s="28">
-        <v>45999</v>
+        <v>45964</v>
       </c>
       <c r="F42" s="28">
-        <v>46008</v>
+        <v>45995</v>
       </c>
       <c r="G42" s="29" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="31"/>
@@ -4789,73 +5730,74 @@
       <c r="R42" s="31"/>
       <c r="S42" s="32"/>
       <c r="T42" s="33"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
-      <c r="Y42" s="31"/>
-      <c r="Z42" s="32"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
-      <c r="AG42" s="32"/>
-      <c r="AH42" s="33"/>
-      <c r="AI42" s="31"/>
-      <c r="AJ42" s="31"/>
-      <c r="AK42" s="31"/>
-      <c r="AL42" s="31"/>
-      <c r="AM42" s="31"/>
-      <c r="AN42" s="32"/>
-      <c r="AO42" s="33"/>
-      <c r="AP42" s="31"/>
-      <c r="AQ42" s="31"/>
-      <c r="AR42" s="31"/>
-      <c r="AS42" s="31"/>
-      <c r="AT42" s="31"/>
-      <c r="AU42" s="32"/>
-      <c r="AV42" s="33"/>
-      <c r="AW42" s="31"/>
-      <c r="AX42" s="31"/>
-      <c r="AY42" s="31"/>
-      <c r="AZ42" s="31"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="30"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="30"/>
+      <c r="AN42" s="30"/>
+      <c r="AO42" s="30"/>
+      <c r="AP42" s="30"/>
+      <c r="AQ42" s="30"/>
+      <c r="AR42" s="30"/>
+      <c r="AS42" s="30"/>
+      <c r="AT42" s="30"/>
+      <c r="AU42" s="30"/>
+      <c r="AV42" s="30"/>
+      <c r="AW42" s="30"/>
+      <c r="AX42" s="30"/>
+      <c r="AY42" s="30"/>
+      <c r="AZ42" s="30"/>
       <c r="BA42" s="31"/>
       <c r="BB42" s="32"/>
       <c r="BC42" s="33"/>
-      <c r="BD42" s="30"/>
-      <c r="BE42" s="30"/>
-      <c r="BF42" s="30"/>
-      <c r="BG42" s="30"/>
-      <c r="BH42" s="30"/>
-      <c r="BI42" s="30"/>
-      <c r="BJ42" s="30"/>
-      <c r="BK42" s="30"/>
-      <c r="BL42" s="30"/>
-      <c r="BM42" s="30"/>
+      <c r="BD42" s="31"/>
+      <c r="BE42" s="31"/>
+      <c r="BF42" s="31"/>
+      <c r="BG42" s="31"/>
+      <c r="BH42" s="31"/>
+      <c r="BI42" s="31"/>
+      <c r="BJ42" s="31"/>
+      <c r="BK42" s="31"/>
+      <c r="BL42" s="31"/>
+      <c r="BM42" s="31"/>
       <c r="BN42" s="31"/>
     </row>
     <row r="43" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A43" s="45"/>
-      <c r="B43" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="26">
-        <v>0</v>
+      <c r="A43" s="64"/>
+      <c r="B43" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="26" t="str">
+        <f ca="1">IF(F43=E43, IF(TODAY()&gt;F43, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F43) - E43) / (F43 - E43) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D43" s="27">
-        <f>IF(AND(F43&lt;&gt;"", E43&lt;&gt;""), F43-E43+1, "")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E43" s="28">
-        <v>46010</v>
+        <v>45996</v>
       </c>
       <c r="F43" s="28">
-        <v>46010</v>
+        <v>45996</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H43" s="31"/>
       <c r="I43" s="31"/>
@@ -4902,7 +5844,7 @@
       <c r="AX43" s="31"/>
       <c r="AY43" s="31"/>
       <c r="AZ43" s="31"/>
-      <c r="BA43" s="31"/>
+      <c r="BA43" s="30"/>
       <c r="BB43" s="32"/>
       <c r="BC43" s="33"/>
       <c r="BD43" s="31"/>
@@ -4917,26 +5859,27 @@
       <c r="BM43" s="31"/>
       <c r="BN43" s="31"/>
     </row>
-    <row r="44" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="46"/>
-      <c r="B44" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="26">
-        <v>0</v>
+    <row r="44" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A44" s="65"/>
+      <c r="B44" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="26" t="str">
+        <f ca="1">IF(F44=E44, IF(TODAY()&gt;F44, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F44) - E44) / (F44 - E44) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D44" s="27">
-        <f>IF(AND(F44&lt;&gt;"", E44&lt;&gt;""), F44-E44+1, "")</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E44" s="28">
-        <v>46010</v>
+        <v>45997</v>
       </c>
       <c r="F44" s="28">
-        <v>46010</v>
+        <v>45998</v>
       </c>
       <c r="G44" s="29" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H44" s="31"/>
       <c r="I44" s="31"/>
@@ -4984,8 +5927,8 @@
       <c r="AY44" s="31"/>
       <c r="AZ44" s="31"/>
       <c r="BA44" s="31"/>
-      <c r="BB44" s="32"/>
-      <c r="BC44" s="33"/>
+      <c r="BB44" s="30"/>
+      <c r="BC44" s="30"/>
       <c r="BD44" s="31"/>
       <c r="BE44" s="31"/>
       <c r="BF44" s="31"/>
@@ -4998,81 +5941,474 @@
       <c r="BM44" s="31"/>
       <c r="BN44" s="31"/>
     </row>
-    <row r="45" spans="1:66">
-      <c r="E45" s="7"/>
-      <c r="F45" s="1"/>
-      <c r="I45" s="3"/>
-    </row>
-    <row r="46" spans="1:66">
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="1:66">
-      <c r="E47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="1:66">
-      <c r="I48" s="3"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="8" t="s">
-        <v>106</v>
-      </c>
+    <row r="45" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A45" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="26" t="str">
+        <f ca="1">IF(F45=E45, IF(TODAY()&gt;F45, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F45) - E45) / (F45 - E45) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D45" s="27">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E45" s="28">
+        <v>45999</v>
+      </c>
+      <c r="F45" s="28">
+        <v>46010</v>
+      </c>
+      <c r="G45" s="39"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
+      <c r="X45" s="31"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="32"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
+      <c r="AD45" s="31"/>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="32"/>
+      <c r="AH45" s="33"/>
+      <c r="AI45" s="31"/>
+      <c r="AJ45" s="31"/>
+      <c r="AK45" s="31"/>
+      <c r="AL45" s="31"/>
+      <c r="AM45" s="31"/>
+      <c r="AN45" s="32"/>
+      <c r="AO45" s="33"/>
+      <c r="AP45" s="31"/>
+      <c r="AQ45" s="31"/>
+      <c r="AR45" s="31"/>
+      <c r="AS45" s="31"/>
+      <c r="AT45" s="31"/>
+      <c r="AU45" s="32"/>
+      <c r="AV45" s="33"/>
+      <c r="AW45" s="31"/>
+      <c r="AX45" s="31"/>
+      <c r="AY45" s="31"/>
+      <c r="AZ45" s="31"/>
+      <c r="BA45" s="31"/>
+      <c r="BB45" s="32"/>
+      <c r="BC45" s="33"/>
+      <c r="BD45" s="40"/>
+      <c r="BE45" s="40"/>
+      <c r="BF45" s="40"/>
+      <c r="BG45" s="40"/>
+      <c r="BH45" s="40"/>
+      <c r="BI45" s="40"/>
+      <c r="BJ45" s="40"/>
+      <c r="BK45" s="40"/>
+      <c r="BL45" s="40"/>
+      <c r="BM45" s="40"/>
+      <c r="BN45" s="40"/>
+    </row>
+    <row r="46" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A46" s="44"/>
+      <c r="B46" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="26" t="str">
+        <f ca="1">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D46" s="27">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E46" s="28">
+        <v>45999</v>
+      </c>
+      <c r="F46" s="28">
+        <v>46008</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
+      <c r="AE46" s="31"/>
+      <c r="AF46" s="31"/>
+      <c r="AG46" s="32"/>
+      <c r="AH46" s="33"/>
+      <c r="AI46" s="31"/>
+      <c r="AJ46" s="31"/>
+      <c r="AK46" s="31"/>
+      <c r="AL46" s="31"/>
+      <c r="AM46" s="31"/>
+      <c r="AN46" s="32"/>
+      <c r="AO46" s="33"/>
+      <c r="AP46" s="31"/>
+      <c r="AQ46" s="31"/>
+      <c r="AR46" s="31"/>
+      <c r="AS46" s="31"/>
+      <c r="AT46" s="31"/>
+      <c r="AU46" s="32"/>
+      <c r="AV46" s="33"/>
+      <c r="AW46" s="31"/>
+      <c r="AX46" s="31"/>
+      <c r="AY46" s="31"/>
+      <c r="AZ46" s="31"/>
+      <c r="BA46" s="31"/>
+      <c r="BB46" s="32"/>
+      <c r="BC46" s="33"/>
+      <c r="BD46" s="30"/>
+      <c r="BE46" s="30"/>
+      <c r="BF46" s="30"/>
+      <c r="BG46" s="30"/>
+      <c r="BH46" s="30"/>
+      <c r="BI46" s="30"/>
+      <c r="BJ46" s="30"/>
+      <c r="BK46" s="30"/>
+      <c r="BL46" s="30"/>
+      <c r="BM46" s="30"/>
+      <c r="BN46" s="31"/>
+    </row>
+    <row r="47" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A47" s="44"/>
+      <c r="B47" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="26" t="str">
+        <f ca="1">IF(F47=E47, IF(TODAY()&gt;F47, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F47) - E47) / (F47 - E47) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D47" s="27">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E47" s="28">
+        <v>45999</v>
+      </c>
+      <c r="F47" s="28">
+        <v>46008</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="31"/>
+      <c r="X47" s="31"/>
+      <c r="Y47" s="31"/>
+      <c r="Z47" s="32"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="31"/>
+      <c r="AD47" s="31"/>
+      <c r="AE47" s="31"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="32"/>
+      <c r="AH47" s="33"/>
+      <c r="AI47" s="31"/>
+      <c r="AJ47" s="31"/>
+      <c r="AK47" s="31"/>
+      <c r="AL47" s="31"/>
+      <c r="AM47" s="31"/>
+      <c r="AN47" s="32"/>
+      <c r="AO47" s="33"/>
+      <c r="AP47" s="31"/>
+      <c r="AQ47" s="31"/>
+      <c r="AR47" s="31"/>
+      <c r="AS47" s="31"/>
+      <c r="AT47" s="31"/>
+      <c r="AU47" s="32"/>
+      <c r="AV47" s="33"/>
+      <c r="AW47" s="31"/>
+      <c r="AX47" s="31"/>
+      <c r="AY47" s="31"/>
+      <c r="AZ47" s="31"/>
+      <c r="BA47" s="31"/>
+      <c r="BB47" s="32"/>
+      <c r="BC47" s="33"/>
+      <c r="BD47" s="30"/>
+      <c r="BE47" s="30"/>
+      <c r="BF47" s="30"/>
+      <c r="BG47" s="30"/>
+      <c r="BH47" s="30"/>
+      <c r="BI47" s="30"/>
+      <c r="BJ47" s="30"/>
+      <c r="BK47" s="30"/>
+      <c r="BL47" s="30"/>
+      <c r="BM47" s="30"/>
+      <c r="BN47" s="31"/>
+    </row>
+    <row r="48" spans="1:66" ht="15.75" thickBot="1">
+      <c r="A48" s="44"/>
+      <c r="B48" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="26" t="str">
+        <f ca="1">IF(F48=E48, IF(TODAY()&gt;F48, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F48) - E48) / (F48 - E48) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D48" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E48" s="28">
+        <v>46010</v>
+      </c>
+      <c r="F48" s="28">
+        <v>46010</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="31"/>
+      <c r="V48" s="31"/>
+      <c r="W48" s="31"/>
+      <c r="X48" s="31"/>
+      <c r="Y48" s="31"/>
+      <c r="Z48" s="32"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="31"/>
+      <c r="AC48" s="31"/>
+      <c r="AD48" s="31"/>
+      <c r="AE48" s="31"/>
+      <c r="AF48" s="31"/>
+      <c r="AG48" s="32"/>
+      <c r="AH48" s="33"/>
+      <c r="AI48" s="31"/>
+      <c r="AJ48" s="31"/>
+      <c r="AK48" s="31"/>
+      <c r="AL48" s="31"/>
+      <c r="AM48" s="31"/>
+      <c r="AN48" s="32"/>
+      <c r="AO48" s="33"/>
+      <c r="AP48" s="31"/>
+      <c r="AQ48" s="31"/>
+      <c r="AR48" s="31"/>
+      <c r="AS48" s="31"/>
+      <c r="AT48" s="31"/>
+      <c r="AU48" s="32"/>
+      <c r="AV48" s="33"/>
+      <c r="AW48" s="31"/>
+      <c r="AX48" s="31"/>
+      <c r="AY48" s="31"/>
+      <c r="AZ48" s="31"/>
+      <c r="BA48" s="31"/>
+      <c r="BB48" s="32"/>
+      <c r="BC48" s="33"/>
+      <c r="BD48" s="31"/>
+      <c r="BE48" s="31"/>
+      <c r="BF48" s="31"/>
+      <c r="BG48" s="31"/>
+      <c r="BH48" s="31"/>
+      <c r="BI48" s="31"/>
+      <c r="BJ48" s="31"/>
+      <c r="BK48" s="31"/>
+      <c r="BL48" s="31"/>
+      <c r="BM48" s="31"/>
+      <c r="BN48" s="31"/>
+    </row>
+    <row r="49" spans="1:66" ht="15" customHeight="1" thickBot="1">
+      <c r="A49" s="45"/>
+      <c r="B49" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="26" t="str">
+        <f ca="1">IF(F49=E49, IF(TODAY()&gt;F49, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F49) - E49) / (F49 - E49) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D49" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E49" s="28">
+        <v>46010</v>
+      </c>
+      <c r="F49" s="28">
+        <v>46010</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
+      <c r="AE49" s="31"/>
+      <c r="AF49" s="31"/>
+      <c r="AG49" s="32"/>
+      <c r="AH49" s="33"/>
+      <c r="AI49" s="31"/>
+      <c r="AJ49" s="31"/>
+      <c r="AK49" s="31"/>
+      <c r="AL49" s="31"/>
+      <c r="AM49" s="31"/>
+      <c r="AN49" s="32"/>
+      <c r="AO49" s="33"/>
+      <c r="AP49" s="31"/>
+      <c r="AQ49" s="31"/>
+      <c r="AR49" s="31"/>
+      <c r="AS49" s="31"/>
+      <c r="AT49" s="31"/>
+      <c r="AU49" s="32"/>
+      <c r="AV49" s="33"/>
+      <c r="AW49" s="31"/>
+      <c r="AX49" s="31"/>
+      <c r="AY49" s="31"/>
+      <c r="AZ49" s="31"/>
+      <c r="BA49" s="31"/>
+      <c r="BB49" s="32"/>
+      <c r="BC49" s="33"/>
+      <c r="BD49" s="31"/>
+      <c r="BE49" s="31"/>
+      <c r="BF49" s="31"/>
+      <c r="BG49" s="31"/>
+      <c r="BH49" s="31"/>
+      <c r="BI49" s="31"/>
+      <c r="BJ49" s="31"/>
+      <c r="BK49" s="31"/>
+      <c r="BL49" s="31"/>
+      <c r="BM49" s="31"/>
+      <c r="BN49" s="31"/>
+    </row>
+    <row r="50" spans="1:66">
+      <c r="E50" s="7"/>
+      <c r="F50" s="1"/>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="2:9" ht="16.5">
-      <c r="B51" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="3"/>
+    <row r="51" spans="1:66">
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="10" t="s">
-        <v>108</v>
-      </c>
+    <row r="52" spans="1:66">
+      <c r="E52" s="1"/>
+      <c r="G52" s="1"/>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="2:9">
-      <c r="C53" s="3"/>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="C54" s="3"/>
-    </row>
-    <row r="55" spans="2:9"/>
-    <row r="56" spans="2:9"/>
-    <row r="57" spans="2:9" ht="16.5">
-      <c r="B57" s="2"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-    </row>
-    <row r="58" spans="2:9">
+    <row r="53" spans="1:66">
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:66">
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:66">
+      <c r="B55" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:66" ht="16.5">
+      <c r="B56" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="3"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:66">
+      <c r="B57" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:66">
       <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" spans="2:9" ht="16.5">
-      <c r="B59" s="2"/>
-      <c r="D59" s="3"/>
-    </row>
-    <row r="60" spans="2:9">
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="2:9">
+    </row>
+    <row r="59" spans="1:66">
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="1:66"/>
+    <row r="61" spans="1:66"/>
+    <row r="62" spans="1:66" ht="16.5">
+      <c r="B62" s="2"/>
+      <c r="C62" s="3"/>
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="2:9">
+    <row r="63" spans="1:66">
+      <c r="C63" s="3"/>
       <c r="D63" s="3"/>
     </row>
-    <row r="64" spans="2:9">
+    <row r="64" spans="1:66" ht="16.5">
+      <c r="B64" s="2"/>
       <c r="D64" s="3"/>
     </row>
     <row r="65" spans="3:8">
@@ -5080,16 +6416,36 @@
       <c r="D65" s="3"/>
     </row>
     <row r="66" spans="3:8">
-      <c r="H66" s="11"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+    </row>
+    <row r="67" spans="3:8">
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68" spans="3:8">
+      <c r="D68" s="3"/>
+    </row>
+    <row r="69" spans="3:8">
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="3:8">
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" spans="3:8">
+      <c r="H71" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A12:A39"/>
-    <mergeCell ref="A40:A44"/>
+  <mergeCells count="9">
+    <mergeCell ref="A45:A49"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:W1"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A4:A11"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DCC612-50F1-40C5-9DBF-4A15F14B9C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE8477-5D9E-40EA-BE18-1A5865BF7FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="133">
   <si>
     <t>팀명</t>
   </si>
@@ -1277,7 +1277,18 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
+    <t>이재빈</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>김석현</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>메인페이지 프로토타입 구현</t>
+  </si>
+  <si>
+    <t>정윤성</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1480,7 +1491,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1555,19 +1566,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBBC04"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC5E0B3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4A7D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1757,7 +1774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1870,21 +1887,33 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1918,41 +1947,53 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1960,6 +2001,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9FC5E8"/>
+      <color rgb="FFB4A7D6"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2175,7 +2222,7 @@
   <dimension ref="A1:BN71"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="38.140625" customWidth="1"/>
+    <col min="2" max="2" width="60.5703125" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2186,31 +2233,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48" t="s">
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -2274,7 +2321,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="53" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -2462,7 +2509,7 @@
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="50"/>
+      <c r="G3" s="54"/>
       <c r="H3" s="21">
         <v>45951</v>
       </c>
@@ -2642,7 +2689,7 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="55" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="25" t="s">
@@ -2662,7 +2709,7 @@
       <c r="F4" s="28">
         <v>45952</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H4" s="30"/>
@@ -2726,7 +2773,7 @@
       <c r="BN4" s="31"/>
     </row>
     <row r="5" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="52"/>
+      <c r="A5" s="56"/>
       <c r="B5" s="25" t="s">
         <v>73</v>
       </c>
@@ -2744,7 +2791,7 @@
       <c r="F5" s="28">
         <v>45952</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="30"/>
@@ -2808,7 +2855,7 @@
       <c r="BN5" s="31"/>
     </row>
     <row r="6" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="52"/>
+      <c r="A6" s="56"/>
       <c r="B6" s="25" t="s">
         <v>74</v>
       </c>
@@ -2826,7 +2873,7 @@
       <c r="F6" s="28">
         <v>45952</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="30"/>
@@ -2890,7 +2937,7 @@
       <c r="BN6" s="31"/>
     </row>
     <row r="7" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="52"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="34" t="s">
         <v>75</v>
       </c>
@@ -2908,7 +2955,7 @@
       <c r="F7" s="28">
         <v>45961</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H7" s="30"/>
@@ -2972,12 +3019,12 @@
       <c r="BN7" s="31"/>
     </row>
     <row r="8" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="52"/>
+      <c r="A8" s="56"/>
       <c r="B8" s="35" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="26" t="str">
-        <f ca="1">ROUND(MAX(0, MIN(TODAY(), F8) - E8) / (F8 - E8) * 100, 1) &amp; "%"</f>
+        <f t="shared" ref="C8:C16" ca="1" si="1">IF(F8=E8, IF(TODAY()&gt;F8, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F8) - E8) / (F8 - E8) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D8" s="27">
@@ -3054,13 +3101,13 @@
       <c r="BN8" s="31"/>
     </row>
     <row r="9" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="52"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="26" t="e">
-        <f>B17+B21,B28,B33</f>
-        <v>#VALUE!</v>
+      <c r="C9" s="26" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>100%</v>
       </c>
       <c r="D9" s="27">
         <f t="shared" si="0"/>
@@ -3072,7 +3119,7 @@
       <c r="F9" s="28">
         <v>45962</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H9" s="31"/>
@@ -3136,12 +3183,12 @@
       <c r="BN9" s="31"/>
     </row>
     <row r="10" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="34" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="26" t="str">
-        <f ca="1">IF(F10=E10, IF(TODAY()&gt;F10, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F10) - E10) / (F10 - E10) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>100%</v>
       </c>
       <c r="D10" s="27">
@@ -3154,7 +3201,7 @@
       <c r="F10" s="28">
         <v>45961</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="31"/>
@@ -3218,12 +3265,12 @@
       <c r="BN10" s="31"/>
     </row>
     <row r="11" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="57"/>
       <c r="B11" s="37" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="26" t="str">
-        <f ca="1">IF(F11=E11, IF(TODAY()&gt;F11, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F11) - E11) / (F11 - E11) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>100%</v>
       </c>
       <c r="D11" s="27">
@@ -3236,8 +3283,8 @@
       <c r="F11" s="28">
         <v>45958</v>
       </c>
-      <c r="G11" s="29" t="s">
-        <v>102</v>
+      <c r="G11" s="63" t="s">
+        <v>110</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
@@ -3300,27 +3347,29 @@
       <c r="BN11" s="31"/>
     </row>
     <row r="12" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="26" t="str">
-        <f ca="1">IF(F12=E12, IF(TODAY()&gt;F12, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F12) - E12) / (F12 - E12) * 100, 1) &amp; "%")</f>
+      <c r="C12" s="59" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>100%</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="60">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="61">
         <v>45959</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="61">
         <v>45959</v>
       </c>
-      <c r="G12" s="39"/>
+      <c r="G12" s="62" t="s">
+        <v>100</v>
+      </c>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
@@ -3329,7 +3378,7 @@
       <c r="M12" s="33"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
-      <c r="P12" s="40"/>
+      <c r="P12" s="38"/>
       <c r="Q12" s="31"/>
       <c r="R12" s="31"/>
       <c r="S12" s="32"/>
@@ -3382,12 +3431,12 @@
       <c r="BN12" s="31"/>
     </row>
     <row r="13" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="64"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="25" t="s">
         <v>82</v>
       </c>
       <c r="C13" s="26" t="str">
-        <f ca="1">IF(F13=E13, IF(TODAY()&gt;F13, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F13) - E13) / (F13 - E13) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>100%</v>
       </c>
       <c r="D13" s="27">
@@ -3400,7 +3449,7 @@
       <c r="F13" s="28">
         <v>45959</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H13" s="31"/>
@@ -3464,12 +3513,12 @@
       <c r="BN13" s="31"/>
     </row>
     <row r="14" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="25" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="26" t="str">
-        <f ca="1">IF(F14=E14, IF(TODAY()&gt;F14, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F14) - E14) / (F14 - E14) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>100%</v>
       </c>
       <c r="D14" s="27">
@@ -3482,7 +3531,7 @@
       <c r="F14" s="28">
         <v>45959</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H14" s="31"/>
@@ -3546,25 +3595,27 @@
       <c r="BN14" s="31"/>
     </row>
     <row r="15" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="64"/>
-      <c r="B15" s="38" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="26" t="str">
-        <f ca="1">IF(F15=E15, IF(TODAY()&gt;F15, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F15) - E15) / (F15 - E15) * 100, 1) &amp; "%")</f>
+      <c r="C15" s="59" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>11.8%</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="60">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="61">
         <v>45964</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="61">
         <v>45981</v>
       </c>
-      <c r="G15" s="39"/>
+      <c r="G15" s="62" t="s">
+        <v>100</v>
+      </c>
       <c r="H15" s="31"/>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
@@ -3578,24 +3629,24 @@
       <c r="R15" s="31"/>
       <c r="S15" s="32"/>
       <c r="T15" s="33"/>
-      <c r="U15" s="40"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="40"/>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="40"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="40"/>
-      <c r="AD15" s="40"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="40"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="40"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="40"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="38"/>
+      <c r="AL15" s="38"/>
       <c r="AM15" s="31"/>
       <c r="AN15" s="32"/>
       <c r="AO15" s="33"/>
@@ -3626,12 +3677,12 @@
       <c r="BN15" s="31"/>
     </row>
     <row r="16" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="64"/>
-      <c r="B16" s="54" t="s">
+      <c r="A16" s="45"/>
+      <c r="B16" s="41" t="s">
         <v>122</v>
       </c>
       <c r="C16" s="26" t="str">
-        <f ca="1">IF(F16=E16, IF(TODAY()&gt;F16, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F16) - E16) / (F16 - E16) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>0%</v>
       </c>
       <c r="D16" s="27">
@@ -3708,15 +3759,15 @@
       <c r="BN16" s="31"/>
     </row>
     <row r="17" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="64"/>
-      <c r="B17" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="67"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
@@ -3778,8 +3829,8 @@
       <c r="BN17" s="31"/>
     </row>
     <row r="18" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="64"/>
-      <c r="B18" s="56" t="s">
+      <c r="A18" s="45"/>
+      <c r="B18" s="43" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="26" t="str">
@@ -3796,7 +3847,7 @@
       <c r="F18" s="28">
         <v>45965</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="64" t="s">
         <v>110</v>
       </c>
       <c r="H18" s="31"/>
@@ -3860,7 +3911,7 @@
       <c r="BN18" s="31"/>
     </row>
     <row r="19" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="64"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="37" t="s">
         <v>88</v>
       </c>
@@ -3878,7 +3929,7 @@
       <c r="F19" s="28">
         <v>45967</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="64" t="s">
         <v>107</v>
       </c>
       <c r="H19" s="31"/>
@@ -3942,8 +3993,8 @@
       <c r="BN19" s="31"/>
     </row>
     <row r="20" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="64"/>
-      <c r="B20" s="42" t="s">
+      <c r="A20" s="45"/>
+      <c r="B20" s="40" t="s">
         <v>123</v>
       </c>
       <c r="C20" s="26" t="str">
@@ -4024,15 +4075,15 @@
       <c r="BN20" s="31"/>
     </row>
     <row r="21" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="64"/>
-      <c r="B21" s="57" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="70"/>
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
@@ -4094,12 +4145,12 @@
       <c r="BN21" s="31"/>
     </row>
     <row r="22" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="64"/>
-      <c r="B22" s="54" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="41" t="s">
         <v>124</v>
       </c>
       <c r="C22" s="26" t="str">
-        <f ca="1">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C22:C27" ca="1" si="2">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
       <c r="D22" s="27">
@@ -4112,7 +4163,9 @@
       <c r="F22" s="28">
         <v>45969</v>
       </c>
-      <c r="G22" s="29"/>
+      <c r="G22" s="29" t="s">
+        <v>129</v>
+      </c>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
@@ -4174,12 +4227,12 @@
       <c r="BN22" s="31"/>
     </row>
     <row r="23" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="64"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="45"/>
+      <c r="B23" s="39" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="26" t="str">
-        <f ca="1">IF(F23=E23, IF(TODAY()&gt;F23, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F23) - E23) / (F23 - E23) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>20%</v>
       </c>
       <c r="D23" s="27">
@@ -4192,7 +4245,7 @@
       <c r="F23" s="28">
         <v>45970</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="64" t="s">
         <v>104</v>
       </c>
       <c r="H23" s="31"/>
@@ -4256,12 +4309,12 @@
       <c r="BN23" s="31"/>
     </row>
     <row r="24" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="45"/>
       <c r="B24" s="37" t="s">
         <v>106</v>
       </c>
       <c r="C24" s="26" t="str">
-        <f ca="1">IF(F24=E24, IF(TODAY()&gt;F24, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F24) - E24) / (F24 - E24) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>16.7%</v>
       </c>
       <c r="D24" s="27">
@@ -4274,7 +4327,7 @@
       <c r="F24" s="28">
         <v>45971</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="64" t="s">
         <v>105</v>
       </c>
       <c r="H24" s="31"/>
@@ -4338,12 +4391,12 @@
       <c r="BN24" s="31"/>
     </row>
     <row r="25" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="64"/>
-      <c r="B25" s="42" t="s">
+      <c r="A25" s="45"/>
+      <c r="B25" s="40" t="s">
         <v>119</v>
       </c>
       <c r="C25" s="26" t="str">
-        <f ca="1">IF(F25=E25, IF(TODAY()&gt;F25, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F25) - E25) / (F25 - E25) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0%</v>
       </c>
       <c r="D25" s="27">
@@ -4356,7 +4409,9 @@
       <c r="F25" s="28">
         <v>45969</v>
       </c>
-      <c r="G25" s="29"/>
+      <c r="G25" s="29" t="s">
+        <v>130</v>
+      </c>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
@@ -4418,16 +4473,16 @@
       <c r="BN25" s="31"/>
     </row>
     <row r="26" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="64"/>
-      <c r="B26" s="42" t="s">
+      <c r="A26" s="45"/>
+      <c r="B26" s="40" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="26" t="str">
-        <f ca="1">IF(F26=E26, IF(TODAY()&gt;F26, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F26) - E26) / (F26 - E26) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0%</v>
       </c>
       <c r="D26" s="27">
-        <f t="shared" ref="D26:D27" si="1">IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26-E26+1, "")</f>
+        <f t="shared" ref="D26:D27" si="3">IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26-E26+1, "")</f>
         <v>2</v>
       </c>
       <c r="E26" s="28">
@@ -4436,7 +4491,9 @@
       <c r="F26" s="28">
         <v>45969</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="29" t="s">
+        <v>130</v>
+      </c>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
@@ -4498,16 +4555,16 @@
       <c r="BN26" s="31"/>
     </row>
     <row r="27" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="64"/>
-      <c r="B27" s="42" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="40" t="s">
         <v>121</v>
       </c>
       <c r="C27" s="26" t="str">
-        <f ca="1">IF(F27=E27, IF(TODAY()&gt;F27, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F27) - E27) / (F27 - E27) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0%</v>
       </c>
       <c r="D27" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E27" s="28">
@@ -4516,7 +4573,9 @@
       <c r="F27" s="28">
         <v>45969</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="29" t="s">
+        <v>130</v>
+      </c>
       <c r="H27" s="31"/>
       <c r="I27" s="31"/>
       <c r="J27" s="31"/>
@@ -4578,15 +4637,15 @@
       <c r="BN27" s="31"/>
     </row>
     <row r="28" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="64"/>
-      <c r="B28" s="60" t="s">
+      <c r="A28" s="45"/>
+      <c r="B28" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="62"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="73"/>
       <c r="H28" s="31"/>
       <c r="I28" s="31"/>
       <c r="J28" s="31"/>
@@ -4648,8 +4707,8 @@
       <c r="BN28" s="31"/>
     </row>
     <row r="29" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="42" t="s">
+      <c r="A29" s="45"/>
+      <c r="B29" s="40" t="s">
         <v>118</v>
       </c>
       <c r="C29" s="26" t="str">
@@ -4666,7 +4725,9 @@
       <c r="F29" s="28">
         <v>45977</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="29" t="s">
+        <v>132</v>
+      </c>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="J29" s="31"/>
@@ -4728,8 +4789,8 @@
       <c r="BN29" s="31"/>
     </row>
     <row r="30" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="64"/>
-      <c r="B30" s="54" t="s">
+      <c r="A30" s="45"/>
+      <c r="B30" s="41" t="s">
         <v>125</v>
       </c>
       <c r="C30" s="26" t="str">
@@ -4737,7 +4798,7 @@
         <v>0%</v>
       </c>
       <c r="D30" s="27">
-        <f t="shared" ref="D30" si="2">IF(AND(F30&lt;&gt;"", E30&lt;&gt;""), F30-E30+1, "")</f>
+        <f t="shared" ref="D30" si="4">IF(AND(F30&lt;&gt;"", E30&lt;&gt;""), F30-E30+1, "")</f>
         <v>6</v>
       </c>
       <c r="E30" s="28">
@@ -4746,7 +4807,9 @@
       <c r="F30" s="28">
         <v>45977</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="29" t="s">
+        <v>132</v>
+      </c>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="J30" s="31"/>
@@ -4808,7 +4871,7 @@
       <c r="BN30" s="31"/>
     </row>
     <row r="31" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="64"/>
+      <c r="A31" s="45"/>
       <c r="B31" s="37" t="s">
         <v>89</v>
       </c>
@@ -4826,7 +4889,7 @@
       <c r="F31" s="28">
         <v>45971</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="64" t="s">
         <v>107</v>
       </c>
       <c r="H31" s="31"/>
@@ -4890,7 +4953,7 @@
       <c r="BN31" s="31"/>
     </row>
     <row r="32" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="64"/>
+      <c r="A32" s="45"/>
       <c r="B32" s="37" t="s">
         <v>85</v>
       </c>
@@ -4908,7 +4971,7 @@
       <c r="F32" s="28">
         <v>45981</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="64" t="s">
         <v>107</v>
       </c>
       <c r="H32" s="31"/>
@@ -4972,15 +5035,15 @@
       <c r="BN32" s="31"/>
     </row>
     <row r="33" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="64"/>
-      <c r="B33" s="60" t="s">
+      <c r="A33" s="45"/>
+      <c r="B33" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="62"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="73"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
@@ -5042,12 +5105,12 @@
       <c r="BN33" s="31"/>
     </row>
     <row r="34" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="64"/>
-      <c r="B34" s="54" t="s">
+      <c r="A34" s="45"/>
+      <c r="B34" s="41" t="s">
         <v>117</v>
       </c>
       <c r="C34" s="26" t="str">
-        <f ca="1">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C34:C49" ca="1" si="5">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
       <c r="D34" s="27">
@@ -5124,12 +5187,12 @@
       <c r="BN34" s="31"/>
     </row>
     <row r="35" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="64"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="37" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="26" t="str">
-        <f ca="1">IF(F35=E35, IF(TODAY()&gt;F35, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F35) - E35) / (F35 - E35) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>16.7%</v>
       </c>
       <c r="D35" s="27">
@@ -5142,7 +5205,7 @@
       <c r="F35" s="28">
         <v>45971</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="G35" s="64" t="s">
         <v>105</v>
       </c>
       <c r="H35" s="31"/>
@@ -5206,25 +5269,27 @@
       <c r="BN35" s="31"/>
     </row>
     <row r="36" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A36" s="64"/>
-      <c r="B36" s="38" t="s">
+      <c r="A36" s="45"/>
+      <c r="B36" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="26" t="str">
-        <f ca="1">IF(F36=E36, IF(TODAY()&gt;F36, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F36) - E36) / (F36 - E36) * 100, 1) &amp; "%")</f>
+      <c r="C36" s="59" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v>5.9%</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="60">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="61">
         <v>45964</v>
       </c>
-      <c r="F36" s="28">
+      <c r="F36" s="61">
         <v>45998</v>
       </c>
-      <c r="G36" s="39"/>
+      <c r="G36" s="62" t="s">
+        <v>100</v>
+      </c>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="J36" s="31"/>
@@ -5238,41 +5303,41 @@
       <c r="R36" s="31"/>
       <c r="S36" s="32"/>
       <c r="T36" s="33"/>
-      <c r="U36" s="40"/>
-      <c r="V36" s="40"/>
-      <c r="W36" s="40"/>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="40"/>
-      <c r="AA36" s="40"/>
-      <c r="AB36" s="40"/>
-      <c r="AC36" s="40"/>
-      <c r="AD36" s="40"/>
-      <c r="AE36" s="40"/>
-      <c r="AF36" s="40"/>
-      <c r="AG36" s="40"/>
-      <c r="AH36" s="40"/>
-      <c r="AI36" s="40"/>
-      <c r="AJ36" s="40"/>
-      <c r="AK36" s="40"/>
-      <c r="AL36" s="40"/>
-      <c r="AM36" s="40"/>
-      <c r="AN36" s="40"/>
-      <c r="AO36" s="40"/>
-      <c r="AP36" s="40"/>
-      <c r="AQ36" s="40"/>
-      <c r="AR36" s="40"/>
-      <c r="AS36" s="40"/>
-      <c r="AT36" s="40"/>
-      <c r="AU36" s="40"/>
-      <c r="AV36" s="40"/>
-      <c r="AW36" s="40"/>
-      <c r="AX36" s="40"/>
-      <c r="AY36" s="40"/>
-      <c r="AZ36" s="40"/>
-      <c r="BA36" s="40"/>
-      <c r="BB36" s="40"/>
-      <c r="BC36" s="40"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="38"/>
+      <c r="AK36" s="38"/>
+      <c r="AL36" s="38"/>
+      <c r="AM36" s="38"/>
+      <c r="AN36" s="38"/>
+      <c r="AO36" s="38"/>
+      <c r="AP36" s="38"/>
+      <c r="AQ36" s="38"/>
+      <c r="AR36" s="38"/>
+      <c r="AS36" s="38"/>
+      <c r="AT36" s="38"/>
+      <c r="AU36" s="38"/>
+      <c r="AV36" s="38"/>
+      <c r="AW36" s="38"/>
+      <c r="AX36" s="38"/>
+      <c r="AY36" s="38"/>
+      <c r="AZ36" s="38"/>
+      <c r="BA36" s="38"/>
+      <c r="BB36" s="38"/>
+      <c r="BC36" s="38"/>
       <c r="BD36" s="31"/>
       <c r="BE36" s="31"/>
       <c r="BF36" s="31"/>
@@ -5286,12 +5351,12 @@
       <c r="BN36" s="31"/>
     </row>
     <row r="37" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A37" s="64"/>
-      <c r="B37" s="54" t="s">
+      <c r="A37" s="45"/>
+      <c r="B37" s="41" t="s">
         <v>128</v>
       </c>
       <c r="C37" s="26" t="str">
-        <f ca="1">IF(F37=E37, IF(TODAY()&gt;F37, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F37) - E37) / (F37 - E37) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D37" s="27">
@@ -5368,12 +5433,12 @@
       <c r="BN37" s="31"/>
     </row>
     <row r="38" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="64"/>
-      <c r="B38" s="54" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="41" t="s">
         <v>115</v>
       </c>
       <c r="C38" s="26" t="str">
-        <f ca="1">IF(F38=E38, IF(TODAY()&gt;F38, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F38) - E38) / (F38 - E38) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D38" s="27">
@@ -5450,12 +5515,12 @@
       <c r="BN38" s="31"/>
     </row>
     <row r="39" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="64"/>
-      <c r="B39" s="55" t="s">
+      <c r="A39" s="45"/>
+      <c r="B39" s="42" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="26" t="str">
-        <f ca="1">IF(F39=E39, IF(TODAY()&gt;F39, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F39) - E39) / (F39 - E39) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D39" s="27">
@@ -5532,12 +5597,12 @@
       <c r="BN39" s="31"/>
     </row>
     <row r="40" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="64"/>
-      <c r="B40" s="54" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="41" t="s">
         <v>113</v>
       </c>
       <c r="C40" s="26" t="str">
-        <f ca="1">IF(F40=E40, IF(TODAY()&gt;F40, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F40) - E40) / (F40 - E40) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D40" s="27">
@@ -5614,12 +5679,12 @@
       <c r="BN40" s="31"/>
     </row>
     <row r="41" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="64"/>
-      <c r="B41" s="55" t="s">
+      <c r="A41" s="45"/>
+      <c r="B41" s="42" t="s">
         <v>112</v>
       </c>
       <c r="C41" s="26" t="str">
-        <f ca="1">IF(F41=E41, IF(TODAY()&gt;F41, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F41) - E41) / (F41 - E41) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D41" s="27">
@@ -5696,12 +5761,12 @@
       <c r="BN41" s="31"/>
     </row>
     <row r="42" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A42" s="64"/>
+      <c r="A42" s="45"/>
       <c r="B42" s="37" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="26" t="str">
-        <f ca="1">IF(F42=E42, IF(TODAY()&gt;F42, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F42) - E42) / (F42 - E42) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>6.5%</v>
       </c>
       <c r="D42" s="27">
@@ -5714,7 +5779,7 @@
       <c r="F42" s="28">
         <v>45995</v>
       </c>
-      <c r="G42" s="29" t="s">
+      <c r="G42" s="64" t="s">
         <v>102</v>
       </c>
       <c r="H42" s="31"/>
@@ -5778,12 +5843,12 @@
       <c r="BN42" s="31"/>
     </row>
     <row r="43" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A43" s="64"/>
-      <c r="B43" s="41" t="s">
+      <c r="A43" s="45"/>
+      <c r="B43" s="39" t="s">
         <v>90</v>
       </c>
       <c r="C43" s="26" t="str">
-        <f ca="1">IF(F43=E43, IF(TODAY()&gt;F43, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F43) - E43) / (F43 - E43) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D43" s="27">
@@ -5796,7 +5861,7 @@
       <c r="F43" s="28">
         <v>45996</v>
       </c>
-      <c r="G43" s="29" t="s">
+      <c r="G43" s="64" t="s">
         <v>102</v>
       </c>
       <c r="H43" s="31"/>
@@ -5860,12 +5925,12 @@
       <c r="BN43" s="31"/>
     </row>
     <row r="44" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="41" t="s">
+      <c r="A44" s="46"/>
+      <c r="B44" s="39" t="s">
         <v>91</v>
       </c>
       <c r="C44" s="26" t="str">
-        <f ca="1">IF(F44=E44, IF(TODAY()&gt;F44, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F44) - E44) / (F44 - E44) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D44" s="27">
@@ -5878,7 +5943,7 @@
       <c r="F44" s="28">
         <v>45998</v>
       </c>
-      <c r="G44" s="29" t="s">
+      <c r="G44" s="64" t="s">
         <v>102</v>
       </c>
       <c r="H44" s="31"/>
@@ -5942,27 +6007,29 @@
       <c r="BN44" s="31"/>
     </row>
     <row r="45" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A45" s="43" t="s">
+      <c r="A45" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="26" t="str">
-        <f ca="1">IF(F45=E45, IF(TODAY()&gt;F45, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F45) - E45) / (F45 - E45) * 100, 1) &amp; "%")</f>
+      <c r="C45" s="59" t="str">
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="60">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="61">
         <v>45999</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="61">
         <v>46010</v>
       </c>
-      <c r="G45" s="39"/>
+      <c r="G45" s="62" t="s">
+        <v>100</v>
+      </c>
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="31"/>
@@ -6011,25 +6078,25 @@
       <c r="BA45" s="31"/>
       <c r="BB45" s="32"/>
       <c r="BC45" s="33"/>
-      <c r="BD45" s="40"/>
-      <c r="BE45" s="40"/>
-      <c r="BF45" s="40"/>
-      <c r="BG45" s="40"/>
-      <c r="BH45" s="40"/>
-      <c r="BI45" s="40"/>
-      <c r="BJ45" s="40"/>
-      <c r="BK45" s="40"/>
-      <c r="BL45" s="40"/>
-      <c r="BM45" s="40"/>
-      <c r="BN45" s="40"/>
+      <c r="BD45" s="38"/>
+      <c r="BE45" s="38"/>
+      <c r="BF45" s="38"/>
+      <c r="BG45" s="38"/>
+      <c r="BH45" s="38"/>
+      <c r="BI45" s="38"/>
+      <c r="BJ45" s="38"/>
+      <c r="BK45" s="38"/>
+      <c r="BL45" s="38"/>
+      <c r="BM45" s="38"/>
+      <c r="BN45" s="38"/>
     </row>
     <row r="46" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A46" s="44"/>
+      <c r="A46" s="48"/>
       <c r="B46" s="25" t="s">
         <v>93</v>
       </c>
       <c r="C46" s="26" t="str">
-        <f ca="1">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D46" s="27">
@@ -6042,7 +6109,7 @@
       <c r="F46" s="28">
         <v>46008</v>
       </c>
-      <c r="G46" s="29" t="s">
+      <c r="G46" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H46" s="31"/>
@@ -6106,12 +6173,12 @@
       <c r="BN46" s="31"/>
     </row>
     <row r="47" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A47" s="44"/>
+      <c r="A47" s="48"/>
       <c r="B47" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="26" t="str">
-        <f ca="1">IF(F47=E47, IF(TODAY()&gt;F47, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F47) - E47) / (F47 - E47) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D47" s="27">
@@ -6124,7 +6191,7 @@
       <c r="F47" s="28">
         <v>46008</v>
       </c>
-      <c r="G47" s="29" t="s">
+      <c r="G47" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H47" s="31"/>
@@ -6188,12 +6255,12 @@
       <c r="BN47" s="31"/>
     </row>
     <row r="48" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A48" s="44"/>
+      <c r="A48" s="48"/>
       <c r="B48" s="25" t="s">
         <v>94</v>
       </c>
       <c r="C48" s="26" t="str">
-        <f ca="1">IF(F48=E48, IF(TODAY()&gt;F48, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F48) - E48) / (F48 - E48) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D48" s="27">
@@ -6206,7 +6273,7 @@
       <c r="F48" s="28">
         <v>46010</v>
       </c>
-      <c r="G48" s="29" t="s">
+      <c r="G48" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H48" s="31"/>
@@ -6270,12 +6337,12 @@
       <c r="BN48" s="31"/>
     </row>
     <row r="49" spans="1:66" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="45"/>
+      <c r="A49" s="49"/>
       <c r="B49" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="26" t="str">
-        <f ca="1">IF(F49=E49, IF(TODAY()&gt;F49, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F49) - E49) / (F49 - E49) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0%</v>
       </c>
       <c r="D49" s="27">
@@ -6288,7 +6355,7 @@
       <c r="F49" s="28">
         <v>46010</v>
       </c>
-      <c r="G49" s="29" t="s">
+      <c r="G49" s="62" t="s">
         <v>100</v>
       </c>
       <c r="H49" s="31"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAE9705-F8D9-493B-A02C-5DCB3A65B575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82040947-ACDA-4725-BA7C-11BF0E3143A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="555" windowWidth="21315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1216,11 +1216,11 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>구매 하기 페이지 UI</t>
+    <t>오승환</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>오승환</t>
+    <t>마이페이지 배송지 UI</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -6749,7 +6749,7 @@
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A46" s="103"/>
       <c r="B46" s="93" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" s="20" t="str">
         <f t="shared" ref="C46" ca="1" si="12">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
@@ -6766,7 +6766,7 @@
         <v>45980</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H46" s="60"/>
       <c r="I46" s="61"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A14E15-0BA5-4F7E-955F-A0C7C9FF1242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3D8518-8EFD-492C-8141-F01F6849223F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="157">
   <si>
     <t>팀명</t>
   </si>
@@ -1292,6 +1292,10 @@
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <t>이미지 업로드 기능</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1300,7 +1304,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1575,6 +1579,27 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF00B0F0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
@@ -2239,7 +2264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2547,12 +2572,6 @@
     <xf numFmtId="0" fontId="28" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2574,9 +2593,6 @@
     <xf numFmtId="0" fontId="22" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2598,6 +2614,9 @@
     <xf numFmtId="0" fontId="28" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2658,8 +2677,26 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="37" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2885,7 +2922,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO90"/>
+  <dimension ref="A1:BO91"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -2900,31 +2937,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128" t="s">
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
+      <c r="Q1" s="125"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -2988,7 +3025,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="129" t="s">
+      <c r="G2" s="127" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3179,7 +3216,7 @@
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="130"/>
+      <c r="G3" s="128"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3362,7 +3399,7 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="129" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="77" t="s">
@@ -3447,7 +3484,7 @@
       <c r="BO4" s="55"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="132"/>
+      <c r="A5" s="130"/>
       <c r="B5" s="77" t="s">
         <v>73</v>
       </c>
@@ -3530,7 +3567,7 @@
       <c r="BO5" s="60"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="132"/>
+      <c r="A6" s="130"/>
       <c r="B6" s="77" t="s">
         <v>74</v>
       </c>
@@ -3613,7 +3650,7 @@
       <c r="BO6" s="60"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="132"/>
+      <c r="A7" s="130"/>
       <c r="B7" s="78" t="s">
         <v>75</v>
       </c>
@@ -3696,7 +3733,7 @@
       <c r="BO7" s="60"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="132"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="79" t="s">
         <v>76</v>
       </c>
@@ -3779,7 +3816,7 @@
       <c r="BO8" s="60"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="132"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="77" t="s">
         <v>77</v>
       </c>
@@ -3862,7 +3899,7 @@
       <c r="BO9" s="60"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="132"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="78" t="s">
         <v>78</v>
       </c>
@@ -3945,7 +3982,7 @@
       <c r="BO10" s="60"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="133"/>
+      <c r="A11" s="131"/>
       <c r="B11" s="80" t="s">
         <v>79</v>
       </c>
@@ -4028,7 +4065,7 @@
       <c r="BO11" s="60"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="118" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="81" t="s">
@@ -4113,7 +4150,7 @@
       <c r="BO12" s="60"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="121"/>
+      <c r="A13" s="119"/>
       <c r="B13" s="82" t="s">
         <v>82</v>
       </c>
@@ -4196,7 +4233,7 @@
       <c r="BO13" s="60"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="121"/>
+      <c r="A14" s="119"/>
       <c r="B14" s="83" t="s">
         <v>83</v>
       </c>
@@ -4279,7 +4316,7 @@
       <c r="BO14" s="60"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="121"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="81" t="s">
         <v>84</v>
       </c>
@@ -4362,7 +4399,7 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="121"/>
+      <c r="A16" s="119"/>
       <c r="B16" s="84" t="s">
         <v>123</v>
       </c>
@@ -4445,78 +4482,78 @@
       <c r="BO16" s="53"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="136" t="s">
+      <c r="A17" s="119"/>
+      <c r="B17" s="134" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
-      <c r="U17" s="124"/>
-      <c r="V17" s="124"/>
-      <c r="W17" s="124"/>
-      <c r="X17" s="124"/>
-      <c r="Y17" s="124"/>
-      <c r="Z17" s="124"/>
-      <c r="AA17" s="124"/>
-      <c r="AB17" s="124"/>
-      <c r="AC17" s="124"/>
-      <c r="AD17" s="124"/>
-      <c r="AE17" s="124"/>
-      <c r="AF17" s="124"/>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124"/>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="124"/>
-      <c r="AM17" s="124"/>
-      <c r="AN17" s="124"/>
-      <c r="AO17" s="124"/>
-      <c r="AP17" s="124"/>
-      <c r="AQ17" s="124"/>
-      <c r="AR17" s="124"/>
-      <c r="AS17" s="124"/>
-      <c r="AT17" s="124"/>
-      <c r="AU17" s="124"/>
-      <c r="AV17" s="124"/>
-      <c r="AW17" s="124"/>
-      <c r="AX17" s="124"/>
-      <c r="AY17" s="124"/>
-      <c r="AZ17" s="124"/>
-      <c r="BA17" s="124"/>
-      <c r="BB17" s="124"/>
-      <c r="BC17" s="124"/>
-      <c r="BD17" s="124"/>
-      <c r="BE17" s="124"/>
-      <c r="BF17" s="124"/>
-      <c r="BG17" s="124"/>
-      <c r="BH17" s="124"/>
-      <c r="BI17" s="124"/>
-      <c r="BJ17" s="124"/>
-      <c r="BK17" s="124"/>
-      <c r="BL17" s="124"/>
-      <c r="BM17" s="124"/>
-      <c r="BN17" s="124"/>
-      <c r="BO17" s="125"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="122"/>
+      <c r="V17" s="122"/>
+      <c r="W17" s="122"/>
+      <c r="X17" s="122"/>
+      <c r="Y17" s="122"/>
+      <c r="Z17" s="122"/>
+      <c r="AA17" s="122"/>
+      <c r="AB17" s="122"/>
+      <c r="AC17" s="122"/>
+      <c r="AD17" s="122"/>
+      <c r="AE17" s="122"/>
+      <c r="AF17" s="122"/>
+      <c r="AG17" s="122"/>
+      <c r="AH17" s="122"/>
+      <c r="AI17" s="122"/>
+      <c r="AJ17" s="122"/>
+      <c r="AK17" s="122"/>
+      <c r="AL17" s="122"/>
+      <c r="AM17" s="122"/>
+      <c r="AN17" s="122"/>
+      <c r="AO17" s="122"/>
+      <c r="AP17" s="122"/>
+      <c r="AQ17" s="122"/>
+      <c r="AR17" s="122"/>
+      <c r="AS17" s="122"/>
+      <c r="AT17" s="122"/>
+      <c r="AU17" s="122"/>
+      <c r="AV17" s="122"/>
+      <c r="AW17" s="122"/>
+      <c r="AX17" s="122"/>
+      <c r="AY17" s="122"/>
+      <c r="AZ17" s="122"/>
+      <c r="BA17" s="122"/>
+      <c r="BB17" s="122"/>
+      <c r="BC17" s="122"/>
+      <c r="BD17" s="122"/>
+      <c r="BE17" s="122"/>
+      <c r="BF17" s="122"/>
+      <c r="BG17" s="122"/>
+      <c r="BH17" s="122"/>
+      <c r="BI17" s="122"/>
+      <c r="BJ17" s="122"/>
+      <c r="BK17" s="122"/>
+      <c r="BL17" s="122"/>
+      <c r="BM17" s="122"/>
+      <c r="BN17" s="122"/>
+      <c r="BO17" s="123"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="121"/>
+      <c r="A18" s="119"/>
       <c r="B18" s="85" t="s">
         <v>124</v>
       </c>
@@ -4599,7 +4636,7 @@
       <c r="BO18" s="55"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="121"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="86" t="s">
         <v>87</v>
       </c>
@@ -4682,7 +4719,7 @@
       <c r="BO19" s="60"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="121"/>
+      <c r="A20" s="119"/>
       <c r="B20" s="87" t="s">
         <v>113</v>
       </c>
@@ -4765,78 +4802,78 @@
       <c r="BO20" s="60"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="121"/>
-      <c r="B21" s="134" t="s">
+      <c r="A21" s="119"/>
+      <c r="B21" s="132" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="123"/>
-      <c r="I21" s="124"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
-      <c r="T21" s="124"/>
-      <c r="U21" s="124"/>
-      <c r="V21" s="124"/>
-      <c r="W21" s="124"/>
-      <c r="X21" s="124"/>
-      <c r="Y21" s="124"/>
-      <c r="Z21" s="124"/>
-      <c r="AA21" s="124"/>
-      <c r="AB21" s="124"/>
-      <c r="AC21" s="124"/>
-      <c r="AD21" s="124"/>
-      <c r="AE21" s="124"/>
-      <c r="AF21" s="124"/>
-      <c r="AG21" s="124"/>
-      <c r="AH21" s="124"/>
-      <c r="AI21" s="124"/>
-      <c r="AJ21" s="124"/>
-      <c r="AK21" s="124"/>
-      <c r="AL21" s="124"/>
-      <c r="AM21" s="124"/>
-      <c r="AN21" s="124"/>
-      <c r="AO21" s="124"/>
-      <c r="AP21" s="124"/>
-      <c r="AQ21" s="124"/>
-      <c r="AR21" s="124"/>
-      <c r="AS21" s="124"/>
-      <c r="AT21" s="124"/>
-      <c r="AU21" s="124"/>
-      <c r="AV21" s="124"/>
-      <c r="AW21" s="124"/>
-      <c r="AX21" s="124"/>
-      <c r="AY21" s="124"/>
-      <c r="AZ21" s="124"/>
-      <c r="BA21" s="124"/>
-      <c r="BB21" s="124"/>
-      <c r="BC21" s="124"/>
-      <c r="BD21" s="124"/>
-      <c r="BE21" s="124"/>
-      <c r="BF21" s="124"/>
-      <c r="BG21" s="124"/>
-      <c r="BH21" s="124"/>
-      <c r="BI21" s="124"/>
-      <c r="BJ21" s="124"/>
-      <c r="BK21" s="124"/>
-      <c r="BL21" s="124"/>
-      <c r="BM21" s="124"/>
-      <c r="BN21" s="124"/>
-      <c r="BO21" s="125"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="122"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="122"/>
+      <c r="N21" s="122"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="122"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="122"/>
+      <c r="S21" s="122"/>
+      <c r="T21" s="122"/>
+      <c r="U21" s="122"/>
+      <c r="V21" s="122"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="122"/>
+      <c r="Y21" s="122"/>
+      <c r="Z21" s="122"/>
+      <c r="AA21" s="122"/>
+      <c r="AB21" s="122"/>
+      <c r="AC21" s="122"/>
+      <c r="AD21" s="122"/>
+      <c r="AE21" s="122"/>
+      <c r="AF21" s="122"/>
+      <c r="AG21" s="122"/>
+      <c r="AH21" s="122"/>
+      <c r="AI21" s="122"/>
+      <c r="AJ21" s="122"/>
+      <c r="AK21" s="122"/>
+      <c r="AL21" s="122"/>
+      <c r="AM21" s="122"/>
+      <c r="AN21" s="122"/>
+      <c r="AO21" s="122"/>
+      <c r="AP21" s="122"/>
+      <c r="AQ21" s="122"/>
+      <c r="AR21" s="122"/>
+      <c r="AS21" s="122"/>
+      <c r="AT21" s="122"/>
+      <c r="AU21" s="122"/>
+      <c r="AV21" s="122"/>
+      <c r="AW21" s="122"/>
+      <c r="AX21" s="122"/>
+      <c r="AY21" s="122"/>
+      <c r="AZ21" s="122"/>
+      <c r="BA21" s="122"/>
+      <c r="BB21" s="122"/>
+      <c r="BC21" s="122"/>
+      <c r="BD21" s="122"/>
+      <c r="BE21" s="122"/>
+      <c r="BF21" s="122"/>
+      <c r="BG21" s="122"/>
+      <c r="BH21" s="122"/>
+      <c r="BI21" s="122"/>
+      <c r="BJ21" s="122"/>
+      <c r="BK21" s="122"/>
+      <c r="BL21" s="122"/>
+      <c r="BM21" s="122"/>
+      <c r="BN21" s="122"/>
+      <c r="BO21" s="123"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="121"/>
+      <c r="A22" s="119"/>
       <c r="B22" s="88" t="s">
         <v>125</v>
       </c>
@@ -4919,7 +4956,7 @@
       <c r="BO22" s="60"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="121"/>
+      <c r="A23" s="119"/>
       <c r="B23" s="89" t="s">
         <v>85</v>
       </c>
@@ -5002,7 +5039,7 @@
       <c r="BO23" s="60"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="121"/>
+      <c r="A24" s="119"/>
       <c r="B24" s="90" t="s">
         <v>151</v>
       </c>
@@ -5085,7 +5122,7 @@
       <c r="BO24" s="60"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="121"/>
+      <c r="A25" s="119"/>
       <c r="B25" s="90" t="s">
         <v>147</v>
       </c>
@@ -5168,7 +5205,7 @@
       <c r="BO25" s="60"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="121"/>
+      <c r="A26" s="119"/>
       <c r="B26" s="91" t="s">
         <v>139</v>
       </c>
@@ -5249,7 +5286,7 @@
       <c r="BO26" s="60"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="121"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="92" t="s">
         <v>140</v>
       </c>
@@ -5330,7 +5367,7 @@
       <c r="BO27" s="60"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="121"/>
+      <c r="A28" s="119"/>
       <c r="B28" s="92" t="s">
         <v>152</v>
       </c>
@@ -5411,7 +5448,7 @@
       <c r="BO28" s="60"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="121"/>
+      <c r="A29" s="119"/>
       <c r="B29" s="93" t="s">
         <v>104</v>
       </c>
@@ -5494,7 +5531,7 @@
       <c r="BO29" s="28"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="121"/>
+      <c r="A30" s="119"/>
       <c r="B30" s="87" t="s">
         <v>111</v>
       </c>
@@ -5577,7 +5614,7 @@
       <c r="BO30" s="60"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="121"/>
+      <c r="A31" s="119"/>
       <c r="B31" s="88" t="s">
         <v>126</v>
       </c>
@@ -5660,7 +5697,7 @@
       <c r="BO31" s="60"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="121"/>
+      <c r="A32" s="119"/>
       <c r="B32" s="87" t="s">
         <v>112</v>
       </c>
@@ -5743,7 +5780,7 @@
       <c r="BO32" s="60"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="121"/>
+      <c r="A33" s="119"/>
       <c r="B33" s="100" t="s">
         <v>143</v>
       </c>
@@ -5826,7 +5863,7 @@
       <c r="BO33" s="60"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="121"/>
+      <c r="A34" s="119"/>
       <c r="B34" s="100" t="s">
         <v>146</v>
       </c>
@@ -5909,8 +5946,8 @@
       <c r="BO34" s="60"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="121"/>
-      <c r="B35" s="140" t="s">
+      <c r="A35" s="119"/>
+      <c r="B35" s="117" t="s">
         <v>121</v>
       </c>
       <c r="C35" s="39" t="str">
@@ -5992,7 +6029,7 @@
       <c r="BO35" s="60"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="121"/>
+      <c r="A36" s="119"/>
       <c r="B36" s="72" t="s">
         <v>122</v>
       </c>
@@ -6075,7 +6112,7 @@
       <c r="BO36" s="60"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="121"/>
+      <c r="A37" s="119"/>
       <c r="B37" s="72" t="s">
         <v>133</v>
       </c>
@@ -6158,7 +6195,7 @@
       <c r="BO37" s="60"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="121"/>
+      <c r="A38" s="119"/>
       <c r="B38" s="88" t="s">
         <v>142</v>
       </c>
@@ -6241,78 +6278,78 @@
       <c r="BO38" s="60"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="121"/>
-      <c r="B39" s="135" t="s">
+      <c r="A39" s="119"/>
+      <c r="B39" s="133" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="135"/>
-      <c r="D39" s="135"/>
-      <c r="E39" s="135"/>
-      <c r="F39" s="135"/>
-      <c r="G39" s="135"/>
-      <c r="H39" s="123"/>
-      <c r="I39" s="124"/>
-      <c r="J39" s="124"/>
-      <c r="K39" s="124"/>
-      <c r="L39" s="124"/>
-      <c r="M39" s="124"/>
-      <c r="N39" s="124"/>
-      <c r="O39" s="124"/>
-      <c r="P39" s="124"/>
-      <c r="Q39" s="124"/>
-      <c r="R39" s="124"/>
-      <c r="S39" s="124"/>
-      <c r="T39" s="124"/>
-      <c r="U39" s="124"/>
-      <c r="V39" s="124"/>
-      <c r="W39" s="124"/>
-      <c r="X39" s="124"/>
-      <c r="Y39" s="124"/>
-      <c r="Z39" s="124"/>
-      <c r="AA39" s="124"/>
-      <c r="AB39" s="124"/>
-      <c r="AC39" s="124"/>
-      <c r="AD39" s="124"/>
-      <c r="AE39" s="124"/>
-      <c r="AF39" s="124"/>
-      <c r="AG39" s="124"/>
-      <c r="AH39" s="124"/>
-      <c r="AI39" s="124"/>
-      <c r="AJ39" s="124"/>
-      <c r="AK39" s="124"/>
-      <c r="AL39" s="124"/>
-      <c r="AM39" s="124"/>
-      <c r="AN39" s="124"/>
-      <c r="AO39" s="124"/>
-      <c r="AP39" s="124"/>
-      <c r="AQ39" s="124"/>
-      <c r="AR39" s="124"/>
-      <c r="AS39" s="124"/>
-      <c r="AT39" s="124"/>
-      <c r="AU39" s="124"/>
-      <c r="AV39" s="124"/>
-      <c r="AW39" s="124"/>
-      <c r="AX39" s="124"/>
-      <c r="AY39" s="124"/>
-      <c r="AZ39" s="124"/>
-      <c r="BA39" s="124"/>
-      <c r="BB39" s="124"/>
-      <c r="BC39" s="124"/>
-      <c r="BD39" s="124"/>
-      <c r="BE39" s="124"/>
-      <c r="BF39" s="124"/>
-      <c r="BG39" s="124"/>
-      <c r="BH39" s="124"/>
-      <c r="BI39" s="124"/>
-      <c r="BJ39" s="124"/>
-      <c r="BK39" s="124"/>
-      <c r="BL39" s="124"/>
-      <c r="BM39" s="124"/>
-      <c r="BN39" s="124"/>
-      <c r="BO39" s="125"/>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="121"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="122"/>
+      <c r="N39" s="122"/>
+      <c r="O39" s="122"/>
+      <c r="P39" s="122"/>
+      <c r="Q39" s="122"/>
+      <c r="R39" s="122"/>
+      <c r="S39" s="122"/>
+      <c r="T39" s="122"/>
+      <c r="U39" s="122"/>
+      <c r="V39" s="122"/>
+      <c r="W39" s="122"/>
+      <c r="X39" s="122"/>
+      <c r="Y39" s="122"/>
+      <c r="Z39" s="122"/>
+      <c r="AA39" s="122"/>
+      <c r="AB39" s="122"/>
+      <c r="AC39" s="122"/>
+      <c r="AD39" s="122"/>
+      <c r="AE39" s="122"/>
+      <c r="AF39" s="122"/>
+      <c r="AG39" s="122"/>
+      <c r="AH39" s="122"/>
+      <c r="AI39" s="122"/>
+      <c r="AJ39" s="122"/>
+      <c r="AK39" s="122"/>
+      <c r="AL39" s="122"/>
+      <c r="AM39" s="122"/>
+      <c r="AN39" s="122"/>
+      <c r="AO39" s="122"/>
+      <c r="AP39" s="122"/>
+      <c r="AQ39" s="122"/>
+      <c r="AR39" s="122"/>
+      <c r="AS39" s="122"/>
+      <c r="AT39" s="122"/>
+      <c r="AU39" s="122"/>
+      <c r="AV39" s="122"/>
+      <c r="AW39" s="122"/>
+      <c r="AX39" s="122"/>
+      <c r="AY39" s="122"/>
+      <c r="AZ39" s="122"/>
+      <c r="BA39" s="122"/>
+      <c r="BB39" s="122"/>
+      <c r="BC39" s="122"/>
+      <c r="BD39" s="122"/>
+      <c r="BE39" s="122"/>
+      <c r="BF39" s="122"/>
+      <c r="BG39" s="122"/>
+      <c r="BH39" s="122"/>
+      <c r="BI39" s="122"/>
+      <c r="BJ39" s="122"/>
+      <c r="BK39" s="122"/>
+      <c r="BL39" s="122"/>
+      <c r="BM39" s="122"/>
+      <c r="BN39" s="122"/>
+      <c r="BO39" s="123"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="121"/>
+      <c r="A40" s="119"/>
       <c r="B40" s="87" t="s">
         <v>110</v>
       </c>
@@ -6395,7 +6432,7 @@
       <c r="BO40" s="60"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="121"/>
+      <c r="A41" s="119"/>
       <c r="B41" s="88" t="s">
         <v>127</v>
       </c>
@@ -6478,7 +6515,7 @@
       <c r="BO41" s="60"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="121"/>
+      <c r="A42" s="119"/>
       <c r="B42" s="88" t="s">
         <v>134</v>
       </c>
@@ -6561,7 +6598,7 @@
       <c r="BO42" s="60"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="121"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="93" t="s">
         <v>136</v>
       </c>
@@ -6644,7 +6681,7 @@
       <c r="BO43" s="60"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="121"/>
+      <c r="A44" s="119"/>
       <c r="B44" s="91" t="s">
         <v>144</v>
       </c>
@@ -6727,7 +6764,7 @@
       <c r="BO44" s="60"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="121"/>
+      <c r="A45" s="119"/>
       <c r="B45" s="91" t="s">
         <v>138</v>
       </c>
@@ -6810,7 +6847,7 @@
       <c r="BO45" s="60"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="121"/>
+      <c r="A46" s="119"/>
       <c r="B46" s="92" t="s">
         <v>154</v>
       </c>
@@ -6893,7 +6930,7 @@
       <c r="BO46" s="60"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="121"/>
+      <c r="A47" s="119"/>
       <c r="B47" s="91" t="s">
         <v>148</v>
       </c>
@@ -6967,7 +7004,7 @@
       <c r="BO47" s="60"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="121"/>
+      <c r="A48" s="119"/>
       <c r="B48" s="92" t="s">
         <v>141</v>
       </c>
@@ -7044,7 +7081,7 @@
       <c r="BO48" s="60"/>
     </row>
     <row r="49" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="121"/>
+      <c r="A49" s="119"/>
       <c r="B49" s="92" t="s">
         <v>149</v>
       </c>
@@ -7121,7 +7158,7 @@
       <c r="BO49" s="60"/>
     </row>
     <row r="50" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A50" s="121"/>
+      <c r="A50" s="119"/>
       <c r="B50" s="92" t="s">
         <v>150</v>
       </c>
@@ -7198,87 +7235,87 @@
       <c r="BO50" s="29"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A51" s="121"/>
-      <c r="B51" s="135" t="s">
+      <c r="A51" s="119"/>
+      <c r="B51" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="135"/>
-      <c r="D51" s="135"/>
-      <c r="E51" s="135"/>
-      <c r="F51" s="135"/>
-      <c r="G51" s="135"/>
-      <c r="H51" s="123"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="124"/>
-      <c r="L51" s="124"/>
-      <c r="M51" s="124"/>
-      <c r="N51" s="124"/>
-      <c r="O51" s="124"/>
-      <c r="P51" s="124"/>
-      <c r="Q51" s="124"/>
-      <c r="R51" s="124"/>
-      <c r="S51" s="124"/>
-      <c r="T51" s="124"/>
-      <c r="U51" s="124"/>
-      <c r="V51" s="124"/>
-      <c r="W51" s="124"/>
-      <c r="X51" s="124"/>
-      <c r="Y51" s="124"/>
-      <c r="Z51" s="124"/>
-      <c r="AA51" s="124"/>
-      <c r="AB51" s="124"/>
-      <c r="AC51" s="124"/>
-      <c r="AD51" s="124"/>
-      <c r="AE51" s="124"/>
-      <c r="AF51" s="124"/>
-      <c r="AG51" s="124"/>
-      <c r="AH51" s="124"/>
-      <c r="AI51" s="124"/>
-      <c r="AJ51" s="124"/>
-      <c r="AK51" s="124"/>
-      <c r="AL51" s="124"/>
-      <c r="AM51" s="124"/>
-      <c r="AN51" s="124"/>
-      <c r="AO51" s="124"/>
-      <c r="AP51" s="124"/>
-      <c r="AQ51" s="124"/>
-      <c r="AR51" s="124"/>
-      <c r="AS51" s="124"/>
-      <c r="AT51" s="124"/>
-      <c r="AU51" s="124"/>
-      <c r="AV51" s="124"/>
-      <c r="AW51" s="124"/>
-      <c r="AX51" s="124"/>
-      <c r="AY51" s="124"/>
-      <c r="AZ51" s="124"/>
-      <c r="BA51" s="124"/>
-      <c r="BB51" s="124"/>
-      <c r="BC51" s="124"/>
-      <c r="BD51" s="124"/>
-      <c r="BE51" s="124"/>
-      <c r="BF51" s="124"/>
-      <c r="BG51" s="124"/>
-      <c r="BH51" s="124"/>
-      <c r="BI51" s="124"/>
-      <c r="BJ51" s="124"/>
-      <c r="BK51" s="124"/>
-      <c r="BL51" s="124"/>
-      <c r="BM51" s="124"/>
-      <c r="BN51" s="124"/>
-      <c r="BO51" s="125"/>
+      <c r="C51" s="133"/>
+      <c r="D51" s="133"/>
+      <c r="E51" s="133"/>
+      <c r="F51" s="133"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="121"/>
+      <c r="I51" s="122"/>
+      <c r="J51" s="122"/>
+      <c r="K51" s="122"/>
+      <c r="L51" s="122"/>
+      <c r="M51" s="122"/>
+      <c r="N51" s="122"/>
+      <c r="O51" s="122"/>
+      <c r="P51" s="122"/>
+      <c r="Q51" s="122"/>
+      <c r="R51" s="122"/>
+      <c r="S51" s="122"/>
+      <c r="T51" s="122"/>
+      <c r="U51" s="122"/>
+      <c r="V51" s="122"/>
+      <c r="W51" s="122"/>
+      <c r="X51" s="122"/>
+      <c r="Y51" s="122"/>
+      <c r="Z51" s="122"/>
+      <c r="AA51" s="122"/>
+      <c r="AB51" s="122"/>
+      <c r="AC51" s="122"/>
+      <c r="AD51" s="122"/>
+      <c r="AE51" s="122"/>
+      <c r="AF51" s="122"/>
+      <c r="AG51" s="122"/>
+      <c r="AH51" s="122"/>
+      <c r="AI51" s="122"/>
+      <c r="AJ51" s="122"/>
+      <c r="AK51" s="122"/>
+      <c r="AL51" s="122"/>
+      <c r="AM51" s="122"/>
+      <c r="AN51" s="122"/>
+      <c r="AO51" s="122"/>
+      <c r="AP51" s="122"/>
+      <c r="AQ51" s="122"/>
+      <c r="AR51" s="122"/>
+      <c r="AS51" s="122"/>
+      <c r="AT51" s="122"/>
+      <c r="AU51" s="122"/>
+      <c r="AV51" s="122"/>
+      <c r="AW51" s="122"/>
+      <c r="AX51" s="122"/>
+      <c r="AY51" s="122"/>
+      <c r="AZ51" s="122"/>
+      <c r="BA51" s="122"/>
+      <c r="BB51" s="122"/>
+      <c r="BC51" s="122"/>
+      <c r="BD51" s="122"/>
+      <c r="BE51" s="122"/>
+      <c r="BF51" s="122"/>
+      <c r="BG51" s="122"/>
+      <c r="BH51" s="122"/>
+      <c r="BI51" s="122"/>
+      <c r="BJ51" s="122"/>
+      <c r="BK51" s="122"/>
+      <c r="BL51" s="122"/>
+      <c r="BM51" s="122"/>
+      <c r="BN51" s="122"/>
+      <c r="BO51" s="123"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A52" s="121"/>
+      <c r="A52" s="119"/>
       <c r="B52" s="101" t="s">
         <v>128</v>
       </c>
       <c r="C52" s="44" t="str">
-        <f t="shared" ref="C52:C69" ca="1" si="16">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C52:C70" ca="1" si="16">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="106" t="str">
-        <f t="shared" ref="D52:D69" si="17">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
+      <c r="D52" s="104" t="str">
+        <f t="shared" ref="D52:D70" si="17">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
         <v>7일</v>
       </c>
       <c r="E52" s="45">
@@ -7352,28 +7389,28 @@
       <c r="BO52" s="60"/>
     </row>
     <row r="53" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A53" s="138"/>
-      <c r="B53" s="113" t="s">
+      <c r="A53" s="136"/>
+      <c r="B53" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="115" t="str">
+      <c r="C53" s="112" t="str">
         <f t="shared" ref="C53" ca="1" si="18">IF(F53=E53, IF(TODAY()&gt;F53, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F53) - E53) / (F53 - E53) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D53" s="116" t="str">
+      <c r="D53" s="113" t="str">
         <f t="shared" ref="D53:D54" si="19">IF(AND(F53&lt;&gt;"", E53&lt;&gt;""), F53 - E53 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
-      <c r="E53" s="117">
+      <c r="E53" s="114">
         <v>45971</v>
       </c>
-      <c r="F53" s="117">
+      <c r="F53" s="114">
         <v>45979</v>
       </c>
-      <c r="G53" s="119" t="s">
+      <c r="G53" s="116" t="s">
         <v>103</v>
       </c>
-      <c r="H53" s="105"/>
+      <c r="H53" s="103"/>
       <c r="I53" s="60"/>
       <c r="J53" s="60"/>
       <c r="K53" s="60"/>
@@ -7435,28 +7472,28 @@
       <c r="BO53" s="60"/>
     </row>
     <row r="54" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="138"/>
-      <c r="B54" s="114" t="s">
+      <c r="A54" s="136"/>
+      <c r="B54" s="111" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="115" t="str">
+      <c r="C54" s="112" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>100%</v>
       </c>
-      <c r="D54" s="116" t="str">
+      <c r="D54" s="113" t="str">
         <f t="shared" si="19"/>
         <v>2일</v>
       </c>
-      <c r="E54" s="117">
+      <c r="E54" s="114">
         <v>45979</v>
       </c>
-      <c r="F54" s="117">
+      <c r="F54" s="114">
         <v>45980</v>
       </c>
-      <c r="G54" s="118" t="s">
+      <c r="G54" s="115" t="s">
         <v>117</v>
       </c>
-      <c r="H54" s="105"/>
+      <c r="H54" s="103"/>
       <c r="I54" s="60"/>
       <c r="J54" s="60"/>
       <c r="K54" s="60"/>
@@ -7518,25 +7555,25 @@
       <c r="BO54" s="60"/>
     </row>
     <row r="55" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A55" s="121"/>
-      <c r="B55" s="107" t="s">
+      <c r="A55" s="119"/>
+      <c r="B55" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="108" t="str">
+      <c r="C55" s="106" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>0%</v>
       </c>
-      <c r="D55" s="109" t="str">
+      <c r="D55" s="107" t="str">
         <f t="shared" si="17"/>
         <v>19일</v>
       </c>
-      <c r="E55" s="110">
+      <c r="E55" s="108">
         <v>45980</v>
       </c>
-      <c r="F55" s="110">
+      <c r="F55" s="108">
         <v>45998</v>
       </c>
-      <c r="G55" s="111" t="s">
+      <c r="G55" s="109" t="s">
         <v>135</v>
       </c>
       <c r="H55" s="59"/>
@@ -7601,25 +7638,25 @@
       <c r="BO55" s="60"/>
     </row>
     <row r="56" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="121"/>
-      <c r="B56" s="103" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="112" t="str">
-        <f t="shared" ca="1" si="16"/>
+      <c r="A56" s="119"/>
+      <c r="B56" s="142" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="143" t="str">
+        <f t="shared" ref="C56" ca="1" si="20">IF(F56=E56, IF(TODAY()&gt;F56, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F56) - E56) / (F56 - E56) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
-      <c r="D56" s="104" t="str">
-        <f t="shared" si="17"/>
-        <v>3일</v>
-      </c>
-      <c r="E56" s="22">
+      <c r="D56" s="144" t="str">
+        <f t="shared" ref="D56" si="21">IF(AND(F56&lt;&gt;"", E56&lt;&gt;""), F56 - E56 + 1 &amp; "일", "")</f>
+        <v>2일</v>
+      </c>
+      <c r="E56" s="75">
         <v>45980</v>
       </c>
-      <c r="F56" s="22">
-        <v>45982</v>
-      </c>
-      <c r="G56" s="69" t="s">
+      <c r="F56" s="75">
+        <v>45981</v>
+      </c>
+      <c r="G56" s="141" t="s">
         <v>117</v>
       </c>
       <c r="H56" s="59"/>
@@ -7684,21 +7721,27 @@
       <c r="BO56" s="60"/>
     </row>
     <row r="57" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A57" s="121"/>
-      <c r="B57" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C57" s="32" t="str">
+      <c r="A57" s="119"/>
+      <c r="B57" s="138" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="139" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>100%</v>
-      </c>
-      <c r="D57" s="21" t="str">
+        <v>0%</v>
+      </c>
+      <c r="D57" s="140" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="69"/>
+        <v>2일</v>
+      </c>
+      <c r="E57" s="75">
+        <v>45980</v>
+      </c>
+      <c r="F57" s="75">
+        <v>45981</v>
+      </c>
+      <c r="G57" s="141" t="s">
+        <v>117</v>
+      </c>
       <c r="H57" s="59"/>
       <c r="I57" s="60"/>
       <c r="J57" s="60"/>
@@ -7760,12 +7803,12 @@
       <c r="BN57" s="60"/>
       <c r="BO57" s="60"/>
     </row>
-    <row r="58" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A58" s="121"/>
+    <row r="58" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A58" s="119"/>
       <c r="B58" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="20" t="str">
+        <v>130</v>
+      </c>
+      <c r="C58" s="32" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>100%</v>
       </c>
@@ -7838,9 +7881,9 @@
       <c r="BO58" s="60"/>
     </row>
     <row r="59" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A59" s="121"/>
+      <c r="A59" s="119"/>
       <c r="B59" s="94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59" s="20" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -7915,27 +7958,21 @@
       <c r="BO59" s="60"/>
     </row>
     <row r="60" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A60" s="121"/>
-      <c r="B60" s="95" t="s">
-        <v>155</v>
+      <c r="A60" s="119"/>
+      <c r="B60" s="94" t="s">
+        <v>132</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f t="shared" ref="C60" ca="1" si="20">IF(F60=E60, IF(TODAY()&gt;F60, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F60) - E60) / (F60 - E60) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>100%</v>
       </c>
       <c r="D60" s="21" t="str">
-        <f>IF(AND(F60&lt;&gt;"", E60&lt;&gt;""), F60 - E60 + 1 &amp; "일", "")</f>
-        <v>10일</v>
-      </c>
-      <c r="E60" s="22">
-        <v>45989</v>
-      </c>
-      <c r="F60" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G60" s="68" t="s">
-        <v>117</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="69"/>
       <c r="H60" s="59"/>
       <c r="I60" s="60"/>
       <c r="J60" s="60"/>
@@ -7998,22 +8035,26 @@
       <c r="BO60" s="60"/>
     </row>
     <row r="61" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A61" s="139"/>
+      <c r="A61" s="119"/>
       <c r="B61" s="95" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>100%</v>
+        <f t="shared" ref="C61" ca="1" si="22">IF(F61=E61, IF(TODAY()&gt;F61, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F61) - E61) / (F61 - E61) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D61" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
+        <f>IF(AND(F61&lt;&gt;"", E61&lt;&gt;""), F61 - E61 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E61" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F61" s="22">
+        <v>45998</v>
+      </c>
       <c r="G61" s="68" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60"/>
@@ -8074,14 +8115,12 @@
       <c r="BL61" s="60"/>
       <c r="BM61" s="60"/>
       <c r="BN61" s="60"/>
-      <c r="BO61" s="29"/>
+      <c r="BO61" s="60"/>
     </row>
-    <row r="62" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A62" s="120" t="s">
-        <v>90</v>
-      </c>
-      <c r="B62" s="96" t="s">
-        <v>2</v>
+    <row r="62" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A62" s="137"/>
+      <c r="B62" s="95" t="s">
+        <v>137</v>
       </c>
       <c r="C62" s="20" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -8093,8 +8132,8 @@
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
-      <c r="G62" s="70" t="s">
-        <v>100</v>
+      <c r="G62" s="68" t="s">
+        <v>135</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60"/>
@@ -8155,15 +8194,17 @@
       <c r="BL62" s="60"/>
       <c r="BM62" s="60"/>
       <c r="BN62" s="60"/>
-      <c r="BO62" s="60"/>
+      <c r="BO62" s="29"/>
     </row>
-    <row r="63" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A63" s="121"/>
-      <c r="B63" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="31" t="str">
-        <f t="shared" ref="C63" ca="1" si="21">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
+    <row r="63" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A63" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="20" t="str">
+        <f t="shared" ca="1" si="16"/>
         <v>100%</v>
       </c>
       <c r="D63" s="21" t="str">
@@ -8237,11 +8278,14 @@
       <c r="BO63" s="60"/>
     </row>
     <row r="64" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A64" s="121"/>
+      <c r="A64" s="119"/>
       <c r="B64" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="67"/>
+        <v>88</v>
+      </c>
+      <c r="C64" s="31" t="str">
+        <f t="shared" ref="C64" ca="1" si="23">IF(F64=E64, IF(TODAY()&gt;F64, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F64) - E64) / (F64 - E64) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
+      </c>
       <c r="D64" s="21" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8313,26 +8357,19 @@
       <c r="BO64" s="60"/>
     </row>
     <row r="65" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A65" s="121"/>
-      <c r="B65" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" s="35" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>0%</v>
-      </c>
-      <c r="D65" s="71" t="str">
+      <c r="A65" s="119"/>
+      <c r="B65" s="97" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>12일</v>
-      </c>
-      <c r="E65" s="36">
-        <v>45999</v>
-      </c>
-      <c r="F65" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>98</v>
+        <v/>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60"/>
@@ -8395,26 +8432,26 @@
       <c r="BN65" s="60"/>
       <c r="BO65" s="60"/>
     </row>
-    <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="121"/>
-      <c r="B66" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="32" t="str">
+    <row r="66" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A66" s="119"/>
+      <c r="B66" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="35" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>0%</v>
       </c>
-      <c r="D66" s="21" t="str">
+      <c r="D66" s="71" t="str">
         <f t="shared" si="17"/>
-        <v>10일</v>
-      </c>
-      <c r="E66" s="33">
+        <v>12일</v>
+      </c>
+      <c r="E66" s="36">
         <v>45999</v>
       </c>
-      <c r="F66" s="33">
-        <v>46008</v>
-      </c>
-      <c r="G66" s="34" t="s">
+      <c r="F66" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G66" s="37" t="s">
         <v>98</v>
       </c>
       <c r="H66" s="59"/>
@@ -8478,12 +8515,12 @@
       <c r="BN66" s="60"/>
       <c r="BO66" s="60"/>
     </row>
-    <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A67" s="121"/>
-      <c r="B67" s="95" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="20" t="str">
+    <row r="67" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A67" s="119"/>
+      <c r="B67" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" s="32" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>0%</v>
       </c>
@@ -8491,13 +8528,13 @@
         <f t="shared" si="17"/>
         <v>10일</v>
       </c>
-      <c r="E67" s="22">
+      <c r="E67" s="33">
         <v>45999</v>
       </c>
-      <c r="F67" s="22">
+      <c r="F67" s="33">
         <v>46008</v>
       </c>
-      <c r="G67" s="23" t="s">
+      <c r="G67" s="34" t="s">
         <v>98</v>
       </c>
       <c r="H67" s="59"/>
@@ -8561,10 +8598,10 @@
       <c r="BN67" s="60"/>
       <c r="BO67" s="60"/>
     </row>
-    <row r="68" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A68" s="121"/>
+    <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A68" s="119"/>
       <c r="B68" s="95" t="s">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="C68" s="20" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -8572,13 +8609,13 @@
       </c>
       <c r="D68" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>1일</v>
+        <v>10일</v>
       </c>
       <c r="E68" s="22">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="F68" s="22">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="G68" s="23" t="s">
         <v>98</v>
@@ -8645,9 +8682,9 @@
       <c r="BO68" s="60"/>
     </row>
     <row r="69" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A69" s="122"/>
+      <c r="A69" s="119"/>
       <c r="B69" s="95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C69" s="20" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -8727,12 +8764,92 @@
       <c r="BN69" s="60"/>
       <c r="BO69" s="60"/>
     </row>
-    <row r="70" spans="1:67">
-      <c r="E70" s="7"/>
-      <c r="F70" s="1"/>
-      <c r="I70" s="3"/>
+    <row r="70" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A70" s="120"/>
+      <c r="B70" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" s="20" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v>0%</v>
+      </c>
+      <c r="D70" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v>1일</v>
+      </c>
+      <c r="E70" s="22">
+        <v>46010</v>
+      </c>
+      <c r="F70" s="22">
+        <v>46010</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H70" s="59"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+      <c r="L70" s="61"/>
+      <c r="M70" s="62"/>
+      <c r="N70" s="60"/>
+      <c r="O70" s="60"/>
+      <c r="P70" s="60"/>
+      <c r="Q70" s="60"/>
+      <c r="R70" s="60"/>
+      <c r="S70" s="61"/>
+      <c r="T70" s="62"/>
+      <c r="U70" s="60"/>
+      <c r="V70" s="60"/>
+      <c r="W70" s="60"/>
+      <c r="X70" s="60"/>
+      <c r="Y70" s="60"/>
+      <c r="Z70" s="61"/>
+      <c r="AA70" s="62"/>
+      <c r="AB70" s="60"/>
+      <c r="AC70" s="60"/>
+      <c r="AD70" s="60"/>
+      <c r="AE70" s="60"/>
+      <c r="AF70" s="60"/>
+      <c r="AG70" s="61"/>
+      <c r="AH70" s="62"/>
+      <c r="AI70" s="60"/>
+      <c r="AJ70" s="60"/>
+      <c r="AK70" s="60"/>
+      <c r="AL70" s="60"/>
+      <c r="AM70" s="60"/>
+      <c r="AN70" s="61"/>
+      <c r="AO70" s="62"/>
+      <c r="AP70" s="60"/>
+      <c r="AQ70" s="60"/>
+      <c r="AR70" s="60"/>
+      <c r="AS70" s="60"/>
+      <c r="AT70" s="60"/>
+      <c r="AU70" s="61"/>
+      <c r="AV70" s="62"/>
+      <c r="AW70" s="60"/>
+      <c r="AX70" s="60"/>
+      <c r="AY70" s="60"/>
+      <c r="AZ70" s="60"/>
+      <c r="BA70" s="60"/>
+      <c r="BB70" s="61"/>
+      <c r="BC70" s="62"/>
+      <c r="BD70" s="60"/>
+      <c r="BE70" s="60"/>
+      <c r="BF70" s="60"/>
+      <c r="BG70" s="60"/>
+      <c r="BH70" s="60"/>
+      <c r="BI70" s="61"/>
+      <c r="BJ70" s="62"/>
+      <c r="BK70" s="60"/>
+      <c r="BL70" s="60"/>
+      <c r="BM70" s="60"/>
+      <c r="BN70" s="60"/>
+      <c r="BO70" s="60"/>
     </row>
     <row r="71" spans="1:67">
+      <c r="E71" s="7"/>
+      <c r="F71" s="1"/>
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:67">
@@ -8745,45 +8862,44 @@
       <c r="I74" s="3"/>
     </row>
     <row r="75" spans="1:67">
-      <c r="B75" s="8" t="s">
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" spans="1:67">
+      <c r="B76" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:67" ht="16.5">
-      <c r="B76" s="9" t="s">
+    <row r="77" spans="1:67" ht="16.5">
+      <c r="B77" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="1:67">
-      <c r="B77" s="10" t="s">
-        <v>96</v>
-      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:67">
-      <c r="C78" s="3"/>
+      <c r="B78" s="10" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="79" spans="1:67">
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="1:67"/>
+    <row r="80" spans="1:67">
+      <c r="C80" s="3"/>
+    </row>
     <row r="81" spans="2:8"/>
-    <row r="82" spans="2:8" ht="16.5">
-      <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-    </row>
-    <row r="83" spans="2:8">
+    <row r="82" spans="2:8"/>
+    <row r="83" spans="2:8" ht="16.5">
+      <c r="B83" s="2"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="2:8" ht="16.5">
-      <c r="B84" s="2"/>
+    <row r="84" spans="2:8">
+      <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="2:8">
-      <c r="C85" s="3"/>
+    <row r="85" spans="2:8" ht="16.5">
+      <c r="B85" s="2"/>
       <c r="D85" s="3"/>
     </row>
     <row r="86" spans="2:8">
@@ -8791,22 +8907,26 @@
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="2:8">
+      <c r="C87" s="3"/>
       <c r="D87" s="3"/>
     </row>
     <row r="88" spans="2:8">
       <c r="D88" s="3"/>
-      <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8">
       <c r="D89" s="3"/>
+      <c r="H89" s="11"/>
     </row>
     <row r="90" spans="2:8" ht="15" customHeight="1">
-      <c r="C90" s="3"/>
       <c r="D90" s="3"/>
+    </row>
+    <row r="91" spans="2:8" ht="15" customHeight="1">
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A62:A69"/>
+    <mergeCell ref="A63:A70"/>
     <mergeCell ref="H51:BO51"/>
     <mergeCell ref="H39:BO39"/>
     <mergeCell ref="C1:E1"/>
@@ -8817,7 +8937,7 @@
     <mergeCell ref="B39:G39"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A61"/>
+    <mergeCell ref="A12:A62"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
   </mergeCells>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3D8518-8EFD-492C-8141-F01F6849223F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D88C988-5A55-4DA9-AA79-A643A42263FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="555" windowWidth="21315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="156">
   <si>
     <t>팀명</t>
   </si>
@@ -895,9 +895,6 @@
     <t>리뷰 커뮤니티 시스템 강화(추천, 비추천, 신고, 별점, 댓글)</t>
   </si>
   <si>
-    <t>정렬, 검색 기능(리뷰, 상품 등)</t>
-  </si>
-  <si>
     <t>회원의 피부 타입에 추천되는 상품 추천 알고리즘</t>
   </si>
   <si>
@@ -1017,33 +1014,7 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">마이페이지 찜 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>마이페이지 결제수단 UI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 상세 UI(QnA,리뷰 포함)</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1115,28 +1086,6 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상품 상세페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
@@ -1171,32 +1120,6 @@
   </si>
   <si>
     <t>마이페이지 장바구니 UI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">리뷰 작성 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 페이지와 연결되는 리뷰 UI</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1296,6 +1219,117 @@
     <t>이미지 업로드 기능</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품 상세페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">마이페이지 찜 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시연</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">리뷰 작성 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1304,7 +1338,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1604,6 +1638,20 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="7"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="7"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1721,7 +1769,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -2249,22 +2297,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2581,9 +2618,6 @@
     <xf numFmtId="0" fontId="14" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="21" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2617,6 +2651,36 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="37" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2675,27 +2739,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="37" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2922,7 +2965,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO91"/>
+  <dimension ref="A1:BO89"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -2937,31 +2980,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="124" t="s">
+      <c r="C1" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="126" t="s">
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3025,7 +3068,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="127" t="s">
+      <c r="G2" s="136" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3216,7 +3259,7 @@
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="128"/>
+      <c r="G3" s="137"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3399,7 +3442,7 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="129" t="s">
+      <c r="A4" s="138" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="77" t="s">
@@ -3484,7 +3527,7 @@
       <c r="BO4" s="55"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="130"/>
+      <c r="A5" s="139"/>
       <c r="B5" s="77" t="s">
         <v>73</v>
       </c>
@@ -3567,7 +3610,7 @@
       <c r="BO5" s="60"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="130"/>
+      <c r="A6" s="139"/>
       <c r="B6" s="77" t="s">
         <v>74</v>
       </c>
@@ -3650,7 +3693,7 @@
       <c r="BO6" s="60"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="130"/>
+      <c r="A7" s="139"/>
       <c r="B7" s="78" t="s">
         <v>75</v>
       </c>
@@ -3733,7 +3776,7 @@
       <c r="BO7" s="60"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="130"/>
+      <c r="A8" s="139"/>
       <c r="B8" s="79" t="s">
         <v>76</v>
       </c>
@@ -3816,7 +3859,7 @@
       <c r="BO8" s="60"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="130"/>
+      <c r="A9" s="139"/>
       <c r="B9" s="77" t="s">
         <v>77</v>
       </c>
@@ -3899,7 +3942,7 @@
       <c r="BO9" s="60"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="130"/>
+      <c r="A10" s="139"/>
       <c r="B10" s="78" t="s">
         <v>78</v>
       </c>
@@ -3982,7 +4025,7 @@
       <c r="BO10" s="60"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="131"/>
+      <c r="A11" s="140"/>
       <c r="B11" s="80" t="s">
         <v>79</v>
       </c>
@@ -4065,7 +4108,7 @@
       <c r="BO11" s="60"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="127" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="81" t="s">
@@ -4150,7 +4193,7 @@
       <c r="BO12" s="60"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="119"/>
+      <c r="A13" s="128"/>
       <c r="B13" s="82" t="s">
         <v>82</v>
       </c>
@@ -4233,7 +4276,7 @@
       <c r="BO13" s="60"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="119"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="83" t="s">
         <v>83</v>
       </c>
@@ -4316,13 +4359,13 @@
       <c r="BO14" s="60"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="119"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="81" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="35" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>94.1%</v>
+        <v>100%</v>
       </c>
       <c r="D15" s="21" t="str">
         <f t="shared" si="0"/>
@@ -4399,7 +4442,7 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="119"/>
+      <c r="A16" s="128"/>
       <c r="B16" s="84" t="s">
         <v>123</v>
       </c>
@@ -4482,78 +4525,78 @@
       <c r="BO16" s="53"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="119"/>
-      <c r="B17" s="134" t="s">
+      <c r="A17" s="128"/>
+      <c r="B17" s="143" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="122"/>
-      <c r="K17" s="122"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="122"/>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="122"/>
-      <c r="U17" s="122"/>
-      <c r="V17" s="122"/>
-      <c r="W17" s="122"/>
-      <c r="X17" s="122"/>
-      <c r="Y17" s="122"/>
-      <c r="Z17" s="122"/>
-      <c r="AA17" s="122"/>
-      <c r="AB17" s="122"/>
-      <c r="AC17" s="122"/>
-      <c r="AD17" s="122"/>
-      <c r="AE17" s="122"/>
-      <c r="AF17" s="122"/>
-      <c r="AG17" s="122"/>
-      <c r="AH17" s="122"/>
-      <c r="AI17" s="122"/>
-      <c r="AJ17" s="122"/>
-      <c r="AK17" s="122"/>
-      <c r="AL17" s="122"/>
-      <c r="AM17" s="122"/>
-      <c r="AN17" s="122"/>
-      <c r="AO17" s="122"/>
-      <c r="AP17" s="122"/>
-      <c r="AQ17" s="122"/>
-      <c r="AR17" s="122"/>
-      <c r="AS17" s="122"/>
-      <c r="AT17" s="122"/>
-      <c r="AU17" s="122"/>
-      <c r="AV17" s="122"/>
-      <c r="AW17" s="122"/>
-      <c r="AX17" s="122"/>
-      <c r="AY17" s="122"/>
-      <c r="AZ17" s="122"/>
-      <c r="BA17" s="122"/>
-      <c r="BB17" s="122"/>
-      <c r="BC17" s="122"/>
-      <c r="BD17" s="122"/>
-      <c r="BE17" s="122"/>
-      <c r="BF17" s="122"/>
-      <c r="BG17" s="122"/>
-      <c r="BH17" s="122"/>
-      <c r="BI17" s="122"/>
-      <c r="BJ17" s="122"/>
-      <c r="BK17" s="122"/>
-      <c r="BL17" s="122"/>
-      <c r="BM17" s="122"/>
-      <c r="BN17" s="122"/>
-      <c r="BO17" s="123"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="131"/>
+      <c r="N17" s="131"/>
+      <c r="O17" s="131"/>
+      <c r="P17" s="131"/>
+      <c r="Q17" s="131"/>
+      <c r="R17" s="131"/>
+      <c r="S17" s="131"/>
+      <c r="T17" s="131"/>
+      <c r="U17" s="131"/>
+      <c r="V17" s="131"/>
+      <c r="W17" s="131"/>
+      <c r="X17" s="131"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="131"/>
+      <c r="AA17" s="131"/>
+      <c r="AB17" s="131"/>
+      <c r="AC17" s="131"/>
+      <c r="AD17" s="131"/>
+      <c r="AE17" s="131"/>
+      <c r="AF17" s="131"/>
+      <c r="AG17" s="131"/>
+      <c r="AH17" s="131"/>
+      <c r="AI17" s="131"/>
+      <c r="AJ17" s="131"/>
+      <c r="AK17" s="131"/>
+      <c r="AL17" s="131"/>
+      <c r="AM17" s="131"/>
+      <c r="AN17" s="131"/>
+      <c r="AO17" s="131"/>
+      <c r="AP17" s="131"/>
+      <c r="AQ17" s="131"/>
+      <c r="AR17" s="131"/>
+      <c r="AS17" s="131"/>
+      <c r="AT17" s="131"/>
+      <c r="AU17" s="131"/>
+      <c r="AV17" s="131"/>
+      <c r="AW17" s="131"/>
+      <c r="AX17" s="131"/>
+      <c r="AY17" s="131"/>
+      <c r="AZ17" s="131"/>
+      <c r="BA17" s="131"/>
+      <c r="BB17" s="131"/>
+      <c r="BC17" s="131"/>
+      <c r="BD17" s="131"/>
+      <c r="BE17" s="131"/>
+      <c r="BF17" s="131"/>
+      <c r="BG17" s="131"/>
+      <c r="BH17" s="131"/>
+      <c r="BI17" s="131"/>
+      <c r="BJ17" s="131"/>
+      <c r="BK17" s="131"/>
+      <c r="BL17" s="131"/>
+      <c r="BM17" s="131"/>
+      <c r="BN17" s="131"/>
+      <c r="BO17" s="132"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="119"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="85" t="s">
         <v>124</v>
       </c>
@@ -4636,13 +4679,13 @@
       <c r="BO18" s="55"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="119"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="86" t="s">
         <v>87</v>
       </c>
       <c r="C19" s="73" t="str">
         <f ca="1">IF(F19=E19, IF(TODAY()&gt;F19, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F19) - E19) / (F19 - E19) * 100, 1) &amp; "%")</f>
-        <v>93.8%</v>
+        <v>100%</v>
       </c>
       <c r="D19" s="74" t="str">
         <f>IF(AND(F19&lt;&gt;"", E19&lt;&gt;""), F19 - E19 + 1 &amp; "일", "")</f>
@@ -4719,7 +4762,7 @@
       <c r="BO19" s="60"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="119"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="87" t="s">
         <v>113</v>
       </c>
@@ -4802,87 +4845,87 @@
       <c r="BO20" s="60"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="119"/>
-      <c r="B21" s="132" t="s">
+      <c r="A21" s="128"/>
+      <c r="B21" s="141" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="122"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="122"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="122"/>
-      <c r="Q21" s="122"/>
-      <c r="R21" s="122"/>
-      <c r="S21" s="122"/>
-      <c r="T21" s="122"/>
-      <c r="U21" s="122"/>
-      <c r="V21" s="122"/>
-      <c r="W21" s="122"/>
-      <c r="X21" s="122"/>
-      <c r="Y21" s="122"/>
-      <c r="Z21" s="122"/>
-      <c r="AA21" s="122"/>
-      <c r="AB21" s="122"/>
-      <c r="AC21" s="122"/>
-      <c r="AD21" s="122"/>
-      <c r="AE21" s="122"/>
-      <c r="AF21" s="122"/>
-      <c r="AG21" s="122"/>
-      <c r="AH21" s="122"/>
-      <c r="AI21" s="122"/>
-      <c r="AJ21" s="122"/>
-      <c r="AK21" s="122"/>
-      <c r="AL21" s="122"/>
-      <c r="AM21" s="122"/>
-      <c r="AN21" s="122"/>
-      <c r="AO21" s="122"/>
-      <c r="AP21" s="122"/>
-      <c r="AQ21" s="122"/>
-      <c r="AR21" s="122"/>
-      <c r="AS21" s="122"/>
-      <c r="AT21" s="122"/>
-      <c r="AU21" s="122"/>
-      <c r="AV21" s="122"/>
-      <c r="AW21" s="122"/>
-      <c r="AX21" s="122"/>
-      <c r="AY21" s="122"/>
-      <c r="AZ21" s="122"/>
-      <c r="BA21" s="122"/>
-      <c r="BB21" s="122"/>
-      <c r="BC21" s="122"/>
-      <c r="BD21" s="122"/>
-      <c r="BE21" s="122"/>
-      <c r="BF21" s="122"/>
-      <c r="BG21" s="122"/>
-      <c r="BH21" s="122"/>
-      <c r="BI21" s="122"/>
-      <c r="BJ21" s="122"/>
-      <c r="BK21" s="122"/>
-      <c r="BL21" s="122"/>
-      <c r="BM21" s="122"/>
-      <c r="BN21" s="122"/>
-      <c r="BO21" s="123"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="131"/>
+      <c r="U21" s="131"/>
+      <c r="V21" s="131"/>
+      <c r="W21" s="131"/>
+      <c r="X21" s="131"/>
+      <c r="Y21" s="131"/>
+      <c r="Z21" s="131"/>
+      <c r="AA21" s="131"/>
+      <c r="AB21" s="131"/>
+      <c r="AC21" s="131"/>
+      <c r="AD21" s="131"/>
+      <c r="AE21" s="131"/>
+      <c r="AF21" s="131"/>
+      <c r="AG21" s="131"/>
+      <c r="AH21" s="131"/>
+      <c r="AI21" s="131"/>
+      <c r="AJ21" s="131"/>
+      <c r="AK21" s="131"/>
+      <c r="AL21" s="131"/>
+      <c r="AM21" s="131"/>
+      <c r="AN21" s="131"/>
+      <c r="AO21" s="131"/>
+      <c r="AP21" s="131"/>
+      <c r="AQ21" s="131"/>
+      <c r="AR21" s="131"/>
+      <c r="AS21" s="131"/>
+      <c r="AT21" s="131"/>
+      <c r="AU21" s="131"/>
+      <c r="AV21" s="131"/>
+      <c r="AW21" s="131"/>
+      <c r="AX21" s="131"/>
+      <c r="AY21" s="131"/>
+      <c r="AZ21" s="131"/>
+      <c r="BA21" s="131"/>
+      <c r="BB21" s="131"/>
+      <c r="BC21" s="131"/>
+      <c r="BD21" s="131"/>
+      <c r="BE21" s="131"/>
+      <c r="BF21" s="131"/>
+      <c r="BG21" s="131"/>
+      <c r="BH21" s="131"/>
+      <c r="BI21" s="131"/>
+      <c r="BJ21" s="131"/>
+      <c r="BK21" s="131"/>
+      <c r="BL21" s="131"/>
+      <c r="BM21" s="131"/>
+      <c r="BN21" s="131"/>
+      <c r="BO21" s="132"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="119"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="88" t="s">
         <v>125</v>
       </c>
       <c r="C22" s="39" t="str">
-        <f t="shared" ref="C22:C37" ca="1" si="2">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C22:C39" ca="1" si="2">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D22" s="40" t="str">
-        <f t="shared" ref="D22:D38" si="3">IF(AND(F22&lt;&gt;"", E22&lt;&gt;""), F22 - E22 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D22:D40" si="3">IF(AND(F22&lt;&gt;"", E22&lt;&gt;""), F22 - E22 + 1 &amp; "일", "")</f>
         <v>2일</v>
       </c>
       <c r="E22" s="41">
@@ -4956,7 +4999,7 @@
       <c r="BO22" s="60"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="119"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="89" t="s">
         <v>85</v>
       </c>
@@ -5039,9 +5082,9 @@
       <c r="BO23" s="60"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="119"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="90" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C24" s="39" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5122,13 +5165,13 @@
       <c r="BO24" s="60"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="119"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="90" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C25" s="39" t="str">
         <f t="shared" ref="C25" ca="1" si="4">IF(F25=E25, IF(TODAY()&gt;F25, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F25) - E25) / (F25 - E25) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D25" s="40" t="str">
         <f>IF(AND(F25&lt;&gt;"", E25&lt;&gt;""), F25 - E25 + 1 &amp; "일", "")</f>
@@ -5205,25 +5248,27 @@
       <c r="BO25" s="60"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="91" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="20" t="str">
+      <c r="A26" s="128"/>
+      <c r="B26" s="85" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="39" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0%</v>
-      </c>
-      <c r="D26" s="21" t="str">
-        <f t="shared" ref="D26:D28" si="5">IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26 - E26 + 1 &amp; "일", "")</f>
-        <v>3일</v>
-      </c>
-      <c r="E26" s="22">
+        <v>100%</v>
+      </c>
+      <c r="D26" s="40" t="str">
+        <f t="shared" ref="D26:D30" si="5">IF(AND(F26&lt;&gt;"", E26&lt;&gt;""), F26 - E26 + 1 &amp; "일", "")</f>
+        <v>2일</v>
+      </c>
+      <c r="E26" s="41">
         <v>45980</v>
       </c>
-      <c r="F26" s="22">
-        <v>45982</v>
-      </c>
-      <c r="G26" s="30"/>
+      <c r="F26" s="41">
+        <v>45981</v>
+      </c>
+      <c r="G26" s="52" t="s">
+        <v>147</v>
+      </c>
       <c r="H26" s="59"/>
       <c r="I26" s="60"/>
       <c r="J26" s="60"/>
@@ -5286,9 +5331,9 @@
       <c r="BO26" s="60"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="119"/>
-      <c r="B27" s="92" t="s">
-        <v>140</v>
+      <c r="A27" s="128"/>
+      <c r="B27" s="91" t="s">
+        <v>137</v>
       </c>
       <c r="C27" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5296,15 +5341,17 @@
       </c>
       <c r="D27" s="21" t="str">
         <f t="shared" si="5"/>
-        <v>3일</v>
+        <v>2일</v>
       </c>
       <c r="E27" s="22">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="F27" s="22">
         <v>45982</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="H27" s="59"/>
       <c r="I27" s="60"/>
       <c r="J27" s="60"/>
@@ -5367,25 +5414,27 @@
       <c r="BO27" s="60"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="119"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="92" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C28" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D28" s="21" t="str">
         <f t="shared" si="5"/>
-        <v>3일</v>
+        <v>1일</v>
       </c>
       <c r="E28" s="22">
         <v>45980</v>
       </c>
       <c r="F28" s="22">
-        <v>45982</v>
-      </c>
-      <c r="G28" s="30"/>
+        <v>45980</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>147</v>
+      </c>
       <c r="H28" s="59"/>
       <c r="I28" s="60"/>
       <c r="J28" s="60"/>
@@ -5448,27 +5497,25 @@
       <c r="BO28" s="60"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="119"/>
-      <c r="B29" s="93" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="39" t="str">
+      <c r="A29" s="128"/>
+      <c r="B29" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>100%</v>
-      </c>
-      <c r="D29" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v>7일</v>
-      </c>
-      <c r="E29" s="41">
-        <v>45965</v>
-      </c>
-      <c r="F29" s="41">
-        <v>45971</v>
-      </c>
-      <c r="G29" s="52" t="s">
-        <v>103</v>
-      </c>
+        <v>50%</v>
+      </c>
+      <c r="D29" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v>3일</v>
+      </c>
+      <c r="E29" s="22">
+        <v>45980</v>
+      </c>
+      <c r="F29" s="22">
+        <v>45982</v>
+      </c>
+      <c r="G29" s="30"/>
       <c r="H29" s="59"/>
       <c r="I29" s="60"/>
       <c r="J29" s="60"/>
@@ -5483,13 +5530,13 @@
       <c r="S29" s="61"/>
       <c r="T29" s="62"/>
       <c r="U29" s="60"/>
-      <c r="V29" s="63"/>
-      <c r="W29" s="63"/>
-      <c r="X29" s="63"/>
-      <c r="Y29" s="63"/>
-      <c r="Z29" s="63"/>
-      <c r="AA29" s="63"/>
-      <c r="AB29" s="63"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="61"/>
+      <c r="AA29" s="62"/>
+      <c r="AB29" s="60"/>
       <c r="AC29" s="60"/>
       <c r="AD29" s="60"/>
       <c r="AE29" s="60"/>
@@ -5498,9 +5545,9 @@
       <c r="AH29" s="62"/>
       <c r="AI29" s="60"/>
       <c r="AJ29" s="60"/>
-      <c r="AK29" s="60"/>
-      <c r="AL29" s="60"/>
-      <c r="AM29" s="60"/>
+      <c r="AK29" s="63"/>
+      <c r="AL29" s="63"/>
+      <c r="AM29" s="63"/>
       <c r="AN29" s="61"/>
       <c r="AO29" s="62"/>
       <c r="AP29" s="60"/>
@@ -5528,29 +5575,29 @@
       <c r="BL29" s="60"/>
       <c r="BM29" s="60"/>
       <c r="BN29" s="60"/>
-      <c r="BO29" s="28"/>
+      <c r="BO29" s="60"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="87" t="s">
-        <v>111</v>
+      <c r="A30" s="128"/>
+      <c r="B30" s="124" t="s">
+        <v>146</v>
       </c>
       <c r="C30" s="39" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>100%</v>
+        <v>50%</v>
       </c>
       <c r="D30" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v>7일</v>
+        <f t="shared" si="5"/>
+        <v>3일</v>
       </c>
       <c r="E30" s="41">
-        <v>45971</v>
+        <v>45980</v>
       </c>
       <c r="F30" s="41">
-        <v>45977</v>
-      </c>
-      <c r="G30" s="43" t="s">
-        <v>117</v>
+        <v>45982</v>
+      </c>
+      <c r="G30" s="52" t="s">
+        <v>102</v>
       </c>
       <c r="H30" s="59"/>
       <c r="I30" s="60"/>
@@ -5572,18 +5619,18 @@
       <c r="Y30" s="60"/>
       <c r="Z30" s="61"/>
       <c r="AA30" s="62"/>
-      <c r="AB30" s="58"/>
-      <c r="AC30" s="58"/>
-      <c r="AD30" s="58"/>
-      <c r="AE30" s="58"/>
-      <c r="AF30" s="58"/>
-      <c r="AG30" s="58"/>
-      <c r="AH30" s="58"/>
+      <c r="AB30" s="60"/>
+      <c r="AC30" s="60"/>
+      <c r="AD30" s="60"/>
+      <c r="AE30" s="60"/>
+      <c r="AF30" s="60"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="62"/>
       <c r="AI30" s="60"/>
       <c r="AJ30" s="60"/>
-      <c r="AK30" s="60"/>
-      <c r="AL30" s="60"/>
-      <c r="AM30" s="60"/>
+      <c r="AK30" s="63"/>
+      <c r="AL30" s="63"/>
+      <c r="AM30" s="63"/>
       <c r="AN30" s="61"/>
       <c r="AO30" s="62"/>
       <c r="AP30" s="60"/>
@@ -5614,12 +5661,12 @@
       <c r="BO30" s="60"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="88" t="s">
-        <v>126</v>
+      <c r="A31" s="128"/>
+      <c r="B31" s="93" t="s">
+        <v>104</v>
       </c>
       <c r="C31" s="39" t="str">
-        <f ca="1">IF(F31=E31, IF(TODAY()&gt;F31, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F31) - E31) / (F31 - E31) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
       <c r="D31" s="40" t="str">
@@ -5627,13 +5674,13 @@
         <v>7일</v>
       </c>
       <c r="E31" s="41">
+        <v>45965</v>
+      </c>
+      <c r="F31" s="41">
         <v>45971</v>
       </c>
-      <c r="F31" s="41">
-        <v>45977</v>
-      </c>
-      <c r="G31" s="43" t="s">
-        <v>117</v>
+      <c r="G31" s="52" t="s">
+        <v>103</v>
       </c>
       <c r="H31" s="59"/>
       <c r="I31" s="60"/>
@@ -5649,19 +5696,19 @@
       <c r="S31" s="61"/>
       <c r="T31" s="62"/>
       <c r="U31" s="60"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="60"/>
-      <c r="Y31" s="60"/>
-      <c r="Z31" s="61"/>
-      <c r="AA31" s="62"/>
+      <c r="V31" s="63"/>
+      <c r="W31" s="63"/>
+      <c r="X31" s="63"/>
+      <c r="Y31" s="63"/>
+      <c r="Z31" s="63"/>
+      <c r="AA31" s="63"/>
       <c r="AB31" s="63"/>
-      <c r="AC31" s="63"/>
-      <c r="AD31" s="63"/>
-      <c r="AE31" s="63"/>
-      <c r="AF31" s="63"/>
-      <c r="AG31" s="63"/>
-      <c r="AH31" s="63"/>
+      <c r="AC31" s="60"/>
+      <c r="AD31" s="60"/>
+      <c r="AE31" s="60"/>
+      <c r="AF31" s="60"/>
+      <c r="AG31" s="61"/>
+      <c r="AH31" s="62"/>
       <c r="AI31" s="60"/>
       <c r="AJ31" s="60"/>
       <c r="AK31" s="60"/>
@@ -5694,15 +5741,15 @@
       <c r="BL31" s="60"/>
       <c r="BM31" s="60"/>
       <c r="BN31" s="60"/>
-      <c r="BO31" s="60"/>
+      <c r="BO31" s="28"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="119"/>
+      <c r="A32" s="128"/>
       <c r="B32" s="87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32" s="39" t="str">
-        <f ca="1">IF(F32=E32, IF(TODAY()&gt;F32, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F32) - E32) / (F32 - E32) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
       <c r="D32" s="40" t="str">
@@ -5780,23 +5827,23 @@
       <c r="BO32" s="60"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="119"/>
-      <c r="B33" s="100" t="s">
-        <v>143</v>
+      <c r="A33" s="128"/>
+      <c r="B33" s="88" t="s">
+        <v>126</v>
       </c>
       <c r="C33" s="39" t="str">
         <f ca="1">IF(F33=E33, IF(TODAY()&gt;F33, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F33) - E33) / (F33 - E33) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D33" s="40" t="str">
-        <f t="shared" ref="D33" si="6">IF(AND(F33&lt;&gt;"", E33&lt;&gt;""), F33 - E33 + 1 &amp; "일", "")</f>
-        <v>1일</v>
+        <f t="shared" si="3"/>
+        <v>7일</v>
       </c>
       <c r="E33" s="41">
-        <v>45980</v>
+        <v>45971</v>
       </c>
       <c r="F33" s="41">
-        <v>45980</v>
+        <v>45977</v>
       </c>
       <c r="G33" s="43" t="s">
         <v>117</v>
@@ -5821,16 +5868,16 @@
       <c r="Y33" s="60"/>
       <c r="Z33" s="61"/>
       <c r="AA33" s="62"/>
-      <c r="AB33" s="60"/>
-      <c r="AC33" s="60"/>
-      <c r="AD33" s="60"/>
-      <c r="AE33" s="60"/>
-      <c r="AF33" s="60"/>
-      <c r="AG33" s="61"/>
-      <c r="AH33" s="58"/>
-      <c r="AI33" s="58"/>
-      <c r="AJ33" s="58"/>
-      <c r="AK33" s="58"/>
+      <c r="AB33" s="63"/>
+      <c r="AC33" s="63"/>
+      <c r="AD33" s="63"/>
+      <c r="AE33" s="63"/>
+      <c r="AF33" s="63"/>
+      <c r="AG33" s="63"/>
+      <c r="AH33" s="63"/>
+      <c r="AI33" s="60"/>
+      <c r="AJ33" s="60"/>
+      <c r="AK33" s="60"/>
       <c r="AL33" s="60"/>
       <c r="AM33" s="60"/>
       <c r="AN33" s="61"/>
@@ -5863,26 +5910,26 @@
       <c r="BO33" s="60"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="119"/>
-      <c r="B34" s="100" t="s">
-        <v>146</v>
+      <c r="A34" s="128"/>
+      <c r="B34" s="87" t="s">
+        <v>112</v>
       </c>
       <c r="C34" s="39" t="str">
         <f ca="1">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D34" s="40" t="str">
-        <f t="shared" ref="D34" si="7">IF(AND(F34&lt;&gt;"", E34&lt;&gt;""), F34 - E34 + 1 &amp; "일", "")</f>
-        <v>1일</v>
+        <f t="shared" si="3"/>
+        <v>7일</v>
       </c>
       <c r="E34" s="41">
-        <v>45980</v>
+        <v>45971</v>
       </c>
       <c r="F34" s="41">
-        <v>45980</v>
+        <v>45977</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H34" s="59"/>
       <c r="I34" s="60"/>
@@ -5904,16 +5951,16 @@
       <c r="Y34" s="60"/>
       <c r="Z34" s="61"/>
       <c r="AA34" s="62"/>
-      <c r="AB34" s="60"/>
-      <c r="AC34" s="60"/>
-      <c r="AD34" s="60"/>
-      <c r="AE34" s="60"/>
-      <c r="AF34" s="60"/>
-      <c r="AG34" s="61"/>
-      <c r="AH34" s="63"/>
-      <c r="AI34" s="63"/>
-      <c r="AJ34" s="63"/>
-      <c r="AK34" s="63"/>
+      <c r="AB34" s="58"/>
+      <c r="AC34" s="58"/>
+      <c r="AD34" s="58"/>
+      <c r="AE34" s="58"/>
+      <c r="AF34" s="58"/>
+      <c r="AG34" s="58"/>
+      <c r="AH34" s="58"/>
+      <c r="AI34" s="60"/>
+      <c r="AJ34" s="60"/>
+      <c r="AK34" s="60"/>
       <c r="AL34" s="60"/>
       <c r="AM34" s="60"/>
       <c r="AN34" s="61"/>
@@ -5946,26 +5993,26 @@
       <c r="BO34" s="60"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="119"/>
-      <c r="B35" s="117" t="s">
-        <v>121</v>
+      <c r="A35" s="128"/>
+      <c r="B35" s="100" t="s">
+        <v>140</v>
       </c>
       <c r="C35" s="39" t="str">
         <f ca="1">IF(F35=E35, IF(TODAY()&gt;F35, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F35) - E35) / (F35 - E35) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D35" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v>4일</v>
+        <f t="shared" ref="D35" si="6">IF(AND(F35&lt;&gt;"", E35&lt;&gt;""), F35 - E35 + 1 &amp; "일", "")</f>
+        <v>1일</v>
       </c>
       <c r="E35" s="41">
-        <v>45977</v>
+        <v>45980</v>
       </c>
       <c r="F35" s="41">
         <v>45980</v>
       </c>
       <c r="G35" s="43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="59"/>
       <c r="I35" s="60"/>
@@ -6029,26 +6076,26 @@
       <c r="BO35" s="60"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="119"/>
-      <c r="B36" s="72" t="s">
-        <v>122</v>
+      <c r="A36" s="128"/>
+      <c r="B36" s="100" t="s">
+        <v>142</v>
       </c>
       <c r="C36" s="39" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF(F36=E36, IF(TODAY()&gt;F36, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F36) - E36) / (F36 - E36) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D36" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v>4일</v>
+        <f t="shared" ref="D36" si="7">IF(AND(F36&lt;&gt;"", E36&lt;&gt;""), F36 - E36 + 1 &amp; "일", "")</f>
+        <v>1일</v>
       </c>
       <c r="E36" s="41">
-        <v>45977</v>
+        <v>45980</v>
       </c>
       <c r="F36" s="41">
         <v>45980</v>
       </c>
       <c r="G36" s="43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H36" s="59"/>
       <c r="I36" s="60"/>
@@ -6112,12 +6159,12 @@
       <c r="BO36" s="60"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="119"/>
-      <c r="B37" s="72" t="s">
-        <v>133</v>
+      <c r="A37" s="128"/>
+      <c r="B37" s="116" t="s">
+        <v>121</v>
       </c>
       <c r="C37" s="39" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF(F37=E37, IF(TODAY()&gt;F37, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F37) - E37) / (F37 - E37) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D37" s="40" t="str">
@@ -6131,28 +6178,28 @@
         <v>45980</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="H37" s="54"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="56"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="55"/>
-      <c r="V37" s="55"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="55"/>
-      <c r="Y37" s="55"/>
-      <c r="Z37" s="56"/>
-      <c r="AA37" s="57"/>
+        <v>116</v>
+      </c>
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="60"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="60"/>
+      <c r="V37" s="60"/>
+      <c r="W37" s="60"/>
+      <c r="X37" s="60"/>
+      <c r="Y37" s="60"/>
+      <c r="Z37" s="61"/>
+      <c r="AA37" s="62"/>
       <c r="AB37" s="60"/>
       <c r="AC37" s="60"/>
       <c r="AD37" s="60"/>
@@ -6163,44 +6210,44 @@
       <c r="AI37" s="58"/>
       <c r="AJ37" s="58"/>
       <c r="AK37" s="58"/>
-      <c r="AL37" s="55"/>
-      <c r="AM37" s="55"/>
-      <c r="AN37" s="56"/>
-      <c r="AO37" s="57"/>
-      <c r="AP37" s="55"/>
-      <c r="AQ37" s="55"/>
-      <c r="AR37" s="55"/>
-      <c r="AS37" s="55"/>
-      <c r="AT37" s="55"/>
-      <c r="AU37" s="56"/>
-      <c r="AV37" s="57"/>
-      <c r="AW37" s="55"/>
-      <c r="AX37" s="55"/>
-      <c r="AY37" s="55"/>
-      <c r="AZ37" s="55"/>
-      <c r="BA37" s="55"/>
-      <c r="BB37" s="56"/>
-      <c r="BC37" s="57"/>
-      <c r="BD37" s="55"/>
-      <c r="BE37" s="55"/>
-      <c r="BF37" s="55"/>
-      <c r="BG37" s="55"/>
-      <c r="BH37" s="55"/>
-      <c r="BI37" s="56"/>
-      <c r="BJ37" s="57"/>
-      <c r="BK37" s="55"/>
-      <c r="BL37" s="55"/>
-      <c r="BM37" s="55"/>
-      <c r="BN37" s="55"/>
+      <c r="AL37" s="60"/>
+      <c r="AM37" s="60"/>
+      <c r="AN37" s="61"/>
+      <c r="AO37" s="62"/>
+      <c r="AP37" s="60"/>
+      <c r="AQ37" s="60"/>
+      <c r="AR37" s="60"/>
+      <c r="AS37" s="60"/>
+      <c r="AT37" s="60"/>
+      <c r="AU37" s="61"/>
+      <c r="AV37" s="62"/>
+      <c r="AW37" s="60"/>
+      <c r="AX37" s="60"/>
+      <c r="AY37" s="60"/>
+      <c r="AZ37" s="60"/>
+      <c r="BA37" s="60"/>
+      <c r="BB37" s="61"/>
+      <c r="BC37" s="62"/>
+      <c r="BD37" s="60"/>
+      <c r="BE37" s="60"/>
+      <c r="BF37" s="60"/>
+      <c r="BG37" s="60"/>
+      <c r="BH37" s="60"/>
+      <c r="BI37" s="61"/>
+      <c r="BJ37" s="62"/>
+      <c r="BK37" s="60"/>
+      <c r="BL37" s="60"/>
+      <c r="BM37" s="60"/>
+      <c r="BN37" s="60"/>
       <c r="BO37" s="60"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="119"/>
-      <c r="B38" s="88" t="s">
-        <v>142</v>
+      <c r="A38" s="128"/>
+      <c r="B38" s="72" t="s">
+        <v>122</v>
       </c>
       <c r="C38" s="39" t="str">
-        <f t="shared" ref="C38" ca="1" si="8">IF(F38=E38, IF(TODAY()&gt;F38, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F38) - E38) / (F38 - E38) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
       <c r="D38" s="40" t="str">
@@ -6214,7 +6261,7 @@
         <v>45980</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H38" s="59"/>
       <c r="I38" s="60"/>
@@ -6278,97 +6325,109 @@
       <c r="BO38" s="60"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="119"/>
-      <c r="B39" s="133" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="133"/>
-      <c r="D39" s="133"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="121"/>
-      <c r="I39" s="122"/>
-      <c r="J39" s="122"/>
-      <c r="K39" s="122"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="122"/>
-      <c r="N39" s="122"/>
-      <c r="O39" s="122"/>
-      <c r="P39" s="122"/>
-      <c r="Q39" s="122"/>
-      <c r="R39" s="122"/>
-      <c r="S39" s="122"/>
-      <c r="T39" s="122"/>
-      <c r="U39" s="122"/>
-      <c r="V39" s="122"/>
-      <c r="W39" s="122"/>
-      <c r="X39" s="122"/>
-      <c r="Y39" s="122"/>
-      <c r="Z39" s="122"/>
-      <c r="AA39" s="122"/>
-      <c r="AB39" s="122"/>
-      <c r="AC39" s="122"/>
-      <c r="AD39" s="122"/>
-      <c r="AE39" s="122"/>
-      <c r="AF39" s="122"/>
-      <c r="AG39" s="122"/>
-      <c r="AH39" s="122"/>
-      <c r="AI39" s="122"/>
-      <c r="AJ39" s="122"/>
-      <c r="AK39" s="122"/>
-      <c r="AL39" s="122"/>
-      <c r="AM39" s="122"/>
-      <c r="AN39" s="122"/>
-      <c r="AO39" s="122"/>
-      <c r="AP39" s="122"/>
-      <c r="AQ39" s="122"/>
-      <c r="AR39" s="122"/>
-      <c r="AS39" s="122"/>
-      <c r="AT39" s="122"/>
-      <c r="AU39" s="122"/>
-      <c r="AV39" s="122"/>
-      <c r="AW39" s="122"/>
-      <c r="AX39" s="122"/>
-      <c r="AY39" s="122"/>
-      <c r="AZ39" s="122"/>
-      <c r="BA39" s="122"/>
-      <c r="BB39" s="122"/>
-      <c r="BC39" s="122"/>
-      <c r="BD39" s="122"/>
-      <c r="BE39" s="122"/>
-      <c r="BF39" s="122"/>
-      <c r="BG39" s="122"/>
-      <c r="BH39" s="122"/>
-      <c r="BI39" s="122"/>
-      <c r="BJ39" s="122"/>
-      <c r="BK39" s="122"/>
-      <c r="BL39" s="122"/>
-      <c r="BM39" s="122"/>
-      <c r="BN39" s="122"/>
-      <c r="BO39" s="123"/>
+      <c r="A39" s="128"/>
+      <c r="B39" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="39" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>100%</v>
+      </c>
+      <c r="D39" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>4일</v>
+      </c>
+      <c r="E39" s="41">
+        <v>45977</v>
+      </c>
+      <c r="F39" s="41">
+        <v>45980</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="54"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="55"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="55"/>
+      <c r="V39" s="55"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="55"/>
+      <c r="Z39" s="56"/>
+      <c r="AA39" s="57"/>
+      <c r="AB39" s="60"/>
+      <c r="AC39" s="60"/>
+      <c r="AD39" s="60"/>
+      <c r="AE39" s="60"/>
+      <c r="AF39" s="60"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="58"/>
+      <c r="AI39" s="58"/>
+      <c r="AJ39" s="58"/>
+      <c r="AK39" s="58"/>
+      <c r="AL39" s="55"/>
+      <c r="AM39" s="55"/>
+      <c r="AN39" s="56"/>
+      <c r="AO39" s="57"/>
+      <c r="AP39" s="55"/>
+      <c r="AQ39" s="55"/>
+      <c r="AR39" s="55"/>
+      <c r="AS39" s="55"/>
+      <c r="AT39" s="55"/>
+      <c r="AU39" s="56"/>
+      <c r="AV39" s="57"/>
+      <c r="AW39" s="55"/>
+      <c r="AX39" s="55"/>
+      <c r="AY39" s="55"/>
+      <c r="AZ39" s="55"/>
+      <c r="BA39" s="55"/>
+      <c r="BB39" s="56"/>
+      <c r="BC39" s="57"/>
+      <c r="BD39" s="55"/>
+      <c r="BE39" s="55"/>
+      <c r="BF39" s="55"/>
+      <c r="BG39" s="55"/>
+      <c r="BH39" s="55"/>
+      <c r="BI39" s="56"/>
+      <c r="BJ39" s="57"/>
+      <c r="BK39" s="55"/>
+      <c r="BL39" s="55"/>
+      <c r="BM39" s="55"/>
+      <c r="BN39" s="55"/>
+      <c r="BO39" s="60"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="119"/>
-      <c r="B40" s="87" t="s">
-        <v>110</v>
+      <c r="A40" s="128"/>
+      <c r="B40" s="88" t="s">
+        <v>139</v>
       </c>
       <c r="C40" s="39" t="str">
-        <f t="shared" ref="C40:C50" ca="1" si="9">IF(F40=E40, IF(TODAY()&gt;F40, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F40) - E40) / (F40 - E40) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C40" ca="1" si="8">IF(F40=E40, IF(TODAY()&gt;F40, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F40) - E40) / (F40 - E40) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D40" s="40" t="str">
-        <f t="shared" ref="D40:D43" si="10">IF(AND(F40&lt;&gt;"", E40&lt;&gt;""), F40 - E40 + 1 &amp; "일", "")</f>
-        <v>7일</v>
+        <f t="shared" si="3"/>
+        <v>4일</v>
       </c>
       <c r="E40" s="41">
-        <v>45971</v>
+        <v>45977</v>
       </c>
       <c r="F40" s="41">
-        <v>45977</v>
+        <v>45980</v>
       </c>
       <c r="G40" s="43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H40" s="59"/>
       <c r="I40" s="60"/>
@@ -6390,16 +6449,16 @@
       <c r="Y40" s="60"/>
       <c r="Z40" s="61"/>
       <c r="AA40" s="62"/>
-      <c r="AB40" s="58"/>
-      <c r="AC40" s="58"/>
-      <c r="AD40" s="58"/>
-      <c r="AE40" s="58"/>
-      <c r="AF40" s="58"/>
-      <c r="AG40" s="58"/>
-      <c r="AH40" s="58"/>
-      <c r="AI40" s="60"/>
-      <c r="AJ40" s="60"/>
-      <c r="AK40" s="60"/>
+      <c r="AB40" s="60"/>
+      <c r="AC40" s="60"/>
+      <c r="AD40" s="60"/>
+      <c r="AE40" s="60"/>
+      <c r="AF40" s="60"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="63"/>
+      <c r="AI40" s="63"/>
+      <c r="AJ40" s="63"/>
+      <c r="AK40" s="63"/>
       <c r="AL40" s="60"/>
       <c r="AM40" s="60"/>
       <c r="AN40" s="61"/>
@@ -6432,106 +6491,94 @@
       <c r="BO40" s="60"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="119"/>
-      <c r="B41" s="88" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="39" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>100%</v>
-      </c>
-      <c r="D41" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>7일</v>
-      </c>
-      <c r="E41" s="41">
-        <v>45971</v>
-      </c>
-      <c r="F41" s="41">
-        <v>45977</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="H41" s="59"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="62"/>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60"/>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="61"/>
-      <c r="T41" s="62"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="60"/>
-      <c r="W41" s="60"/>
-      <c r="X41" s="60"/>
-      <c r="Y41" s="60"/>
-      <c r="Z41" s="61"/>
-      <c r="AA41" s="62"/>
-      <c r="AB41" s="63"/>
-      <c r="AC41" s="63"/>
-      <c r="AD41" s="63"/>
-      <c r="AE41" s="63"/>
-      <c r="AF41" s="63"/>
-      <c r="AG41" s="63"/>
-      <c r="AH41" s="63"/>
-      <c r="AI41" s="60"/>
-      <c r="AJ41" s="60"/>
-      <c r="AK41" s="60"/>
-      <c r="AL41" s="60"/>
-      <c r="AM41" s="60"/>
-      <c r="AN41" s="61"/>
-      <c r="AO41" s="62"/>
-      <c r="AP41" s="60"/>
-      <c r="AQ41" s="60"/>
-      <c r="AR41" s="60"/>
-      <c r="AS41" s="60"/>
-      <c r="AT41" s="60"/>
-      <c r="AU41" s="61"/>
-      <c r="AV41" s="62"/>
-      <c r="AW41" s="60"/>
-      <c r="AX41" s="60"/>
-      <c r="AY41" s="60"/>
-      <c r="AZ41" s="60"/>
-      <c r="BA41" s="60"/>
-      <c r="BB41" s="61"/>
-      <c r="BC41" s="62"/>
-      <c r="BD41" s="60"/>
-      <c r="BE41" s="60"/>
-      <c r="BF41" s="60"/>
-      <c r="BG41" s="60"/>
-      <c r="BH41" s="60"/>
-      <c r="BI41" s="61"/>
-      <c r="BJ41" s="62"/>
-      <c r="BK41" s="60"/>
-      <c r="BL41" s="60"/>
-      <c r="BM41" s="60"/>
-      <c r="BN41" s="60"/>
-      <c r="BO41" s="60"/>
+      <c r="A41" s="128"/>
+      <c r="B41" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="142"/>
+      <c r="D41" s="142"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="131"/>
+      <c r="J41" s="131"/>
+      <c r="K41" s="131"/>
+      <c r="L41" s="131"/>
+      <c r="M41" s="131"/>
+      <c r="N41" s="131"/>
+      <c r="O41" s="131"/>
+      <c r="P41" s="131"/>
+      <c r="Q41" s="131"/>
+      <c r="R41" s="131"/>
+      <c r="S41" s="131"/>
+      <c r="T41" s="131"/>
+      <c r="U41" s="131"/>
+      <c r="V41" s="131"/>
+      <c r="W41" s="131"/>
+      <c r="X41" s="131"/>
+      <c r="Y41" s="131"/>
+      <c r="Z41" s="131"/>
+      <c r="AA41" s="131"/>
+      <c r="AB41" s="131"/>
+      <c r="AC41" s="131"/>
+      <c r="AD41" s="131"/>
+      <c r="AE41" s="131"/>
+      <c r="AF41" s="131"/>
+      <c r="AG41" s="131"/>
+      <c r="AH41" s="131"/>
+      <c r="AI41" s="131"/>
+      <c r="AJ41" s="131"/>
+      <c r="AK41" s="131"/>
+      <c r="AL41" s="131"/>
+      <c r="AM41" s="131"/>
+      <c r="AN41" s="131"/>
+      <c r="AO41" s="131"/>
+      <c r="AP41" s="131"/>
+      <c r="AQ41" s="131"/>
+      <c r="AR41" s="131"/>
+      <c r="AS41" s="131"/>
+      <c r="AT41" s="131"/>
+      <c r="AU41" s="131"/>
+      <c r="AV41" s="131"/>
+      <c r="AW41" s="131"/>
+      <c r="AX41" s="131"/>
+      <c r="AY41" s="131"/>
+      <c r="AZ41" s="131"/>
+      <c r="BA41" s="131"/>
+      <c r="BB41" s="131"/>
+      <c r="BC41" s="131"/>
+      <c r="BD41" s="131"/>
+      <c r="BE41" s="131"/>
+      <c r="BF41" s="131"/>
+      <c r="BG41" s="131"/>
+      <c r="BH41" s="131"/>
+      <c r="BI41" s="131"/>
+      <c r="BJ41" s="131"/>
+      <c r="BK41" s="131"/>
+      <c r="BL41" s="131"/>
+      <c r="BM41" s="131"/>
+      <c r="BN41" s="131"/>
+      <c r="BO41" s="132"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="119"/>
-      <c r="B42" s="88" t="s">
-        <v>134</v>
+      <c r="A42" s="128"/>
+      <c r="B42" s="87" t="s">
+        <v>110</v>
       </c>
       <c r="C42" s="39" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ref="C42:C48" ca="1" si="9">IF(F42=E42, IF(TODAY()&gt;F42, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F42) - E42) / (F42 - E42) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D42" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>10일</v>
+        <f t="shared" ref="D42:D47" si="10">IF(AND(F42&lt;&gt;"", E42&lt;&gt;""), F42 - E42 + 1 &amp; "일", "")</f>
+        <v>7일</v>
       </c>
       <c r="E42" s="41">
         <v>45971</v>
       </c>
       <c r="F42" s="41">
-        <v>45980</v>
+        <v>45977</v>
       </c>
       <c r="G42" s="43" t="s">
         <v>119</v>
@@ -6598,26 +6645,26 @@
       <c r="BO42" s="60"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="119"/>
-      <c r="B43" s="93" t="s">
-        <v>136</v>
+      <c r="A43" s="128"/>
+      <c r="B43" s="88" t="s">
+        <v>127</v>
       </c>
       <c r="C43" s="39" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D43" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>1일</v>
+        <v>7일</v>
       </c>
       <c r="E43" s="41">
-        <v>45980</v>
+        <v>45971</v>
       </c>
       <c r="F43" s="41">
-        <v>45980</v>
-      </c>
-      <c r="G43" s="52" t="s">
-        <v>105</v>
+        <v>45977</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>119</v>
       </c>
       <c r="H43" s="59"/>
       <c r="I43" s="60"/>
@@ -6639,16 +6686,16 @@
       <c r="Y43" s="60"/>
       <c r="Z43" s="61"/>
       <c r="AA43" s="62"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="60"/>
-      <c r="AE43" s="60"/>
-      <c r="AF43" s="60"/>
-      <c r="AG43" s="61"/>
-      <c r="AH43" s="62"/>
+      <c r="AB43" s="63"/>
+      <c r="AC43" s="63"/>
+      <c r="AD43" s="63"/>
+      <c r="AE43" s="63"/>
+      <c r="AF43" s="63"/>
+      <c r="AG43" s="63"/>
+      <c r="AH43" s="63"/>
       <c r="AI43" s="60"/>
       <c r="AJ43" s="60"/>
-      <c r="AK43" s="63"/>
+      <c r="AK43" s="60"/>
       <c r="AL43" s="60"/>
       <c r="AM43" s="60"/>
       <c r="AN43" s="61"/>
@@ -6681,26 +6728,26 @@
       <c r="BO43" s="60"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="119"/>
-      <c r="B44" s="91" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="20" t="str">
-        <f ca="1">IF(F44=E44, IF(TODAY()&gt;F44, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F44) - E44) / (F44 - E44) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+      <c r="A44" s="128"/>
+      <c r="B44" s="88" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="39" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>100%</v>
       </c>
       <c r="D44" s="40" t="str">
-        <f t="shared" ref="D44:D45" si="11">IF(AND(F44&lt;&gt;"", E44&lt;&gt;""), F44 - E44 + 1 &amp; "일", "")</f>
-        <v>1일</v>
+        <f t="shared" si="10"/>
+        <v>10일</v>
       </c>
       <c r="E44" s="41">
-        <v>45980</v>
+        <v>45971</v>
       </c>
       <c r="F44" s="41">
         <v>45980</v>
       </c>
-      <c r="G44" s="52" t="s">
-        <v>105</v>
+      <c r="G44" s="43" t="s">
+        <v>119</v>
       </c>
       <c r="H44" s="59"/>
       <c r="I44" s="60"/>
@@ -6722,13 +6769,13 @@
       <c r="Y44" s="60"/>
       <c r="Z44" s="61"/>
       <c r="AA44" s="62"/>
-      <c r="AB44" s="60"/>
-      <c r="AC44" s="60"/>
-      <c r="AD44" s="60"/>
-      <c r="AE44" s="60"/>
-      <c r="AF44" s="60"/>
-      <c r="AG44" s="61"/>
-      <c r="AH44" s="62"/>
+      <c r="AB44" s="58"/>
+      <c r="AC44" s="58"/>
+      <c r="AD44" s="58"/>
+      <c r="AE44" s="58"/>
+      <c r="AF44" s="58"/>
+      <c r="AG44" s="58"/>
+      <c r="AH44" s="58"/>
       <c r="AI44" s="60"/>
       <c r="AJ44" s="60"/>
       <c r="AK44" s="60"/>
@@ -6764,25 +6811,25 @@
       <c r="BO44" s="60"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="119"/>
-      <c r="B45" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="C45" s="20" t="str">
+      <c r="A45" s="128"/>
+      <c r="B45" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="39" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>0%</v>
-      </c>
-      <c r="D45" s="21" t="str">
-        <f t="shared" si="11"/>
+        <v>100%</v>
+      </c>
+      <c r="D45" s="40" t="str">
+        <f t="shared" si="10"/>
         <v>1일</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="41">
         <v>45980</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="41">
         <v>45980</v>
       </c>
-      <c r="G45" s="30" t="s">
+      <c r="G45" s="52" t="s">
         <v>105</v>
       </c>
       <c r="H45" s="59"/>
@@ -6814,7 +6861,7 @@
       <c r="AH45" s="62"/>
       <c r="AI45" s="60"/>
       <c r="AJ45" s="60"/>
-      <c r="AK45" s="60"/>
+      <c r="AK45" s="63"/>
       <c r="AL45" s="60"/>
       <c r="AM45" s="60"/>
       <c r="AN45" s="61"/>
@@ -6847,26 +6894,26 @@
       <c r="BO45" s="60"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="119"/>
-      <c r="B46" s="92" t="s">
-        <v>154</v>
-      </c>
-      <c r="C46" s="20" t="str">
-        <f t="shared" ref="C46" ca="1" si="12">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
-      </c>
-      <c r="D46" s="21" t="str">
-        <f t="shared" ref="D46:D50" si="13">IF(AND(F46&lt;&gt;"", E46&lt;&gt;""), F46 - E46 + 1 &amp; "일", "")</f>
-        <v>1일</v>
-      </c>
-      <c r="E46" s="22">
+      <c r="A46" s="128"/>
+      <c r="B46" s="125" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" s="73" t="str">
+        <f ca="1">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
+        <v>50%</v>
+      </c>
+      <c r="D46" s="74" t="str">
+        <f t="shared" si="10"/>
+        <v>3일</v>
+      </c>
+      <c r="E46" s="75">
         <v>45980</v>
       </c>
-      <c r="F46" s="22">
-        <v>45980</v>
-      </c>
-      <c r="G46" s="30" t="s">
-        <v>153</v>
+      <c r="F46" s="75">
+        <v>45982</v>
+      </c>
+      <c r="G46" s="76" t="s">
+        <v>105</v>
       </c>
       <c r="H46" s="59"/>
       <c r="I46" s="60"/>
@@ -6930,18 +6977,27 @@
       <c r="BO46" s="60"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="119"/>
-      <c r="B47" s="91" t="s">
-        <v>148</v>
-      </c>
-      <c r="C47" s="20" t="str">
+      <c r="A47" s="128"/>
+      <c r="B47" s="85" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="39" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>100%</v>
-      </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="30"/>
+        <v>0%</v>
+      </c>
+      <c r="D47" s="40" t="str">
+        <f t="shared" si="10"/>
+        <v>1일</v>
+      </c>
+      <c r="E47" s="41">
+        <v>45981</v>
+      </c>
+      <c r="F47" s="41">
+        <v>45981</v>
+      </c>
+      <c r="G47" s="52" t="s">
+        <v>154</v>
+      </c>
       <c r="H47" s="59"/>
       <c r="I47" s="60"/>
       <c r="J47" s="60"/>
@@ -7004,16 +7060,16 @@
       <c r="BO47" s="60"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="119"/>
+      <c r="A48" s="128"/>
       <c r="B48" s="92" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C48" s="20" t="str">
         <f t="shared" ca="1" si="9"/>
         <v>100%</v>
       </c>
       <c r="D48" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D48" si="11">IF(AND(F48&lt;&gt;"", E48&lt;&gt;""), F48 - E48 + 1 &amp; "일", "")</f>
         <v/>
       </c>
       <c r="E48" s="22"/>
@@ -7078,101 +7134,101 @@
       <c r="BL48" s="60"/>
       <c r="BM48" s="60"/>
       <c r="BN48" s="60"/>
-      <c r="BO48" s="60"/>
+      <c r="BO48" s="29"/>
     </row>
-    <row r="49" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="119"/>
-      <c r="B49" s="92" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" s="20" t="str">
-        <f t="shared" ref="C49" ca="1" si="14">IF(F49=E49, IF(TODAY()&gt;F49, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F49) - E49) / (F49 - E49) * 100, 1) &amp; "%")</f>
+    <row r="49" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A49" s="128"/>
+      <c r="B49" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="142"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="142"/>
+      <c r="F49" s="142"/>
+      <c r="G49" s="142"/>
+      <c r="H49" s="130"/>
+      <c r="I49" s="131"/>
+      <c r="J49" s="131"/>
+      <c r="K49" s="131"/>
+      <c r="L49" s="131"/>
+      <c r="M49" s="131"/>
+      <c r="N49" s="131"/>
+      <c r="O49" s="131"/>
+      <c r="P49" s="131"/>
+      <c r="Q49" s="131"/>
+      <c r="R49" s="131"/>
+      <c r="S49" s="131"/>
+      <c r="T49" s="131"/>
+      <c r="U49" s="131"/>
+      <c r="V49" s="131"/>
+      <c r="W49" s="131"/>
+      <c r="X49" s="131"/>
+      <c r="Y49" s="131"/>
+      <c r="Z49" s="131"/>
+      <c r="AA49" s="131"/>
+      <c r="AB49" s="131"/>
+      <c r="AC49" s="131"/>
+      <c r="AD49" s="131"/>
+      <c r="AE49" s="131"/>
+      <c r="AF49" s="131"/>
+      <c r="AG49" s="131"/>
+      <c r="AH49" s="131"/>
+      <c r="AI49" s="131"/>
+      <c r="AJ49" s="131"/>
+      <c r="AK49" s="131"/>
+      <c r="AL49" s="131"/>
+      <c r="AM49" s="131"/>
+      <c r="AN49" s="131"/>
+      <c r="AO49" s="131"/>
+      <c r="AP49" s="131"/>
+      <c r="AQ49" s="131"/>
+      <c r="AR49" s="131"/>
+      <c r="AS49" s="131"/>
+      <c r="AT49" s="131"/>
+      <c r="AU49" s="131"/>
+      <c r="AV49" s="131"/>
+      <c r="AW49" s="131"/>
+      <c r="AX49" s="131"/>
+      <c r="AY49" s="131"/>
+      <c r="AZ49" s="131"/>
+      <c r="BA49" s="131"/>
+      <c r="BB49" s="131"/>
+      <c r="BC49" s="131"/>
+      <c r="BD49" s="131"/>
+      <c r="BE49" s="131"/>
+      <c r="BF49" s="131"/>
+      <c r="BG49" s="131"/>
+      <c r="BH49" s="131"/>
+      <c r="BI49" s="131"/>
+      <c r="BJ49" s="131"/>
+      <c r="BK49" s="131"/>
+      <c r="BL49" s="131"/>
+      <c r="BM49" s="131"/>
+      <c r="BN49" s="131"/>
+      <c r="BO49" s="132"/>
+    </row>
+    <row r="50" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A50" s="128"/>
+      <c r="B50" s="101" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="44" t="str">
+        <f t="shared" ref="C50:C68" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D49" s="21" t="str">
-        <f t="shared" ref="D49" si="15">IF(AND(F49&lt;&gt;"", E49&lt;&gt;""), F49 - E49 + 1 &amp; "일", "")</f>
-        <v/>
-      </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="56"/>
-      <c r="M49" s="57"/>
-      <c r="N49" s="55"/>
-      <c r="O49" s="55"/>
-      <c r="P49" s="55"/>
-      <c r="Q49" s="55"/>
-      <c r="R49" s="55"/>
-      <c r="S49" s="56"/>
-      <c r="T49" s="57"/>
-      <c r="U49" s="55"/>
-      <c r="V49" s="55"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="55"/>
-      <c r="Y49" s="55"/>
-      <c r="Z49" s="56"/>
-      <c r="AA49" s="57"/>
-      <c r="AB49" s="60"/>
-      <c r="AC49" s="60"/>
-      <c r="AD49" s="60"/>
-      <c r="AE49" s="60"/>
-      <c r="AF49" s="60"/>
-      <c r="AG49" s="61"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="55"/>
-      <c r="AJ49" s="55"/>
-      <c r="AK49" s="55"/>
-      <c r="AL49" s="55"/>
-      <c r="AM49" s="55"/>
-      <c r="AN49" s="56"/>
-      <c r="AO49" s="57"/>
-      <c r="AP49" s="55"/>
-      <c r="AQ49" s="55"/>
-      <c r="AR49" s="55"/>
-      <c r="AS49" s="55"/>
-      <c r="AT49" s="55"/>
-      <c r="AU49" s="56"/>
-      <c r="AV49" s="57"/>
-      <c r="AW49" s="55"/>
-      <c r="AX49" s="55"/>
-      <c r="AY49" s="55"/>
-      <c r="AZ49" s="55"/>
-      <c r="BA49" s="55"/>
-      <c r="BB49" s="56"/>
-      <c r="BC49" s="57"/>
-      <c r="BD49" s="55"/>
-      <c r="BE49" s="55"/>
-      <c r="BF49" s="55"/>
-      <c r="BG49" s="55"/>
-      <c r="BH49" s="55"/>
-      <c r="BI49" s="56"/>
-      <c r="BJ49" s="57"/>
-      <c r="BK49" s="55"/>
-      <c r="BL49" s="55"/>
-      <c r="BM49" s="55"/>
-      <c r="BN49" s="55"/>
-      <c r="BO49" s="60"/>
-    </row>
-    <row r="50" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A50" s="119"/>
-      <c r="B50" s="92" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" s="20" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>100%</v>
-      </c>
-      <c r="D50" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="30"/>
+      <c r="D50" s="104" t="str">
+        <f t="shared" ref="D50:D68" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
+        <v>7일</v>
+      </c>
+      <c r="E50" s="45">
+        <v>45971</v>
+      </c>
+      <c r="F50" s="45">
+        <v>45977</v>
+      </c>
+      <c r="G50" s="102" t="s">
+        <v>101</v>
+      </c>
       <c r="H50" s="59"/>
       <c r="I50" s="60"/>
       <c r="J50" s="60"/>
@@ -7232,102 +7288,114 @@
       <c r="BL50" s="60"/>
       <c r="BM50" s="60"/>
       <c r="BN50" s="60"/>
-      <c r="BO50" s="29"/>
+      <c r="BO50" s="60"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A51" s="119"/>
-      <c r="B51" s="133" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="133"/>
-      <c r="D51" s="133"/>
-      <c r="E51" s="133"/>
-      <c r="F51" s="133"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="121"/>
-      <c r="I51" s="122"/>
-      <c r="J51" s="122"/>
-      <c r="K51" s="122"/>
-      <c r="L51" s="122"/>
-      <c r="M51" s="122"/>
-      <c r="N51" s="122"/>
-      <c r="O51" s="122"/>
-      <c r="P51" s="122"/>
-      <c r="Q51" s="122"/>
-      <c r="R51" s="122"/>
-      <c r="S51" s="122"/>
-      <c r="T51" s="122"/>
-      <c r="U51" s="122"/>
-      <c r="V51" s="122"/>
-      <c r="W51" s="122"/>
-      <c r="X51" s="122"/>
-      <c r="Y51" s="122"/>
-      <c r="Z51" s="122"/>
-      <c r="AA51" s="122"/>
-      <c r="AB51" s="122"/>
-      <c r="AC51" s="122"/>
-      <c r="AD51" s="122"/>
-      <c r="AE51" s="122"/>
-      <c r="AF51" s="122"/>
-      <c r="AG51" s="122"/>
-      <c r="AH51" s="122"/>
-      <c r="AI51" s="122"/>
-      <c r="AJ51" s="122"/>
-      <c r="AK51" s="122"/>
-      <c r="AL51" s="122"/>
-      <c r="AM51" s="122"/>
-      <c r="AN51" s="122"/>
-      <c r="AO51" s="122"/>
-      <c r="AP51" s="122"/>
-      <c r="AQ51" s="122"/>
-      <c r="AR51" s="122"/>
-      <c r="AS51" s="122"/>
-      <c r="AT51" s="122"/>
-      <c r="AU51" s="122"/>
-      <c r="AV51" s="122"/>
-      <c r="AW51" s="122"/>
-      <c r="AX51" s="122"/>
-      <c r="AY51" s="122"/>
-      <c r="AZ51" s="122"/>
-      <c r="BA51" s="122"/>
-      <c r="BB51" s="122"/>
-      <c r="BC51" s="122"/>
-      <c r="BD51" s="122"/>
-      <c r="BE51" s="122"/>
-      <c r="BF51" s="122"/>
-      <c r="BG51" s="122"/>
-      <c r="BH51" s="122"/>
-      <c r="BI51" s="122"/>
-      <c r="BJ51" s="122"/>
-      <c r="BK51" s="122"/>
-      <c r="BL51" s="122"/>
-      <c r="BM51" s="122"/>
-      <c r="BN51" s="122"/>
-      <c r="BO51" s="123"/>
+      <c r="A51" s="145"/>
+      <c r="B51" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="111" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
+      </c>
+      <c r="D51" s="112" t="str">
+        <f t="shared" si="13"/>
+        <v>9일</v>
+      </c>
+      <c r="E51" s="113">
+        <v>45971</v>
+      </c>
+      <c r="F51" s="113">
+        <v>45979</v>
+      </c>
+      <c r="G51" s="115" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" s="103"/>
+      <c r="I51" s="60"/>
+      <c r="J51" s="60"/>
+      <c r="K51" s="60"/>
+      <c r="L51" s="61"/>
+      <c r="M51" s="62"/>
+      <c r="N51" s="60"/>
+      <c r="O51" s="60"/>
+      <c r="P51" s="60"/>
+      <c r="Q51" s="60"/>
+      <c r="R51" s="60"/>
+      <c r="S51" s="61"/>
+      <c r="T51" s="62"/>
+      <c r="U51" s="60"/>
+      <c r="V51" s="60"/>
+      <c r="W51" s="60"/>
+      <c r="X51" s="60"/>
+      <c r="Y51" s="60"/>
+      <c r="Z51" s="61"/>
+      <c r="AA51" s="62"/>
+      <c r="AB51" s="60"/>
+      <c r="AC51" s="60"/>
+      <c r="AD51" s="60"/>
+      <c r="AE51" s="60"/>
+      <c r="AF51" s="60"/>
+      <c r="AG51" s="61"/>
+      <c r="AH51" s="62"/>
+      <c r="AI51" s="60"/>
+      <c r="AJ51" s="60"/>
+      <c r="AK51" s="60"/>
+      <c r="AL51" s="60"/>
+      <c r="AM51" s="60"/>
+      <c r="AN51" s="61"/>
+      <c r="AO51" s="62"/>
+      <c r="AP51" s="60"/>
+      <c r="AQ51" s="60"/>
+      <c r="AR51" s="60"/>
+      <c r="AS51" s="60"/>
+      <c r="AT51" s="60"/>
+      <c r="AU51" s="61"/>
+      <c r="AV51" s="62"/>
+      <c r="AW51" s="60"/>
+      <c r="AX51" s="60"/>
+      <c r="AY51" s="60"/>
+      <c r="AZ51" s="60"/>
+      <c r="BA51" s="60"/>
+      <c r="BB51" s="61"/>
+      <c r="BC51" s="62"/>
+      <c r="BD51" s="60"/>
+      <c r="BE51" s="60"/>
+      <c r="BF51" s="60"/>
+      <c r="BG51" s="60"/>
+      <c r="BH51" s="60"/>
+      <c r="BI51" s="61"/>
+      <c r="BJ51" s="62"/>
+      <c r="BK51" s="60"/>
+      <c r="BL51" s="60"/>
+      <c r="BM51" s="60"/>
+      <c r="BN51" s="60"/>
+      <c r="BO51" s="60"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A52" s="119"/>
-      <c r="B52" s="101" t="s">
-        <v>128</v>
-      </c>
-      <c r="C52" s="44" t="str">
-        <f t="shared" ref="C52:C70" ca="1" si="16">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
+      <c r="A52" s="145"/>
+      <c r="B52" s="109" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="111" t="str">
+        <f t="shared" ref="C52" ca="1" si="14">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="104" t="str">
-        <f t="shared" ref="D52:D70" si="17">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
-        <v>7일</v>
-      </c>
-      <c r="E52" s="45">
+      <c r="D52" s="112" t="str">
+        <f t="shared" ref="D52:D53" si="15">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
+        <v>9일</v>
+      </c>
+      <c r="E52" s="113">
         <v>45971</v>
       </c>
-      <c r="F52" s="45">
-        <v>45977</v>
-      </c>
-      <c r="G52" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="H52" s="59"/>
+      <c r="F52" s="113">
+        <v>45979</v>
+      </c>
+      <c r="G52" s="115" t="s">
+        <v>103</v>
+      </c>
+      <c r="H52" s="103"/>
       <c r="I52" s="60"/>
       <c r="J52" s="60"/>
       <c r="K52" s="60"/>
@@ -7388,27 +7456,27 @@
       <c r="BN52" s="60"/>
       <c r="BO52" s="60"/>
     </row>
-    <row r="53" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A53" s="136"/>
+    <row r="53" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A53" s="145"/>
       <c r="B53" s="110" t="s">
-        <v>86</v>
-      </c>
-      <c r="C53" s="112" t="str">
-        <f t="shared" ref="C53" ca="1" si="18">IF(F53=E53, IF(TODAY()&gt;F53, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F53) - E53) / (F53 - E53) * 100, 1) &amp; "%")</f>
+        <v>141</v>
+      </c>
+      <c r="C53" s="111" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D53" s="113" t="str">
-        <f t="shared" ref="D53:D54" si="19">IF(AND(F53&lt;&gt;"", E53&lt;&gt;""), F53 - E53 + 1 &amp; "일", "")</f>
-        <v>9일</v>
-      </c>
-      <c r="E53" s="114">
-        <v>45971</v>
-      </c>
-      <c r="F53" s="114">
+      <c r="D53" s="112" t="str">
+        <f t="shared" si="15"/>
+        <v>2일</v>
+      </c>
+      <c r="E53" s="113">
         <v>45979</v>
       </c>
-      <c r="G53" s="116" t="s">
-        <v>103</v>
+      <c r="F53" s="113">
+        <v>45980</v>
+      </c>
+      <c r="G53" s="114" t="s">
+        <v>117</v>
       </c>
       <c r="H53" s="103"/>
       <c r="I53" s="60"/>
@@ -7472,28 +7540,28 @@
       <c r="BO53" s="60"/>
     </row>
     <row r="54" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="136"/>
-      <c r="B54" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" s="112" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>100%</v>
-      </c>
-      <c r="D54" s="113" t="str">
-        <f t="shared" si="19"/>
-        <v>2일</v>
-      </c>
-      <c r="E54" s="114">
-        <v>45979</v>
-      </c>
-      <c r="F54" s="114">
+      <c r="A54" s="128"/>
+      <c r="B54" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="32" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>5.6%</v>
+      </c>
+      <c r="D54" s="106" t="str">
+        <f t="shared" si="13"/>
+        <v>19일</v>
+      </c>
+      <c r="E54" s="107">
         <v>45980</v>
       </c>
-      <c r="G54" s="115" t="s">
-        <v>117</v>
-      </c>
-      <c r="H54" s="103"/>
+      <c r="F54" s="107">
+        <v>45998</v>
+      </c>
+      <c r="G54" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="H54" s="59"/>
       <c r="I54" s="60"/>
       <c r="J54" s="60"/>
       <c r="K54" s="60"/>
@@ -7555,26 +7623,26 @@
       <c r="BO54" s="60"/>
     </row>
     <row r="55" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A55" s="119"/>
-      <c r="B55" s="105" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="106" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>0%</v>
-      </c>
-      <c r="D55" s="107" t="str">
-        <f t="shared" si="17"/>
-        <v>19일</v>
-      </c>
-      <c r="E55" s="108">
+      <c r="A55" s="128"/>
+      <c r="B55" s="121" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="122" t="str">
+        <f t="shared" ref="C55" ca="1" si="16">IF(F55=E55, IF(TODAY()&gt;F55, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F55) - E55) / (F55 - E55) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
+      </c>
+      <c r="D55" s="123" t="str">
+        <f t="shared" ref="D55" si="17">IF(AND(F55&lt;&gt;"", E55&lt;&gt;""), F55 - E55 + 1 &amp; "일", "")</f>
+        <v>2일</v>
+      </c>
+      <c r="E55" s="75">
         <v>45980</v>
       </c>
-      <c r="F55" s="108">
-        <v>45998</v>
-      </c>
-      <c r="G55" s="109" t="s">
-        <v>135</v>
+      <c r="F55" s="75">
+        <v>45981</v>
+      </c>
+      <c r="G55" s="120" t="s">
+        <v>117</v>
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="60"/>
@@ -7638,25 +7706,25 @@
       <c r="BO55" s="60"/>
     </row>
     <row r="56" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="119"/>
-      <c r="B56" s="142" t="s">
-        <v>156</v>
-      </c>
-      <c r="C56" s="143" t="str">
-        <f t="shared" ref="C56" ca="1" si="20">IF(F56=E56, IF(TODAY()&gt;F56, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F56) - E56) / (F56 - E56) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
-      </c>
-      <c r="D56" s="144" t="str">
-        <f t="shared" ref="D56" si="21">IF(AND(F56&lt;&gt;"", E56&lt;&gt;""), F56 - E56 + 1 &amp; "일", "")</f>
-        <v>2일</v>
+      <c r="A56" s="128"/>
+      <c r="B56" s="117" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="118" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>50%</v>
+      </c>
+      <c r="D56" s="119" t="str">
+        <f t="shared" si="13"/>
+        <v>3일</v>
       </c>
       <c r="E56" s="75">
         <v>45980</v>
       </c>
       <c r="F56" s="75">
-        <v>45981</v>
-      </c>
-      <c r="G56" s="141" t="s">
+        <v>45982</v>
+      </c>
+      <c r="G56" s="120" t="s">
         <v>117</v>
       </c>
       <c r="H56" s="59"/>
@@ -7721,27 +7789,21 @@
       <c r="BO56" s="60"/>
     </row>
     <row r="57" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A57" s="119"/>
-      <c r="B57" s="138" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="139" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>0%</v>
-      </c>
-      <c r="D57" s="140" t="str">
-        <f t="shared" si="17"/>
-        <v>2일</v>
-      </c>
-      <c r="E57" s="75">
-        <v>45980</v>
-      </c>
-      <c r="F57" s="75">
-        <v>45981</v>
-      </c>
-      <c r="G57" s="141" t="s">
-        <v>117</v>
-      </c>
+      <c r="A57" s="128"/>
+      <c r="B57" s="94" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="32" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
+      </c>
+      <c r="D57" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="69"/>
       <c r="H57" s="59"/>
       <c r="I57" s="60"/>
       <c r="J57" s="60"/>
@@ -7803,17 +7865,17 @@
       <c r="BN57" s="60"/>
       <c r="BO57" s="60"/>
     </row>
-    <row r="58" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A58" s="119"/>
+    <row r="58" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A58" s="128"/>
       <c r="B58" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="32" t="str">
-        <f t="shared" ca="1" si="16"/>
+        <v>131</v>
+      </c>
+      <c r="C58" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
       <c r="D58" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E58" s="22"/>
@@ -7881,21 +7943,27 @@
       <c r="BO58" s="60"/>
     </row>
     <row r="59" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A59" s="119"/>
-      <c r="B59" s="94" t="s">
-        <v>131</v>
+      <c r="A59" s="128"/>
+      <c r="B59" s="95" t="s">
+        <v>149</v>
       </c>
       <c r="C59" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>100%</v>
+        <f t="shared" ref="C59" ca="1" si="18">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D59" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="69"/>
+        <f>IF(AND(F59&lt;&gt;"", E59&lt;&gt;""), F59 - E59 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E59" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F59" s="22">
+        <v>45998</v>
+      </c>
+      <c r="G59" s="68" t="s">
+        <v>117</v>
+      </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60"/>
       <c r="J59" s="60"/>
@@ -7958,21 +8026,23 @@
       <c r="BO59" s="60"/>
     </row>
     <row r="60" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A60" s="119"/>
-      <c r="B60" s="94" t="s">
-        <v>132</v>
+      <c r="A60" s="146"/>
+      <c r="B60" s="95" t="s">
+        <v>136</v>
       </c>
       <c r="C60" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
       <c r="D60" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
-      <c r="G60" s="69"/>
+      <c r="G60" s="68" t="s">
+        <v>134</v>
+      </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60"/>
       <c r="J60" s="60"/>
@@ -8032,29 +8102,27 @@
       <c r="BL60" s="60"/>
       <c r="BM60" s="60"/>
       <c r="BN60" s="60"/>
-      <c r="BO60" s="60"/>
+      <c r="BO60" s="29"/>
     </row>
-    <row r="61" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A61" s="119"/>
-      <c r="B61" s="95" t="s">
-        <v>155</v>
+    <row r="61" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A61" s="127" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="96" t="s">
+        <v>2</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f t="shared" ref="C61" ca="1" si="22">IF(F61=E61, IF(TODAY()&gt;F61, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F61) - E61) / (F61 - E61) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
       </c>
       <c r="D61" s="21" t="str">
-        <f>IF(AND(F61&lt;&gt;"", E61&lt;&gt;""), F61 - E61 + 1 &amp; "일", "")</f>
-        <v>10일</v>
-      </c>
-      <c r="E61" s="22">
-        <v>45989</v>
-      </c>
-      <c r="F61" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G61" s="68" t="s">
-        <v>117</v>
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60"/>
@@ -8118,22 +8186,22 @@
       <c r="BO61" s="60"/>
     </row>
     <row r="62" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A62" s="137"/>
-      <c r="B62" s="95" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
+      <c r="A62" s="128"/>
+      <c r="B62" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="31" t="str">
+        <f t="shared" ref="C62" ca="1" si="19">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D62" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
-      <c r="G62" s="68" t="s">
-        <v>135</v>
+      <c r="G62" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60"/>
@@ -8194,21 +8262,16 @@
       <c r="BL62" s="60"/>
       <c r="BM62" s="60"/>
       <c r="BN62" s="60"/>
-      <c r="BO62" s="29"/>
+      <c r="BO62" s="60"/>
     </row>
-    <row r="63" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A63" s="118" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" s="96" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>100%</v>
-      </c>
+    <row r="63" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A63" s="128"/>
+      <c r="B63" s="97" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="67"/>
       <c r="D63" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E63" s="22"/>
@@ -8278,22 +8341,26 @@
       <c r="BO63" s="60"/>
     </row>
     <row r="64" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A64" s="119"/>
-      <c r="B64" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="31" t="str">
-        <f t="shared" ref="C64" ca="1" si="23">IF(F64=E64, IF(TODAY()&gt;F64, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F64) - E64) / (F64 - E64) * 100, 1) &amp; "%")</f>
-        <v>100%</v>
-      </c>
-      <c r="D64" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="70" t="s">
-        <v>100</v>
+      <c r="A64" s="128"/>
+      <c r="B64" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="35" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
+      <c r="D64" s="71" t="str">
+        <f t="shared" si="13"/>
+        <v>12일</v>
+      </c>
+      <c r="E64" s="36">
+        <v>45999</v>
+      </c>
+      <c r="F64" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="H64" s="59"/>
       <c r="I64" s="60"/>
@@ -8356,20 +8423,27 @@
       <c r="BN64" s="60"/>
       <c r="BO64" s="60"/>
     </row>
-    <row r="65" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A65" s="119"/>
-      <c r="B65" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C65" s="67"/>
+    <row r="65" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A65" s="128"/>
+      <c r="B65" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="32" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
       <c r="D65" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="70" t="s">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>10일</v>
+      </c>
+      <c r="E65" s="33">
+        <v>45999</v>
+      </c>
+      <c r="F65" s="33">
+        <v>46008</v>
+      </c>
+      <c r="G65" s="34" t="s">
+        <v>98</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60"/>
@@ -8432,26 +8506,26 @@
       <c r="BN65" s="60"/>
       <c r="BO65" s="60"/>
     </row>
-    <row r="66" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A66" s="119"/>
-      <c r="B66" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" s="35" t="str">
-        <f t="shared" ca="1" si="16"/>
+    <row r="66" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A66" s="128"/>
+      <c r="B66" s="95" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
-      <c r="D66" s="71" t="str">
-        <f t="shared" si="17"/>
-        <v>12일</v>
-      </c>
-      <c r="E66" s="36">
+      <c r="D66" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>10일</v>
+      </c>
+      <c r="E66" s="22">
         <v>45999</v>
       </c>
-      <c r="F66" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G66" s="37" t="s">
+      <c r="F66" s="22">
+        <v>46008</v>
+      </c>
+      <c r="G66" s="23" t="s">
         <v>98</v>
       </c>
       <c r="H66" s="59"/>
@@ -8515,26 +8589,26 @@
       <c r="BN66" s="60"/>
       <c r="BO66" s="60"/>
     </row>
-    <row r="67" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A67" s="119"/>
-      <c r="B67" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C67" s="32" t="str">
-        <f t="shared" ca="1" si="16"/>
+    <row r="67" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A67" s="128"/>
+      <c r="B67" s="95" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
       <c r="D67" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v>10일</v>
-      </c>
-      <c r="E67" s="33">
-        <v>45999</v>
-      </c>
-      <c r="F67" s="33">
-        <v>46008</v>
-      </c>
-      <c r="G67" s="34" t="s">
+        <f t="shared" si="13"/>
+        <v>1일</v>
+      </c>
+      <c r="E67" s="22">
+        <v>46010</v>
+      </c>
+      <c r="F67" s="22">
+        <v>46010</v>
+      </c>
+      <c r="G67" s="23" t="s">
         <v>98</v>
       </c>
       <c r="H67" s="59"/>
@@ -8598,24 +8672,24 @@
       <c r="BN67" s="60"/>
       <c r="BO67" s="60"/>
     </row>
-    <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A68" s="119"/>
+    <row r="68" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A68" s="129"/>
       <c r="B68" s="95" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C68" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
       <c r="D68" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v>10일</v>
+        <f t="shared" si="13"/>
+        <v>1일</v>
       </c>
       <c r="E68" s="22">
-        <v>45999</v>
+        <v>46010</v>
       </c>
       <c r="F68" s="22">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="G68" s="23" t="s">
         <v>98</v>
@@ -8681,175 +8755,15 @@
       <c r="BN68" s="60"/>
       <c r="BO68" s="60"/>
     </row>
-    <row r="69" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A69" s="119"/>
-      <c r="B69" s="95" t="s">
-        <v>92</v>
-      </c>
-      <c r="C69" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>0%</v>
-      </c>
-      <c r="D69" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v>1일</v>
-      </c>
-      <c r="E69" s="22">
-        <v>46010</v>
-      </c>
-      <c r="F69" s="22">
-        <v>46010</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="H69" s="59"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="60"/>
-      <c r="K69" s="60"/>
-      <c r="L69" s="61"/>
-      <c r="M69" s="62"/>
-      <c r="N69" s="60"/>
-      <c r="O69" s="60"/>
-      <c r="P69" s="60"/>
-      <c r="Q69" s="60"/>
-      <c r="R69" s="60"/>
-      <c r="S69" s="61"/>
-      <c r="T69" s="62"/>
-      <c r="U69" s="60"/>
-      <c r="V69" s="60"/>
-      <c r="W69" s="60"/>
-      <c r="X69" s="60"/>
-      <c r="Y69" s="60"/>
-      <c r="Z69" s="61"/>
-      <c r="AA69" s="62"/>
-      <c r="AB69" s="60"/>
-      <c r="AC69" s="60"/>
-      <c r="AD69" s="60"/>
-      <c r="AE69" s="60"/>
-      <c r="AF69" s="60"/>
-      <c r="AG69" s="61"/>
-      <c r="AH69" s="62"/>
-      <c r="AI69" s="60"/>
-      <c r="AJ69" s="60"/>
-      <c r="AK69" s="60"/>
-      <c r="AL69" s="60"/>
-      <c r="AM69" s="60"/>
-      <c r="AN69" s="61"/>
-      <c r="AO69" s="62"/>
-      <c r="AP69" s="60"/>
-      <c r="AQ69" s="60"/>
-      <c r="AR69" s="60"/>
-      <c r="AS69" s="60"/>
-      <c r="AT69" s="60"/>
-      <c r="AU69" s="61"/>
-      <c r="AV69" s="62"/>
-      <c r="AW69" s="60"/>
-      <c r="AX69" s="60"/>
-      <c r="AY69" s="60"/>
-      <c r="AZ69" s="60"/>
-      <c r="BA69" s="60"/>
-      <c r="BB69" s="61"/>
-      <c r="BC69" s="62"/>
-      <c r="BD69" s="60"/>
-      <c r="BE69" s="60"/>
-      <c r="BF69" s="60"/>
-      <c r="BG69" s="60"/>
-      <c r="BH69" s="60"/>
-      <c r="BI69" s="61"/>
-      <c r="BJ69" s="62"/>
-      <c r="BK69" s="60"/>
-      <c r="BL69" s="60"/>
-      <c r="BM69" s="60"/>
-      <c r="BN69" s="60"/>
-      <c r="BO69" s="60"/>
+    <row r="69" spans="1:67">
+      <c r="E69" s="7"/>
+      <c r="F69" s="1"/>
+      <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A70" s="120"/>
-      <c r="B70" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" s="20" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v>0%</v>
-      </c>
-      <c r="D70" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v>1일</v>
-      </c>
-      <c r="E70" s="22">
-        <v>46010</v>
-      </c>
-      <c r="F70" s="22">
-        <v>46010</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="H70" s="59"/>
-      <c r="I70" s="60"/>
-      <c r="J70" s="60"/>
-      <c r="K70" s="60"/>
-      <c r="L70" s="61"/>
-      <c r="M70" s="62"/>
-      <c r="N70" s="60"/>
-      <c r="O70" s="60"/>
-      <c r="P70" s="60"/>
-      <c r="Q70" s="60"/>
-      <c r="R70" s="60"/>
-      <c r="S70" s="61"/>
-      <c r="T70" s="62"/>
-      <c r="U70" s="60"/>
-      <c r="V70" s="60"/>
-      <c r="W70" s="60"/>
-      <c r="X70" s="60"/>
-      <c r="Y70" s="60"/>
-      <c r="Z70" s="61"/>
-      <c r="AA70" s="62"/>
-      <c r="AB70" s="60"/>
-      <c r="AC70" s="60"/>
-      <c r="AD70" s="60"/>
-      <c r="AE70" s="60"/>
-      <c r="AF70" s="60"/>
-      <c r="AG70" s="61"/>
-      <c r="AH70" s="62"/>
-      <c r="AI70" s="60"/>
-      <c r="AJ70" s="60"/>
-      <c r="AK70" s="60"/>
-      <c r="AL70" s="60"/>
-      <c r="AM70" s="60"/>
-      <c r="AN70" s="61"/>
-      <c r="AO70" s="62"/>
-      <c r="AP70" s="60"/>
-      <c r="AQ70" s="60"/>
-      <c r="AR70" s="60"/>
-      <c r="AS70" s="60"/>
-      <c r="AT70" s="60"/>
-      <c r="AU70" s="61"/>
-      <c r="AV70" s="62"/>
-      <c r="AW70" s="60"/>
-      <c r="AX70" s="60"/>
-      <c r="AY70" s="60"/>
-      <c r="AZ70" s="60"/>
-      <c r="BA70" s="60"/>
-      <c r="BB70" s="61"/>
-      <c r="BC70" s="62"/>
-      <c r="BD70" s="60"/>
-      <c r="BE70" s="60"/>
-      <c r="BF70" s="60"/>
-      <c r="BG70" s="60"/>
-      <c r="BH70" s="60"/>
-      <c r="BI70" s="61"/>
-      <c r="BJ70" s="62"/>
-      <c r="BK70" s="60"/>
-      <c r="BL70" s="60"/>
-      <c r="BM70" s="60"/>
-      <c r="BN70" s="60"/>
-      <c r="BO70" s="60"/>
+    <row r="70" spans="1:67">
+      <c r="I70" s="3"/>
     </row>
     <row r="71" spans="1:67">
-      <c r="E71" s="7"/>
-      <c r="F71" s="1"/>
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:67">
@@ -8859,85 +8773,79 @@
       <c r="I73" s="3"/>
     </row>
     <row r="74" spans="1:67">
-      <c r="I74" s="3"/>
+      <c r="B74" s="8" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="75" spans="1:67">
-      <c r="I75" s="3"/>
+    <row r="75" spans="1:67" ht="16.5">
+      <c r="B75" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" spans="1:67">
-      <c r="B76" s="8" t="s">
-        <v>94</v>
+      <c r="B76" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:67" ht="16.5">
-      <c r="B77" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="3"/>
+    <row r="77" spans="1:67">
+      <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:67">
-      <c r="B78" s="10" t="s">
-        <v>96</v>
-      </c>
+      <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="1:67">
-      <c r="C79" s="3"/>
+    <row r="79" spans="1:67"/>
+    <row r="80" spans="1:67"/>
+    <row r="81" spans="2:8" ht="16.5">
+      <c r="B81" s="2"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
     </row>
-    <row r="80" spans="1:67">
-      <c r="C80" s="3"/>
+    <row r="82" spans="2:8">
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
     </row>
-    <row r="81" spans="2:8"/>
-    <row r="82" spans="2:8"/>
     <row r="83" spans="2:8" ht="16.5">
       <c r="B83" s="2"/>
-      <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
     <row r="84" spans="2:8">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="2:8" ht="16.5">
-      <c r="B85" s="2"/>
+    <row r="85" spans="2:8">
+      <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
     <row r="86" spans="2:8">
-      <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="2:8">
-      <c r="C87" s="3"/>
       <c r="D87" s="3"/>
+      <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="D88" s="3"/>
     </row>
-    <row r="89" spans="2:8">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
+      <c r="C89" s="3"/>
       <c r="D89" s="3"/>
-      <c r="H89" s="11"/>
-    </row>
-    <row r="90" spans="2:8" ht="15" customHeight="1">
-      <c r="D90" s="3"/>
-    </row>
-    <row r="91" spans="2:8" ht="15" customHeight="1">
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="H51:BO51"/>
-    <mergeCell ref="H39:BO39"/>
+    <mergeCell ref="A61:A68"/>
+    <mergeCell ref="H49:BO49"/>
+    <mergeCell ref="H41:BO41"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:W1"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B49:G49"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A62"/>
+    <mergeCell ref="A12:A60"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
   </mergeCells>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D88C988-5A55-4DA9-AA79-A643A42263FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC8A8D1-A363-4BA5-AD96-68C412FF5609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="555" windowWidth="21315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="157">
   <si>
     <t>팀명</t>
   </si>
@@ -1330,6 +1330,10 @@
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <t>전체 페이지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1338,7 +1342,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1619,27 +1623,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FF00B0F0"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color theme="7"/>
       <name val="Arial"/>
       <family val="3"/>
@@ -1769,7 +1752,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -2232,32 +2215,6 @@
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2288,20 +2245,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2627,34 +2575,28 @@
     <xf numFmtId="0" fontId="22" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="37" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="37" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2663,31 +2605,25 @@
     <xf numFmtId="0" fontId="38" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2720,9 +2656,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2735,11 +2668,14 @@
     <xf numFmtId="0" fontId="20" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2965,7 +2901,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO89"/>
+  <dimension ref="A1:BO90"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -2980,31 +2916,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="133" t="s">
+      <c r="C1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="135" t="s">
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="130"/>
+      <c r="U1" s="130"/>
+      <c r="V1" s="130"/>
+      <c r="W1" s="130"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3068,7 +3004,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="136" t="s">
+      <c r="G2" s="132" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3259,7 +3195,7 @@
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="137"/>
+      <c r="G3" s="133"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3442,7 +3378,7 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="134" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="77" t="s">
@@ -3527,7 +3463,7 @@
       <c r="BO4" s="55"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="139"/>
+      <c r="A5" s="135"/>
       <c r="B5" s="77" t="s">
         <v>73</v>
       </c>
@@ -3610,7 +3546,7 @@
       <c r="BO5" s="60"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="139"/>
+      <c r="A6" s="135"/>
       <c r="B6" s="77" t="s">
         <v>74</v>
       </c>
@@ -3693,7 +3629,7 @@
       <c r="BO6" s="60"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="139"/>
+      <c r="A7" s="135"/>
       <c r="B7" s="78" t="s">
         <v>75</v>
       </c>
@@ -3776,7 +3712,7 @@
       <c r="BO7" s="60"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="139"/>
+      <c r="A8" s="135"/>
       <c r="B8" s="79" t="s">
         <v>76</v>
       </c>
@@ -3859,7 +3795,7 @@
       <c r="BO8" s="60"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="139"/>
+      <c r="A9" s="135"/>
       <c r="B9" s="77" t="s">
         <v>77</v>
       </c>
@@ -3942,7 +3878,7 @@
       <c r="BO9" s="60"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="139"/>
+      <c r="A10" s="135"/>
       <c r="B10" s="78" t="s">
         <v>78</v>
       </c>
@@ -4025,7 +3961,7 @@
       <c r="BO10" s="60"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="140"/>
+      <c r="A11" s="135"/>
       <c r="B11" s="80" t="s">
         <v>79</v>
       </c>
@@ -4108,7 +4044,7 @@
       <c r="BO11" s="60"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="140" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="81" t="s">
@@ -4193,7 +4129,7 @@
       <c r="BO12" s="60"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="128"/>
+      <c r="A13" s="124"/>
       <c r="B13" s="82" t="s">
         <v>82</v>
       </c>
@@ -4276,7 +4212,7 @@
       <c r="BO13" s="60"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="128"/>
+      <c r="A14" s="124"/>
       <c r="B14" s="83" t="s">
         <v>83</v>
       </c>
@@ -4359,7 +4295,7 @@
       <c r="BO14" s="60"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="128"/>
+      <c r="A15" s="124"/>
       <c r="B15" s="81" t="s">
         <v>84</v>
       </c>
@@ -4442,7 +4378,7 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="128"/>
+      <c r="A16" s="124"/>
       <c r="B16" s="84" t="s">
         <v>123</v>
       </c>
@@ -4525,78 +4461,78 @@
       <c r="BO16" s="53"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="128"/>
-      <c r="B17" s="143" t="s">
+      <c r="A17" s="124"/>
+      <c r="B17" s="138" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="131"/>
-      <c r="S17" s="131"/>
-      <c r="T17" s="131"/>
-      <c r="U17" s="131"/>
-      <c r="V17" s="131"/>
-      <c r="W17" s="131"/>
-      <c r="X17" s="131"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="131"/>
-      <c r="AA17" s="131"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="131"/>
-      <c r="AD17" s="131"/>
-      <c r="AE17" s="131"/>
-      <c r="AF17" s="131"/>
-      <c r="AG17" s="131"/>
-      <c r="AH17" s="131"/>
-      <c r="AI17" s="131"/>
-      <c r="AJ17" s="131"/>
-      <c r="AK17" s="131"/>
-      <c r="AL17" s="131"/>
-      <c r="AM17" s="131"/>
-      <c r="AN17" s="131"/>
-      <c r="AO17" s="131"/>
-      <c r="AP17" s="131"/>
-      <c r="AQ17" s="131"/>
-      <c r="AR17" s="131"/>
-      <c r="AS17" s="131"/>
-      <c r="AT17" s="131"/>
-      <c r="AU17" s="131"/>
-      <c r="AV17" s="131"/>
-      <c r="AW17" s="131"/>
-      <c r="AX17" s="131"/>
-      <c r="AY17" s="131"/>
-      <c r="AZ17" s="131"/>
-      <c r="BA17" s="131"/>
-      <c r="BB17" s="131"/>
-      <c r="BC17" s="131"/>
-      <c r="BD17" s="131"/>
-      <c r="BE17" s="131"/>
-      <c r="BF17" s="131"/>
-      <c r="BG17" s="131"/>
-      <c r="BH17" s="131"/>
-      <c r="BI17" s="131"/>
-      <c r="BJ17" s="131"/>
-      <c r="BK17" s="131"/>
-      <c r="BL17" s="131"/>
-      <c r="BM17" s="131"/>
-      <c r="BN17" s="131"/>
-      <c r="BO17" s="132"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="127"/>
+      <c r="U17" s="127"/>
+      <c r="V17" s="127"/>
+      <c r="W17" s="127"/>
+      <c r="X17" s="127"/>
+      <c r="Y17" s="127"/>
+      <c r="Z17" s="127"/>
+      <c r="AA17" s="127"/>
+      <c r="AB17" s="127"/>
+      <c r="AC17" s="127"/>
+      <c r="AD17" s="127"/>
+      <c r="AE17" s="127"/>
+      <c r="AF17" s="127"/>
+      <c r="AG17" s="127"/>
+      <c r="AH17" s="127"/>
+      <c r="AI17" s="127"/>
+      <c r="AJ17" s="127"/>
+      <c r="AK17" s="127"/>
+      <c r="AL17" s="127"/>
+      <c r="AM17" s="127"/>
+      <c r="AN17" s="127"/>
+      <c r="AO17" s="127"/>
+      <c r="AP17" s="127"/>
+      <c r="AQ17" s="127"/>
+      <c r="AR17" s="127"/>
+      <c r="AS17" s="127"/>
+      <c r="AT17" s="127"/>
+      <c r="AU17" s="127"/>
+      <c r="AV17" s="127"/>
+      <c r="AW17" s="127"/>
+      <c r="AX17" s="127"/>
+      <c r="AY17" s="127"/>
+      <c r="AZ17" s="127"/>
+      <c r="BA17" s="127"/>
+      <c r="BB17" s="127"/>
+      <c r="BC17" s="127"/>
+      <c r="BD17" s="127"/>
+      <c r="BE17" s="127"/>
+      <c r="BF17" s="127"/>
+      <c r="BG17" s="127"/>
+      <c r="BH17" s="127"/>
+      <c r="BI17" s="127"/>
+      <c r="BJ17" s="127"/>
+      <c r="BK17" s="127"/>
+      <c r="BL17" s="127"/>
+      <c r="BM17" s="127"/>
+      <c r="BN17" s="127"/>
+      <c r="BO17" s="128"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="128"/>
+      <c r="A18" s="124"/>
       <c r="B18" s="85" t="s">
         <v>124</v>
       </c>
@@ -4679,7 +4615,7 @@
       <c r="BO18" s="55"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="128"/>
+      <c r="A19" s="124"/>
       <c r="B19" s="86" t="s">
         <v>87</v>
       </c>
@@ -4762,7 +4698,7 @@
       <c r="BO19" s="60"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="128"/>
+      <c r="A20" s="124"/>
       <c r="B20" s="87" t="s">
         <v>113</v>
       </c>
@@ -4845,78 +4781,78 @@
       <c r="BO20" s="60"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="128"/>
-      <c r="B21" s="141" t="s">
+      <c r="A21" s="124"/>
+      <c r="B21" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="131"/>
-      <c r="T21" s="131"/>
-      <c r="U21" s="131"/>
-      <c r="V21" s="131"/>
-      <c r="W21" s="131"/>
-      <c r="X21" s="131"/>
-      <c r="Y21" s="131"/>
-      <c r="Z21" s="131"/>
-      <c r="AA21" s="131"/>
-      <c r="AB21" s="131"/>
-      <c r="AC21" s="131"/>
-      <c r="AD21" s="131"/>
-      <c r="AE21" s="131"/>
-      <c r="AF21" s="131"/>
-      <c r="AG21" s="131"/>
-      <c r="AH21" s="131"/>
-      <c r="AI21" s="131"/>
-      <c r="AJ21" s="131"/>
-      <c r="AK21" s="131"/>
-      <c r="AL21" s="131"/>
-      <c r="AM21" s="131"/>
-      <c r="AN21" s="131"/>
-      <c r="AO21" s="131"/>
-      <c r="AP21" s="131"/>
-      <c r="AQ21" s="131"/>
-      <c r="AR21" s="131"/>
-      <c r="AS21" s="131"/>
-      <c r="AT21" s="131"/>
-      <c r="AU21" s="131"/>
-      <c r="AV21" s="131"/>
-      <c r="AW21" s="131"/>
-      <c r="AX21" s="131"/>
-      <c r="AY21" s="131"/>
-      <c r="AZ21" s="131"/>
-      <c r="BA21" s="131"/>
-      <c r="BB21" s="131"/>
-      <c r="BC21" s="131"/>
-      <c r="BD21" s="131"/>
-      <c r="BE21" s="131"/>
-      <c r="BF21" s="131"/>
-      <c r="BG21" s="131"/>
-      <c r="BH21" s="131"/>
-      <c r="BI21" s="131"/>
-      <c r="BJ21" s="131"/>
-      <c r="BK21" s="131"/>
-      <c r="BL21" s="131"/>
-      <c r="BM21" s="131"/>
-      <c r="BN21" s="131"/>
-      <c r="BO21" s="132"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="127"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="127"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="127"/>
+      <c r="U21" s="127"/>
+      <c r="V21" s="127"/>
+      <c r="W21" s="127"/>
+      <c r="X21" s="127"/>
+      <c r="Y21" s="127"/>
+      <c r="Z21" s="127"/>
+      <c r="AA21" s="127"/>
+      <c r="AB21" s="127"/>
+      <c r="AC21" s="127"/>
+      <c r="AD21" s="127"/>
+      <c r="AE21" s="127"/>
+      <c r="AF21" s="127"/>
+      <c r="AG21" s="127"/>
+      <c r="AH21" s="127"/>
+      <c r="AI21" s="127"/>
+      <c r="AJ21" s="127"/>
+      <c r="AK21" s="127"/>
+      <c r="AL21" s="127"/>
+      <c r="AM21" s="127"/>
+      <c r="AN21" s="127"/>
+      <c r="AO21" s="127"/>
+      <c r="AP21" s="127"/>
+      <c r="AQ21" s="127"/>
+      <c r="AR21" s="127"/>
+      <c r="AS21" s="127"/>
+      <c r="AT21" s="127"/>
+      <c r="AU21" s="127"/>
+      <c r="AV21" s="127"/>
+      <c r="AW21" s="127"/>
+      <c r="AX21" s="127"/>
+      <c r="AY21" s="127"/>
+      <c r="AZ21" s="127"/>
+      <c r="BA21" s="127"/>
+      <c r="BB21" s="127"/>
+      <c r="BC21" s="127"/>
+      <c r="BD21" s="127"/>
+      <c r="BE21" s="127"/>
+      <c r="BF21" s="127"/>
+      <c r="BG21" s="127"/>
+      <c r="BH21" s="127"/>
+      <c r="BI21" s="127"/>
+      <c r="BJ21" s="127"/>
+      <c r="BK21" s="127"/>
+      <c r="BL21" s="127"/>
+      <c r="BM21" s="127"/>
+      <c r="BN21" s="127"/>
+      <c r="BO21" s="128"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="128"/>
+      <c r="A22" s="124"/>
       <c r="B22" s="88" t="s">
         <v>125</v>
       </c>
@@ -4999,7 +4935,7 @@
       <c r="BO22" s="60"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="89" t="s">
         <v>85</v>
       </c>
@@ -5082,7 +5018,7 @@
       <c r="BO23" s="60"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="128"/>
+      <c r="A24" s="124"/>
       <c r="B24" s="90" t="s">
         <v>145</v>
       </c>
@@ -5165,7 +5101,7 @@
       <c r="BO24" s="60"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="128"/>
+      <c r="A25" s="124"/>
       <c r="B25" s="90" t="s">
         <v>143</v>
       </c>
@@ -5248,7 +5184,7 @@
       <c r="BO25" s="60"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="128"/>
+      <c r="A26" s="124"/>
       <c r="B26" s="85" t="s">
         <v>153</v>
       </c>
@@ -5331,13 +5267,13 @@
       <c r="BO26" s="60"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="128"/>
+      <c r="A27" s="124"/>
       <c r="B27" s="91" t="s">
         <v>137</v>
       </c>
       <c r="C27" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D27" s="21" t="str">
         <f t="shared" si="5"/>
@@ -5414,7 +5350,7 @@
       <c r="BO27" s="60"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="128"/>
+      <c r="A28" s="124"/>
       <c r="B28" s="92" t="s">
         <v>148</v>
       </c>
@@ -5497,13 +5433,13 @@
       <c r="BO28" s="60"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="128"/>
+      <c r="A29" s="124"/>
       <c r="B29" s="92" t="s">
         <v>138</v>
       </c>
       <c r="C29" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>50%</v>
+        <v>100%</v>
       </c>
       <c r="D29" s="21" t="str">
         <f t="shared" si="5"/>
@@ -5578,13 +5514,13 @@
       <c r="BO29" s="60"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="128"/>
-      <c r="B30" s="124" t="s">
+      <c r="A30" s="124"/>
+      <c r="B30" s="119" t="s">
         <v>146</v>
       </c>
       <c r="C30" s="39" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>50%</v>
+        <v>100%</v>
       </c>
       <c r="D30" s="40" t="str">
         <f t="shared" si="5"/>
@@ -5661,7 +5597,7 @@
       <c r="BO30" s="60"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="128"/>
+      <c r="A31" s="124"/>
       <c r="B31" s="93" t="s">
         <v>104</v>
       </c>
@@ -5744,7 +5680,7 @@
       <c r="BO31" s="28"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="128"/>
+      <c r="A32" s="124"/>
       <c r="B32" s="87" t="s">
         <v>111</v>
       </c>
@@ -5827,7 +5763,7 @@
       <c r="BO32" s="60"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="128"/>
+      <c r="A33" s="124"/>
       <c r="B33" s="88" t="s">
         <v>126</v>
       </c>
@@ -5910,7 +5846,7 @@
       <c r="BO33" s="60"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="128"/>
+      <c r="A34" s="124"/>
       <c r="B34" s="87" t="s">
         <v>112</v>
       </c>
@@ -5993,7 +5929,7 @@
       <c r="BO34" s="60"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="128"/>
+      <c r="A35" s="124"/>
       <c r="B35" s="100" t="s">
         <v>140</v>
       </c>
@@ -6076,7 +6012,7 @@
       <c r="BO35" s="60"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="128"/>
+      <c r="A36" s="124"/>
       <c r="B36" s="100" t="s">
         <v>142</v>
       </c>
@@ -6159,8 +6095,8 @@
       <c r="BO36" s="60"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="128"/>
-      <c r="B37" s="116" t="s">
+      <c r="A37" s="124"/>
+      <c r="B37" s="114" t="s">
         <v>121</v>
       </c>
       <c r="C37" s="39" t="str">
@@ -6242,7 +6178,7 @@
       <c r="BO37" s="60"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="128"/>
+      <c r="A38" s="124"/>
       <c r="B38" s="72" t="s">
         <v>122</v>
       </c>
@@ -6325,7 +6261,7 @@
       <c r="BO38" s="60"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="128"/>
+      <c r="A39" s="124"/>
       <c r="B39" s="72" t="s">
         <v>132</v>
       </c>
@@ -6408,7 +6344,7 @@
       <c r="BO39" s="60"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="128"/>
+      <c r="A40" s="124"/>
       <c r="B40" s="88" t="s">
         <v>139</v>
       </c>
@@ -6491,78 +6427,78 @@
       <c r="BO40" s="60"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="128"/>
-      <c r="B41" s="142" t="s">
+      <c r="A41" s="124"/>
+      <c r="B41" s="137" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="142"/>
-      <c r="D41" s="142"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="130"/>
-      <c r="I41" s="131"/>
-      <c r="J41" s="131"/>
-      <c r="K41" s="131"/>
-      <c r="L41" s="131"/>
-      <c r="M41" s="131"/>
-      <c r="N41" s="131"/>
-      <c r="O41" s="131"/>
-      <c r="P41" s="131"/>
-      <c r="Q41" s="131"/>
-      <c r="R41" s="131"/>
-      <c r="S41" s="131"/>
-      <c r="T41" s="131"/>
-      <c r="U41" s="131"/>
-      <c r="V41" s="131"/>
-      <c r="W41" s="131"/>
-      <c r="X41" s="131"/>
-      <c r="Y41" s="131"/>
-      <c r="Z41" s="131"/>
-      <c r="AA41" s="131"/>
-      <c r="AB41" s="131"/>
-      <c r="AC41" s="131"/>
-      <c r="AD41" s="131"/>
-      <c r="AE41" s="131"/>
-      <c r="AF41" s="131"/>
-      <c r="AG41" s="131"/>
-      <c r="AH41" s="131"/>
-      <c r="AI41" s="131"/>
-      <c r="AJ41" s="131"/>
-      <c r="AK41" s="131"/>
-      <c r="AL41" s="131"/>
-      <c r="AM41" s="131"/>
-      <c r="AN41" s="131"/>
-      <c r="AO41" s="131"/>
-      <c r="AP41" s="131"/>
-      <c r="AQ41" s="131"/>
-      <c r="AR41" s="131"/>
-      <c r="AS41" s="131"/>
-      <c r="AT41" s="131"/>
-      <c r="AU41" s="131"/>
-      <c r="AV41" s="131"/>
-      <c r="AW41" s="131"/>
-      <c r="AX41" s="131"/>
-      <c r="AY41" s="131"/>
-      <c r="AZ41" s="131"/>
-      <c r="BA41" s="131"/>
-      <c r="BB41" s="131"/>
-      <c r="BC41" s="131"/>
-      <c r="BD41" s="131"/>
-      <c r="BE41" s="131"/>
-      <c r="BF41" s="131"/>
-      <c r="BG41" s="131"/>
-      <c r="BH41" s="131"/>
-      <c r="BI41" s="131"/>
-      <c r="BJ41" s="131"/>
-      <c r="BK41" s="131"/>
-      <c r="BL41" s="131"/>
-      <c r="BM41" s="131"/>
-      <c r="BN41" s="131"/>
-      <c r="BO41" s="132"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="137"/>
+      <c r="G41" s="137"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="127"/>
+      <c r="P41" s="127"/>
+      <c r="Q41" s="127"/>
+      <c r="R41" s="127"/>
+      <c r="S41" s="127"/>
+      <c r="T41" s="127"/>
+      <c r="U41" s="127"/>
+      <c r="V41" s="127"/>
+      <c r="W41" s="127"/>
+      <c r="X41" s="127"/>
+      <c r="Y41" s="127"/>
+      <c r="Z41" s="127"/>
+      <c r="AA41" s="127"/>
+      <c r="AB41" s="127"/>
+      <c r="AC41" s="127"/>
+      <c r="AD41" s="127"/>
+      <c r="AE41" s="127"/>
+      <c r="AF41" s="127"/>
+      <c r="AG41" s="127"/>
+      <c r="AH41" s="127"/>
+      <c r="AI41" s="127"/>
+      <c r="AJ41" s="127"/>
+      <c r="AK41" s="127"/>
+      <c r="AL41" s="127"/>
+      <c r="AM41" s="127"/>
+      <c r="AN41" s="127"/>
+      <c r="AO41" s="127"/>
+      <c r="AP41" s="127"/>
+      <c r="AQ41" s="127"/>
+      <c r="AR41" s="127"/>
+      <c r="AS41" s="127"/>
+      <c r="AT41" s="127"/>
+      <c r="AU41" s="127"/>
+      <c r="AV41" s="127"/>
+      <c r="AW41" s="127"/>
+      <c r="AX41" s="127"/>
+      <c r="AY41" s="127"/>
+      <c r="AZ41" s="127"/>
+      <c r="BA41" s="127"/>
+      <c r="BB41" s="127"/>
+      <c r="BC41" s="127"/>
+      <c r="BD41" s="127"/>
+      <c r="BE41" s="127"/>
+      <c r="BF41" s="127"/>
+      <c r="BG41" s="127"/>
+      <c r="BH41" s="127"/>
+      <c r="BI41" s="127"/>
+      <c r="BJ41" s="127"/>
+      <c r="BK41" s="127"/>
+      <c r="BL41" s="127"/>
+      <c r="BM41" s="127"/>
+      <c r="BN41" s="127"/>
+      <c r="BO41" s="128"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="128"/>
+      <c r="A42" s="124"/>
       <c r="B42" s="87" t="s">
         <v>110</v>
       </c>
@@ -6645,7 +6581,7 @@
       <c r="BO42" s="60"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="128"/>
+      <c r="A43" s="124"/>
       <c r="B43" s="88" t="s">
         <v>127</v>
       </c>
@@ -6728,7 +6664,7 @@
       <c r="BO43" s="60"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="128"/>
+      <c r="A44" s="124"/>
       <c r="B44" s="88" t="s">
         <v>133</v>
       </c>
@@ -6811,7 +6747,7 @@
       <c r="BO44" s="60"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="128"/>
+      <c r="A45" s="124"/>
       <c r="B45" s="93" t="s">
         <v>135</v>
       </c>
@@ -6894,13 +6830,13 @@
       <c r="BO45" s="60"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="128"/>
-      <c r="B46" s="125" t="s">
+      <c r="A46" s="124"/>
+      <c r="B46" s="120" t="s">
         <v>152</v>
       </c>
       <c r="C46" s="73" t="str">
         <f ca="1">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
-        <v>50%</v>
+        <v>100%</v>
       </c>
       <c r="D46" s="74" t="str">
         <f t="shared" si="10"/>
@@ -6977,13 +6913,13 @@
       <c r="BO46" s="60"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="128"/>
+      <c r="A47" s="124"/>
       <c r="B47" s="85" t="s">
         <v>155</v>
       </c>
       <c r="C47" s="39" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="D47" s="40" t="str">
         <f t="shared" si="10"/>
@@ -7060,7 +6996,7 @@
       <c r="BO47" s="60"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="128"/>
+      <c r="A48" s="124"/>
       <c r="B48" s="92" t="s">
         <v>144</v>
       </c>
@@ -7136,88 +7072,88 @@
       <c r="BN48" s="60"/>
       <c r="BO48" s="29"/>
     </row>
-    <row r="49" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A49" s="128"/>
-      <c r="B49" s="142" t="s">
+    <row r="49" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A49" s="124"/>
+      <c r="B49" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="142"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="142"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="130"/>
-      <c r="I49" s="131"/>
-      <c r="J49" s="131"/>
-      <c r="K49" s="131"/>
-      <c r="L49" s="131"/>
-      <c r="M49" s="131"/>
-      <c r="N49" s="131"/>
-      <c r="O49" s="131"/>
-      <c r="P49" s="131"/>
-      <c r="Q49" s="131"/>
-      <c r="R49" s="131"/>
-      <c r="S49" s="131"/>
-      <c r="T49" s="131"/>
-      <c r="U49" s="131"/>
-      <c r="V49" s="131"/>
-      <c r="W49" s="131"/>
-      <c r="X49" s="131"/>
-      <c r="Y49" s="131"/>
-      <c r="Z49" s="131"/>
-      <c r="AA49" s="131"/>
-      <c r="AB49" s="131"/>
-      <c r="AC49" s="131"/>
-      <c r="AD49" s="131"/>
-      <c r="AE49" s="131"/>
-      <c r="AF49" s="131"/>
-      <c r="AG49" s="131"/>
-      <c r="AH49" s="131"/>
-      <c r="AI49" s="131"/>
-      <c r="AJ49" s="131"/>
-      <c r="AK49" s="131"/>
-      <c r="AL49" s="131"/>
-      <c r="AM49" s="131"/>
-      <c r="AN49" s="131"/>
-      <c r="AO49" s="131"/>
-      <c r="AP49" s="131"/>
-      <c r="AQ49" s="131"/>
-      <c r="AR49" s="131"/>
-      <c r="AS49" s="131"/>
-      <c r="AT49" s="131"/>
-      <c r="AU49" s="131"/>
-      <c r="AV49" s="131"/>
-      <c r="AW49" s="131"/>
-      <c r="AX49" s="131"/>
-      <c r="AY49" s="131"/>
-      <c r="AZ49" s="131"/>
-      <c r="BA49" s="131"/>
-      <c r="BB49" s="131"/>
-      <c r="BC49" s="131"/>
-      <c r="BD49" s="131"/>
-      <c r="BE49" s="131"/>
-      <c r="BF49" s="131"/>
-      <c r="BG49" s="131"/>
-      <c r="BH49" s="131"/>
-      <c r="BI49" s="131"/>
-      <c r="BJ49" s="131"/>
-      <c r="BK49" s="131"/>
-      <c r="BL49" s="131"/>
-      <c r="BM49" s="131"/>
-      <c r="BN49" s="131"/>
-      <c r="BO49" s="132"/>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="127"/>
+      <c r="J49" s="127"/>
+      <c r="K49" s="127"/>
+      <c r="L49" s="127"/>
+      <c r="M49" s="127"/>
+      <c r="N49" s="127"/>
+      <c r="O49" s="127"/>
+      <c r="P49" s="127"/>
+      <c r="Q49" s="127"/>
+      <c r="R49" s="127"/>
+      <c r="S49" s="127"/>
+      <c r="T49" s="127"/>
+      <c r="U49" s="127"/>
+      <c r="V49" s="127"/>
+      <c r="W49" s="127"/>
+      <c r="X49" s="127"/>
+      <c r="Y49" s="127"/>
+      <c r="Z49" s="127"/>
+      <c r="AA49" s="127"/>
+      <c r="AB49" s="127"/>
+      <c r="AC49" s="127"/>
+      <c r="AD49" s="127"/>
+      <c r="AE49" s="127"/>
+      <c r="AF49" s="127"/>
+      <c r="AG49" s="127"/>
+      <c r="AH49" s="127"/>
+      <c r="AI49" s="127"/>
+      <c r="AJ49" s="127"/>
+      <c r="AK49" s="127"/>
+      <c r="AL49" s="127"/>
+      <c r="AM49" s="127"/>
+      <c r="AN49" s="127"/>
+      <c r="AO49" s="127"/>
+      <c r="AP49" s="127"/>
+      <c r="AQ49" s="127"/>
+      <c r="AR49" s="127"/>
+      <c r="AS49" s="127"/>
+      <c r="AT49" s="127"/>
+      <c r="AU49" s="127"/>
+      <c r="AV49" s="127"/>
+      <c r="AW49" s="127"/>
+      <c r="AX49" s="127"/>
+      <c r="AY49" s="127"/>
+      <c r="AZ49" s="127"/>
+      <c r="BA49" s="127"/>
+      <c r="BB49" s="127"/>
+      <c r="BC49" s="127"/>
+      <c r="BD49" s="127"/>
+      <c r="BE49" s="127"/>
+      <c r="BF49" s="127"/>
+      <c r="BG49" s="127"/>
+      <c r="BH49" s="127"/>
+      <c r="BI49" s="127"/>
+      <c r="BJ49" s="127"/>
+      <c r="BK49" s="127"/>
+      <c r="BL49" s="127"/>
+      <c r="BM49" s="127"/>
+      <c r="BN49" s="127"/>
+      <c r="BO49" s="128"/>
     </row>
-    <row r="50" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A50" s="128"/>
+    <row r="50" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A50" s="124"/>
       <c r="B50" s="101" t="s">
         <v>128</v>
       </c>
       <c r="C50" s="44" t="str">
-        <f t="shared" ref="C50:C68" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C50:C69" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D50" s="104" t="str">
-        <f t="shared" ref="D50:D68" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D50:D69" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
         <v>7일</v>
       </c>
       <c r="E50" s="45">
@@ -7290,26 +7226,26 @@
       <c r="BN50" s="60"/>
       <c r="BO50" s="60"/>
     </row>
-    <row r="51" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A51" s="145"/>
-      <c r="B51" s="126" t="s">
+    <row r="51" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A51" s="124"/>
+      <c r="B51" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="111" t="str">
+      <c r="C51" s="109" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D51" s="112" t="str">
+      <c r="D51" s="110" t="str">
         <f t="shared" si="13"/>
         <v>9일</v>
       </c>
-      <c r="E51" s="113">
+      <c r="E51" s="111">
         <v>45971</v>
       </c>
-      <c r="F51" s="113">
+      <c r="F51" s="111">
         <v>45979</v>
       </c>
-      <c r="G51" s="115" t="s">
+      <c r="G51" s="113" t="s">
         <v>103</v>
       </c>
       <c r="H51" s="103"/>
@@ -7373,26 +7309,26 @@
       <c r="BN51" s="60"/>
       <c r="BO51" s="60"/>
     </row>
-    <row r="52" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A52" s="145"/>
-      <c r="B52" s="109" t="s">
+    <row r="52" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A52" s="124"/>
+      <c r="B52" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="111" t="str">
+      <c r="C52" s="109" t="str">
         <f t="shared" ref="C52" ca="1" si="14">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="112" t="str">
-        <f t="shared" ref="D52:D53" si="15">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
+      <c r="D52" s="110" t="str">
+        <f t="shared" ref="D52:D55" si="15">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
-      <c r="E52" s="113">
+      <c r="E52" s="111">
         <v>45971</v>
       </c>
-      <c r="F52" s="113">
+      <c r="F52" s="111">
         <v>45979</v>
       </c>
-      <c r="G52" s="115" t="s">
+      <c r="G52" s="113" t="s">
         <v>103</v>
       </c>
       <c r="H52" s="103"/>
@@ -7456,28 +7392,16 @@
       <c r="BN52" s="60"/>
       <c r="BO52" s="60"/>
     </row>
-    <row r="53" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A53" s="145"/>
-      <c r="B53" s="110" t="s">
-        <v>141</v>
-      </c>
-      <c r="C53" s="111" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>100%</v>
-      </c>
-      <c r="D53" s="112" t="str">
-        <f t="shared" si="15"/>
-        <v>2일</v>
-      </c>
-      <c r="E53" s="113">
-        <v>45979</v>
-      </c>
-      <c r="F53" s="113">
-        <v>45980</v>
-      </c>
-      <c r="G53" s="114" t="s">
-        <v>117</v>
-      </c>
+    <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A53" s="124"/>
+      <c r="B53" s="141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="141"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="F53" s="141"/>
+      <c r="G53" s="141"/>
       <c r="H53" s="103"/>
       <c r="I53" s="60"/>
       <c r="J53" s="60"/>
@@ -7540,26 +7464,26 @@
       <c r="BO53" s="60"/>
     </row>
     <row r="54" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="128"/>
-      <c r="B54" s="105" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="32" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>5.6%</v>
-      </c>
-      <c r="D54" s="106" t="str">
-        <f t="shared" si="13"/>
-        <v>19일</v>
-      </c>
-      <c r="E54" s="107">
+      <c r="A54" s="124"/>
+      <c r="B54" s="87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" s="47" t="str">
+        <f t="shared" ref="C54" ca="1" si="16">IF(F54=E54, IF(TODAY()&gt;F54, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F54) - E54) / (F54 - E54) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
+      </c>
+      <c r="D54" s="40" t="str">
+        <f t="shared" ref="D54" si="17">IF(AND(F54&lt;&gt;"", E54&lt;&gt;""), F54 - E54 + 1 &amp; "일", "")</f>
+        <v>2일</v>
+      </c>
+      <c r="E54" s="41">
         <v>45980</v>
       </c>
-      <c r="F54" s="107">
-        <v>45998</v>
-      </c>
-      <c r="G54" s="108" t="s">
-        <v>134</v>
+      <c r="F54" s="41">
+        <v>45981</v>
+      </c>
+      <c r="G54" s="142" t="s">
+        <v>117</v>
       </c>
       <c r="H54" s="59"/>
       <c r="I54" s="60"/>
@@ -7623,28 +7547,28 @@
       <c r="BO54" s="60"/>
     </row>
     <row r="55" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A55" s="128"/>
-      <c r="B55" s="121" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="122" t="str">
-        <f t="shared" ref="C55" ca="1" si="16">IF(F55=E55, IF(TODAY()&gt;F55, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F55) - E55) / (F55 - E55) * 100, 1) &amp; "%")</f>
+      <c r="A55" s="124"/>
+      <c r="B55" s="123" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="109" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D55" s="123" t="str">
-        <f t="shared" ref="D55" si="17">IF(AND(F55&lt;&gt;"", E55&lt;&gt;""), F55 - E55 + 1 &amp; "일", "")</f>
+      <c r="D55" s="110" t="str">
+        <f t="shared" si="15"/>
         <v>2일</v>
       </c>
-      <c r="E55" s="75">
+      <c r="E55" s="111">
+        <v>45979</v>
+      </c>
+      <c r="F55" s="111">
         <v>45980</v>
       </c>
-      <c r="F55" s="75">
-        <v>45981</v>
-      </c>
-      <c r="G55" s="120" t="s">
+      <c r="G55" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="H55" s="59"/>
+      <c r="H55" s="103"/>
       <c r="I55" s="60"/>
       <c r="J55" s="60"/>
       <c r="K55" s="60"/>
@@ -7706,26 +7630,26 @@
       <c r="BO55" s="60"/>
     </row>
     <row r="56" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="128"/>
-      <c r="B56" s="117" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="118" t="str">
+      <c r="A56" s="124"/>
+      <c r="B56" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>50%</v>
-      </c>
-      <c r="D56" s="119" t="str">
+        <v>11.1%</v>
+      </c>
+      <c r="D56" s="106" t="str">
         <f t="shared" si="13"/>
-        <v>3일</v>
-      </c>
-      <c r="E56" s="75">
+        <v>19일</v>
+      </c>
+      <c r="E56" s="107">
         <v>45980</v>
       </c>
-      <c r="F56" s="75">
-        <v>45982</v>
-      </c>
-      <c r="G56" s="120" t="s">
-        <v>117</v>
+      <c r="F56" s="107">
+        <v>45998</v>
+      </c>
+      <c r="G56" s="108" t="s">
+        <v>134</v>
       </c>
       <c r="H56" s="59"/>
       <c r="I56" s="60"/>
@@ -7789,21 +7713,23 @@
       <c r="BO56" s="60"/>
     </row>
     <row r="57" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A57" s="128"/>
-      <c r="B57" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C57" s="32" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="A57" s="124"/>
+      <c r="B57" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="20" t="str">
+        <f ca="1">IF(F57=E57, IF(TODAY()&gt;F57, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F57) - E57) / (F57 - E57) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D57" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f>IF(AND(F57&lt;&gt;"", E57&lt;&gt;""), F57 - E57 + 1 &amp; "일", "")</f>
         <v/>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
-      <c r="G57" s="69"/>
+      <c r="G57" s="68" t="s">
+        <v>134</v>
+      </c>
       <c r="H57" s="59"/>
       <c r="I57" s="60"/>
       <c r="J57" s="60"/>
@@ -7865,22 +7791,28 @@
       <c r="BN57" s="60"/>
       <c r="BO57" s="60"/>
     </row>
-    <row r="58" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A58" s="128"/>
-      <c r="B58" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="20" t="str">
+    <row r="58" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A58" s="124"/>
+      <c r="B58" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="116" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D58" s="21" t="str">
+      <c r="D58" s="117" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="69"/>
+        <v>3일</v>
+      </c>
+      <c r="E58" s="75">
+        <v>45980</v>
+      </c>
+      <c r="F58" s="75">
+        <v>45982</v>
+      </c>
+      <c r="G58" s="118" t="s">
+        <v>117</v>
+      </c>
       <c r="H58" s="59"/>
       <c r="I58" s="60"/>
       <c r="J58" s="60"/>
@@ -7942,28 +7874,22 @@
       <c r="BN58" s="60"/>
       <c r="BO58" s="60"/>
     </row>
-    <row r="59" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A59" s="128"/>
-      <c r="B59" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" s="20" t="str">
-        <f t="shared" ref="C59" ca="1" si="18">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+    <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A59" s="124"/>
+      <c r="B59" s="94" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="32" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
       </c>
       <c r="D59" s="21" t="str">
-        <f>IF(AND(F59&lt;&gt;"", E59&lt;&gt;""), F59 - E59 + 1 &amp; "일", "")</f>
-        <v>10일</v>
-      </c>
-      <c r="E59" s="22">
-        <v>45989</v>
-      </c>
-      <c r="F59" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G59" s="68" t="s">
-        <v>117</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="69"/>
       <c r="H59" s="59"/>
       <c r="I59" s="60"/>
       <c r="J59" s="60"/>
@@ -8025,10 +7951,10 @@
       <c r="BN59" s="60"/>
       <c r="BO59" s="60"/>
     </row>
-    <row r="60" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A60" s="146"/>
-      <c r="B60" s="95" t="s">
-        <v>136</v>
+    <row r="60" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A60" s="124"/>
+      <c r="B60" s="94" t="s">
+        <v>131</v>
       </c>
       <c r="C60" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8040,9 +7966,7 @@
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
-      <c r="G60" s="68" t="s">
-        <v>134</v>
-      </c>
+      <c r="G60" s="69"/>
       <c r="H60" s="59"/>
       <c r="I60" s="60"/>
       <c r="J60" s="60"/>
@@ -8102,27 +8026,29 @@
       <c r="BL60" s="60"/>
       <c r="BM60" s="60"/>
       <c r="BN60" s="60"/>
-      <c r="BO60" s="29"/>
+      <c r="BO60" s="60"/>
     </row>
     <row r="61" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A61" s="127" t="s">
-        <v>90</v>
-      </c>
-      <c r="B61" s="96" t="s">
-        <v>2</v>
+      <c r="A61" s="125"/>
+      <c r="B61" s="95" t="s">
+        <v>149</v>
       </c>
       <c r="C61" s="20" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>100%</v>
+        <f t="shared" ref="C61" ca="1" si="18">IF(F61=E61, IF(TODAY()&gt;F61, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F61) - E61) / (F61 - E61) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D61" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="70" t="s">
-        <v>100</v>
+        <f>IF(AND(F61&lt;&gt;"", E61&lt;&gt;""), F61 - E61 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E61" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F61" s="22">
+        <v>45998</v>
+      </c>
+      <c r="G61" s="68" t="s">
+        <v>117</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60"/>
@@ -8185,13 +8111,15 @@
       <c r="BN61" s="60"/>
       <c r="BO61" s="60"/>
     </row>
-    <row r="62" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A62" s="128"/>
-      <c r="B62" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="31" t="str">
-        <f t="shared" ref="C62" ca="1" si="19">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
+    <row r="62" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A62" s="124" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
       <c r="D62" s="21" t="str">
@@ -8265,11 +8193,14 @@
       <c r="BO62" s="60"/>
     </row>
     <row r="63" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A63" s="128"/>
+      <c r="A63" s="124"/>
       <c r="B63" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="67"/>
+        <v>88</v>
+      </c>
+      <c r="C63" s="31" t="str">
+        <f t="shared" ref="C63" ca="1" si="19">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
+      </c>
       <c r="D63" s="21" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -8341,26 +8272,19 @@
       <c r="BO63" s="60"/>
     </row>
     <row r="64" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A64" s="128"/>
-      <c r="B64" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" s="35" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
-      </c>
-      <c r="D64" s="71" t="str">
+      <c r="A64" s="124"/>
+      <c r="B64" s="97" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="67"/>
+      <c r="D64" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>12일</v>
-      </c>
-      <c r="E64" s="36">
-        <v>45999</v>
-      </c>
-      <c r="F64" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>98</v>
+        <v/>
+      </c>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H64" s="59"/>
       <c r="I64" s="60"/>
@@ -8423,26 +8347,26 @@
       <c r="BN64" s="60"/>
       <c r="BO64" s="60"/>
     </row>
-    <row r="65" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A65" s="128"/>
-      <c r="B65" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C65" s="32" t="str">
+    <row r="65" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A65" s="124"/>
+      <c r="B65" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="35" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
-      <c r="D65" s="21" t="str">
+      <c r="D65" s="71" t="str">
         <f t="shared" si="13"/>
-        <v>10일</v>
-      </c>
-      <c r="E65" s="33">
+        <v>12일</v>
+      </c>
+      <c r="E65" s="36">
         <v>45999</v>
       </c>
-      <c r="F65" s="33">
-        <v>46008</v>
-      </c>
-      <c r="G65" s="34" t="s">
+      <c r="F65" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G65" s="37" t="s">
         <v>98</v>
       </c>
       <c r="H65" s="59"/>
@@ -8506,12 +8430,12 @@
       <c r="BN65" s="60"/>
       <c r="BO65" s="60"/>
     </row>
-    <row r="66" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A66" s="128"/>
-      <c r="B66" s="95" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="20" t="str">
+    <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A66" s="124"/>
+      <c r="B66" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C66" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
@@ -8519,13 +8443,13 @@
         <f t="shared" si="13"/>
         <v>10일</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E66" s="33">
         <v>45999</v>
       </c>
-      <c r="F66" s="22">
+      <c r="F66" s="33">
         <v>46008</v>
       </c>
-      <c r="G66" s="23" t="s">
+      <c r="G66" s="34" t="s">
         <v>98</v>
       </c>
       <c r="H66" s="59"/>
@@ -8589,10 +8513,10 @@
       <c r="BN66" s="60"/>
       <c r="BO66" s="60"/>
     </row>
-    <row r="67" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A67" s="128"/>
+    <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A67" s="124"/>
       <c r="B67" s="95" t="s">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="C67" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8600,13 +8524,13 @@
       </c>
       <c r="D67" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>1일</v>
+        <v>10일</v>
       </c>
       <c r="E67" s="22">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="F67" s="22">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="G67" s="23" t="s">
         <v>98</v>
@@ -8673,9 +8597,9 @@
       <c r="BO67" s="60"/>
     </row>
     <row r="68" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A68" s="129"/>
+      <c r="A68" s="124"/>
       <c r="B68" s="95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C68" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8755,12 +8679,92 @@
       <c r="BN68" s="60"/>
       <c r="BO68" s="60"/>
     </row>
-    <row r="69" spans="1:67">
-      <c r="E69" s="7"/>
-      <c r="F69" s="1"/>
-      <c r="I69" s="3"/>
+    <row r="69" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A69" s="125"/>
+      <c r="B69" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
+      <c r="D69" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>1일</v>
+      </c>
+      <c r="E69" s="22">
+        <v>46010</v>
+      </c>
+      <c r="F69" s="22">
+        <v>46010</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H69" s="59"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+      <c r="L69" s="61"/>
+      <c r="M69" s="62"/>
+      <c r="N69" s="60"/>
+      <c r="O69" s="60"/>
+      <c r="P69" s="60"/>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="61"/>
+      <c r="T69" s="62"/>
+      <c r="U69" s="60"/>
+      <c r="V69" s="60"/>
+      <c r="W69" s="60"/>
+      <c r="X69" s="60"/>
+      <c r="Y69" s="60"/>
+      <c r="Z69" s="61"/>
+      <c r="AA69" s="62"/>
+      <c r="AB69" s="60"/>
+      <c r="AC69" s="60"/>
+      <c r="AD69" s="60"/>
+      <c r="AE69" s="60"/>
+      <c r="AF69" s="60"/>
+      <c r="AG69" s="61"/>
+      <c r="AH69" s="62"/>
+      <c r="AI69" s="60"/>
+      <c r="AJ69" s="60"/>
+      <c r="AK69" s="60"/>
+      <c r="AL69" s="60"/>
+      <c r="AM69" s="60"/>
+      <c r="AN69" s="61"/>
+      <c r="AO69" s="62"/>
+      <c r="AP69" s="60"/>
+      <c r="AQ69" s="60"/>
+      <c r="AR69" s="60"/>
+      <c r="AS69" s="60"/>
+      <c r="AT69" s="60"/>
+      <c r="AU69" s="61"/>
+      <c r="AV69" s="62"/>
+      <c r="AW69" s="60"/>
+      <c r="AX69" s="60"/>
+      <c r="AY69" s="60"/>
+      <c r="AZ69" s="60"/>
+      <c r="BA69" s="60"/>
+      <c r="BB69" s="61"/>
+      <c r="BC69" s="62"/>
+      <c r="BD69" s="60"/>
+      <c r="BE69" s="60"/>
+      <c r="BF69" s="60"/>
+      <c r="BG69" s="60"/>
+      <c r="BH69" s="60"/>
+      <c r="BI69" s="61"/>
+      <c r="BJ69" s="62"/>
+      <c r="BK69" s="60"/>
+      <c r="BL69" s="60"/>
+      <c r="BM69" s="60"/>
+      <c r="BN69" s="60"/>
+      <c r="BO69" s="60"/>
     </row>
     <row r="70" spans="1:67">
+      <c r="E70" s="7"/>
+      <c r="F70" s="1"/>
       <c r="I70" s="3"/>
     </row>
     <row r="71" spans="1:67">
@@ -8773,45 +8777,44 @@
       <c r="I73" s="3"/>
     </row>
     <row r="74" spans="1:67">
-      <c r="B74" s="8" t="s">
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" spans="1:67">
+      <c r="B75" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="1:67" ht="16.5">
-      <c r="B75" s="9" t="s">
+    <row r="76" spans="1:67" ht="16.5">
+      <c r="B76" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:67">
-      <c r="B76" s="10" t="s">
-        <v>96</v>
-      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" spans="1:67">
-      <c r="C77" s="3"/>
+      <c r="B77" s="10" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="78" spans="1:67">
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="1:67"/>
+    <row r="79" spans="1:67">
+      <c r="C79" s="3"/>
+    </row>
     <row r="80" spans="1:67"/>
-    <row r="81" spans="2:8" ht="16.5">
-      <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-    </row>
-    <row r="82" spans="2:8">
+    <row r="81" spans="2:8"/>
+    <row r="82" spans="2:8" ht="16.5">
+      <c r="B82" s="2"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="2:8" ht="16.5">
-      <c r="B83" s="2"/>
+    <row r="83" spans="2:8">
+      <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="2:8">
-      <c r="C84" s="3"/>
+    <row r="84" spans="2:8" ht="16.5">
+      <c r="B84" s="2"/>
       <c r="D84" s="3"/>
     </row>
     <row r="85" spans="2:8">
@@ -8819,22 +8822,26 @@
       <c r="D85" s="3"/>
     </row>
     <row r="86" spans="2:8">
+      <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="2:8">
       <c r="D87" s="3"/>
-      <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8">
       <c r="D88" s="3"/>
+      <c r="H88" s="11"/>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
-      <c r="C89" s="3"/>
       <c r="D89" s="3"/>
     </row>
+    <row r="90" spans="2:8" ht="15" customHeight="1">
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A61:A68"/>
+  <mergeCells count="15">
+    <mergeCell ref="A62:A69"/>
     <mergeCell ref="H49:BO49"/>
     <mergeCell ref="H41:BO41"/>
     <mergeCell ref="C1:E1"/>
@@ -8845,9 +8852,10 @@
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A60"/>
+    <mergeCell ref="A12:A61"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
+    <mergeCell ref="B53:G53"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC8A8D1-A363-4BA5-AD96-68C412FF5609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83CF6DD-8ABB-4C8B-ADA1-D4D6475F7FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="555" windowWidth="21315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="159">
   <si>
     <t>팀명</t>
   </si>
@@ -1334,6 +1334,32 @@
     <t>전체 페이지</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">바우만 타입 게시판 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>바우만 타입 게시판 시스템</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1342,7 +1368,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1633,6 +1659,20 @@
       <color theme="7"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -2249,7 +2289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2674,7 +2714,34 @@
     <xf numFmtId="0" fontId="23" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2901,7 +2968,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO90"/>
+  <dimension ref="A1:BO92"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -7149,11 +7216,11 @@
         <v>128</v>
       </c>
       <c r="C50" s="44" t="str">
-        <f t="shared" ref="C50:C69" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C50:C71" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D50" s="104" t="str">
-        <f t="shared" ref="D50:D69" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D50:D71" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
         <v>7일</v>
       </c>
       <c r="E50" s="45">
@@ -7394,14 +7461,14 @@
     </row>
     <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
       <c r="A53" s="124"/>
-      <c r="B53" s="141" t="s">
+      <c r="B53" s="144" t="s">
         <v>156</v>
       </c>
       <c r="C53" s="141"/>
       <c r="D53" s="141"/>
       <c r="E53" s="141"/>
       <c r="F53" s="141"/>
-      <c r="G53" s="141"/>
+      <c r="G53" s="145"/>
       <c r="H53" s="103"/>
       <c r="I53" s="60"/>
       <c r="J53" s="60"/>
@@ -7465,24 +7532,24 @@
     </row>
     <row r="54" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A54" s="124"/>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="100" t="s">
         <v>150</v>
       </c>
       <c r="C54" s="47" t="str">
         <f t="shared" ref="C54" ca="1" si="16">IF(F54=E54, IF(TODAY()&gt;F54, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F54) - E54) / (F54 - E54) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D54" s="40" t="str">
+      <c r="D54" s="142" t="str">
         <f t="shared" ref="D54" si="17">IF(AND(F54&lt;&gt;"", E54&lt;&gt;""), F54 - E54 + 1 &amp; "일", "")</f>
         <v>2일</v>
       </c>
-      <c r="E54" s="41">
+      <c r="E54" s="48">
         <v>45980</v>
       </c>
-      <c r="F54" s="41">
+      <c r="F54" s="48">
         <v>45981</v>
       </c>
-      <c r="G54" s="142" t="s">
+      <c r="G54" s="143" t="s">
         <v>117</v>
       </c>
       <c r="H54" s="59"/>
@@ -7719,14 +7786,18 @@
       </c>
       <c r="C57" s="20" t="str">
         <f ca="1">IF(F57=E57, IF(TODAY()&gt;F57, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F57) - E57) / (F57 - E57) * 100, 1) &amp; "%")</f>
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="D57" s="21" t="str">
         <f>IF(AND(F57&lt;&gt;"", E57&lt;&gt;""), F57 - E57 + 1 &amp; "일", "")</f>
-        <v/>
-      </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
+        <v>14일</v>
+      </c>
+      <c r="E57" s="22">
+        <v>45985</v>
+      </c>
+      <c r="F57" s="22">
+        <v>45998</v>
+      </c>
       <c r="G57" s="68" t="s">
         <v>134</v>
       </c>
@@ -7793,25 +7864,25 @@
     </row>
     <row r="58" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A58" s="124"/>
-      <c r="B58" s="115" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="116" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>100%</v>
-      </c>
-      <c r="D58" s="117" t="str">
-        <f t="shared" si="13"/>
-        <v>3일</v>
-      </c>
-      <c r="E58" s="75">
-        <v>45980</v>
-      </c>
-      <c r="F58" s="75">
-        <v>45982</v>
-      </c>
-      <c r="G58" s="118" t="s">
-        <v>117</v>
+      <c r="B58" s="146" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" s="147" t="str">
+        <f ca="1">IF(F58=E58, IF(TODAY()&gt;F58, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F58) - E58) / (F58 - E58) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
+      </c>
+      <c r="D58" s="148" t="str">
+        <f>IF(AND(F58&lt;&gt;"", E58&lt;&gt;""), F58 - E58 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E58" s="149">
+        <v>45989</v>
+      </c>
+      <c r="F58" s="149">
+        <v>45998</v>
+      </c>
+      <c r="G58" s="150" t="s">
+        <v>108</v>
       </c>
       <c r="H58" s="59"/>
       <c r="I58" s="60"/>
@@ -7876,20 +7947,26 @@
     </row>
     <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A59" s="124"/>
-      <c r="B59" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C59" s="32" t="str">
-        <f t="shared" ca="1" si="12"/>
+      <c r="B59" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="116" t="str">
+        <f ca="1">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D59" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="69"/>
+      <c r="D59" s="117" t="str">
+        <f>IF(AND(F59&lt;&gt;"", E59&lt;&gt;""), F59 - E59 + 1 &amp; "일", "")</f>
+        <v>3일</v>
+      </c>
+      <c r="E59" s="75">
+        <v>45980</v>
+      </c>
+      <c r="F59" s="75">
+        <v>45982</v>
+      </c>
+      <c r="G59" s="118" t="s">
+        <v>117</v>
+      </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60"/>
       <c r="J59" s="60"/>
@@ -7951,22 +8028,28 @@
       <c r="BN59" s="60"/>
       <c r="BO59" s="60"/>
     </row>
-    <row r="60" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+    <row r="60" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A60" s="124"/>
       <c r="B60" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="20" t="str">
+        <v>130</v>
+      </c>
+      <c r="C60" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="D60" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="69"/>
+        <f>IF(AND(F60&lt;&gt;"", E60&lt;&gt;""), F60 - E60 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E60" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F60" s="22">
+        <v>45998</v>
+      </c>
+      <c r="G60" s="69" t="s">
+        <v>119</v>
+      </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60"/>
       <c r="J60" s="60"/>
@@ -8028,13 +8111,13 @@
       <c r="BN60" s="60"/>
       <c r="BO60" s="60"/>
     </row>
-    <row r="61" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A61" s="125"/>
-      <c r="B61" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="20" t="str">
-        <f t="shared" ref="C61" ca="1" si="18">IF(F61=E61, IF(TODAY()&gt;F61, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F61) - E61) / (F61 - E61) * 100, 1) &amp; "%")</f>
+    <row r="61" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A61" s="124"/>
+      <c r="B61" s="151" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="32" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
       <c r="D61" s="21" t="str">
@@ -8047,8 +8130,8 @@
       <c r="F61" s="22">
         <v>45998</v>
       </c>
-      <c r="G61" s="68" t="s">
-        <v>117</v>
+      <c r="G61" s="69" t="s">
+        <v>107</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60"/>
@@ -8112,24 +8195,26 @@
       <c r="BO61" s="60"/>
     </row>
     <row r="62" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A62" s="124" t="s">
-        <v>90</v>
-      </c>
-      <c r="B62" s="96" t="s">
-        <v>2</v>
+      <c r="A62" s="124"/>
+      <c r="B62" s="94" t="s">
+        <v>131</v>
       </c>
       <c r="C62" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="D62" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="70" t="s">
-        <v>100</v>
+        <f>IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E62" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F62" s="22">
+        <v>45998</v>
+      </c>
+      <c r="G62" s="69" t="s">
+        <v>116</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60"/>
@@ -8192,23 +8277,27 @@
       <c r="BN62" s="60"/>
       <c r="BO62" s="60"/>
     </row>
-    <row r="63" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A63" s="124"/>
-      <c r="B63" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="31" t="str">
-        <f t="shared" ref="C63" ca="1" si="19">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
-        <v>100%</v>
+    <row r="63" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A63" s="125"/>
+      <c r="B63" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="20" t="str">
+        <f t="shared" ref="C63" ca="1" si="18">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
+        <v>0%</v>
       </c>
       <c r="D63" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="70" t="s">
-        <v>100</v>
+        <f>IF(AND(F63&lt;&gt;"", E63&lt;&gt;""), F63 - E63 + 1 &amp; "일", "")</f>
+        <v>10일</v>
+      </c>
+      <c r="E63" s="22">
+        <v>45989</v>
+      </c>
+      <c r="F63" s="22">
+        <v>45998</v>
+      </c>
+      <c r="G63" s="68" t="s">
+        <v>117</v>
       </c>
       <c r="H63" s="59"/>
       <c r="I63" s="60"/>
@@ -8271,12 +8360,17 @@
       <c r="BN63" s="60"/>
       <c r="BO63" s="60"/>
     </row>
-    <row r="64" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A64" s="124"/>
-      <c r="B64" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="67"/>
+    <row r="64" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A64" s="124" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
+      </c>
       <c r="D64" s="21" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -8349,25 +8443,21 @@
     </row>
     <row r="65" spans="1:67" ht="15.75" thickBot="1">
       <c r="A65" s="124"/>
-      <c r="B65" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" s="35" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
-      </c>
-      <c r="D65" s="71" t="str">
+      <c r="B65" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="31" t="str">
+        <f t="shared" ref="C65" ca="1" si="19">IF(F65=E65, IF(TODAY()&gt;F65, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F65) - E65) / (F65 - E65) * 100, 1) &amp; "%")</f>
+        <v>100%</v>
+      </c>
+      <c r="D65" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>12일</v>
-      </c>
-      <c r="E65" s="36">
-        <v>45999</v>
-      </c>
-      <c r="F65" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>98</v>
+        <v/>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60"/>
@@ -8430,27 +8520,20 @@
       <c r="BN65" s="60"/>
       <c r="BO65" s="60"/>
     </row>
-    <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
+    <row r="66" spans="1:67" ht="15.75" thickBot="1">
       <c r="A66" s="124"/>
-      <c r="B66" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="32" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
-      </c>
+      <c r="B66" s="97" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="67"/>
       <c r="D66" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>10일</v>
-      </c>
-      <c r="E66" s="33">
-        <v>45999</v>
-      </c>
-      <c r="F66" s="33">
-        <v>46008</v>
-      </c>
-      <c r="G66" s="34" t="s">
-        <v>98</v>
+        <v/>
+      </c>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="70" t="s">
+        <v>100</v>
       </c>
       <c r="H66" s="59"/>
       <c r="I66" s="60"/>
@@ -8513,26 +8596,26 @@
       <c r="BN66" s="60"/>
       <c r="BO66" s="60"/>
     </row>
-    <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+    <row r="67" spans="1:67" ht="15.75" thickBot="1">
       <c r="A67" s="124"/>
-      <c r="B67" s="95" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="20" t="str">
+      <c r="B67" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="35" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
-      <c r="D67" s="21" t="str">
+      <c r="D67" s="71" t="str">
         <f t="shared" si="13"/>
-        <v>10일</v>
-      </c>
-      <c r="E67" s="22">
+        <v>12일</v>
+      </c>
+      <c r="E67" s="36">
         <v>45999</v>
       </c>
-      <c r="F67" s="22">
-        <v>46008</v>
-      </c>
-      <c r="G67" s="23" t="s">
+      <c r="F67" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G67" s="37" t="s">
         <v>98</v>
       </c>
       <c r="H67" s="59"/>
@@ -8596,26 +8679,26 @@
       <c r="BN67" s="60"/>
       <c r="BO67" s="60"/>
     </row>
-    <row r="68" spans="1:67" ht="15.75" thickBot="1">
+    <row r="68" spans="1:67" ht="15" customHeight="1" thickBot="1">
       <c r="A68" s="124"/>
-      <c r="B68" s="95" t="s">
-        <v>92</v>
-      </c>
-      <c r="C68" s="20" t="str">
+      <c r="B68" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
       <c r="D68" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>1일</v>
-      </c>
-      <c r="E68" s="22">
-        <v>46010</v>
-      </c>
-      <c r="F68" s="22">
-        <v>46010</v>
-      </c>
-      <c r="G68" s="23" t="s">
+        <v>10일</v>
+      </c>
+      <c r="E68" s="33">
+        <v>45999</v>
+      </c>
+      <c r="F68" s="33">
+        <v>46008</v>
+      </c>
+      <c r="G68" s="34" t="s">
         <v>98</v>
       </c>
       <c r="H68" s="59"/>
@@ -8679,10 +8762,10 @@
       <c r="BN68" s="60"/>
       <c r="BO68" s="60"/>
     </row>
-    <row r="69" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A69" s="125"/>
+    <row r="69" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A69" s="124"/>
       <c r="B69" s="95" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="C69" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8690,13 +8773,13 @@
       </c>
       <c r="D69" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>1일</v>
+        <v>10일</v>
       </c>
       <c r="E69" s="22">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="F69" s="22">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="G69" s="23" t="s">
         <v>98</v>
@@ -8762,15 +8845,175 @@
       <c r="BN69" s="60"/>
       <c r="BO69" s="60"/>
     </row>
-    <row r="70" spans="1:67">
-      <c r="E70" s="7"/>
-      <c r="F70" s="1"/>
-      <c r="I70" s="3"/>
+    <row r="70" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A70" s="124"/>
+      <c r="B70" s="95" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
+      <c r="D70" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>1일</v>
+      </c>
+      <c r="E70" s="22">
+        <v>46010</v>
+      </c>
+      <c r="F70" s="22">
+        <v>46010</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H70" s="59"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+      <c r="L70" s="61"/>
+      <c r="M70" s="62"/>
+      <c r="N70" s="60"/>
+      <c r="O70" s="60"/>
+      <c r="P70" s="60"/>
+      <c r="Q70" s="60"/>
+      <c r="R70" s="60"/>
+      <c r="S70" s="61"/>
+      <c r="T70" s="62"/>
+      <c r="U70" s="60"/>
+      <c r="V70" s="60"/>
+      <c r="W70" s="60"/>
+      <c r="X70" s="60"/>
+      <c r="Y70" s="60"/>
+      <c r="Z70" s="61"/>
+      <c r="AA70" s="62"/>
+      <c r="AB70" s="60"/>
+      <c r="AC70" s="60"/>
+      <c r="AD70" s="60"/>
+      <c r="AE70" s="60"/>
+      <c r="AF70" s="60"/>
+      <c r="AG70" s="61"/>
+      <c r="AH70" s="62"/>
+      <c r="AI70" s="60"/>
+      <c r="AJ70" s="60"/>
+      <c r="AK70" s="60"/>
+      <c r="AL70" s="60"/>
+      <c r="AM70" s="60"/>
+      <c r="AN70" s="61"/>
+      <c r="AO70" s="62"/>
+      <c r="AP70" s="60"/>
+      <c r="AQ70" s="60"/>
+      <c r="AR70" s="60"/>
+      <c r="AS70" s="60"/>
+      <c r="AT70" s="60"/>
+      <c r="AU70" s="61"/>
+      <c r="AV70" s="62"/>
+      <c r="AW70" s="60"/>
+      <c r="AX70" s="60"/>
+      <c r="AY70" s="60"/>
+      <c r="AZ70" s="60"/>
+      <c r="BA70" s="60"/>
+      <c r="BB70" s="61"/>
+      <c r="BC70" s="62"/>
+      <c r="BD70" s="60"/>
+      <c r="BE70" s="60"/>
+      <c r="BF70" s="60"/>
+      <c r="BG70" s="60"/>
+      <c r="BH70" s="60"/>
+      <c r="BI70" s="61"/>
+      <c r="BJ70" s="62"/>
+      <c r="BK70" s="60"/>
+      <c r="BL70" s="60"/>
+      <c r="BM70" s="60"/>
+      <c r="BN70" s="60"/>
+      <c r="BO70" s="60"/>
     </row>
-    <row r="71" spans="1:67">
-      <c r="I71" s="3"/>
+    <row r="71" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A71" s="125"/>
+      <c r="B71" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" s="20" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
+      <c r="D71" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>1일</v>
+      </c>
+      <c r="E71" s="22">
+        <v>46010</v>
+      </c>
+      <c r="F71" s="22">
+        <v>46010</v>
+      </c>
+      <c r="G71" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H71" s="59"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="60"/>
+      <c r="L71" s="61"/>
+      <c r="M71" s="62"/>
+      <c r="N71" s="60"/>
+      <c r="O71" s="60"/>
+      <c r="P71" s="60"/>
+      <c r="Q71" s="60"/>
+      <c r="R71" s="60"/>
+      <c r="S71" s="61"/>
+      <c r="T71" s="62"/>
+      <c r="U71" s="60"/>
+      <c r="V71" s="60"/>
+      <c r="W71" s="60"/>
+      <c r="X71" s="60"/>
+      <c r="Y71" s="60"/>
+      <c r="Z71" s="61"/>
+      <c r="AA71" s="62"/>
+      <c r="AB71" s="60"/>
+      <c r="AC71" s="60"/>
+      <c r="AD71" s="60"/>
+      <c r="AE71" s="60"/>
+      <c r="AF71" s="60"/>
+      <c r="AG71" s="61"/>
+      <c r="AH71" s="62"/>
+      <c r="AI71" s="60"/>
+      <c r="AJ71" s="60"/>
+      <c r="AK71" s="60"/>
+      <c r="AL71" s="60"/>
+      <c r="AM71" s="60"/>
+      <c r="AN71" s="61"/>
+      <c r="AO71" s="62"/>
+      <c r="AP71" s="60"/>
+      <c r="AQ71" s="60"/>
+      <c r="AR71" s="60"/>
+      <c r="AS71" s="60"/>
+      <c r="AT71" s="60"/>
+      <c r="AU71" s="61"/>
+      <c r="AV71" s="62"/>
+      <c r="AW71" s="60"/>
+      <c r="AX71" s="60"/>
+      <c r="AY71" s="60"/>
+      <c r="AZ71" s="60"/>
+      <c r="BA71" s="60"/>
+      <c r="BB71" s="61"/>
+      <c r="BC71" s="62"/>
+      <c r="BD71" s="60"/>
+      <c r="BE71" s="60"/>
+      <c r="BF71" s="60"/>
+      <c r="BG71" s="60"/>
+      <c r="BH71" s="60"/>
+      <c r="BI71" s="61"/>
+      <c r="BJ71" s="62"/>
+      <c r="BK71" s="60"/>
+      <c r="BL71" s="60"/>
+      <c r="BM71" s="60"/>
+      <c r="BN71" s="60"/>
+      <c r="BO71" s="60"/>
     </row>
     <row r="72" spans="1:67">
+      <c r="E72" s="7"/>
+      <c r="F72" s="1"/>
       <c r="I72" s="3"/>
     </row>
     <row r="73" spans="1:67">
@@ -8780,68 +9023,74 @@
       <c r="I74" s="3"/>
     </row>
     <row r="75" spans="1:67">
-      <c r="B75" s="8" t="s">
-        <v>94</v>
-      </c>
+      <c r="I75" s="3"/>
     </row>
-    <row r="76" spans="1:67" ht="16.5">
-      <c r="B76" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3"/>
+    <row r="76" spans="1:67">
+      <c r="I76" s="3"/>
     </row>
     <row r="77" spans="1:67">
-      <c r="B77" s="10" t="s">
-        <v>96</v>
+      <c r="B77" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:67">
-      <c r="C78" s="3"/>
+    <row r="78" spans="1:67" ht="16.5">
+      <c r="B78" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="1:67">
-      <c r="C79" s="3"/>
+      <c r="B79" s="10" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="80" spans="1:67"/>
-    <row r="81" spans="2:8"/>
-    <row r="82" spans="2:8" ht="16.5">
-      <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+    <row r="80" spans="1:67">
+      <c r="C80" s="3"/>
     </row>
-    <row r="83" spans="2:8">
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+    <row r="81" spans="2:8">
+      <c r="C81" s="3"/>
     </row>
+    <row r="82" spans="2:8"/>
+    <row r="83" spans="2:8"/>
     <row r="84" spans="2:8" ht="16.5">
       <c r="B84" s="2"/>
+      <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
     <row r="85" spans="2:8">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="2:8">
-      <c r="C86" s="3"/>
+    <row r="86" spans="2:8" ht="16.5">
+      <c r="B86" s="2"/>
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="2:8">
+      <c r="C87" s="3"/>
       <c r="D87" s="3"/>
     </row>
     <row r="88" spans="2:8">
+      <c r="C88" s="3"/>
       <c r="D88" s="3"/>
-      <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8">
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="2:8" ht="15" customHeight="1">
-      <c r="C90" s="3"/>
+    <row r="90" spans="2:8">
       <c r="D90" s="3"/>
+      <c r="H90" s="11"/>
+    </row>
+    <row r="91" spans="2:8" ht="15" customHeight="1">
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="2:8" ht="15" customHeight="1">
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A62:A69"/>
+    <mergeCell ref="A64:A71"/>
     <mergeCell ref="H49:BO49"/>
     <mergeCell ref="H41:BO41"/>
     <mergeCell ref="C1:E1"/>
@@ -8852,7 +9101,7 @@
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A61"/>
+    <mergeCell ref="A12:A63"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
     <mergeCell ref="B53:G53"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83CF6DD-8ABB-4C8B-ADA1-D4D6475F7FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3756CA5-7293-46CF-AB39-5681A69DC62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="555" windowWidth="21315" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
   <si>
     <t>팀명</t>
   </si>
@@ -1356,10 +1356,6 @@
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
-  <si>
-    <t>바우만 타입 게시판 시스템</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -1368,7 +1364,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1665,13 +1661,6 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -2289,7 +2278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2489,9 +2478,6 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2660,6 +2646,27 @@
     <xf numFmtId="0" fontId="31" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2711,37 +2718,16 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2968,7 +2954,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO92"/>
+  <dimension ref="A1:BO91"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -2983,31 +2969,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="C1" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="131" t="s">
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="130"/>
-      <c r="R1" s="130"/>
-      <c r="S1" s="130"/>
-      <c r="T1" s="130"/>
-      <c r="U1" s="130"/>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="136"/>
+      <c r="W1" s="136"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3071,7 +3057,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="132" t="s">
+      <c r="G2" s="138" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3256,13 +3242,13 @@
       </c>
     </row>
     <row r="3" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="99"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="133"/>
+      <c r="G3" s="139"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3445,10 +3431,10 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="134" t="s">
+      <c r="A4" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="76" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="39" t="str">
@@ -3530,8 +3516,8 @@
       <c r="BO4" s="55"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="135"/>
-      <c r="B5" s="77" t="s">
+      <c r="A5" s="141"/>
+      <c r="B5" s="76" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="39" t="str">
@@ -3613,8 +3599,8 @@
       <c r="BO5" s="60"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="135"/>
-      <c r="B6" s="77" t="s">
+      <c r="A6" s="141"/>
+      <c r="B6" s="76" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="39" t="str">
@@ -3696,8 +3682,8 @@
       <c r="BO6" s="60"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="135"/>
-      <c r="B7" s="78" t="s">
+      <c r="A7" s="141"/>
+      <c r="B7" s="77" t="s">
         <v>75</v>
       </c>
       <c r="C7" s="39" t="str">
@@ -3779,8 +3765,8 @@
       <c r="BO7" s="60"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="135"/>
-      <c r="B8" s="79" t="s">
+      <c r="A8" s="141"/>
+      <c r="B8" s="78" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="39" t="str">
@@ -3862,8 +3848,8 @@
       <c r="BO8" s="60"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="135"/>
-      <c r="B9" s="77" t="s">
+      <c r="A9" s="141"/>
+      <c r="B9" s="76" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="39" t="str">
@@ -3945,8 +3931,8 @@
       <c r="BO9" s="60"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="135"/>
-      <c r="B10" s="78" t="s">
+      <c r="A10" s="141"/>
+      <c r="B10" s="77" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="39" t="str">
@@ -4028,8 +4014,8 @@
       <c r="BO10" s="60"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="135"/>
-      <c r="B11" s="80" t="s">
+      <c r="A11" s="141"/>
+      <c r="B11" s="79" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="44" t="str">
@@ -4111,10 +4097,10 @@
       <c r="BO11" s="60"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="146" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="80" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="35" t="str">
@@ -4196,8 +4182,8 @@
       <c r="BO12" s="60"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="82" t="s">
+      <c r="A13" s="130"/>
+      <c r="B13" s="81" t="s">
         <v>82</v>
       </c>
       <c r="C13" s="47" t="str">
@@ -4279,8 +4265,8 @@
       <c r="BO13" s="60"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="124"/>
-      <c r="B14" s="83" t="s">
+      <c r="A14" s="130"/>
+      <c r="B14" s="82" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="44" t="str">
@@ -4362,8 +4348,8 @@
       <c r="BO14" s="60"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="124"/>
-      <c r="B15" s="81" t="s">
+      <c r="A15" s="130"/>
+      <c r="B15" s="80" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="35" t="str">
@@ -4445,8 +4431,8 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="124"/>
-      <c r="B16" s="84" t="s">
+      <c r="A16" s="130"/>
+      <c r="B16" s="83" t="s">
         <v>123</v>
       </c>
       <c r="C16" s="47" t="str">
@@ -4528,79 +4514,79 @@
       <c r="BO16" s="53"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="124"/>
-      <c r="B17" s="138" t="s">
+      <c r="A17" s="130"/>
+      <c r="B17" s="144" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="127"/>
-      <c r="W17" s="127"/>
-      <c r="X17" s="127"/>
-      <c r="Y17" s="127"/>
-      <c r="Z17" s="127"/>
-      <c r="AA17" s="127"/>
-      <c r="AB17" s="127"/>
-      <c r="AC17" s="127"/>
-      <c r="AD17" s="127"/>
-      <c r="AE17" s="127"/>
-      <c r="AF17" s="127"/>
-      <c r="AG17" s="127"/>
-      <c r="AH17" s="127"/>
-      <c r="AI17" s="127"/>
-      <c r="AJ17" s="127"/>
-      <c r="AK17" s="127"/>
-      <c r="AL17" s="127"/>
-      <c r="AM17" s="127"/>
-      <c r="AN17" s="127"/>
-      <c r="AO17" s="127"/>
-      <c r="AP17" s="127"/>
-      <c r="AQ17" s="127"/>
-      <c r="AR17" s="127"/>
-      <c r="AS17" s="127"/>
-      <c r="AT17" s="127"/>
-      <c r="AU17" s="127"/>
-      <c r="AV17" s="127"/>
-      <c r="AW17" s="127"/>
-      <c r="AX17" s="127"/>
-      <c r="AY17" s="127"/>
-      <c r="AZ17" s="127"/>
-      <c r="BA17" s="127"/>
-      <c r="BB17" s="127"/>
-      <c r="BC17" s="127"/>
-      <c r="BD17" s="127"/>
-      <c r="BE17" s="127"/>
-      <c r="BF17" s="127"/>
-      <c r="BG17" s="127"/>
-      <c r="BH17" s="127"/>
-      <c r="BI17" s="127"/>
-      <c r="BJ17" s="127"/>
-      <c r="BK17" s="127"/>
-      <c r="BL17" s="127"/>
-      <c r="BM17" s="127"/>
-      <c r="BN17" s="127"/>
-      <c r="BO17" s="128"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="133"/>
+      <c r="S17" s="133"/>
+      <c r="T17" s="133"/>
+      <c r="U17" s="133"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="133"/>
+      <c r="X17" s="133"/>
+      <c r="Y17" s="133"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="133"/>
+      <c r="AB17" s="133"/>
+      <c r="AC17" s="133"/>
+      <c r="AD17" s="133"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="133"/>
+      <c r="AG17" s="133"/>
+      <c r="AH17" s="133"/>
+      <c r="AI17" s="133"/>
+      <c r="AJ17" s="133"/>
+      <c r="AK17" s="133"/>
+      <c r="AL17" s="133"/>
+      <c r="AM17" s="133"/>
+      <c r="AN17" s="133"/>
+      <c r="AO17" s="133"/>
+      <c r="AP17" s="133"/>
+      <c r="AQ17" s="133"/>
+      <c r="AR17" s="133"/>
+      <c r="AS17" s="133"/>
+      <c r="AT17" s="133"/>
+      <c r="AU17" s="133"/>
+      <c r="AV17" s="133"/>
+      <c r="AW17" s="133"/>
+      <c r="AX17" s="133"/>
+      <c r="AY17" s="133"/>
+      <c r="AZ17" s="133"/>
+      <c r="BA17" s="133"/>
+      <c r="BB17" s="133"/>
+      <c r="BC17" s="133"/>
+      <c r="BD17" s="133"/>
+      <c r="BE17" s="133"/>
+      <c r="BF17" s="133"/>
+      <c r="BG17" s="133"/>
+      <c r="BH17" s="133"/>
+      <c r="BI17" s="133"/>
+      <c r="BJ17" s="133"/>
+      <c r="BK17" s="133"/>
+      <c r="BL17" s="133"/>
+      <c r="BM17" s="133"/>
+      <c r="BN17" s="133"/>
+      <c r="BO17" s="134"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="124"/>
-      <c r="B18" s="85" t="s">
+      <c r="A18" s="130"/>
+      <c r="B18" s="84" t="s">
         <v>124</v>
       </c>
       <c r="C18" s="39" t="str">
@@ -4682,25 +4668,25 @@
       <c r="BO18" s="55"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="124"/>
-      <c r="B19" s="86" t="s">
+      <c r="A19" s="130"/>
+      <c r="B19" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="73" t="str">
+      <c r="C19" s="72" t="str">
         <f ca="1">IF(F19=E19, IF(TODAY()&gt;F19, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F19) - E19) / (F19 - E19) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D19" s="74" t="str">
+      <c r="D19" s="73" t="str">
         <f>IF(AND(F19&lt;&gt;"", E19&lt;&gt;""), F19 - E19 + 1 &amp; "일", "")</f>
         <v>17일</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="74">
         <v>45965</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="74">
         <v>45981</v>
       </c>
-      <c r="G19" s="76" t="s">
+      <c r="G19" s="75" t="s">
         <v>105</v>
       </c>
       <c r="H19" s="59"/>
@@ -4765,8 +4751,8 @@
       <c r="BO19" s="60"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="124"/>
-      <c r="B20" s="87" t="s">
+      <c r="A20" s="130"/>
+      <c r="B20" s="86" t="s">
         <v>113</v>
       </c>
       <c r="C20" s="39" t="str">
@@ -4848,79 +4834,79 @@
       <c r="BO20" s="60"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="124"/>
-      <c r="B21" s="136" t="s">
+      <c r="A21" s="130"/>
+      <c r="B21" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="136"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="127"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="127"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="127"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="127"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="127"/>
-      <c r="W21" s="127"/>
-      <c r="X21" s="127"/>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-      <c r="AA21" s="127"/>
-      <c r="AB21" s="127"/>
-      <c r="AC21" s="127"/>
-      <c r="AD21" s="127"/>
-      <c r="AE21" s="127"/>
-      <c r="AF21" s="127"/>
-      <c r="AG21" s="127"/>
-      <c r="AH21" s="127"/>
-      <c r="AI21" s="127"/>
-      <c r="AJ21" s="127"/>
-      <c r="AK21" s="127"/>
-      <c r="AL21" s="127"/>
-      <c r="AM21" s="127"/>
-      <c r="AN21" s="127"/>
-      <c r="AO21" s="127"/>
-      <c r="AP21" s="127"/>
-      <c r="AQ21" s="127"/>
-      <c r="AR21" s="127"/>
-      <c r="AS21" s="127"/>
-      <c r="AT21" s="127"/>
-      <c r="AU21" s="127"/>
-      <c r="AV21" s="127"/>
-      <c r="AW21" s="127"/>
-      <c r="AX21" s="127"/>
-      <c r="AY21" s="127"/>
-      <c r="AZ21" s="127"/>
-      <c r="BA21" s="127"/>
-      <c r="BB21" s="127"/>
-      <c r="BC21" s="127"/>
-      <c r="BD21" s="127"/>
-      <c r="BE21" s="127"/>
-      <c r="BF21" s="127"/>
-      <c r="BG21" s="127"/>
-      <c r="BH21" s="127"/>
-      <c r="BI21" s="127"/>
-      <c r="BJ21" s="127"/>
-      <c r="BK21" s="127"/>
-      <c r="BL21" s="127"/>
-      <c r="BM21" s="127"/>
-      <c r="BN21" s="127"/>
-      <c r="BO21" s="128"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="133"/>
+      <c r="T21" s="133"/>
+      <c r="U21" s="133"/>
+      <c r="V21" s="133"/>
+      <c r="W21" s="133"/>
+      <c r="X21" s="133"/>
+      <c r="Y21" s="133"/>
+      <c r="Z21" s="133"/>
+      <c r="AA21" s="133"/>
+      <c r="AB21" s="133"/>
+      <c r="AC21" s="133"/>
+      <c r="AD21" s="133"/>
+      <c r="AE21" s="133"/>
+      <c r="AF21" s="133"/>
+      <c r="AG21" s="133"/>
+      <c r="AH21" s="133"/>
+      <c r="AI21" s="133"/>
+      <c r="AJ21" s="133"/>
+      <c r="AK21" s="133"/>
+      <c r="AL21" s="133"/>
+      <c r="AM21" s="133"/>
+      <c r="AN21" s="133"/>
+      <c r="AO21" s="133"/>
+      <c r="AP21" s="133"/>
+      <c r="AQ21" s="133"/>
+      <c r="AR21" s="133"/>
+      <c r="AS21" s="133"/>
+      <c r="AT21" s="133"/>
+      <c r="AU21" s="133"/>
+      <c r="AV21" s="133"/>
+      <c r="AW21" s="133"/>
+      <c r="AX21" s="133"/>
+      <c r="AY21" s="133"/>
+      <c r="AZ21" s="133"/>
+      <c r="BA21" s="133"/>
+      <c r="BB21" s="133"/>
+      <c r="BC21" s="133"/>
+      <c r="BD21" s="133"/>
+      <c r="BE21" s="133"/>
+      <c r="BF21" s="133"/>
+      <c r="BG21" s="133"/>
+      <c r="BH21" s="133"/>
+      <c r="BI21" s="133"/>
+      <c r="BJ21" s="133"/>
+      <c r="BK21" s="133"/>
+      <c r="BL21" s="133"/>
+      <c r="BM21" s="133"/>
+      <c r="BN21" s="133"/>
+      <c r="BO21" s="134"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="124"/>
-      <c r="B22" s="88" t="s">
+      <c r="A22" s="130"/>
+      <c r="B22" s="87" t="s">
         <v>125</v>
       </c>
       <c r="C22" s="39" t="str">
@@ -5002,8 +4988,8 @@
       <c r="BO22" s="60"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="124"/>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="130"/>
+      <c r="B23" s="88" t="s">
         <v>85</v>
       </c>
       <c r="C23" s="39" t="str">
@@ -5085,8 +5071,8 @@
       <c r="BO23" s="60"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="124"/>
-      <c r="B24" s="90" t="s">
+      <c r="A24" s="130"/>
+      <c r="B24" s="89" t="s">
         <v>145</v>
       </c>
       <c r="C24" s="39" t="str">
@@ -5168,8 +5154,8 @@
       <c r="BO24" s="60"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="124"/>
-      <c r="B25" s="90" t="s">
+      <c r="A25" s="130"/>
+      <c r="B25" s="89" t="s">
         <v>143</v>
       </c>
       <c r="C25" s="39" t="str">
@@ -5251,8 +5237,8 @@
       <c r="BO25" s="60"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="124"/>
-      <c r="B26" s="85" t="s">
+      <c r="A26" s="130"/>
+      <c r="B26" s="84" t="s">
         <v>153</v>
       </c>
       <c r="C26" s="39" t="str">
@@ -5334,8 +5320,8 @@
       <c r="BO26" s="60"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="124"/>
-      <c r="B27" s="91" t="s">
+      <c r="A27" s="130"/>
+      <c r="B27" s="90" t="s">
         <v>137</v>
       </c>
       <c r="C27" s="20" t="str">
@@ -5417,8 +5403,8 @@
       <c r="BO27" s="60"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="124"/>
-      <c r="B28" s="92" t="s">
+      <c r="A28" s="130"/>
+      <c r="B28" s="91" t="s">
         <v>148</v>
       </c>
       <c r="C28" s="20" t="str">
@@ -5500,8 +5486,8 @@
       <c r="BO28" s="60"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="124"/>
-      <c r="B29" s="92" t="s">
+      <c r="A29" s="130"/>
+      <c r="B29" s="91" t="s">
         <v>138</v>
       </c>
       <c r="C29" s="20" t="str">
@@ -5581,8 +5567,8 @@
       <c r="BO29" s="60"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="124"/>
-      <c r="B30" s="119" t="s">
+      <c r="A30" s="130"/>
+      <c r="B30" s="118" t="s">
         <v>146</v>
       </c>
       <c r="C30" s="39" t="str">
@@ -5664,8 +5650,8 @@
       <c r="BO30" s="60"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="124"/>
-      <c r="B31" s="93" t="s">
+      <c r="A31" s="130"/>
+      <c r="B31" s="92" t="s">
         <v>104</v>
       </c>
       <c r="C31" s="39" t="str">
@@ -5747,8 +5733,8 @@
       <c r="BO31" s="28"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="124"/>
-      <c r="B32" s="87" t="s">
+      <c r="A32" s="130"/>
+      <c r="B32" s="86" t="s">
         <v>111</v>
       </c>
       <c r="C32" s="39" t="str">
@@ -5830,8 +5816,8 @@
       <c r="BO32" s="60"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="124"/>
-      <c r="B33" s="88" t="s">
+      <c r="A33" s="130"/>
+      <c r="B33" s="87" t="s">
         <v>126</v>
       </c>
       <c r="C33" s="39" t="str">
@@ -5913,8 +5899,8 @@
       <c r="BO33" s="60"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="124"/>
-      <c r="B34" s="87" t="s">
+      <c r="A34" s="130"/>
+      <c r="B34" s="86" t="s">
         <v>112</v>
       </c>
       <c r="C34" s="39" t="str">
@@ -5996,8 +5982,8 @@
       <c r="BO34" s="60"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="124"/>
-      <c r="B35" s="100" t="s">
+      <c r="A35" s="130"/>
+      <c r="B35" s="99" t="s">
         <v>140</v>
       </c>
       <c r="C35" s="39" t="str">
@@ -6079,8 +6065,8 @@
       <c r="BO35" s="60"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="124"/>
-      <c r="B36" s="100" t="s">
+      <c r="A36" s="130"/>
+      <c r="B36" s="99" t="s">
         <v>142</v>
       </c>
       <c r="C36" s="39" t="str">
@@ -6162,8 +6148,8 @@
       <c r="BO36" s="60"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="124"/>
-      <c r="B37" s="114" t="s">
+      <c r="A37" s="130"/>
+      <c r="B37" s="113" t="s">
         <v>121</v>
       </c>
       <c r="C37" s="39" t="str">
@@ -6245,8 +6231,8 @@
       <c r="BO37" s="60"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="124"/>
-      <c r="B38" s="72" t="s">
+      <c r="A38" s="130"/>
+      <c r="B38" s="71" t="s">
         <v>122</v>
       </c>
       <c r="C38" s="39" t="str">
@@ -6328,8 +6314,8 @@
       <c r="BO38" s="60"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="124"/>
-      <c r="B39" s="72" t="s">
+      <c r="A39" s="130"/>
+      <c r="B39" s="71" t="s">
         <v>132</v>
       </c>
       <c r="C39" s="39" t="str">
@@ -6411,8 +6397,8 @@
       <c r="BO39" s="60"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="124"/>
-      <c r="B40" s="88" t="s">
+      <c r="A40" s="130"/>
+      <c r="B40" s="87" t="s">
         <v>139</v>
       </c>
       <c r="C40" s="39" t="str">
@@ -6494,79 +6480,79 @@
       <c r="BO40" s="60"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="124"/>
-      <c r="B41" s="137" t="s">
+      <c r="A41" s="130"/>
+      <c r="B41" s="143" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="137"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="127"/>
-      <c r="L41" s="127"/>
-      <c r="M41" s="127"/>
-      <c r="N41" s="127"/>
-      <c r="O41" s="127"/>
-      <c r="P41" s="127"/>
-      <c r="Q41" s="127"/>
-      <c r="R41" s="127"/>
-      <c r="S41" s="127"/>
-      <c r="T41" s="127"/>
-      <c r="U41" s="127"/>
-      <c r="V41" s="127"/>
-      <c r="W41" s="127"/>
-      <c r="X41" s="127"/>
-      <c r="Y41" s="127"/>
-      <c r="Z41" s="127"/>
-      <c r="AA41" s="127"/>
-      <c r="AB41" s="127"/>
-      <c r="AC41" s="127"/>
-      <c r="AD41" s="127"/>
-      <c r="AE41" s="127"/>
-      <c r="AF41" s="127"/>
-      <c r="AG41" s="127"/>
-      <c r="AH41" s="127"/>
-      <c r="AI41" s="127"/>
-      <c r="AJ41" s="127"/>
-      <c r="AK41" s="127"/>
-      <c r="AL41" s="127"/>
-      <c r="AM41" s="127"/>
-      <c r="AN41" s="127"/>
-      <c r="AO41" s="127"/>
-      <c r="AP41" s="127"/>
-      <c r="AQ41" s="127"/>
-      <c r="AR41" s="127"/>
-      <c r="AS41" s="127"/>
-      <c r="AT41" s="127"/>
-      <c r="AU41" s="127"/>
-      <c r="AV41" s="127"/>
-      <c r="AW41" s="127"/>
-      <c r="AX41" s="127"/>
-      <c r="AY41" s="127"/>
-      <c r="AZ41" s="127"/>
-      <c r="BA41" s="127"/>
-      <c r="BB41" s="127"/>
-      <c r="BC41" s="127"/>
-      <c r="BD41" s="127"/>
-      <c r="BE41" s="127"/>
-      <c r="BF41" s="127"/>
-      <c r="BG41" s="127"/>
-      <c r="BH41" s="127"/>
-      <c r="BI41" s="127"/>
-      <c r="BJ41" s="127"/>
-      <c r="BK41" s="127"/>
-      <c r="BL41" s="127"/>
-      <c r="BM41" s="127"/>
-      <c r="BN41" s="127"/>
-      <c r="BO41" s="128"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="143"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="143"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="132"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133"/>
+      <c r="M41" s="133"/>
+      <c r="N41" s="133"/>
+      <c r="O41" s="133"/>
+      <c r="P41" s="133"/>
+      <c r="Q41" s="133"/>
+      <c r="R41" s="133"/>
+      <c r="S41" s="133"/>
+      <c r="T41" s="133"/>
+      <c r="U41" s="133"/>
+      <c r="V41" s="133"/>
+      <c r="W41" s="133"/>
+      <c r="X41" s="133"/>
+      <c r="Y41" s="133"/>
+      <c r="Z41" s="133"/>
+      <c r="AA41" s="133"/>
+      <c r="AB41" s="133"/>
+      <c r="AC41" s="133"/>
+      <c r="AD41" s="133"/>
+      <c r="AE41" s="133"/>
+      <c r="AF41" s="133"/>
+      <c r="AG41" s="133"/>
+      <c r="AH41" s="133"/>
+      <c r="AI41" s="133"/>
+      <c r="AJ41" s="133"/>
+      <c r="AK41" s="133"/>
+      <c r="AL41" s="133"/>
+      <c r="AM41" s="133"/>
+      <c r="AN41" s="133"/>
+      <c r="AO41" s="133"/>
+      <c r="AP41" s="133"/>
+      <c r="AQ41" s="133"/>
+      <c r="AR41" s="133"/>
+      <c r="AS41" s="133"/>
+      <c r="AT41" s="133"/>
+      <c r="AU41" s="133"/>
+      <c r="AV41" s="133"/>
+      <c r="AW41" s="133"/>
+      <c r="AX41" s="133"/>
+      <c r="AY41" s="133"/>
+      <c r="AZ41" s="133"/>
+      <c r="BA41" s="133"/>
+      <c r="BB41" s="133"/>
+      <c r="BC41" s="133"/>
+      <c r="BD41" s="133"/>
+      <c r="BE41" s="133"/>
+      <c r="BF41" s="133"/>
+      <c r="BG41" s="133"/>
+      <c r="BH41" s="133"/>
+      <c r="BI41" s="133"/>
+      <c r="BJ41" s="133"/>
+      <c r="BK41" s="133"/>
+      <c r="BL41" s="133"/>
+      <c r="BM41" s="133"/>
+      <c r="BN41" s="133"/>
+      <c r="BO41" s="134"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="124"/>
-      <c r="B42" s="87" t="s">
+      <c r="A42" s="130"/>
+      <c r="B42" s="86" t="s">
         <v>110</v>
       </c>
       <c r="C42" s="39" t="str">
@@ -6648,8 +6634,8 @@
       <c r="BO42" s="60"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="124"/>
-      <c r="B43" s="88" t="s">
+      <c r="A43" s="130"/>
+      <c r="B43" s="87" t="s">
         <v>127</v>
       </c>
       <c r="C43" s="39" t="str">
@@ -6731,8 +6717,8 @@
       <c r="BO43" s="60"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="124"/>
-      <c r="B44" s="88" t="s">
+      <c r="A44" s="130"/>
+      <c r="B44" s="87" t="s">
         <v>133</v>
       </c>
       <c r="C44" s="39" t="str">
@@ -6814,8 +6800,8 @@
       <c r="BO44" s="60"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="124"/>
-      <c r="B45" s="93" t="s">
+      <c r="A45" s="130"/>
+      <c r="B45" s="92" t="s">
         <v>135</v>
       </c>
       <c r="C45" s="39" t="str">
@@ -6897,25 +6883,25 @@
       <c r="BO45" s="60"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="124"/>
-      <c r="B46" s="120" t="s">
+      <c r="A46" s="130"/>
+      <c r="B46" s="119" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="73" t="str">
+      <c r="C46" s="72" t="str">
         <f ca="1">IF(F46=E46, IF(TODAY()&gt;F46, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F46) - E46) / (F46 - E46) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D46" s="74" t="str">
+      <c r="D46" s="73" t="str">
         <f t="shared" si="10"/>
         <v>3일</v>
       </c>
-      <c r="E46" s="75">
+      <c r="E46" s="74">
         <v>45980</v>
       </c>
-      <c r="F46" s="75">
+      <c r="F46" s="74">
         <v>45982</v>
       </c>
-      <c r="G46" s="76" t="s">
+      <c r="G46" s="75" t="s">
         <v>105</v>
       </c>
       <c r="H46" s="59"/>
@@ -6980,8 +6966,8 @@
       <c r="BO46" s="60"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="124"/>
-      <c r="B47" s="85" t="s">
+      <c r="A47" s="130"/>
+      <c r="B47" s="84" t="s">
         <v>155</v>
       </c>
       <c r="C47" s="39" t="str">
@@ -7063,8 +7049,8 @@
       <c r="BO47" s="60"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="124"/>
-      <c r="B48" s="92" t="s">
+      <c r="A48" s="130"/>
+      <c r="B48" s="91" t="s">
         <v>144</v>
       </c>
       <c r="C48" s="20" t="str">
@@ -7140,87 +7126,87 @@
       <c r="BO48" s="29"/>
     </row>
     <row r="49" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A49" s="124"/>
-      <c r="B49" s="137" t="s">
+      <c r="A49" s="130"/>
+      <c r="B49" s="143" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="126"/>
-      <c r="I49" s="127"/>
-      <c r="J49" s="127"/>
-      <c r="K49" s="127"/>
-      <c r="L49" s="127"/>
-      <c r="M49" s="127"/>
-      <c r="N49" s="127"/>
-      <c r="O49" s="127"/>
-      <c r="P49" s="127"/>
-      <c r="Q49" s="127"/>
-      <c r="R49" s="127"/>
-      <c r="S49" s="127"/>
-      <c r="T49" s="127"/>
-      <c r="U49" s="127"/>
-      <c r="V49" s="127"/>
-      <c r="W49" s="127"/>
-      <c r="X49" s="127"/>
-      <c r="Y49" s="127"/>
-      <c r="Z49" s="127"/>
-      <c r="AA49" s="127"/>
-      <c r="AB49" s="127"/>
-      <c r="AC49" s="127"/>
-      <c r="AD49" s="127"/>
-      <c r="AE49" s="127"/>
-      <c r="AF49" s="127"/>
-      <c r="AG49" s="127"/>
-      <c r="AH49" s="127"/>
-      <c r="AI49" s="127"/>
-      <c r="AJ49" s="127"/>
-      <c r="AK49" s="127"/>
-      <c r="AL49" s="127"/>
-      <c r="AM49" s="127"/>
-      <c r="AN49" s="127"/>
-      <c r="AO49" s="127"/>
-      <c r="AP49" s="127"/>
-      <c r="AQ49" s="127"/>
-      <c r="AR49" s="127"/>
-      <c r="AS49" s="127"/>
-      <c r="AT49" s="127"/>
-      <c r="AU49" s="127"/>
-      <c r="AV49" s="127"/>
-      <c r="AW49" s="127"/>
-      <c r="AX49" s="127"/>
-      <c r="AY49" s="127"/>
-      <c r="AZ49" s="127"/>
-      <c r="BA49" s="127"/>
-      <c r="BB49" s="127"/>
-      <c r="BC49" s="127"/>
-      <c r="BD49" s="127"/>
-      <c r="BE49" s="127"/>
-      <c r="BF49" s="127"/>
-      <c r="BG49" s="127"/>
-      <c r="BH49" s="127"/>
-      <c r="BI49" s="127"/>
-      <c r="BJ49" s="127"/>
-      <c r="BK49" s="127"/>
-      <c r="BL49" s="127"/>
-      <c r="BM49" s="127"/>
-      <c r="BN49" s="127"/>
-      <c r="BO49" s="128"/>
+      <c r="C49" s="143"/>
+      <c r="D49" s="143"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="143"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="132"/>
+      <c r="I49" s="133"/>
+      <c r="J49" s="133"/>
+      <c r="K49" s="133"/>
+      <c r="L49" s="133"/>
+      <c r="M49" s="133"/>
+      <c r="N49" s="133"/>
+      <c r="O49" s="133"/>
+      <c r="P49" s="133"/>
+      <c r="Q49" s="133"/>
+      <c r="R49" s="133"/>
+      <c r="S49" s="133"/>
+      <c r="T49" s="133"/>
+      <c r="U49" s="133"/>
+      <c r="V49" s="133"/>
+      <c r="W49" s="133"/>
+      <c r="X49" s="133"/>
+      <c r="Y49" s="133"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="133"/>
+      <c r="AB49" s="133"/>
+      <c r="AC49" s="133"/>
+      <c r="AD49" s="133"/>
+      <c r="AE49" s="133"/>
+      <c r="AF49" s="133"/>
+      <c r="AG49" s="133"/>
+      <c r="AH49" s="133"/>
+      <c r="AI49" s="133"/>
+      <c r="AJ49" s="133"/>
+      <c r="AK49" s="133"/>
+      <c r="AL49" s="133"/>
+      <c r="AM49" s="133"/>
+      <c r="AN49" s="133"/>
+      <c r="AO49" s="133"/>
+      <c r="AP49" s="133"/>
+      <c r="AQ49" s="133"/>
+      <c r="AR49" s="133"/>
+      <c r="AS49" s="133"/>
+      <c r="AT49" s="133"/>
+      <c r="AU49" s="133"/>
+      <c r="AV49" s="133"/>
+      <c r="AW49" s="133"/>
+      <c r="AX49" s="133"/>
+      <c r="AY49" s="133"/>
+      <c r="AZ49" s="133"/>
+      <c r="BA49" s="133"/>
+      <c r="BB49" s="133"/>
+      <c r="BC49" s="133"/>
+      <c r="BD49" s="133"/>
+      <c r="BE49" s="133"/>
+      <c r="BF49" s="133"/>
+      <c r="BG49" s="133"/>
+      <c r="BH49" s="133"/>
+      <c r="BI49" s="133"/>
+      <c r="BJ49" s="133"/>
+      <c r="BK49" s="133"/>
+      <c r="BL49" s="133"/>
+      <c r="BM49" s="133"/>
+      <c r="BN49" s="133"/>
+      <c r="BO49" s="134"/>
     </row>
     <row r="50" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A50" s="124"/>
-      <c r="B50" s="101" t="s">
+      <c r="A50" s="130"/>
+      <c r="B50" s="100" t="s">
         <v>128</v>
       </c>
       <c r="C50" s="44" t="str">
-        <f t="shared" ref="C50:C71" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C50:C70" ca="1" si="12">IF(F50=E50, IF(TODAY()&gt;F50, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F50) - E50) / (F50 - E50) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D50" s="104" t="str">
-        <f t="shared" ref="D50:D71" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
+      <c r="D50" s="103" t="str">
+        <f t="shared" ref="D50:D70" si="13">IF(AND(F50&lt;&gt;"", E50&lt;&gt;""), F50 - E50 + 1 &amp; "일", "")</f>
         <v>7일</v>
       </c>
       <c r="E50" s="45">
@@ -7229,7 +7215,7 @@
       <c r="F50" s="45">
         <v>45977</v>
       </c>
-      <c r="G50" s="102" t="s">
+      <c r="G50" s="101" t="s">
         <v>101</v>
       </c>
       <c r="H50" s="59"/>
@@ -7294,28 +7280,28 @@
       <c r="BO50" s="60"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51" s="124"/>
-      <c r="B51" s="121" t="s">
+      <c r="A51" s="130"/>
+      <c r="B51" s="120" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="109" t="str">
+      <c r="C51" s="108" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D51" s="110" t="str">
+      <c r="D51" s="109" t="str">
         <f t="shared" si="13"/>
         <v>9일</v>
       </c>
-      <c r="E51" s="111">
+      <c r="E51" s="110">
         <v>45971</v>
       </c>
-      <c r="F51" s="111">
+      <c r="F51" s="110">
         <v>45979</v>
       </c>
-      <c r="G51" s="113" t="s">
+      <c r="G51" s="112" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="103"/>
+      <c r="H51" s="102"/>
       <c r="I51" s="60"/>
       <c r="J51" s="60"/>
       <c r="K51" s="60"/>
@@ -7377,28 +7363,28 @@
       <c r="BO51" s="60"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52" s="124"/>
-      <c r="B52" s="122" t="s">
+      <c r="A52" s="130"/>
+      <c r="B52" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="109" t="str">
+      <c r="C52" s="108" t="str">
         <f t="shared" ref="C52" ca="1" si="14">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="110" t="str">
+      <c r="D52" s="109" t="str">
         <f t="shared" ref="D52:D55" si="15">IF(AND(F52&lt;&gt;"", E52&lt;&gt;""), F52 - E52 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
-      <c r="E52" s="111">
+      <c r="E52" s="110">
         <v>45971</v>
       </c>
-      <c r="F52" s="111">
+      <c r="F52" s="110">
         <v>45979</v>
       </c>
-      <c r="G52" s="113" t="s">
+      <c r="G52" s="112" t="s">
         <v>103</v>
       </c>
-      <c r="H52" s="103"/>
+      <c r="H52" s="102"/>
       <c r="I52" s="60"/>
       <c r="J52" s="60"/>
       <c r="K52" s="60"/>
@@ -7460,86 +7446,86 @@
       <c r="BO52" s="60"/>
     </row>
     <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53" s="124"/>
-      <c r="B53" s="144" t="s">
+      <c r="A53" s="130"/>
+      <c r="B53" s="147" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="141"/>
-      <c r="G53" s="145"/>
-      <c r="H53" s="103"/>
-      <c r="I53" s="60"/>
-      <c r="J53" s="60"/>
-      <c r="K53" s="60"/>
-      <c r="L53" s="61"/>
-      <c r="M53" s="62"/>
-      <c r="N53" s="60"/>
-      <c r="O53" s="60"/>
-      <c r="P53" s="60"/>
-      <c r="Q53" s="60"/>
-      <c r="R53" s="60"/>
-      <c r="S53" s="61"/>
-      <c r="T53" s="62"/>
-      <c r="U53" s="60"/>
-      <c r="V53" s="60"/>
-      <c r="W53" s="60"/>
-      <c r="X53" s="60"/>
-      <c r="Y53" s="60"/>
-      <c r="Z53" s="61"/>
-      <c r="AA53" s="62"/>
-      <c r="AB53" s="60"/>
-      <c r="AC53" s="60"/>
-      <c r="AD53" s="60"/>
-      <c r="AE53" s="60"/>
-      <c r="AF53" s="60"/>
-      <c r="AG53" s="61"/>
-      <c r="AH53" s="62"/>
-      <c r="AI53" s="60"/>
-      <c r="AJ53" s="60"/>
-      <c r="AK53" s="60"/>
-      <c r="AL53" s="60"/>
-      <c r="AM53" s="60"/>
-      <c r="AN53" s="61"/>
-      <c r="AO53" s="62"/>
-      <c r="AP53" s="60"/>
-      <c r="AQ53" s="60"/>
-      <c r="AR53" s="60"/>
-      <c r="AS53" s="60"/>
-      <c r="AT53" s="60"/>
-      <c r="AU53" s="61"/>
-      <c r="AV53" s="62"/>
-      <c r="AW53" s="60"/>
-      <c r="AX53" s="60"/>
-      <c r="AY53" s="60"/>
-      <c r="AZ53" s="60"/>
-      <c r="BA53" s="60"/>
-      <c r="BB53" s="61"/>
-      <c r="BC53" s="62"/>
-      <c r="BD53" s="60"/>
-      <c r="BE53" s="60"/>
-      <c r="BF53" s="60"/>
-      <c r="BG53" s="60"/>
-      <c r="BH53" s="60"/>
-      <c r="BI53" s="61"/>
-      <c r="BJ53" s="62"/>
-      <c r="BK53" s="60"/>
-      <c r="BL53" s="60"/>
-      <c r="BM53" s="60"/>
-      <c r="BN53" s="60"/>
-      <c r="BO53" s="60"/>
+      <c r="C53" s="148"/>
+      <c r="D53" s="148"/>
+      <c r="E53" s="148"/>
+      <c r="F53" s="148"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="132"/>
+      <c r="I53" s="133"/>
+      <c r="J53" s="133"/>
+      <c r="K53" s="133"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="133"/>
+      <c r="N53" s="133"/>
+      <c r="O53" s="133"/>
+      <c r="P53" s="133"/>
+      <c r="Q53" s="133"/>
+      <c r="R53" s="133"/>
+      <c r="S53" s="133"/>
+      <c r="T53" s="133"/>
+      <c r="U53" s="133"/>
+      <c r="V53" s="133"/>
+      <c r="W53" s="133"/>
+      <c r="X53" s="133"/>
+      <c r="Y53" s="133"/>
+      <c r="Z53" s="133"/>
+      <c r="AA53" s="133"/>
+      <c r="AB53" s="133"/>
+      <c r="AC53" s="133"/>
+      <c r="AD53" s="133"/>
+      <c r="AE53" s="133"/>
+      <c r="AF53" s="133"/>
+      <c r="AG53" s="133"/>
+      <c r="AH53" s="133"/>
+      <c r="AI53" s="133"/>
+      <c r="AJ53" s="133"/>
+      <c r="AK53" s="133"/>
+      <c r="AL53" s="133"/>
+      <c r="AM53" s="133"/>
+      <c r="AN53" s="133"/>
+      <c r="AO53" s="133"/>
+      <c r="AP53" s="133"/>
+      <c r="AQ53" s="133"/>
+      <c r="AR53" s="133"/>
+      <c r="AS53" s="133"/>
+      <c r="AT53" s="133"/>
+      <c r="AU53" s="133"/>
+      <c r="AV53" s="133"/>
+      <c r="AW53" s="133"/>
+      <c r="AX53" s="133"/>
+      <c r="AY53" s="133"/>
+      <c r="AZ53" s="133"/>
+      <c r="BA53" s="133"/>
+      <c r="BB53" s="133"/>
+      <c r="BC53" s="133"/>
+      <c r="BD53" s="133"/>
+      <c r="BE53" s="133"/>
+      <c r="BF53" s="133"/>
+      <c r="BG53" s="133"/>
+      <c r="BH53" s="133"/>
+      <c r="BI53" s="133"/>
+      <c r="BJ53" s="133"/>
+      <c r="BK53" s="133"/>
+      <c r="BL53" s="133"/>
+      <c r="BM53" s="133"/>
+      <c r="BN53" s="133"/>
+      <c r="BO53" s="134"/>
     </row>
     <row r="54" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="124"/>
-      <c r="B54" s="100" t="s">
+      <c r="A54" s="130"/>
+      <c r="B54" s="99" t="s">
         <v>150</v>
       </c>
       <c r="C54" s="47" t="str">
         <f t="shared" ref="C54" ca="1" si="16">IF(F54=E54, IF(TODAY()&gt;F54, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F54) - E54) / (F54 - E54) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D54" s="142" t="str">
+      <c r="D54" s="123" t="str">
         <f t="shared" ref="D54" si="17">IF(AND(F54&lt;&gt;"", E54&lt;&gt;""), F54 - E54 + 1 &amp; "일", "")</f>
         <v>2일</v>
       </c>
@@ -7549,7 +7535,7 @@
       <c r="F54" s="48">
         <v>45981</v>
       </c>
-      <c r="G54" s="143" t="s">
+      <c r="G54" s="124" t="s">
         <v>117</v>
       </c>
       <c r="H54" s="59"/>
@@ -7614,28 +7600,28 @@
       <c r="BO54" s="60"/>
     </row>
     <row r="55" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A55" s="124"/>
-      <c r="B55" s="123" t="s">
+      <c r="A55" s="130"/>
+      <c r="B55" s="122" t="s">
         <v>141</v>
       </c>
-      <c r="C55" s="109" t="str">
+      <c r="C55" s="108" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>100%</v>
       </c>
-      <c r="D55" s="110" t="str">
+      <c r="D55" s="109" t="str">
         <f t="shared" si="15"/>
         <v>2일</v>
       </c>
-      <c r="E55" s="111">
+      <c r="E55" s="110">
         <v>45979</v>
       </c>
-      <c r="F55" s="111">
+      <c r="F55" s="110">
         <v>45980</v>
       </c>
-      <c r="G55" s="112" t="s">
+      <c r="G55" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="H55" s="103"/>
+      <c r="H55" s="102"/>
       <c r="I55" s="60"/>
       <c r="J55" s="60"/>
       <c r="K55" s="60"/>
@@ -7697,25 +7683,25 @@
       <c r="BO55" s="60"/>
     </row>
     <row r="56" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="124"/>
-      <c r="B56" s="105" t="s">
+      <c r="A56" s="130"/>
+      <c r="B56" s="104" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>11.1%</v>
-      </c>
-      <c r="D56" s="106" t="str">
+        <v>33.3%</v>
+      </c>
+      <c r="D56" s="105" t="str">
         <f t="shared" si="13"/>
         <v>19일</v>
       </c>
-      <c r="E56" s="107">
+      <c r="E56" s="106">
         <v>45980</v>
       </c>
-      <c r="F56" s="107">
+      <c r="F56" s="106">
         <v>45998</v>
       </c>
-      <c r="G56" s="108" t="s">
+      <c r="G56" s="107" t="s">
         <v>134</v>
       </c>
       <c r="H56" s="59"/>
@@ -7780,16 +7766,16 @@
       <c r="BO56" s="60"/>
     </row>
     <row r="57" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A57" s="124"/>
-      <c r="B57" s="95" t="s">
+      <c r="A57" s="130"/>
+      <c r="B57" s="94" t="s">
         <v>136</v>
       </c>
       <c r="C57" s="20" t="str">
         <f ca="1">IF(F57=E57, IF(TODAY()&gt;F57, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F57) - E57) / (F57 - E57) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <v>7.7%</v>
       </c>
       <c r="D57" s="21" t="str">
-        <f>IF(AND(F57&lt;&gt;"", E57&lt;&gt;""), F57 - E57 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D57:D62" si="18">IF(AND(F57&lt;&gt;"", E57&lt;&gt;""), F57 - E57 + 1 &amp; "일", "")</f>
         <v>14일</v>
       </c>
       <c r="E57" s="22">
@@ -7798,7 +7784,7 @@
       <c r="F57" s="22">
         <v>45998</v>
       </c>
-      <c r="G57" s="68" t="s">
+      <c r="G57" s="67" t="s">
         <v>134</v>
       </c>
       <c r="H57" s="59"/>
@@ -7863,25 +7849,25 @@
       <c r="BO57" s="60"/>
     </row>
     <row r="58" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A58" s="124"/>
-      <c r="B58" s="146" t="s">
+      <c r="A58" s="130"/>
+      <c r="B58" s="125" t="s">
         <v>157</v>
       </c>
-      <c r="C58" s="147" t="str">
+      <c r="C58" s="126" t="str">
         <f ca="1">IF(F58=E58, IF(TODAY()&gt;F58, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F58) - E58) / (F58 - E58) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
-      <c r="D58" s="148" t="str">
-        <f>IF(AND(F58&lt;&gt;"", E58&lt;&gt;""), F58 - E58 + 1 &amp; "일", "")</f>
+      <c r="D58" s="127" t="str">
+        <f t="shared" si="18"/>
         <v>10일</v>
       </c>
-      <c r="E58" s="149">
+      <c r="E58" s="128">
         <v>45989</v>
       </c>
-      <c r="F58" s="149">
+      <c r="F58" s="128">
         <v>45998</v>
       </c>
-      <c r="G58" s="150" t="s">
+      <c r="G58" s="129" t="s">
         <v>108</v>
       </c>
       <c r="H58" s="59"/>
@@ -7946,25 +7932,25 @@
       <c r="BO58" s="60"/>
     </row>
     <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A59" s="124"/>
-      <c r="B59" s="115" t="s">
+      <c r="A59" s="130"/>
+      <c r="B59" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="C59" s="116" t="str">
+      <c r="C59" s="115" t="str">
         <f ca="1">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D59" s="117" t="str">
-        <f>IF(AND(F59&lt;&gt;"", E59&lt;&gt;""), F59 - E59 + 1 &amp; "일", "")</f>
+      <c r="D59" s="116" t="str">
+        <f t="shared" si="18"/>
         <v>3일</v>
       </c>
-      <c r="E59" s="75">
+      <c r="E59" s="74">
         <v>45980</v>
       </c>
-      <c r="F59" s="75">
+      <c r="F59" s="74">
         <v>45982</v>
       </c>
-      <c r="G59" s="118" t="s">
+      <c r="G59" s="117" t="s">
         <v>117</v>
       </c>
       <c r="H59" s="59"/>
@@ -8029,25 +8015,25 @@
       <c r="BO59" s="60"/>
     </row>
     <row r="60" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A60" s="124"/>
-      <c r="B60" s="94" t="s">
+      <c r="A60" s="130"/>
+      <c r="B60" s="93" t="s">
         <v>130</v>
       </c>
       <c r="C60" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
+        <v>25%</v>
       </c>
       <c r="D60" s="21" t="str">
-        <f>IF(AND(F60&lt;&gt;"", E60&lt;&gt;""), F60 - E60 + 1 &amp; "일", "")</f>
-        <v>10일</v>
+        <f t="shared" si="18"/>
+        <v>5일</v>
       </c>
       <c r="E60" s="22">
+        <v>45985</v>
+      </c>
+      <c r="F60" s="22">
         <v>45989</v>
       </c>
-      <c r="F60" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G60" s="69" t="s">
+      <c r="G60" s="68" t="s">
         <v>119</v>
       </c>
       <c r="H60" s="59"/>
@@ -8111,27 +8097,27 @@
       <c r="BN60" s="60"/>
       <c r="BO60" s="60"/>
     </row>
-    <row r="61" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A61" s="124"/>
-      <c r="B61" s="151" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" s="32" t="str">
+    <row r="61" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A61" s="130"/>
+      <c r="B61" s="150" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="72" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
-      </c>
-      <c r="D61" s="21" t="str">
-        <f>IF(AND(F61&lt;&gt;"", E61&lt;&gt;""), F61 - E61 + 1 &amp; "일", "")</f>
-        <v>10일</v>
-      </c>
-      <c r="E61" s="22">
+        <v>25%</v>
+      </c>
+      <c r="D61" s="73" t="str">
+        <f t="shared" si="18"/>
+        <v>5일</v>
+      </c>
+      <c r="E61" s="74">
+        <v>45985</v>
+      </c>
+      <c r="F61" s="74">
         <v>45989</v>
       </c>
-      <c r="F61" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G61" s="69" t="s">
-        <v>107</v>
+      <c r="G61" s="117" t="s">
+        <v>116</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60"/>
@@ -8195,16 +8181,16 @@
       <c r="BO61" s="60"/>
     </row>
     <row r="62" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A62" s="124"/>
+      <c r="A62" s="131"/>
       <c r="B62" s="94" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C62" s="20" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ref="C62" ca="1" si="19">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
       <c r="D62" s="21" t="str">
-        <f>IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
+        <f t="shared" si="18"/>
         <v>10일</v>
       </c>
       <c r="E62" s="22">
@@ -8213,8 +8199,8 @@
       <c r="F62" s="22">
         <v>45998</v>
       </c>
-      <c r="G62" s="69" t="s">
-        <v>116</v>
+      <c r="G62" s="67" t="s">
+        <v>117</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60"/>
@@ -8278,26 +8264,24 @@
       <c r="BO62" s="60"/>
     </row>
     <row r="63" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A63" s="125"/>
+      <c r="A63" s="130" t="s">
+        <v>90</v>
+      </c>
       <c r="B63" s="95" t="s">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="C63" s="20" t="str">
-        <f t="shared" ref="C63" ca="1" si="18">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>100%</v>
       </c>
       <c r="D63" s="21" t="str">
-        <f>IF(AND(F63&lt;&gt;"", E63&lt;&gt;""), F63 - E63 + 1 &amp; "일", "")</f>
-        <v>10일</v>
-      </c>
-      <c r="E63" s="22">
-        <v>45989</v>
-      </c>
-      <c r="F63" s="22">
-        <v>45998</v>
-      </c>
-      <c r="G63" s="68" t="s">
-        <v>117</v>
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="69" t="s">
+        <v>100</v>
       </c>
       <c r="H63" s="59"/>
       <c r="I63" s="60"/>
@@ -8360,15 +8344,13 @@
       <c r="BN63" s="60"/>
       <c r="BO63" s="60"/>
     </row>
-    <row r="64" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A64" s="124" t="s">
-        <v>90</v>
-      </c>
+    <row r="64" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A64" s="130"/>
       <c r="B64" s="96" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="20" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <v>88</v>
+      </c>
+      <c r="C64" s="31" t="str">
+        <f t="shared" ref="C64:C65" ca="1" si="20">IF(F64=E64, IF(TODAY()&gt;F64, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F64) - E64) / (F64 - E64) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D64" s="21" t="str">
@@ -8377,7 +8359,7 @@
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
-      <c r="G64" s="70" t="s">
+      <c r="G64" s="69" t="s">
         <v>100</v>
       </c>
       <c r="H64" s="59"/>
@@ -8442,12 +8424,12 @@
       <c r="BO64" s="60"/>
     </row>
     <row r="65" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A65" s="124"/>
-      <c r="B65" s="97" t="s">
-        <v>88</v>
+      <c r="A65" s="130"/>
+      <c r="B65" s="96" t="s">
+        <v>89</v>
       </c>
       <c r="C65" s="31" t="str">
-        <f t="shared" ref="C65" ca="1" si="19">IF(F65=E65, IF(TODAY()&gt;F65, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F65) - E65) / (F65 - E65) * 100, 1) &amp; "%")</f>
+        <f t="shared" ca="1" si="20"/>
         <v>100%</v>
       </c>
       <c r="D65" s="21" t="str">
@@ -8456,7 +8438,7 @@
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="70" t="s">
+      <c r="G65" s="69" t="s">
         <v>100</v>
       </c>
       <c r="H65" s="59"/>
@@ -8521,19 +8503,26 @@
       <c r="BO65" s="60"/>
     </row>
     <row r="66" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A66" s="124"/>
-      <c r="B66" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C66" s="67"/>
-      <c r="D66" s="21" t="str">
+      <c r="A66" s="130"/>
+      <c r="B66" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="35" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>0%</v>
+      </c>
+      <c r="D66" s="70" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="70" t="s">
-        <v>100</v>
+        <v>12일</v>
+      </c>
+      <c r="E66" s="36">
+        <v>45999</v>
+      </c>
+      <c r="F66" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="H66" s="59"/>
       <c r="I66" s="60"/>
@@ -8596,26 +8585,26 @@
       <c r="BN66" s="60"/>
       <c r="BO66" s="60"/>
     </row>
-    <row r="67" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A67" s="124"/>
-      <c r="B67" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67" s="35" t="str">
+    <row r="67" spans="1:67" ht="15" customHeight="1" thickBot="1">
+      <c r="A67" s="130"/>
+      <c r="B67" s="97" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" s="32" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
-      <c r="D67" s="71" t="str">
+      <c r="D67" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>12일</v>
-      </c>
-      <c r="E67" s="36">
+        <v>10일</v>
+      </c>
+      <c r="E67" s="33">
         <v>45999</v>
       </c>
-      <c r="F67" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G67" s="37" t="s">
+      <c r="F67" s="33">
+        <v>46008</v>
+      </c>
+      <c r="G67" s="34" t="s">
         <v>98</v>
       </c>
       <c r="H67" s="59"/>
@@ -8679,12 +8668,12 @@
       <c r="BN67" s="60"/>
       <c r="BO67" s="60"/>
     </row>
-    <row r="68" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A68" s="124"/>
-      <c r="B68" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C68" s="32" t="str">
+    <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A68" s="130"/>
+      <c r="B68" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>0%</v>
       </c>
@@ -8692,13 +8681,13 @@
         <f t="shared" si="13"/>
         <v>10일</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="22">
         <v>45999</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="22">
         <v>46008</v>
       </c>
-      <c r="G68" s="34" t="s">
+      <c r="G68" s="23" t="s">
         <v>98</v>
       </c>
       <c r="H68" s="59"/>
@@ -8762,10 +8751,10 @@
       <c r="BN68" s="60"/>
       <c r="BO68" s="60"/>
     </row>
-    <row r="69" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A69" s="124"/>
-      <c r="B69" s="95" t="s">
-        <v>3</v>
+    <row r="69" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A69" s="130"/>
+      <c r="B69" s="94" t="s">
+        <v>92</v>
       </c>
       <c r="C69" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8773,13 +8762,13 @@
       </c>
       <c r="D69" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>10일</v>
+        <v>1일</v>
       </c>
       <c r="E69" s="22">
-        <v>45999</v>
+        <v>46010</v>
       </c>
       <c r="F69" s="22">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="G69" s="23" t="s">
         <v>98</v>
@@ -8846,9 +8835,9 @@
       <c r="BO69" s="60"/>
     </row>
     <row r="70" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A70" s="124"/>
-      <c r="B70" s="95" t="s">
-        <v>92</v>
+      <c r="A70" s="131"/>
+      <c r="B70" s="94" t="s">
+        <v>93</v>
       </c>
       <c r="C70" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -8928,92 +8917,12 @@
       <c r="BN70" s="60"/>
       <c r="BO70" s="60"/>
     </row>
-    <row r="71" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A71" s="125"/>
-      <c r="B71" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C71" s="20" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v>0%</v>
-      </c>
-      <c r="D71" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v>1일</v>
-      </c>
-      <c r="E71" s="22">
-        <v>46010</v>
-      </c>
-      <c r="F71" s="22">
-        <v>46010</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="H71" s="59"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="60"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="61"/>
-      <c r="M71" s="62"/>
-      <c r="N71" s="60"/>
-      <c r="O71" s="60"/>
-      <c r="P71" s="60"/>
-      <c r="Q71" s="60"/>
-      <c r="R71" s="60"/>
-      <c r="S71" s="61"/>
-      <c r="T71" s="62"/>
-      <c r="U71" s="60"/>
-      <c r="V71" s="60"/>
-      <c r="W71" s="60"/>
-      <c r="X71" s="60"/>
-      <c r="Y71" s="60"/>
-      <c r="Z71" s="61"/>
-      <c r="AA71" s="62"/>
-      <c r="AB71" s="60"/>
-      <c r="AC71" s="60"/>
-      <c r="AD71" s="60"/>
-      <c r="AE71" s="60"/>
-      <c r="AF71" s="60"/>
-      <c r="AG71" s="61"/>
-      <c r="AH71" s="62"/>
-      <c r="AI71" s="60"/>
-      <c r="AJ71" s="60"/>
-      <c r="AK71" s="60"/>
-      <c r="AL71" s="60"/>
-      <c r="AM71" s="60"/>
-      <c r="AN71" s="61"/>
-      <c r="AO71" s="62"/>
-      <c r="AP71" s="60"/>
-      <c r="AQ71" s="60"/>
-      <c r="AR71" s="60"/>
-      <c r="AS71" s="60"/>
-      <c r="AT71" s="60"/>
-      <c r="AU71" s="61"/>
-      <c r="AV71" s="62"/>
-      <c r="AW71" s="60"/>
-      <c r="AX71" s="60"/>
-      <c r="AY71" s="60"/>
-      <c r="AZ71" s="60"/>
-      <c r="BA71" s="60"/>
-      <c r="BB71" s="61"/>
-      <c r="BC71" s="62"/>
-      <c r="BD71" s="60"/>
-      <c r="BE71" s="60"/>
-      <c r="BF71" s="60"/>
-      <c r="BG71" s="60"/>
-      <c r="BH71" s="60"/>
-      <c r="BI71" s="61"/>
-      <c r="BJ71" s="62"/>
-      <c r="BK71" s="60"/>
-      <c r="BL71" s="60"/>
-      <c r="BM71" s="60"/>
-      <c r="BN71" s="60"/>
-      <c r="BO71" s="60"/>
+    <row r="71" spans="1:67">
+      <c r="E71" s="7"/>
+      <c r="F71" s="1"/>
+      <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:67">
-      <c r="E72" s="7"/>
-      <c r="F72" s="1"/>
       <c r="I72" s="3"/>
     </row>
     <row r="73" spans="1:67">
@@ -9026,44 +8935,45 @@
       <c r="I75" s="3"/>
     </row>
     <row r="76" spans="1:67">
-      <c r="I76" s="3"/>
+      <c r="B76" s="8" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="77" spans="1:67">
-      <c r="B77" s="8" t="s">
-        <v>94</v>
-      </c>
+    <row r="77" spans="1:67" ht="16.5">
+      <c r="B77" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="1:67" ht="16.5">
-      <c r="B78" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="3"/>
+    <row r="78" spans="1:67">
+      <c r="B78" s="10" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="79" spans="1:67">
-      <c r="B79" s="10" t="s">
-        <v>96</v>
-      </c>
+      <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:67">
       <c r="C80" s="3"/>
     </row>
-    <row r="81" spans="2:8">
-      <c r="C81" s="3"/>
+    <row r="81" spans="2:8"/>
+    <row r="82" spans="2:8"/>
+    <row r="83" spans="2:8" ht="16.5">
+      <c r="B83" s="2"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
     </row>
-    <row r="82" spans="2:8"/>
-    <row r="83" spans="2:8"/>
-    <row r="84" spans="2:8" ht="16.5">
-      <c r="B84" s="2"/>
+    <row r="84" spans="2:8">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="2:8">
-      <c r="C85" s="3"/>
+    <row r="85" spans="2:8" ht="16.5">
+      <c r="B85" s="2"/>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="2:8" ht="16.5">
-      <c r="B86" s="2"/>
+    <row r="86" spans="2:8">
+      <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="2:8">
@@ -9071,26 +8981,22 @@
       <c r="D87" s="3"/>
     </row>
     <row r="88" spans="2:8">
-      <c r="C88" s="3"/>
       <c r="D88" s="3"/>
     </row>
     <row r="89" spans="2:8">
       <c r="D89" s="3"/>
+      <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" ht="15" customHeight="1">
       <c r="D90" s="3"/>
-      <c r="H90" s="11"/>
     </row>
     <row r="91" spans="2:8" ht="15" customHeight="1">
+      <c r="C91" s="3"/>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="2:8" ht="15" customHeight="1">
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A64:A71"/>
+  <mergeCells count="16">
+    <mergeCell ref="A63:A70"/>
     <mergeCell ref="H49:BO49"/>
     <mergeCell ref="H41:BO41"/>
     <mergeCell ref="C1:E1"/>
@@ -9101,10 +9007,11 @@
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A63"/>
+    <mergeCell ref="A12:A62"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="H53:BO53"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\redgu\OneDrive\Desktop\related_Re_View\Re_View_Doc\2. WBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325F4765-0B09-4E96-917A-93812B7B0AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209ABEBD-6BC7-44F3-8952-697724395A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1035" windowWidth="20835" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="163">
   <si>
     <t>팀명</t>
   </si>
@@ -466,38 +466,6 @@
   </si>
   <si>
     <t>마이페이지 결제 Preview 및 결제 완료 UI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="7"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>처리 시스템(트랜잭션화 및 이미지 처리)</t>
-    </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1264,12 +1232,158 @@
     <r>
       <rPr>
         <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품 상세페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">후기, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>QnAUI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 페이지와 연결되는 About UI</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AWS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>회원의</t>
+      <t>연결(</t>
     </r>
     <r>
       <rPr>
@@ -1278,7 +1392,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">EC2, S3 </t>
     </r>
     <r>
       <rPr>
@@ -1288,7 +1402,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>피부</t>
+      <t>등)</t>
     </r>
     <r>
       <rPr>
@@ -1307,7 +1421,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>타입에</t>
+      <t xml:space="preserve">및 </t>
     </r>
     <r>
       <rPr>
@@ -1316,7 +1430,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>CICD</t>
     </r>
     <r>
       <rPr>
@@ -1326,16 +1440,13 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>추천되는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>작업</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>FE:BE</t>
     </r>
     <r>
       <rPr>
@@ -1345,156 +1456,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>리뷰 추천 알고리즘</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상품</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>리뷰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상품 상세페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
+      <t>연결 테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">후기, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>QnAUI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 페이지와 연결되는 About UI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AWS </t>
     </r>
     <r>
       <rPr>
@@ -1504,98 +1475,6 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>연결(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">EC2, S3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">및 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CICD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>FE:BE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>연결 테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
       <t>및 버그 보완</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -1692,6 +1571,127 @@
         <family val="3"/>
       </rPr>
       <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리 시스템(트랜잭션화 및 이미지 처리)</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타입에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추천되는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰 추천 알고리즘</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1703,7 +1703,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1922,26 +1922,6 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="7"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="7"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="7"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -1958,30 +1938,9 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="7"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color theme="3"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="7"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -2049,6 +2008,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -2665,7 +2631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2835,12 +2801,6 @@
     <xf numFmtId="0" fontId="22" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2859,39 +2819,18 @@
     <xf numFmtId="0" fontId="22" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="33" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2940,118 +2879,130 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="41" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="35" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="35" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="35" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="35" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3078,10 +3029,10 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3096,7 +3047,7 @@
     <xf numFmtId="0" fontId="20" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3108,19 +3059,22 @@
     <xf numFmtId="0" fontId="23" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3363,31 +3317,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="133" t="s">
+      <c r="C1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="135" t="s">
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3451,7 +3405,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="136" t="s">
+      <c r="G2" s="131" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3636,13 +3590,13 @@
       </c>
     </row>
     <row r="3" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="60"/>
+      <c r="A3" s="58"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="137"/>
+      <c r="G3" s="132"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3825,10 +3779,10 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="66" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="20" t="str">
@@ -3910,8 +3864,8 @@
       <c r="BO4" s="44"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="139"/>
-      <c r="B5" s="72" t="s">
+      <c r="A5" s="134"/>
+      <c r="B5" s="66" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="20" t="str">
@@ -3993,8 +3947,8 @@
       <c r="BO5" s="49"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="139"/>
-      <c r="B6" s="72" t="s">
+      <c r="A6" s="134"/>
+      <c r="B6" s="66" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="20" t="str">
@@ -4076,8 +4030,8 @@
       <c r="BO6" s="49"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="139"/>
-      <c r="B7" s="79" t="s">
+      <c r="A7" s="134"/>
+      <c r="B7" s="70" t="s">
         <v>75</v>
       </c>
       <c r="C7" s="20" t="str">
@@ -4159,8 +4113,8 @@
       <c r="BO7" s="49"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="139"/>
-      <c r="B8" s="80" t="s">
+      <c r="A8" s="134"/>
+      <c r="B8" s="71" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="20" t="str">
@@ -4177,7 +4131,7 @@
       <c r="F8" s="22">
         <v>45966</v>
       </c>
-      <c r="G8" s="81" t="s">
+      <c r="G8" s="72" t="s">
         <v>96</v>
       </c>
       <c r="H8" s="48"/>
@@ -4242,8 +4196,8 @@
       <c r="BO8" s="49"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="139"/>
-      <c r="B9" s="72" t="s">
+      <c r="A9" s="134"/>
+      <c r="B9" s="66" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="20" t="str">
@@ -4325,8 +4279,8 @@
       <c r="BO9" s="49"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="139"/>
-      <c r="B10" s="79" t="s">
+      <c r="A10" s="134"/>
+      <c r="B10" s="70" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="20" t="str">
@@ -4408,8 +4362,8 @@
       <c r="BO10" s="49"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="139"/>
-      <c r="B11" s="82" t="s">
+      <c r="A11" s="134"/>
+      <c r="B11" s="73" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="31" t="str">
@@ -4420,13 +4374,13 @@
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E11" s="83">
+      <c r="E11" s="74">
         <v>45957</v>
       </c>
-      <c r="F11" s="83">
+      <c r="F11" s="74">
         <v>45958</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="75" t="s">
         <v>105</v>
       </c>
       <c r="H11" s="48"/>
@@ -4491,10 +4445,10 @@
       <c r="BO11" s="49"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="144" t="s">
+      <c r="A12" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="57" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="35" t="str">
@@ -4576,8 +4530,8 @@
       <c r="BO12" s="49"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="128"/>
-      <c r="B13" s="78" t="s">
+      <c r="A13" s="123"/>
+      <c r="B13" s="69" t="s">
         <v>82</v>
       </c>
       <c r="C13" s="32" t="str">
@@ -4659,8 +4613,8 @@
       <c r="BO13" s="49"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="128"/>
-      <c r="B14" s="85" t="s">
+      <c r="A14" s="123"/>
+      <c r="B14" s="76" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="31" t="str">
@@ -4671,13 +4625,13 @@
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="74">
         <v>45959</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="74">
         <v>45959</v>
       </c>
-      <c r="G14" s="86" t="s">
+      <c r="G14" s="77" t="s">
         <v>95</v>
       </c>
       <c r="H14" s="48"/>
@@ -4742,8 +4696,8 @@
       <c r="BO14" s="49"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="128"/>
-      <c r="B15" s="59" t="s">
+      <c r="A15" s="123"/>
+      <c r="B15" s="57" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="35" t="str">
@@ -4825,9 +4779,9 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="128"/>
-      <c r="B16" s="87" t="s">
-        <v>137</v>
+      <c r="A16" s="123"/>
+      <c r="B16" s="78" t="s">
+        <v>136</v>
       </c>
       <c r="C16" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4843,7 +4797,7 @@
       <c r="F16" s="33">
         <v>45966</v>
       </c>
-      <c r="G16" s="88" t="s">
+      <c r="G16" s="79" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="48"/>
@@ -4908,80 +4862,80 @@
       <c r="BO16" s="42"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="128"/>
-      <c r="B17" s="142" t="s">
+      <c r="A17" s="123"/>
+      <c r="B17" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="142"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="131"/>
-      <c r="S17" s="131"/>
-      <c r="T17" s="131"/>
-      <c r="U17" s="131"/>
-      <c r="V17" s="131"/>
-      <c r="W17" s="131"/>
-      <c r="X17" s="131"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="131"/>
-      <c r="AA17" s="131"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="131"/>
-      <c r="AD17" s="131"/>
-      <c r="AE17" s="131"/>
-      <c r="AF17" s="131"/>
-      <c r="AG17" s="131"/>
-      <c r="AH17" s="131"/>
-      <c r="AI17" s="131"/>
-      <c r="AJ17" s="131"/>
-      <c r="AK17" s="131"/>
-      <c r="AL17" s="131"/>
-      <c r="AM17" s="131"/>
-      <c r="AN17" s="131"/>
-      <c r="AO17" s="131"/>
-      <c r="AP17" s="131"/>
-      <c r="AQ17" s="131"/>
-      <c r="AR17" s="131"/>
-      <c r="AS17" s="131"/>
-      <c r="AT17" s="131"/>
-      <c r="AU17" s="131"/>
-      <c r="AV17" s="131"/>
-      <c r="AW17" s="131"/>
-      <c r="AX17" s="131"/>
-      <c r="AY17" s="131"/>
-      <c r="AZ17" s="131"/>
-      <c r="BA17" s="131"/>
-      <c r="BB17" s="131"/>
-      <c r="BC17" s="131"/>
-      <c r="BD17" s="131"/>
-      <c r="BE17" s="131"/>
-      <c r="BF17" s="131"/>
-      <c r="BG17" s="131"/>
-      <c r="BH17" s="131"/>
-      <c r="BI17" s="131"/>
-      <c r="BJ17" s="131"/>
-      <c r="BK17" s="131"/>
-      <c r="BL17" s="131"/>
-      <c r="BM17" s="131"/>
-      <c r="BN17" s="131"/>
-      <c r="BO17" s="132"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="126"/>
+      <c r="U17" s="126"/>
+      <c r="V17" s="126"/>
+      <c r="W17" s="126"/>
+      <c r="X17" s="126"/>
+      <c r="Y17" s="126"/>
+      <c r="Z17" s="126"/>
+      <c r="AA17" s="126"/>
+      <c r="AB17" s="126"/>
+      <c r="AC17" s="126"/>
+      <c r="AD17" s="126"/>
+      <c r="AE17" s="126"/>
+      <c r="AF17" s="126"/>
+      <c r="AG17" s="126"/>
+      <c r="AH17" s="126"/>
+      <c r="AI17" s="126"/>
+      <c r="AJ17" s="126"/>
+      <c r="AK17" s="126"/>
+      <c r="AL17" s="126"/>
+      <c r="AM17" s="126"/>
+      <c r="AN17" s="126"/>
+      <c r="AO17" s="126"/>
+      <c r="AP17" s="126"/>
+      <c r="AQ17" s="126"/>
+      <c r="AR17" s="126"/>
+      <c r="AS17" s="126"/>
+      <c r="AT17" s="126"/>
+      <c r="AU17" s="126"/>
+      <c r="AV17" s="126"/>
+      <c r="AW17" s="126"/>
+      <c r="AX17" s="126"/>
+      <c r="AY17" s="126"/>
+      <c r="AZ17" s="126"/>
+      <c r="BA17" s="126"/>
+      <c r="BB17" s="126"/>
+      <c r="BC17" s="126"/>
+      <c r="BD17" s="126"/>
+      <c r="BE17" s="126"/>
+      <c r="BF17" s="126"/>
+      <c r="BG17" s="126"/>
+      <c r="BH17" s="126"/>
+      <c r="BI17" s="126"/>
+      <c r="BJ17" s="126"/>
+      <c r="BK17" s="126"/>
+      <c r="BL17" s="126"/>
+      <c r="BM17" s="126"/>
+      <c r="BN17" s="126"/>
+      <c r="BO17" s="127"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="128"/>
-      <c r="B18" s="69" t="s">
-        <v>138</v>
+      <c r="A18" s="123"/>
+      <c r="B18" s="63" t="s">
+        <v>137</v>
       </c>
       <c r="C18" s="20" t="str">
         <f ca="1">IF(F18=E18, IF(TODAY()&gt;F18, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F18) - E18) / (F18 - E18) * 100, 1) &amp; "%")</f>
@@ -5062,8 +5016,8 @@
       <c r="BO18" s="44"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="128"/>
-      <c r="B19" s="76" t="s">
+      <c r="A19" s="123"/>
+      <c r="B19" s="67" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="20" t="str">
@@ -5145,8 +5099,8 @@
       <c r="BO19" s="49"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="128"/>
-      <c r="B20" s="89" t="s">
+      <c r="A20" s="123"/>
+      <c r="B20" s="80" t="s">
         <v>110</v>
       </c>
       <c r="C20" s="20" t="str">
@@ -5163,7 +5117,7 @@
       <c r="F20" s="22">
         <v>45967</v>
       </c>
-      <c r="G20" s="81" t="s">
+      <c r="G20" s="72" t="s">
         <v>104</v>
       </c>
       <c r="H20" s="48"/>
@@ -5228,80 +5182,80 @@
       <c r="BO20" s="49"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="128"/>
-      <c r="B21" s="140" t="s">
+      <c r="A21" s="123"/>
+      <c r="B21" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="131"/>
-      <c r="T21" s="131"/>
-      <c r="U21" s="131"/>
-      <c r="V21" s="131"/>
-      <c r="W21" s="131"/>
-      <c r="X21" s="131"/>
-      <c r="Y21" s="131"/>
-      <c r="Z21" s="131"/>
-      <c r="AA21" s="131"/>
-      <c r="AB21" s="131"/>
-      <c r="AC21" s="131"/>
-      <c r="AD21" s="131"/>
-      <c r="AE21" s="131"/>
-      <c r="AF21" s="131"/>
-      <c r="AG21" s="131"/>
-      <c r="AH21" s="131"/>
-      <c r="AI21" s="131"/>
-      <c r="AJ21" s="131"/>
-      <c r="AK21" s="131"/>
-      <c r="AL21" s="131"/>
-      <c r="AM21" s="131"/>
-      <c r="AN21" s="131"/>
-      <c r="AO21" s="131"/>
-      <c r="AP21" s="131"/>
-      <c r="AQ21" s="131"/>
-      <c r="AR21" s="131"/>
-      <c r="AS21" s="131"/>
-      <c r="AT21" s="131"/>
-      <c r="AU21" s="131"/>
-      <c r="AV21" s="131"/>
-      <c r="AW21" s="131"/>
-      <c r="AX21" s="131"/>
-      <c r="AY21" s="131"/>
-      <c r="AZ21" s="131"/>
-      <c r="BA21" s="131"/>
-      <c r="BB21" s="131"/>
-      <c r="BC21" s="131"/>
-      <c r="BD21" s="131"/>
-      <c r="BE21" s="131"/>
-      <c r="BF21" s="131"/>
-      <c r="BG21" s="131"/>
-      <c r="BH21" s="131"/>
-      <c r="BI21" s="131"/>
-      <c r="BJ21" s="131"/>
-      <c r="BK21" s="131"/>
-      <c r="BL21" s="131"/>
-      <c r="BM21" s="131"/>
-      <c r="BN21" s="131"/>
-      <c r="BO21" s="132"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="126"/>
+      <c r="S21" s="126"/>
+      <c r="T21" s="126"/>
+      <c r="U21" s="126"/>
+      <c r="V21" s="126"/>
+      <c r="W21" s="126"/>
+      <c r="X21" s="126"/>
+      <c r="Y21" s="126"/>
+      <c r="Z21" s="126"/>
+      <c r="AA21" s="126"/>
+      <c r="AB21" s="126"/>
+      <c r="AC21" s="126"/>
+      <c r="AD21" s="126"/>
+      <c r="AE21" s="126"/>
+      <c r="AF21" s="126"/>
+      <c r="AG21" s="126"/>
+      <c r="AH21" s="126"/>
+      <c r="AI21" s="126"/>
+      <c r="AJ21" s="126"/>
+      <c r="AK21" s="126"/>
+      <c r="AL21" s="126"/>
+      <c r="AM21" s="126"/>
+      <c r="AN21" s="126"/>
+      <c r="AO21" s="126"/>
+      <c r="AP21" s="126"/>
+      <c r="AQ21" s="126"/>
+      <c r="AR21" s="126"/>
+      <c r="AS21" s="126"/>
+      <c r="AT21" s="126"/>
+      <c r="AU21" s="126"/>
+      <c r="AV21" s="126"/>
+      <c r="AW21" s="126"/>
+      <c r="AX21" s="126"/>
+      <c r="AY21" s="126"/>
+      <c r="AZ21" s="126"/>
+      <c r="BA21" s="126"/>
+      <c r="BB21" s="126"/>
+      <c r="BC21" s="126"/>
+      <c r="BD21" s="126"/>
+      <c r="BE21" s="126"/>
+      <c r="BF21" s="126"/>
+      <c r="BG21" s="126"/>
+      <c r="BH21" s="126"/>
+      <c r="BI21" s="126"/>
+      <c r="BJ21" s="126"/>
+      <c r="BK21" s="126"/>
+      <c r="BL21" s="126"/>
+      <c r="BM21" s="126"/>
+      <c r="BN21" s="126"/>
+      <c r="BO21" s="127"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="128"/>
-      <c r="B22" s="90" t="s">
-        <v>139</v>
+      <c r="A22" s="123"/>
+      <c r="B22" s="81" t="s">
+        <v>138</v>
       </c>
       <c r="C22" s="20" t="str">
         <f t="shared" ref="C22:C40" ca="1" si="2">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
@@ -5317,7 +5271,7 @@
       <c r="F22" s="22">
         <v>45969</v>
       </c>
-      <c r="G22" s="81" t="s">
+      <c r="G22" s="72" t="s">
         <v>113</v>
       </c>
       <c r="H22" s="43"/>
@@ -5382,8 +5336,8 @@
       <c r="BO22" s="49"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="128"/>
-      <c r="B23" s="77" t="s">
+      <c r="A23" s="123"/>
+      <c r="B23" s="68" t="s">
         <v>85</v>
       </c>
       <c r="C23" s="20" t="str">
@@ -5465,8 +5419,8 @@
       <c r="BO23" s="49"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="128"/>
-      <c r="B24" s="91" t="s">
+      <c r="A24" s="123"/>
+      <c r="B24" s="82" t="s">
         <v>128</v>
       </c>
       <c r="C24" s="20" t="str">
@@ -5548,8 +5502,8 @@
       <c r="BO24" s="49"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="128"/>
-      <c r="B25" s="91" t="s">
+      <c r="A25" s="123"/>
+      <c r="B25" s="82" t="s">
         <v>127</v>
       </c>
       <c r="C25" s="20" t="str">
@@ -5631,9 +5585,9 @@
       <c r="BO25" s="49"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="128"/>
-      <c r="B26" s="69" t="s">
-        <v>140</v>
+      <c r="A26" s="123"/>
+      <c r="B26" s="63" t="s">
+        <v>139</v>
       </c>
       <c r="C26" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5714,9 +5668,9 @@
       <c r="BO26" s="49"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="128"/>
-      <c r="B27" s="69" t="s">
-        <v>162</v>
+      <c r="A27" s="123"/>
+      <c r="B27" s="63" t="s">
+        <v>160</v>
       </c>
       <c r="C27" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5797,25 +5751,25 @@
       <c r="BO27" s="49"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="128"/>
-      <c r="B28" s="71" t="s">
+      <c r="A28" s="123"/>
+      <c r="B28" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="92" t="str">
+      <c r="C28" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D28" s="93" t="str">
+      <c r="D28" s="84" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E28" s="94">
+      <c r="E28" s="85">
         <v>45980</v>
       </c>
-      <c r="F28" s="94">
+      <c r="F28" s="85">
         <v>45982</v>
       </c>
-      <c r="G28" s="95" t="s">
+      <c r="G28" s="86" t="s">
         <v>130</v>
       </c>
       <c r="H28" s="48"/>
@@ -5880,8 +5834,8 @@
       <c r="BO28" s="49"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="128"/>
-      <c r="B29" s="152" t="s">
+      <c r="A29" s="123"/>
+      <c r="B29" s="122" t="s">
         <v>135</v>
       </c>
       <c r="C29" s="20" t="str">
@@ -5963,8 +5917,8 @@
       <c r="BO29" s="49"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="128"/>
-      <c r="B30" s="70" t="s">
+      <c r="A30" s="123"/>
+      <c r="B30" s="64" t="s">
         <v>124</v>
       </c>
       <c r="C30" s="39" t="str">
@@ -5981,7 +5935,7 @@
       <c r="F30" s="41">
         <v>45988</v>
       </c>
-      <c r="G30" s="30" t="s">
+      <c r="G30" s="143" t="s">
         <v>130</v>
       </c>
       <c r="H30" s="48"/>
@@ -6046,25 +6000,25 @@
       <c r="BO30" s="49"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="128"/>
-      <c r="B31" s="71" t="s">
+      <c r="A31" s="123"/>
+      <c r="B31" s="65" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="92" t="str">
+      <c r="C31" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D31" s="93" t="str">
+      <c r="D31" s="84" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E31" s="94">
+      <c r="E31" s="85">
         <v>45980</v>
       </c>
-      <c r="F31" s="94">
+      <c r="F31" s="85">
         <v>45982</v>
       </c>
-      <c r="G31" s="95" t="s">
+      <c r="G31" s="86" t="s">
         <v>99</v>
       </c>
       <c r="H31" s="48"/>
@@ -6129,25 +6083,25 @@
       <c r="BO31" s="49"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="128"/>
-      <c r="B32" s="96" t="s">
+      <c r="A32" s="123"/>
+      <c r="B32" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="92" t="str">
+      <c r="C32" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D32" s="93" t="str">
+      <c r="D32" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E32" s="94">
+      <c r="E32" s="85">
         <v>45965</v>
       </c>
-      <c r="F32" s="94">
+      <c r="F32" s="85">
         <v>45971</v>
       </c>
-      <c r="G32" s="95" t="s">
+      <c r="G32" s="86" t="s">
         <v>100</v>
       </c>
       <c r="H32" s="48"/>
@@ -6212,25 +6166,25 @@
       <c r="BO32" s="28"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="128"/>
-      <c r="B33" s="97" t="s">
+      <c r="A33" s="123"/>
+      <c r="B33" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="92" t="str">
+      <c r="C33" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D33" s="93" t="str">
+      <c r="D33" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E33" s="94">
+      <c r="E33" s="85">
         <v>45971</v>
       </c>
-      <c r="F33" s="94">
+      <c r="F33" s="85">
         <v>45977</v>
       </c>
-      <c r="G33" s="98" t="s">
+      <c r="G33" s="89" t="s">
         <v>114</v>
       </c>
       <c r="H33" s="48"/>
@@ -6295,25 +6249,25 @@
       <c r="BO33" s="49"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="128"/>
-      <c r="B34" s="99" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="92" t="str">
+      <c r="A34" s="123"/>
+      <c r="B34" s="90" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="83" t="str">
         <f ca="1">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D34" s="93" t="str">
+      <c r="D34" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E34" s="94">
+      <c r="E34" s="85">
         <v>45971</v>
       </c>
-      <c r="F34" s="94">
+      <c r="F34" s="85">
         <v>45977</v>
       </c>
-      <c r="G34" s="98" t="s">
+      <c r="G34" s="89" t="s">
         <v>114</v>
       </c>
       <c r="H34" s="48"/>
@@ -6378,25 +6332,25 @@
       <c r="BO34" s="49"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="128"/>
-      <c r="B35" s="97" t="s">
+      <c r="A35" s="123"/>
+      <c r="B35" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="92" t="str">
+      <c r="C35" s="83" t="str">
         <f ca="1">IF(F35=E35, IF(TODAY()&gt;F35, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F35) - E35) / (F35 - E35) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D35" s="93" t="str">
+      <c r="D35" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E35" s="94">
+      <c r="E35" s="85">
         <v>45971</v>
       </c>
-      <c r="F35" s="94">
+      <c r="F35" s="85">
         <v>45977</v>
       </c>
-      <c r="G35" s="98" t="s">
+      <c r="G35" s="89" t="s">
         <v>114</v>
       </c>
       <c r="H35" s="48"/>
@@ -6461,25 +6415,25 @@
       <c r="BO35" s="49"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="128"/>
-      <c r="B36" s="100" t="s">
+      <c r="A36" s="123"/>
+      <c r="B36" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="92" t="str">
+      <c r="C36" s="83" t="str">
         <f ca="1">IF(F36=E36, IF(TODAY()&gt;F36, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F36) - E36) / (F36 - E36) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D36" s="93" t="str">
+      <c r="D36" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E36" s="94">
+      <c r="E36" s="85">
         <v>45980</v>
       </c>
-      <c r="F36" s="94">
+      <c r="F36" s="85">
         <v>45980</v>
       </c>
-      <c r="G36" s="98" t="s">
+      <c r="G36" s="89" t="s">
         <v>114</v>
       </c>
       <c r="H36" s="48"/>
@@ -6544,25 +6498,25 @@
       <c r="BO36" s="49"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="128"/>
-      <c r="B37" s="100" t="s">
+      <c r="A37" s="123"/>
+      <c r="B37" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="92" t="str">
+      <c r="C37" s="83" t="str">
         <f ca="1">IF(F37=E37, IF(TODAY()&gt;F37, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F37) - E37) / (F37 - E37) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D37" s="93" t="str">
+      <c r="D37" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E37" s="94">
+      <c r="E37" s="85">
         <v>45980</v>
       </c>
-      <c r="F37" s="94">
+      <c r="F37" s="85">
         <v>45980</v>
       </c>
-      <c r="G37" s="98" t="s">
+      <c r="G37" s="89" t="s">
         <v>116</v>
       </c>
       <c r="H37" s="48"/>
@@ -6627,25 +6581,25 @@
       <c r="BO37" s="49"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="128"/>
-      <c r="B38" s="101" t="s">
+      <c r="A38" s="123"/>
+      <c r="B38" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="92" t="str">
+      <c r="C38" s="83" t="str">
         <f ca="1">IF(F38=E38, IF(TODAY()&gt;F38, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F38) - E38) / (F38 - E38) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D38" s="93" t="str">
+      <c r="D38" s="84" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E38" s="94">
+      <c r="E38" s="85">
         <v>45977</v>
       </c>
-      <c r="F38" s="94">
+      <c r="F38" s="85">
         <v>45980</v>
       </c>
-      <c r="G38" s="98" t="s">
+      <c r="G38" s="89" t="s">
         <v>113</v>
       </c>
       <c r="H38" s="48"/>
@@ -6710,25 +6664,25 @@
       <c r="BO38" s="49"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="128"/>
-      <c r="B39" s="102" t="s">
+      <c r="A39" s="123"/>
+      <c r="B39" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="92" t="str">
+      <c r="C39" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D39" s="93" t="str">
+      <c r="D39" s="84" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E39" s="94">
+      <c r="E39" s="85">
         <v>45977</v>
       </c>
-      <c r="F39" s="94">
+      <c r="F39" s="85">
         <v>45980</v>
       </c>
-      <c r="G39" s="98" t="s">
+      <c r="G39" s="89" t="s">
         <v>114</v>
       </c>
       <c r="H39" s="48"/>
@@ -6793,25 +6747,25 @@
       <c r="BO39" s="49"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="128"/>
-      <c r="B40" s="102" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="92" t="str">
+      <c r="A40" s="123"/>
+      <c r="B40" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" s="83" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D40" s="93" t="str">
+      <c r="D40" s="84" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E40" s="94">
+      <c r="E40" s="85">
         <v>45977</v>
       </c>
-      <c r="F40" s="94">
+      <c r="F40" s="85">
         <v>45980</v>
       </c>
-      <c r="G40" s="98" t="s">
+      <c r="G40" s="89" t="s">
         <v>116</v>
       </c>
       <c r="H40" s="43"/>
@@ -6876,25 +6830,25 @@
       <c r="BO40" s="49"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="128"/>
-      <c r="B41" s="99" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" s="92" t="str">
+      <c r="A41" s="123"/>
+      <c r="B41" s="90" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="83" t="str">
         <f t="shared" ref="C41" ca="1" si="5">IF(F41=E41, IF(TODAY()&gt;F41, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F41) - E41) / (F41 - E41) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D41" s="93" t="str">
+      <c r="D41" s="84" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E41" s="94">
+      <c r="E41" s="85">
         <v>45977</v>
       </c>
-      <c r="F41" s="94">
+      <c r="F41" s="85">
         <v>45980</v>
       </c>
-      <c r="G41" s="98" t="s">
+      <c r="G41" s="89" t="s">
         <v>113</v>
       </c>
       <c r="H41" s="48"/>
@@ -6959,96 +6913,96 @@
       <c r="BO41" s="49"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="128"/>
-      <c r="B42" s="141" t="s">
+      <c r="A42" s="123"/>
+      <c r="B42" s="136" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="131"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="131"/>
-      <c r="L42" s="131"/>
-      <c r="M42" s="131"/>
-      <c r="N42" s="131"/>
-      <c r="O42" s="131"/>
-      <c r="P42" s="131"/>
-      <c r="Q42" s="131"/>
-      <c r="R42" s="131"/>
-      <c r="S42" s="131"/>
-      <c r="T42" s="131"/>
-      <c r="U42" s="131"/>
-      <c r="V42" s="131"/>
-      <c r="W42" s="131"/>
-      <c r="X42" s="131"/>
-      <c r="Y42" s="131"/>
-      <c r="Z42" s="131"/>
-      <c r="AA42" s="131"/>
-      <c r="AB42" s="131"/>
-      <c r="AC42" s="131"/>
-      <c r="AD42" s="131"/>
-      <c r="AE42" s="131"/>
-      <c r="AF42" s="131"/>
-      <c r="AG42" s="131"/>
-      <c r="AH42" s="131"/>
-      <c r="AI42" s="131"/>
-      <c r="AJ42" s="131"/>
-      <c r="AK42" s="131"/>
-      <c r="AL42" s="131"/>
-      <c r="AM42" s="131"/>
-      <c r="AN42" s="131"/>
-      <c r="AO42" s="131"/>
-      <c r="AP42" s="131"/>
-      <c r="AQ42" s="131"/>
-      <c r="AR42" s="131"/>
-      <c r="AS42" s="131"/>
-      <c r="AT42" s="131"/>
-      <c r="AU42" s="131"/>
-      <c r="AV42" s="131"/>
-      <c r="AW42" s="131"/>
-      <c r="AX42" s="131"/>
-      <c r="AY42" s="131"/>
-      <c r="AZ42" s="131"/>
-      <c r="BA42" s="131"/>
-      <c r="BB42" s="131"/>
-      <c r="BC42" s="131"/>
-      <c r="BD42" s="131"/>
-      <c r="BE42" s="131"/>
-      <c r="BF42" s="131"/>
-      <c r="BG42" s="131"/>
-      <c r="BH42" s="131"/>
-      <c r="BI42" s="131"/>
-      <c r="BJ42" s="131"/>
-      <c r="BK42" s="131"/>
-      <c r="BL42" s="131"/>
-      <c r="BM42" s="131"/>
-      <c r="BN42" s="131"/>
-      <c r="BO42" s="132"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="136"/>
+      <c r="E42" s="136"/>
+      <c r="F42" s="136"/>
+      <c r="G42" s="136"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
+      <c r="K42" s="126"/>
+      <c r="L42" s="126"/>
+      <c r="M42" s="126"/>
+      <c r="N42" s="126"/>
+      <c r="O42" s="126"/>
+      <c r="P42" s="126"/>
+      <c r="Q42" s="126"/>
+      <c r="R42" s="126"/>
+      <c r="S42" s="126"/>
+      <c r="T42" s="126"/>
+      <c r="U42" s="126"/>
+      <c r="V42" s="126"/>
+      <c r="W42" s="126"/>
+      <c r="X42" s="126"/>
+      <c r="Y42" s="126"/>
+      <c r="Z42" s="126"/>
+      <c r="AA42" s="126"/>
+      <c r="AB42" s="126"/>
+      <c r="AC42" s="126"/>
+      <c r="AD42" s="126"/>
+      <c r="AE42" s="126"/>
+      <c r="AF42" s="126"/>
+      <c r="AG42" s="126"/>
+      <c r="AH42" s="126"/>
+      <c r="AI42" s="126"/>
+      <c r="AJ42" s="126"/>
+      <c r="AK42" s="126"/>
+      <c r="AL42" s="126"/>
+      <c r="AM42" s="126"/>
+      <c r="AN42" s="126"/>
+      <c r="AO42" s="126"/>
+      <c r="AP42" s="126"/>
+      <c r="AQ42" s="126"/>
+      <c r="AR42" s="126"/>
+      <c r="AS42" s="126"/>
+      <c r="AT42" s="126"/>
+      <c r="AU42" s="126"/>
+      <c r="AV42" s="126"/>
+      <c r="AW42" s="126"/>
+      <c r="AX42" s="126"/>
+      <c r="AY42" s="126"/>
+      <c r="AZ42" s="126"/>
+      <c r="BA42" s="126"/>
+      <c r="BB42" s="126"/>
+      <c r="BC42" s="126"/>
+      <c r="BD42" s="126"/>
+      <c r="BE42" s="126"/>
+      <c r="BF42" s="126"/>
+      <c r="BG42" s="126"/>
+      <c r="BH42" s="126"/>
+      <c r="BI42" s="126"/>
+      <c r="BJ42" s="126"/>
+      <c r="BK42" s="126"/>
+      <c r="BL42" s="126"/>
+      <c r="BM42" s="126"/>
+      <c r="BN42" s="126"/>
+      <c r="BO42" s="127"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="128"/>
-      <c r="B43" s="97" t="s">
+      <c r="A43" s="123"/>
+      <c r="B43" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="92" t="str">
+      <c r="C43" s="83" t="str">
         <f t="shared" ref="C43:C50" ca="1" si="6">IF(F43=E43, IF(TODAY()&gt;F43, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F43) - E43) / (F43 - E43) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D43" s="93" t="str">
+      <c r="D43" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E43" s="94">
+      <c r="E43" s="85">
         <v>45971</v>
       </c>
-      <c r="F43" s="94">
+      <c r="F43" s="85">
         <v>45977</v>
       </c>
-      <c r="G43" s="98" t="s">
+      <c r="G43" s="89" t="s">
         <v>116</v>
       </c>
       <c r="H43" s="48"/>
@@ -7113,25 +7067,25 @@
       <c r="BO43" s="49"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="128"/>
-      <c r="B44" s="99" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="92" t="str">
+      <c r="A44" s="123"/>
+      <c r="B44" s="90" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="83" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D44" s="93" t="str">
+      <c r="D44" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E44" s="94">
+      <c r="E44" s="85">
         <v>45971</v>
       </c>
-      <c r="F44" s="94">
+      <c r="F44" s="85">
         <v>45977</v>
       </c>
-      <c r="G44" s="98" t="s">
+      <c r="G44" s="89" t="s">
         <v>116</v>
       </c>
       <c r="H44" s="48"/>
@@ -7196,25 +7150,25 @@
       <c r="BO44" s="49"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="128"/>
-      <c r="B45" s="99" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="92" t="str">
+      <c r="A45" s="123"/>
+      <c r="B45" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="83" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D45" s="93" t="str">
+      <c r="D45" s="84" t="str">
         <f t="shared" si="0"/>
         <v>10일</v>
       </c>
-      <c r="E45" s="94">
+      <c r="E45" s="85">
         <v>45971</v>
       </c>
-      <c r="F45" s="94">
+      <c r="F45" s="85">
         <v>45980</v>
       </c>
-      <c r="G45" s="98" t="s">
+      <c r="G45" s="89" t="s">
         <v>116</v>
       </c>
       <c r="H45" s="48"/>
@@ -7279,25 +7233,25 @@
       <c r="BO45" s="49"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="128"/>
-      <c r="B46" s="103" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="92" t="str">
+      <c r="A46" s="123"/>
+      <c r="B46" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="83" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D46" s="93" t="str">
+      <c r="D46" s="84" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E46" s="94">
+      <c r="E46" s="85">
         <v>45979</v>
       </c>
-      <c r="F46" s="94">
+      <c r="F46" s="85">
         <v>45981</v>
       </c>
-      <c r="G46" s="95" t="s">
+      <c r="G46" s="86" t="s">
         <v>133</v>
       </c>
       <c r="H46" s="48"/>
@@ -7362,25 +7316,25 @@
       <c r="BO46" s="49"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="128"/>
-      <c r="B47" s="104" t="s">
-        <v>156</v>
-      </c>
-      <c r="C47" s="92" t="str">
+      <c r="A47" s="123"/>
+      <c r="B47" s="95" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="83" t="str">
         <f ca="1">IF(F47=E47, IF(TODAY()&gt;F47, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F47) - E47) / (F47 - E47) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D47" s="93" t="str">
+      <c r="D47" s="84" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E47" s="94">
+      <c r="E47" s="85">
         <v>45980</v>
       </c>
-      <c r="F47" s="94">
+      <c r="F47" s="85">
         <v>45982</v>
       </c>
-      <c r="G47" s="95" t="s">
+      <c r="G47" s="86" t="s">
         <v>102</v>
       </c>
       <c r="H47" s="48"/>
@@ -7445,25 +7399,25 @@
       <c r="BO47" s="49"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="128"/>
-      <c r="B48" s="104" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="92" t="str">
+      <c r="A48" s="123"/>
+      <c r="B48" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="83" t="str">
         <f ca="1">IF(F48=E48, IF(TODAY()&gt;F48, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F48) - E48) / (F48 - E48) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D48" s="93" t="str">
+      <c r="D48" s="84" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E48" s="94">
+      <c r="E48" s="85">
         <v>45980</v>
       </c>
-      <c r="F48" s="94">
+      <c r="F48" s="85">
         <v>45982</v>
       </c>
-      <c r="G48" s="95" t="s">
+      <c r="G48" s="86" t="s">
         <v>102</v>
       </c>
       <c r="H48" s="48"/>
@@ -7528,25 +7482,25 @@
       <c r="BO48" s="49"/>
     </row>
     <row r="49" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="128"/>
-      <c r="B49" s="104" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="92" t="str">
+      <c r="A49" s="123"/>
+      <c r="B49" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="83" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D49" s="93" t="str">
+      <c r="D49" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E49" s="94">
+      <c r="E49" s="85">
         <v>45981</v>
       </c>
-      <c r="F49" s="94">
+      <c r="F49" s="85">
         <v>45981</v>
       </c>
-      <c r="G49" s="95" t="s">
+      <c r="G49" s="86" t="s">
         <v>133</v>
       </c>
       <c r="H49" s="48"/>
@@ -7611,25 +7565,25 @@
       <c r="BO49" s="49"/>
     </row>
     <row r="50" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A50" s="128"/>
-      <c r="B50" s="71" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="92" t="str">
+      <c r="A50" s="123"/>
+      <c r="B50" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="83" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D50" s="93" t="str">
+      <c r="D50" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E50" s="94">
+      <c r="E50" s="85">
         <v>45987</v>
       </c>
-      <c r="F50" s="94">
+      <c r="F50" s="85">
         <v>45987</v>
       </c>
-      <c r="G50" s="95" t="s">
+      <c r="G50" s="86" t="s">
         <v>133</v>
       </c>
       <c r="H50" s="48"/>
@@ -7694,96 +7648,96 @@
       <c r="BO50" s="29"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51" s="128"/>
-      <c r="B51" s="141" t="s">
+      <c r="A51" s="123"/>
+      <c r="B51" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="141"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="130"/>
-      <c r="I51" s="131"/>
-      <c r="J51" s="131"/>
-      <c r="K51" s="131"/>
-      <c r="L51" s="131"/>
-      <c r="M51" s="131"/>
-      <c r="N51" s="131"/>
-      <c r="O51" s="131"/>
-      <c r="P51" s="131"/>
-      <c r="Q51" s="131"/>
-      <c r="R51" s="131"/>
-      <c r="S51" s="131"/>
-      <c r="T51" s="131"/>
-      <c r="U51" s="131"/>
-      <c r="V51" s="131"/>
-      <c r="W51" s="131"/>
-      <c r="X51" s="131"/>
-      <c r="Y51" s="131"/>
-      <c r="Z51" s="131"/>
-      <c r="AA51" s="131"/>
-      <c r="AB51" s="131"/>
-      <c r="AC51" s="131"/>
-      <c r="AD51" s="131"/>
-      <c r="AE51" s="131"/>
-      <c r="AF51" s="131"/>
-      <c r="AG51" s="131"/>
-      <c r="AH51" s="131"/>
-      <c r="AI51" s="131"/>
-      <c r="AJ51" s="131"/>
-      <c r="AK51" s="131"/>
-      <c r="AL51" s="131"/>
-      <c r="AM51" s="131"/>
-      <c r="AN51" s="131"/>
-      <c r="AO51" s="131"/>
-      <c r="AP51" s="131"/>
-      <c r="AQ51" s="131"/>
-      <c r="AR51" s="131"/>
-      <c r="AS51" s="131"/>
-      <c r="AT51" s="131"/>
-      <c r="AU51" s="131"/>
-      <c r="AV51" s="131"/>
-      <c r="AW51" s="131"/>
-      <c r="AX51" s="131"/>
-      <c r="AY51" s="131"/>
-      <c r="AZ51" s="131"/>
-      <c r="BA51" s="131"/>
-      <c r="BB51" s="131"/>
-      <c r="BC51" s="131"/>
-      <c r="BD51" s="131"/>
-      <c r="BE51" s="131"/>
-      <c r="BF51" s="131"/>
-      <c r="BG51" s="131"/>
-      <c r="BH51" s="131"/>
-      <c r="BI51" s="131"/>
-      <c r="BJ51" s="131"/>
-      <c r="BK51" s="131"/>
-      <c r="BL51" s="131"/>
-      <c r="BM51" s="131"/>
-      <c r="BN51" s="131"/>
-      <c r="BO51" s="132"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="136"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="136"/>
+      <c r="G51" s="136"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="126"/>
+      <c r="J51" s="126"/>
+      <c r="K51" s="126"/>
+      <c r="L51" s="126"/>
+      <c r="M51" s="126"/>
+      <c r="N51" s="126"/>
+      <c r="O51" s="126"/>
+      <c r="P51" s="126"/>
+      <c r="Q51" s="126"/>
+      <c r="R51" s="126"/>
+      <c r="S51" s="126"/>
+      <c r="T51" s="126"/>
+      <c r="U51" s="126"/>
+      <c r="V51" s="126"/>
+      <c r="W51" s="126"/>
+      <c r="X51" s="126"/>
+      <c r="Y51" s="126"/>
+      <c r="Z51" s="126"/>
+      <c r="AA51" s="126"/>
+      <c r="AB51" s="126"/>
+      <c r="AC51" s="126"/>
+      <c r="AD51" s="126"/>
+      <c r="AE51" s="126"/>
+      <c r="AF51" s="126"/>
+      <c r="AG51" s="126"/>
+      <c r="AH51" s="126"/>
+      <c r="AI51" s="126"/>
+      <c r="AJ51" s="126"/>
+      <c r="AK51" s="126"/>
+      <c r="AL51" s="126"/>
+      <c r="AM51" s="126"/>
+      <c r="AN51" s="126"/>
+      <c r="AO51" s="126"/>
+      <c r="AP51" s="126"/>
+      <c r="AQ51" s="126"/>
+      <c r="AR51" s="126"/>
+      <c r="AS51" s="126"/>
+      <c r="AT51" s="126"/>
+      <c r="AU51" s="126"/>
+      <c r="AV51" s="126"/>
+      <c r="AW51" s="126"/>
+      <c r="AX51" s="126"/>
+      <c r="AY51" s="126"/>
+      <c r="AZ51" s="126"/>
+      <c r="BA51" s="126"/>
+      <c r="BB51" s="126"/>
+      <c r="BC51" s="126"/>
+      <c r="BD51" s="126"/>
+      <c r="BE51" s="126"/>
+      <c r="BF51" s="126"/>
+      <c r="BG51" s="126"/>
+      <c r="BH51" s="126"/>
+      <c r="BI51" s="126"/>
+      <c r="BJ51" s="126"/>
+      <c r="BK51" s="126"/>
+      <c r="BL51" s="126"/>
+      <c r="BM51" s="126"/>
+      <c r="BN51" s="126"/>
+      <c r="BO51" s="127"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52" s="128"/>
-      <c r="B52" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="C52" s="106" t="str">
+      <c r="A52" s="123"/>
+      <c r="B52" s="96" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="97" t="str">
         <f t="shared" ref="C52:C75" ca="1" si="7">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="93" t="str">
+      <c r="D52" s="84" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E52" s="107">
+      <c r="E52" s="98">
         <v>45971</v>
       </c>
-      <c r="F52" s="107">
+      <c r="F52" s="98">
         <v>45977</v>
       </c>
-      <c r="G52" s="108" t="s">
+      <c r="G52" s="99" t="s">
         <v>98</v>
       </c>
       <c r="H52" s="48"/>
@@ -7848,28 +7802,28 @@
       <c r="BO52" s="49"/>
     </row>
     <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53" s="128"/>
-      <c r="B53" s="109" t="s">
-        <v>149</v>
-      </c>
-      <c r="C53" s="110" t="str">
+      <c r="A53" s="123"/>
+      <c r="B53" s="100" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="101" t="str">
         <f t="shared" ref="C53" ca="1" si="8">IF(F53=E53, IF(TODAY()&gt;F53, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F53) - E53) / (F53 - E53) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D53" s="93" t="str">
+      <c r="D53" s="84" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E53" s="111">
+      <c r="E53" s="102">
         <v>45982</v>
       </c>
-      <c r="F53" s="111">
+      <c r="F53" s="102">
         <v>45983</v>
       </c>
-      <c r="G53" s="112" t="s">
+      <c r="G53" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="H53" s="61"/>
+      <c r="H53" s="59"/>
       <c r="I53" s="49"/>
       <c r="J53" s="49"/>
       <c r="K53" s="49"/>
@@ -7931,28 +7885,28 @@
       <c r="BO53" s="49"/>
     </row>
     <row r="54" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A54" s="128"/>
-      <c r="B54" s="109" t="s">
-        <v>150</v>
-      </c>
-      <c r="C54" s="110" t="str">
+      <c r="A54" s="123"/>
+      <c r="B54" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="101" t="str">
         <f t="shared" ref="C54" ca="1" si="9">IF(F54=E54, IF(TODAY()&gt;F54, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F54) - E54) / (F54 - E54) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D54" s="93" t="str">
+      <c r="D54" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E54" s="111">
+      <c r="E54" s="102">
         <v>45982</v>
       </c>
-      <c r="F54" s="111">
+      <c r="F54" s="102">
         <v>45982</v>
       </c>
-      <c r="G54" s="112" t="s">
+      <c r="G54" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="H54" s="61"/>
+      <c r="H54" s="59"/>
       <c r="I54" s="49"/>
       <c r="J54" s="49"/>
       <c r="K54" s="49"/>
@@ -8014,28 +7968,28 @@
       <c r="BO54" s="49"/>
     </row>
     <row r="55" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A55" s="128"/>
-      <c r="B55" s="109" t="s">
-        <v>151</v>
-      </c>
-      <c r="C55" s="110" t="str">
+      <c r="A55" s="123"/>
+      <c r="B55" s="100" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="101" t="str">
         <f t="shared" ref="C55" ca="1" si="10">IF(F55=E55, IF(TODAY()&gt;F55, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F55) - E55) / (F55 - E55) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D55" s="93" t="str">
+      <c r="D55" s="84" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E55" s="111">
+      <c r="E55" s="102">
         <v>45983</v>
       </c>
-      <c r="F55" s="111">
+      <c r="F55" s="102">
         <v>45983</v>
       </c>
-      <c r="G55" s="112" t="s">
+      <c r="G55" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="H55" s="61"/>
+      <c r="H55" s="59"/>
       <c r="I55" s="49"/>
       <c r="J55" s="49"/>
       <c r="K55" s="49"/>
@@ -8097,11 +8051,11 @@
       <c r="BO55" s="49"/>
     </row>
     <row r="56" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A56" s="128"/>
-      <c r="B56" s="148" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" s="149" t="str">
+      <c r="A56" s="123"/>
+      <c r="B56" s="118" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="119" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>100%</v>
       </c>
@@ -8109,16 +8063,16 @@
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E56" s="150">
+      <c r="E56" s="120">
         <v>45983</v>
       </c>
-      <c r="F56" s="150">
+      <c r="F56" s="120">
         <v>45989</v>
       </c>
-      <c r="G56" s="151" t="s">
+      <c r="G56" s="121" t="s">
         <v>100</v>
       </c>
-      <c r="H56" s="61"/>
+      <c r="H56" s="59"/>
       <c r="I56" s="49"/>
       <c r="J56" s="49"/>
       <c r="K56" s="49"/>
@@ -8180,28 +8134,28 @@
       <c r="BO56" s="49"/>
     </row>
     <row r="57" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A57" s="128"/>
-      <c r="B57" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="C57" s="110" t="str">
+      <c r="A57" s="123"/>
+      <c r="B57" s="104" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="101" t="str">
         <f t="shared" ref="C57" ca="1" si="11">IF(F57=E57, IF(TODAY()&gt;F57, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F57) - E57) / (F57 - E57) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D57" s="93" t="str">
+      <c r="D57" s="84" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E57" s="111">
+      <c r="E57" s="102">
         <v>45986</v>
       </c>
-      <c r="F57" s="111">
+      <c r="F57" s="102">
         <v>45987</v>
       </c>
-      <c r="G57" s="112" t="s">
+      <c r="G57" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="H57" s="61"/>
+      <c r="H57" s="59"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
       <c r="K57" s="49"/>
@@ -8263,96 +8217,96 @@
       <c r="BO57" s="49"/>
     </row>
     <row r="58" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A58" s="128"/>
-      <c r="B58" s="145" t="s">
+      <c r="A58" s="123"/>
+      <c r="B58" s="140" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="146"/>
-      <c r="D58" s="146"/>
-      <c r="E58" s="146"/>
-      <c r="F58" s="146"/>
-      <c r="G58" s="147"/>
-      <c r="H58" s="130"/>
-      <c r="I58" s="131"/>
-      <c r="J58" s="131"/>
-      <c r="K58" s="131"/>
-      <c r="L58" s="131"/>
-      <c r="M58" s="131"/>
-      <c r="N58" s="131"/>
-      <c r="O58" s="131"/>
-      <c r="P58" s="131"/>
-      <c r="Q58" s="131"/>
-      <c r="R58" s="131"/>
-      <c r="S58" s="131"/>
-      <c r="T58" s="131"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="131"/>
-      <c r="W58" s="131"/>
-      <c r="X58" s="131"/>
-      <c r="Y58" s="131"/>
-      <c r="Z58" s="131"/>
-      <c r="AA58" s="131"/>
-      <c r="AB58" s="131"/>
-      <c r="AC58" s="131"/>
-      <c r="AD58" s="131"/>
-      <c r="AE58" s="131"/>
-      <c r="AF58" s="131"/>
-      <c r="AG58" s="131"/>
-      <c r="AH58" s="131"/>
-      <c r="AI58" s="131"/>
-      <c r="AJ58" s="131"/>
-      <c r="AK58" s="131"/>
-      <c r="AL58" s="131"/>
-      <c r="AM58" s="131"/>
-      <c r="AN58" s="131"/>
-      <c r="AO58" s="131"/>
-      <c r="AP58" s="131"/>
-      <c r="AQ58" s="131"/>
-      <c r="AR58" s="131"/>
-      <c r="AS58" s="131"/>
-      <c r="AT58" s="131"/>
-      <c r="AU58" s="131"/>
-      <c r="AV58" s="131"/>
-      <c r="AW58" s="131"/>
-      <c r="AX58" s="131"/>
-      <c r="AY58" s="131"/>
-      <c r="AZ58" s="131"/>
-      <c r="BA58" s="131"/>
-      <c r="BB58" s="131"/>
-      <c r="BC58" s="131"/>
-      <c r="BD58" s="131"/>
-      <c r="BE58" s="131"/>
-      <c r="BF58" s="131"/>
-      <c r="BG58" s="131"/>
-      <c r="BH58" s="131"/>
-      <c r="BI58" s="131"/>
-      <c r="BJ58" s="131"/>
-      <c r="BK58" s="131"/>
-      <c r="BL58" s="131"/>
-      <c r="BM58" s="131"/>
-      <c r="BN58" s="131"/>
-      <c r="BO58" s="132"/>
+      <c r="C58" s="141"/>
+      <c r="D58" s="141"/>
+      <c r="E58" s="141"/>
+      <c r="F58" s="141"/>
+      <c r="G58" s="142"/>
+      <c r="H58" s="125"/>
+      <c r="I58" s="126"/>
+      <c r="J58" s="126"/>
+      <c r="K58" s="126"/>
+      <c r="L58" s="126"/>
+      <c r="M58" s="126"/>
+      <c r="N58" s="126"/>
+      <c r="O58" s="126"/>
+      <c r="P58" s="126"/>
+      <c r="Q58" s="126"/>
+      <c r="R58" s="126"/>
+      <c r="S58" s="126"/>
+      <c r="T58" s="126"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="126"/>
+      <c r="W58" s="126"/>
+      <c r="X58" s="126"/>
+      <c r="Y58" s="126"/>
+      <c r="Z58" s="126"/>
+      <c r="AA58" s="126"/>
+      <c r="AB58" s="126"/>
+      <c r="AC58" s="126"/>
+      <c r="AD58" s="126"/>
+      <c r="AE58" s="126"/>
+      <c r="AF58" s="126"/>
+      <c r="AG58" s="126"/>
+      <c r="AH58" s="126"/>
+      <c r="AI58" s="126"/>
+      <c r="AJ58" s="126"/>
+      <c r="AK58" s="126"/>
+      <c r="AL58" s="126"/>
+      <c r="AM58" s="126"/>
+      <c r="AN58" s="126"/>
+      <c r="AO58" s="126"/>
+      <c r="AP58" s="126"/>
+      <c r="AQ58" s="126"/>
+      <c r="AR58" s="126"/>
+      <c r="AS58" s="126"/>
+      <c r="AT58" s="126"/>
+      <c r="AU58" s="126"/>
+      <c r="AV58" s="126"/>
+      <c r="AW58" s="126"/>
+      <c r="AX58" s="126"/>
+      <c r="AY58" s="126"/>
+      <c r="AZ58" s="126"/>
+      <c r="BA58" s="126"/>
+      <c r="BB58" s="126"/>
+      <c r="BC58" s="126"/>
+      <c r="BD58" s="126"/>
+      <c r="BE58" s="126"/>
+      <c r="BF58" s="126"/>
+      <c r="BG58" s="126"/>
+      <c r="BH58" s="126"/>
+      <c r="BI58" s="126"/>
+      <c r="BJ58" s="126"/>
+      <c r="BK58" s="126"/>
+      <c r="BL58" s="126"/>
+      <c r="BM58" s="126"/>
+      <c r="BN58" s="126"/>
+      <c r="BO58" s="127"/>
     </row>
     <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A59" s="128"/>
-      <c r="B59" s="100" t="s">
+      <c r="A59" s="123"/>
+      <c r="B59" s="91" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="114" t="str">
+      <c r="C59" s="105" t="str">
         <f t="shared" ref="C59" ca="1" si="12">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D59" s="93" t="str">
+      <c r="D59" s="84" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E59" s="115">
+      <c r="E59" s="106">
         <v>45980</v>
       </c>
-      <c r="F59" s="115">
+      <c r="F59" s="106">
         <v>45981</v>
       </c>
-      <c r="G59" s="116" t="s">
+      <c r="G59" s="107" t="s">
         <v>114</v>
       </c>
       <c r="H59" s="48"/>
@@ -8417,28 +8371,28 @@
       <c r="BO59" s="49"/>
     </row>
     <row r="60" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A60" s="128"/>
-      <c r="B60" s="117" t="s">
-        <v>153</v>
-      </c>
-      <c r="C60" s="110" t="str">
+      <c r="A60" s="123"/>
+      <c r="B60" s="108" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="101" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>100%</v>
       </c>
-      <c r="D60" s="93" t="str">
+      <c r="D60" s="84" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E60" s="111">
+      <c r="E60" s="102">
         <v>45979</v>
       </c>
-      <c r="F60" s="111">
+      <c r="F60" s="102">
         <v>45980</v>
       </c>
-      <c r="G60" s="118" t="s">
+      <c r="G60" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="H60" s="61"/>
+      <c r="H60" s="59"/>
       <c r="I60" s="49"/>
       <c r="J60" s="49"/>
       <c r="K60" s="49"/>
@@ -8500,25 +8454,25 @@
       <c r="BO60" s="49"/>
     </row>
     <row r="61" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A61" s="128"/>
-      <c r="B61" s="62" t="s">
+      <c r="A61" s="123"/>
+      <c r="B61" s="60" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="32" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>50%</v>
+        <v>66.7%</v>
       </c>
       <c r="D61" s="56" t="str">
         <f t="shared" si="0"/>
         <v>19일</v>
       </c>
-      <c r="E61" s="63">
+      <c r="E61" s="61">
         <v>45980</v>
       </c>
-      <c r="F61" s="63">
+      <c r="F61" s="61">
         <v>45998</v>
       </c>
-      <c r="G61" s="64" t="s">
+      <c r="G61" s="62" t="s">
         <v>123</v>
       </c>
       <c r="H61" s="48"/>
@@ -8583,25 +8537,25 @@
       <c r="BO61" s="49"/>
     </row>
     <row r="62" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A62" s="128"/>
-      <c r="B62" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="65" t="str">
+      <c r="A62" s="123"/>
+      <c r="B62" s="144" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" s="119" t="str">
         <f ca="1">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D62" s="57" t="str">
+      <c r="D62" s="21" t="str">
         <f t="shared" ref="D62:D72" si="13">IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
-      <c r="E62" s="58">
+      <c r="E62" s="22">
         <v>45980</v>
       </c>
-      <c r="F62" s="58">
+      <c r="F62" s="22">
         <v>45988</v>
       </c>
-      <c r="G62" s="66" t="s">
+      <c r="G62" s="145" t="s">
         <v>114</v>
       </c>
       <c r="H62" s="48"/>
@@ -8666,25 +8620,25 @@
       <c r="BO62" s="49"/>
     </row>
     <row r="63" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="128"/>
-      <c r="B63" s="74" t="s">
+      <c r="A63" s="123"/>
+      <c r="B63" s="146" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="65" t="str">
+      <c r="C63" s="119" t="str">
         <f ca="1">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D63" s="57" t="str">
+      <c r="D63" s="21" t="str">
         <f t="shared" si="13"/>
         <v>9일</v>
       </c>
-      <c r="E63" s="58">
+      <c r="E63" s="22">
         <v>45980</v>
       </c>
-      <c r="F63" s="58">
+      <c r="F63" s="22">
         <v>45988</v>
       </c>
-      <c r="G63" s="66" t="s">
+      <c r="G63" s="145" t="s">
         <v>114</v>
       </c>
       <c r="H63" s="48"/>
@@ -8749,25 +8703,25 @@
       <c r="BO63" s="49"/>
     </row>
     <row r="64" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A64" s="128"/>
-      <c r="B64" s="75" t="s">
+      <c r="A64" s="123"/>
+      <c r="B64" s="147" t="s">
         <v>121</v>
       </c>
-      <c r="C64" s="67" t="str">
+      <c r="C64" s="32" t="str">
         <f ca="1">IF(F64=E64, IF(TODAY()&gt;F64, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F64) - E64) / (F64 - E64) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D64" s="57" t="str">
+      <c r="D64" s="21" t="str">
         <f t="shared" si="13"/>
         <v>5일</v>
       </c>
-      <c r="E64" s="58">
+      <c r="E64" s="22">
         <v>45985</v>
       </c>
-      <c r="F64" s="58">
+      <c r="F64" s="22">
         <v>45989</v>
       </c>
-      <c r="G64" s="66" t="s">
+      <c r="G64" s="145" t="s">
         <v>116</v>
       </c>
       <c r="H64" s="48"/>
@@ -8832,25 +8786,27 @@
       <c r="BO64" s="49"/>
     </row>
     <row r="65" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A65" s="128"/>
-      <c r="B65" s="120" t="s">
-        <v>154</v>
-      </c>
-      <c r="C65" s="39" t="str">
+      <c r="A65" s="123"/>
+      <c r="B65" s="148" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="20" t="str">
         <f ca="1">IF(OR(E65="",F65=""), "0%", IF(F65=E65, IF(TODAY()&gt;F65, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F65) - E65) / (F65 - E65) * 100, 1) &amp; "%"))</f>
         <v>100%</v>
       </c>
-      <c r="D65" s="40" t="str">
+      <c r="D65" s="21" t="str">
         <f t="shared" si="13"/>
-        <v>2일</v>
-      </c>
-      <c r="E65" s="41">
+        <v>5일</v>
+      </c>
+      <c r="E65" s="22">
         <v>45988</v>
       </c>
-      <c r="F65" s="41">
-        <v>45989</v>
-      </c>
-      <c r="G65" s="68"/>
+      <c r="F65" s="22">
+        <v>45992</v>
+      </c>
+      <c r="G65" s="145" t="s">
+        <v>113</v>
+      </c>
       <c r="H65" s="48"/>
       <c r="I65" s="49"/>
       <c r="J65" s="49"/>
@@ -8913,25 +8869,25 @@
       <c r="BO65" s="49"/>
     </row>
     <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="128"/>
-      <c r="B66" s="102" t="s">
+      <c r="A66" s="123"/>
+      <c r="B66" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="92" t="str">
+      <c r="C66" s="83" t="str">
         <f ca="1">IF(F66=E66, IF(TODAY()&gt;F66, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F66) - E66) / (F66 - E66) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D66" s="93" t="str">
+      <c r="D66" s="84" t="str">
         <f t="shared" si="13"/>
         <v>2일</v>
       </c>
-      <c r="E66" s="94">
+      <c r="E66" s="85">
         <v>45985</v>
       </c>
-      <c r="F66" s="94">
+      <c r="F66" s="85">
         <v>45986</v>
       </c>
-      <c r="G66" s="119" t="s">
+      <c r="G66" s="110" t="s">
         <v>113</v>
       </c>
       <c r="H66" s="48"/>
@@ -8996,13 +8952,13 @@
       <c r="BO66" s="49"/>
     </row>
     <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A67" s="128"/>
-      <c r="B67" s="121" t="s">
-        <v>158</v>
+      <c r="A67" s="123"/>
+      <c r="B67" s="111" t="s">
+        <v>156</v>
       </c>
       <c r="C67" s="39" t="str">
         <f t="shared" ref="C67" ca="1" si="14">IF(F67=E67, IF(TODAY()&gt;F67, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F67) - E67) / (F67 - E67) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
+        <v>33.3%</v>
       </c>
       <c r="D67" s="40" t="str">
         <f t="shared" si="13"/>
@@ -9014,7 +8970,7 @@
       <c r="F67" s="41">
         <v>45998</v>
       </c>
-      <c r="G67" s="122" t="s">
+      <c r="G67" s="112" t="s">
         <v>114</v>
       </c>
       <c r="H67" s="48"/>
@@ -9079,13 +9035,13 @@
       <c r="BO67" s="49"/>
     </row>
     <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A68" s="129"/>
-      <c r="B68" s="121" t="s">
-        <v>159</v>
+      <c r="A68" s="124"/>
+      <c r="B68" s="111" t="s">
+        <v>157</v>
       </c>
       <c r="C68" s="39" t="str">
         <f ca="1">IF(F68=E68, IF(TODAY()&gt;F68, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F68) - E68) / (F68 - E68) * 100, 1) &amp; "%")</f>
-        <v>30.8%</v>
+        <v>53.8%</v>
       </c>
       <c r="D68" s="40" t="str">
         <f t="shared" si="13"/>
@@ -9097,7 +9053,7 @@
       <c r="F68" s="41">
         <v>45998</v>
       </c>
-      <c r="G68" s="122" t="s">
+      <c r="G68" s="112" t="s">
         <v>123</v>
       </c>
       <c r="H68" s="48"/>
@@ -9162,10 +9118,10 @@
       <c r="BO68" s="49"/>
     </row>
     <row r="69" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A69" s="128" t="s">
+      <c r="A69" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="59" t="s">
+      <c r="B69" s="57" t="s">
         <v>88</v>
       </c>
       <c r="C69" s="35" t="str">
@@ -9247,8 +9203,8 @@
       <c r="BO69" s="53"/>
     </row>
     <row r="70" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A70" s="128"/>
-      <c r="B70" s="123" t="s">
+      <c r="A70" s="123"/>
+      <c r="B70" s="113" t="s">
         <v>2</v>
       </c>
       <c r="C70" s="39" t="str">
@@ -9261,7 +9217,7 @@
       </c>
       <c r="E70" s="41"/>
       <c r="F70" s="41"/>
-      <c r="G70" s="124" t="s">
+      <c r="G70" s="114" t="s">
         <v>97</v>
       </c>
       <c r="H70" s="48"/>
@@ -9326,8 +9282,8 @@
       <c r="BO70" s="49"/>
     </row>
     <row r="71" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A71" s="128"/>
-      <c r="B71" s="125" t="s">
+      <c r="A71" s="123"/>
+      <c r="B71" s="115" t="s">
         <v>87</v>
       </c>
       <c r="C71" s="39" t="str">
@@ -9340,7 +9296,7 @@
       </c>
       <c r="E71" s="41"/>
       <c r="F71" s="41"/>
-      <c r="G71" s="124" t="s">
+      <c r="G71" s="114" t="s">
         <v>97</v>
       </c>
       <c r="H71" s="48"/>
@@ -9405,9 +9361,9 @@
       <c r="BO71" s="49"/>
     </row>
     <row r="72" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A72" s="128"/>
-      <c r="B72" s="126" t="s">
-        <v>160</v>
+      <c r="A72" s="123"/>
+      <c r="B72" s="116" t="s">
+        <v>158</v>
       </c>
       <c r="C72" s="39" t="str">
         <f ca="1">IF(OR(E72="",F72=""), "0%", IF(F72=E72, IF(TODAY()&gt;F72, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F72) - E72) / (F72 - E72) * 100, 1) &amp; "%"))</f>
@@ -9419,7 +9375,7 @@
       </c>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
-      <c r="G72" s="124" t="s">
+      <c r="G72" s="114" t="s">
         <v>97</v>
       </c>
       <c r="H72" s="48"/>
@@ -9484,8 +9440,8 @@
       <c r="BO72" s="49"/>
     </row>
     <row r="73" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A73" s="128"/>
-      <c r="B73" s="121" t="s">
+      <c r="A73" s="123"/>
+      <c r="B73" s="111" t="s">
         <v>3</v>
       </c>
       <c r="C73" s="39" t="str">
@@ -9502,7 +9458,7 @@
       <c r="F73" s="41">
         <v>46008</v>
       </c>
-      <c r="G73" s="127" t="s">
+      <c r="G73" s="117" t="s">
         <v>95</v>
       </c>
       <c r="H73" s="48"/>
@@ -9567,8 +9523,8 @@
       <c r="BO73" s="49"/>
     </row>
     <row r="74" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A74" s="128"/>
-      <c r="B74" s="121" t="s">
+      <c r="A74" s="123"/>
+      <c r="B74" s="111" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="39" t="str">
@@ -9585,7 +9541,7 @@
       <c r="F74" s="41">
         <v>46010</v>
       </c>
-      <c r="G74" s="127" t="s">
+      <c r="G74" s="117" t="s">
         <v>95</v>
       </c>
       <c r="H74" s="48"/>
@@ -9650,8 +9606,8 @@
       <c r="BO74" s="49"/>
     </row>
     <row r="75" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A75" s="129"/>
-      <c r="B75" s="121" t="s">
+      <c r="A75" s="124"/>
+      <c r="B75" s="111" t="s">
         <v>90</v>
       </c>
       <c r="C75" s="39" t="str">
@@ -9668,7 +9624,7 @@
       <c r="F75" s="41">
         <v>46010</v>
       </c>
-      <c r="G75" s="127" t="s">
+      <c r="G75" s="117" t="s">
         <v>95</v>
       </c>
       <c r="H75" s="48"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209ABEBD-6BC7-44F3-8952-697724395A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53B347F-14BB-4C06-84C9-37176FBF9446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1035" windowWidth="20835" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="164">
   <si>
     <t>팀명</t>
   </si>
@@ -1373,7 +1373,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">AWS </t>
+      <t>FE:BE</t>
     </r>
     <r>
       <rPr>
@@ -1383,7 +1383,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>연결(</t>
+      <t>연결 테스트</t>
     </r>
     <r>
       <rPr>
@@ -1392,7 +1392,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">EC2, S3 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1402,16 +1402,229 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>등)</t>
-    </r>
+      <t>및 버그 보완</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프론트엔드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마무리작업</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">상품 관리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마이페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">리뷰(조회,수정,삭제) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리 시스템(트랜잭션화 및 이미지 처리)</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타입에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추천되는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리뷰 추천 알고리즘</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MinIO </t>
     </r>
     <r>
       <rPr>
@@ -1421,65 +1634,20 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">및 </t>
-    </r>
+      <t>연결 및 코드 전반적인 수정</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CICD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>FE:BE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>연결 테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및 버그 보완</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">AWS </t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
@@ -1488,210 +1656,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>프론트엔드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마무리작업</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">상품 관리 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마이페이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">리뷰(조회,수정,삭제) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>UI</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>처리 시스템(트랜잭션화 및 이미지 처리)</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>피부</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>타입에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추천되는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>리뷰 추천 알고리즘</t>
+      <t>및 배포용 코드 수정, 테스트</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1703,7 +1668,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2016,6 +1981,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="20">
@@ -2631,7 +2602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2999,6 +2970,24 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3059,22 +3048,7 @@
     <xf numFmtId="0" fontId="23" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3302,7 +3276,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO96"/>
+  <dimension ref="A1:BO97"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -3317,31 +3291,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="128" t="s">
+      <c r="C1" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="130" t="s">
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="129"/>
-      <c r="T1" s="129"/>
-      <c r="U1" s="129"/>
-      <c r="V1" s="129"/>
-      <c r="W1" s="129"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3405,7 +3379,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="131" t="s">
+      <c r="G2" s="137" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3596,7 +3570,7 @@
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="132"/>
+      <c r="G3" s="138"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3779,7 +3753,7 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="133" t="s">
+      <c r="A4" s="139" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -3864,7 +3838,7 @@
       <c r="BO4" s="44"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="134"/>
+      <c r="A5" s="140"/>
       <c r="B5" s="66" t="s">
         <v>73</v>
       </c>
@@ -3947,7 +3921,7 @@
       <c r="BO5" s="49"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="134"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="66" t="s">
         <v>74</v>
       </c>
@@ -4030,7 +4004,7 @@
       <c r="BO6" s="49"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="134"/>
+      <c r="A7" s="140"/>
       <c r="B7" s="70" t="s">
         <v>75</v>
       </c>
@@ -4113,7 +4087,7 @@
       <c r="BO7" s="49"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="134"/>
+      <c r="A8" s="140"/>
       <c r="B8" s="71" t="s">
         <v>76</v>
       </c>
@@ -4196,7 +4170,7 @@
       <c r="BO8" s="49"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="134"/>
+      <c r="A9" s="140"/>
       <c r="B9" s="66" t="s">
         <v>77</v>
       </c>
@@ -4279,7 +4253,7 @@
       <c r="BO9" s="49"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="134"/>
+      <c r="A10" s="140"/>
       <c r="B10" s="70" t="s">
         <v>78</v>
       </c>
@@ -4362,7 +4336,7 @@
       <c r="BO10" s="49"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="134"/>
+      <c r="A11" s="140"/>
       <c r="B11" s="73" t="s">
         <v>79</v>
       </c>
@@ -4445,7 +4419,7 @@
       <c r="BO11" s="49"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="139" t="s">
+      <c r="A12" s="145" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="57" t="s">
@@ -4530,7 +4504,7 @@
       <c r="BO12" s="49"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="123"/>
+      <c r="A13" s="129"/>
       <c r="B13" s="69" t="s">
         <v>82</v>
       </c>
@@ -4613,7 +4587,7 @@
       <c r="BO13" s="49"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="123"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="76" t="s">
         <v>83</v>
       </c>
@@ -4696,7 +4670,7 @@
       <c r="BO14" s="49"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="123"/>
+      <c r="A15" s="129"/>
       <c r="B15" s="57" t="s">
         <v>84</v>
       </c>
@@ -4779,7 +4753,7 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="123"/>
+      <c r="A16" s="129"/>
       <c r="B16" s="78" t="s">
         <v>136</v>
       </c>
@@ -4862,78 +4836,78 @@
       <c r="BO16" s="42"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="123"/>
-      <c r="B17" s="137" t="s">
+      <c r="A17" s="129"/>
+      <c r="B17" s="143" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="126"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="126"/>
-      <c r="P17" s="126"/>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="126"/>
-      <c r="S17" s="126"/>
-      <c r="T17" s="126"/>
-      <c r="U17" s="126"/>
-      <c r="V17" s="126"/>
-      <c r="W17" s="126"/>
-      <c r="X17" s="126"/>
-      <c r="Y17" s="126"/>
-      <c r="Z17" s="126"/>
-      <c r="AA17" s="126"/>
-      <c r="AB17" s="126"/>
-      <c r="AC17" s="126"/>
-      <c r="AD17" s="126"/>
-      <c r="AE17" s="126"/>
-      <c r="AF17" s="126"/>
-      <c r="AG17" s="126"/>
-      <c r="AH17" s="126"/>
-      <c r="AI17" s="126"/>
-      <c r="AJ17" s="126"/>
-      <c r="AK17" s="126"/>
-      <c r="AL17" s="126"/>
-      <c r="AM17" s="126"/>
-      <c r="AN17" s="126"/>
-      <c r="AO17" s="126"/>
-      <c r="AP17" s="126"/>
-      <c r="AQ17" s="126"/>
-      <c r="AR17" s="126"/>
-      <c r="AS17" s="126"/>
-      <c r="AT17" s="126"/>
-      <c r="AU17" s="126"/>
-      <c r="AV17" s="126"/>
-      <c r="AW17" s="126"/>
-      <c r="AX17" s="126"/>
-      <c r="AY17" s="126"/>
-      <c r="AZ17" s="126"/>
-      <c r="BA17" s="126"/>
-      <c r="BB17" s="126"/>
-      <c r="BC17" s="126"/>
-      <c r="BD17" s="126"/>
-      <c r="BE17" s="126"/>
-      <c r="BF17" s="126"/>
-      <c r="BG17" s="126"/>
-      <c r="BH17" s="126"/>
-      <c r="BI17" s="126"/>
-      <c r="BJ17" s="126"/>
-      <c r="BK17" s="126"/>
-      <c r="BL17" s="126"/>
-      <c r="BM17" s="126"/>
-      <c r="BN17" s="126"/>
-      <c r="BO17" s="127"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="132"/>
+      <c r="R17" s="132"/>
+      <c r="S17" s="132"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="132"/>
+      <c r="V17" s="132"/>
+      <c r="W17" s="132"/>
+      <c r="X17" s="132"/>
+      <c r="Y17" s="132"/>
+      <c r="Z17" s="132"/>
+      <c r="AA17" s="132"/>
+      <c r="AB17" s="132"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="132"/>
+      <c r="AE17" s="132"/>
+      <c r="AF17" s="132"/>
+      <c r="AG17" s="132"/>
+      <c r="AH17" s="132"/>
+      <c r="AI17" s="132"/>
+      <c r="AJ17" s="132"/>
+      <c r="AK17" s="132"/>
+      <c r="AL17" s="132"/>
+      <c r="AM17" s="132"/>
+      <c r="AN17" s="132"/>
+      <c r="AO17" s="132"/>
+      <c r="AP17" s="132"/>
+      <c r="AQ17" s="132"/>
+      <c r="AR17" s="132"/>
+      <c r="AS17" s="132"/>
+      <c r="AT17" s="132"/>
+      <c r="AU17" s="132"/>
+      <c r="AV17" s="132"/>
+      <c r="AW17" s="132"/>
+      <c r="AX17" s="132"/>
+      <c r="AY17" s="132"/>
+      <c r="AZ17" s="132"/>
+      <c r="BA17" s="132"/>
+      <c r="BB17" s="132"/>
+      <c r="BC17" s="132"/>
+      <c r="BD17" s="132"/>
+      <c r="BE17" s="132"/>
+      <c r="BF17" s="132"/>
+      <c r="BG17" s="132"/>
+      <c r="BH17" s="132"/>
+      <c r="BI17" s="132"/>
+      <c r="BJ17" s="132"/>
+      <c r="BK17" s="132"/>
+      <c r="BL17" s="132"/>
+      <c r="BM17" s="132"/>
+      <c r="BN17" s="132"/>
+      <c r="BO17" s="133"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="123"/>
+      <c r="A18" s="129"/>
       <c r="B18" s="63" t="s">
         <v>137</v>
       </c>
@@ -5016,7 +4990,7 @@
       <c r="BO18" s="44"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="123"/>
+      <c r="A19" s="129"/>
       <c r="B19" s="67" t="s">
         <v>86</v>
       </c>
@@ -5099,7 +5073,7 @@
       <c r="BO19" s="49"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="123"/>
+      <c r="A20" s="129"/>
       <c r="B20" s="80" t="s">
         <v>110</v>
       </c>
@@ -5182,78 +5156,78 @@
       <c r="BO20" s="49"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="123"/>
-      <c r="B21" s="135" t="s">
+      <c r="A21" s="129"/>
+      <c r="B21" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="135"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="126"/>
-      <c r="Q21" s="126"/>
-      <c r="R21" s="126"/>
-      <c r="S21" s="126"/>
-      <c r="T21" s="126"/>
-      <c r="U21" s="126"/>
-      <c r="V21" s="126"/>
-      <c r="W21" s="126"/>
-      <c r="X21" s="126"/>
-      <c r="Y21" s="126"/>
-      <c r="Z21" s="126"/>
-      <c r="AA21" s="126"/>
-      <c r="AB21" s="126"/>
-      <c r="AC21" s="126"/>
-      <c r="AD21" s="126"/>
-      <c r="AE21" s="126"/>
-      <c r="AF21" s="126"/>
-      <c r="AG21" s="126"/>
-      <c r="AH21" s="126"/>
-      <c r="AI21" s="126"/>
-      <c r="AJ21" s="126"/>
-      <c r="AK21" s="126"/>
-      <c r="AL21" s="126"/>
-      <c r="AM21" s="126"/>
-      <c r="AN21" s="126"/>
-      <c r="AO21" s="126"/>
-      <c r="AP21" s="126"/>
-      <c r="AQ21" s="126"/>
-      <c r="AR21" s="126"/>
-      <c r="AS21" s="126"/>
-      <c r="AT21" s="126"/>
-      <c r="AU21" s="126"/>
-      <c r="AV21" s="126"/>
-      <c r="AW21" s="126"/>
-      <c r="AX21" s="126"/>
-      <c r="AY21" s="126"/>
-      <c r="AZ21" s="126"/>
-      <c r="BA21" s="126"/>
-      <c r="BB21" s="126"/>
-      <c r="BC21" s="126"/>
-      <c r="BD21" s="126"/>
-      <c r="BE21" s="126"/>
-      <c r="BF21" s="126"/>
-      <c r="BG21" s="126"/>
-      <c r="BH21" s="126"/>
-      <c r="BI21" s="126"/>
-      <c r="BJ21" s="126"/>
-      <c r="BK21" s="126"/>
-      <c r="BL21" s="126"/>
-      <c r="BM21" s="126"/>
-      <c r="BN21" s="126"/>
-      <c r="BO21" s="127"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="132"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="132"/>
+      <c r="T21" s="132"/>
+      <c r="U21" s="132"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="132"/>
+      <c r="X21" s="132"/>
+      <c r="Y21" s="132"/>
+      <c r="Z21" s="132"/>
+      <c r="AA21" s="132"/>
+      <c r="AB21" s="132"/>
+      <c r="AC21" s="132"/>
+      <c r="AD21" s="132"/>
+      <c r="AE21" s="132"/>
+      <c r="AF21" s="132"/>
+      <c r="AG21" s="132"/>
+      <c r="AH21" s="132"/>
+      <c r="AI21" s="132"/>
+      <c r="AJ21" s="132"/>
+      <c r="AK21" s="132"/>
+      <c r="AL21" s="132"/>
+      <c r="AM21" s="132"/>
+      <c r="AN21" s="132"/>
+      <c r="AO21" s="132"/>
+      <c r="AP21" s="132"/>
+      <c r="AQ21" s="132"/>
+      <c r="AR21" s="132"/>
+      <c r="AS21" s="132"/>
+      <c r="AT21" s="132"/>
+      <c r="AU21" s="132"/>
+      <c r="AV21" s="132"/>
+      <c r="AW21" s="132"/>
+      <c r="AX21" s="132"/>
+      <c r="AY21" s="132"/>
+      <c r="AZ21" s="132"/>
+      <c r="BA21" s="132"/>
+      <c r="BB21" s="132"/>
+      <c r="BC21" s="132"/>
+      <c r="BD21" s="132"/>
+      <c r="BE21" s="132"/>
+      <c r="BF21" s="132"/>
+      <c r="BG21" s="132"/>
+      <c r="BH21" s="132"/>
+      <c r="BI21" s="132"/>
+      <c r="BJ21" s="132"/>
+      <c r="BK21" s="132"/>
+      <c r="BL21" s="132"/>
+      <c r="BM21" s="132"/>
+      <c r="BN21" s="132"/>
+      <c r="BO21" s="133"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="123"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="81" t="s">
         <v>138</v>
       </c>
@@ -5336,7 +5310,7 @@
       <c r="BO22" s="49"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="123"/>
+      <c r="A23" s="129"/>
       <c r="B23" s="68" t="s">
         <v>85</v>
       </c>
@@ -5419,7 +5393,7 @@
       <c r="BO23" s="49"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="123"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="82" t="s">
         <v>128</v>
       </c>
@@ -5502,7 +5476,7 @@
       <c r="BO24" s="49"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="123"/>
+      <c r="A25" s="129"/>
       <c r="B25" s="82" t="s">
         <v>127</v>
       </c>
@@ -5585,7 +5559,7 @@
       <c r="BO25" s="49"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="123"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="63" t="s">
         <v>139</v>
       </c>
@@ -5668,9 +5642,9 @@
       <c r="BO26" s="49"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="123"/>
+      <c r="A27" s="129"/>
       <c r="B27" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C27" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5751,7 +5725,7 @@
       <c r="BO27" s="49"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="123"/>
+      <c r="A28" s="129"/>
       <c r="B28" s="65" t="s">
         <v>131</v>
       </c>
@@ -5834,7 +5808,7 @@
       <c r="BO28" s="49"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="123"/>
+      <c r="A29" s="129"/>
       <c r="B29" s="122" t="s">
         <v>135</v>
       </c>
@@ -5917,7 +5891,7 @@
       <c r="BO29" s="49"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="123"/>
+      <c r="A30" s="129"/>
       <c r="B30" s="64" t="s">
         <v>124</v>
       </c>
@@ -5935,7 +5909,7 @@
       <c r="F30" s="41">
         <v>45988</v>
       </c>
-      <c r="G30" s="143" t="s">
+      <c r="G30" s="123" t="s">
         <v>130</v>
       </c>
       <c r="H30" s="48"/>
@@ -6000,7 +5974,7 @@
       <c r="BO30" s="49"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="123"/>
+      <c r="A31" s="129"/>
       <c r="B31" s="65" t="s">
         <v>129</v>
       </c>
@@ -6083,7 +6057,7 @@
       <c r="BO31" s="49"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="123"/>
+      <c r="A32" s="129"/>
       <c r="B32" s="87" t="s">
         <v>101</v>
       </c>
@@ -6166,7 +6140,7 @@
       <c r="BO32" s="28"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="123"/>
+      <c r="A33" s="129"/>
       <c r="B33" s="88" t="s">
         <v>108</v>
       </c>
@@ -6249,7 +6223,7 @@
       <c r="BO33" s="49"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="123"/>
+      <c r="A34" s="129"/>
       <c r="B34" s="90" t="s">
         <v>140</v>
       </c>
@@ -6332,7 +6306,7 @@
       <c r="BO34" s="49"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="123"/>
+      <c r="A35" s="129"/>
       <c r="B35" s="88" t="s">
         <v>109</v>
       </c>
@@ -6415,7 +6389,7 @@
       <c r="BO35" s="49"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="123"/>
+      <c r="A36" s="129"/>
       <c r="B36" s="91" t="s">
         <v>125</v>
       </c>
@@ -6498,7 +6472,7 @@
       <c r="BO36" s="49"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="123"/>
+      <c r="A37" s="129"/>
       <c r="B37" s="91" t="s">
         <v>126</v>
       </c>
@@ -6581,7 +6555,7 @@
       <c r="BO37" s="49"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="123"/>
+      <c r="A38" s="129"/>
       <c r="B38" s="92" t="s">
         <v>118</v>
       </c>
@@ -6664,7 +6638,7 @@
       <c r="BO38" s="49"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="123"/>
+      <c r="A39" s="129"/>
       <c r="B39" s="93" t="s">
         <v>119</v>
       </c>
@@ -6747,7 +6721,7 @@
       <c r="BO39" s="49"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="123"/>
+      <c r="A40" s="129"/>
       <c r="B40" s="93" t="s">
         <v>141</v>
       </c>
@@ -6830,7 +6804,7 @@
       <c r="BO40" s="49"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="123"/>
+      <c r="A41" s="129"/>
       <c r="B41" s="90" t="s">
         <v>142</v>
       </c>
@@ -6913,78 +6887,78 @@
       <c r="BO41" s="49"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="123"/>
-      <c r="B42" s="136" t="s">
+      <c r="A42" s="129"/>
+      <c r="B42" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="136"/>
-      <c r="D42" s="136"/>
-      <c r="E42" s="136"/>
-      <c r="F42" s="136"/>
-      <c r="G42" s="136"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="126"/>
-      <c r="L42" s="126"/>
-      <c r="M42" s="126"/>
-      <c r="N42" s="126"/>
-      <c r="O42" s="126"/>
-      <c r="P42" s="126"/>
-      <c r="Q42" s="126"/>
-      <c r="R42" s="126"/>
-      <c r="S42" s="126"/>
-      <c r="T42" s="126"/>
-      <c r="U42" s="126"/>
-      <c r="V42" s="126"/>
-      <c r="W42" s="126"/>
-      <c r="X42" s="126"/>
-      <c r="Y42" s="126"/>
-      <c r="Z42" s="126"/>
-      <c r="AA42" s="126"/>
-      <c r="AB42" s="126"/>
-      <c r="AC42" s="126"/>
-      <c r="AD42" s="126"/>
-      <c r="AE42" s="126"/>
-      <c r="AF42" s="126"/>
-      <c r="AG42" s="126"/>
-      <c r="AH42" s="126"/>
-      <c r="AI42" s="126"/>
-      <c r="AJ42" s="126"/>
-      <c r="AK42" s="126"/>
-      <c r="AL42" s="126"/>
-      <c r="AM42" s="126"/>
-      <c r="AN42" s="126"/>
-      <c r="AO42" s="126"/>
-      <c r="AP42" s="126"/>
-      <c r="AQ42" s="126"/>
-      <c r="AR42" s="126"/>
-      <c r="AS42" s="126"/>
-      <c r="AT42" s="126"/>
-      <c r="AU42" s="126"/>
-      <c r="AV42" s="126"/>
-      <c r="AW42" s="126"/>
-      <c r="AX42" s="126"/>
-      <c r="AY42" s="126"/>
-      <c r="AZ42" s="126"/>
-      <c r="BA42" s="126"/>
-      <c r="BB42" s="126"/>
-      <c r="BC42" s="126"/>
-      <c r="BD42" s="126"/>
-      <c r="BE42" s="126"/>
-      <c r="BF42" s="126"/>
-      <c r="BG42" s="126"/>
-      <c r="BH42" s="126"/>
-      <c r="BI42" s="126"/>
-      <c r="BJ42" s="126"/>
-      <c r="BK42" s="126"/>
-      <c r="BL42" s="126"/>
-      <c r="BM42" s="126"/>
-      <c r="BN42" s="126"/>
-      <c r="BO42" s="127"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="142"/>
+      <c r="E42" s="142"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="131"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="132"/>
+      <c r="M42" s="132"/>
+      <c r="N42" s="132"/>
+      <c r="O42" s="132"/>
+      <c r="P42" s="132"/>
+      <c r="Q42" s="132"/>
+      <c r="R42" s="132"/>
+      <c r="S42" s="132"/>
+      <c r="T42" s="132"/>
+      <c r="U42" s="132"/>
+      <c r="V42" s="132"/>
+      <c r="W42" s="132"/>
+      <c r="X42" s="132"/>
+      <c r="Y42" s="132"/>
+      <c r="Z42" s="132"/>
+      <c r="AA42" s="132"/>
+      <c r="AB42" s="132"/>
+      <c r="AC42" s="132"/>
+      <c r="AD42" s="132"/>
+      <c r="AE42" s="132"/>
+      <c r="AF42" s="132"/>
+      <c r="AG42" s="132"/>
+      <c r="AH42" s="132"/>
+      <c r="AI42" s="132"/>
+      <c r="AJ42" s="132"/>
+      <c r="AK42" s="132"/>
+      <c r="AL42" s="132"/>
+      <c r="AM42" s="132"/>
+      <c r="AN42" s="132"/>
+      <c r="AO42" s="132"/>
+      <c r="AP42" s="132"/>
+      <c r="AQ42" s="132"/>
+      <c r="AR42" s="132"/>
+      <c r="AS42" s="132"/>
+      <c r="AT42" s="132"/>
+      <c r="AU42" s="132"/>
+      <c r="AV42" s="132"/>
+      <c r="AW42" s="132"/>
+      <c r="AX42" s="132"/>
+      <c r="AY42" s="132"/>
+      <c r="AZ42" s="132"/>
+      <c r="BA42" s="132"/>
+      <c r="BB42" s="132"/>
+      <c r="BC42" s="132"/>
+      <c r="BD42" s="132"/>
+      <c r="BE42" s="132"/>
+      <c r="BF42" s="132"/>
+      <c r="BG42" s="132"/>
+      <c r="BH42" s="132"/>
+      <c r="BI42" s="132"/>
+      <c r="BJ42" s="132"/>
+      <c r="BK42" s="132"/>
+      <c r="BL42" s="132"/>
+      <c r="BM42" s="132"/>
+      <c r="BN42" s="132"/>
+      <c r="BO42" s="133"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="123"/>
+      <c r="A43" s="129"/>
       <c r="B43" s="88" t="s">
         <v>107</v>
       </c>
@@ -7067,7 +7041,7 @@
       <c r="BO43" s="49"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="123"/>
+      <c r="A44" s="129"/>
       <c r="B44" s="90" t="s">
         <v>143</v>
       </c>
@@ -7150,7 +7124,7 @@
       <c r="BO44" s="49"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="123"/>
+      <c r="A45" s="129"/>
       <c r="B45" s="90" t="s">
         <v>144</v>
       </c>
@@ -7233,7 +7207,7 @@
       <c r="BO45" s="49"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="123"/>
+      <c r="A46" s="129"/>
       <c r="B46" s="94" t="s">
         <v>145</v>
       </c>
@@ -7316,7 +7290,7 @@
       <c r="BO46" s="49"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="123"/>
+      <c r="A47" s="129"/>
       <c r="B47" s="95" t="s">
         <v>154</v>
       </c>
@@ -7399,7 +7373,7 @@
       <c r="BO47" s="49"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="123"/>
+      <c r="A48" s="129"/>
       <c r="B48" s="95" t="s">
         <v>153</v>
       </c>
@@ -7482,7 +7456,7 @@
       <c r="BO48" s="49"/>
     </row>
     <row r="49" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="123"/>
+      <c r="A49" s="129"/>
       <c r="B49" s="95" t="s">
         <v>146</v>
       </c>
@@ -7565,7 +7539,7 @@
       <c r="BO49" s="49"/>
     </row>
     <row r="50" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A50" s="123"/>
+      <c r="A50" s="129"/>
       <c r="B50" s="65" t="s">
         <v>155</v>
       </c>
@@ -7648,83 +7622,83 @@
       <c r="BO50" s="29"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51" s="123"/>
-      <c r="B51" s="136" t="s">
+      <c r="A51" s="129"/>
+      <c r="B51" s="142" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="136"/>
-      <c r="D51" s="136"/>
-      <c r="E51" s="136"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="136"/>
-      <c r="H51" s="125"/>
-      <c r="I51" s="126"/>
-      <c r="J51" s="126"/>
-      <c r="K51" s="126"/>
-      <c r="L51" s="126"/>
-      <c r="M51" s="126"/>
-      <c r="N51" s="126"/>
-      <c r="O51" s="126"/>
-      <c r="P51" s="126"/>
-      <c r="Q51" s="126"/>
-      <c r="R51" s="126"/>
-      <c r="S51" s="126"/>
-      <c r="T51" s="126"/>
-      <c r="U51" s="126"/>
-      <c r="V51" s="126"/>
-      <c r="W51" s="126"/>
-      <c r="X51" s="126"/>
-      <c r="Y51" s="126"/>
-      <c r="Z51" s="126"/>
-      <c r="AA51" s="126"/>
-      <c r="AB51" s="126"/>
-      <c r="AC51" s="126"/>
-      <c r="AD51" s="126"/>
-      <c r="AE51" s="126"/>
-      <c r="AF51" s="126"/>
-      <c r="AG51" s="126"/>
-      <c r="AH51" s="126"/>
-      <c r="AI51" s="126"/>
-      <c r="AJ51" s="126"/>
-      <c r="AK51" s="126"/>
-      <c r="AL51" s="126"/>
-      <c r="AM51" s="126"/>
-      <c r="AN51" s="126"/>
-      <c r="AO51" s="126"/>
-      <c r="AP51" s="126"/>
-      <c r="AQ51" s="126"/>
-      <c r="AR51" s="126"/>
-      <c r="AS51" s="126"/>
-      <c r="AT51" s="126"/>
-      <c r="AU51" s="126"/>
-      <c r="AV51" s="126"/>
-      <c r="AW51" s="126"/>
-      <c r="AX51" s="126"/>
-      <c r="AY51" s="126"/>
-      <c r="AZ51" s="126"/>
-      <c r="BA51" s="126"/>
-      <c r="BB51" s="126"/>
-      <c r="BC51" s="126"/>
-      <c r="BD51" s="126"/>
-      <c r="BE51" s="126"/>
-      <c r="BF51" s="126"/>
-      <c r="BG51" s="126"/>
-      <c r="BH51" s="126"/>
-      <c r="BI51" s="126"/>
-      <c r="BJ51" s="126"/>
-      <c r="BK51" s="126"/>
-      <c r="BL51" s="126"/>
-      <c r="BM51" s="126"/>
-      <c r="BN51" s="126"/>
-      <c r="BO51" s="127"/>
+      <c r="C51" s="142"/>
+      <c r="D51" s="142"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="142"/>
+      <c r="G51" s="142"/>
+      <c r="H51" s="131"/>
+      <c r="I51" s="132"/>
+      <c r="J51" s="132"/>
+      <c r="K51" s="132"/>
+      <c r="L51" s="132"/>
+      <c r="M51" s="132"/>
+      <c r="N51" s="132"/>
+      <c r="O51" s="132"/>
+      <c r="P51" s="132"/>
+      <c r="Q51" s="132"/>
+      <c r="R51" s="132"/>
+      <c r="S51" s="132"/>
+      <c r="T51" s="132"/>
+      <c r="U51" s="132"/>
+      <c r="V51" s="132"/>
+      <c r="W51" s="132"/>
+      <c r="X51" s="132"/>
+      <c r="Y51" s="132"/>
+      <c r="Z51" s="132"/>
+      <c r="AA51" s="132"/>
+      <c r="AB51" s="132"/>
+      <c r="AC51" s="132"/>
+      <c r="AD51" s="132"/>
+      <c r="AE51" s="132"/>
+      <c r="AF51" s="132"/>
+      <c r="AG51" s="132"/>
+      <c r="AH51" s="132"/>
+      <c r="AI51" s="132"/>
+      <c r="AJ51" s="132"/>
+      <c r="AK51" s="132"/>
+      <c r="AL51" s="132"/>
+      <c r="AM51" s="132"/>
+      <c r="AN51" s="132"/>
+      <c r="AO51" s="132"/>
+      <c r="AP51" s="132"/>
+      <c r="AQ51" s="132"/>
+      <c r="AR51" s="132"/>
+      <c r="AS51" s="132"/>
+      <c r="AT51" s="132"/>
+      <c r="AU51" s="132"/>
+      <c r="AV51" s="132"/>
+      <c r="AW51" s="132"/>
+      <c r="AX51" s="132"/>
+      <c r="AY51" s="132"/>
+      <c r="AZ51" s="132"/>
+      <c r="BA51" s="132"/>
+      <c r="BB51" s="132"/>
+      <c r="BC51" s="132"/>
+      <c r="BD51" s="132"/>
+      <c r="BE51" s="132"/>
+      <c r="BF51" s="132"/>
+      <c r="BG51" s="132"/>
+      <c r="BH51" s="132"/>
+      <c r="BI51" s="132"/>
+      <c r="BJ51" s="132"/>
+      <c r="BK51" s="132"/>
+      <c r="BL51" s="132"/>
+      <c r="BM51" s="132"/>
+      <c r="BN51" s="132"/>
+      <c r="BO51" s="133"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52" s="123"/>
+      <c r="A52" s="129"/>
       <c r="B52" s="96" t="s">
         <v>147</v>
       </c>
       <c r="C52" s="97" t="str">
-        <f t="shared" ref="C52:C75" ca="1" si="7">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
+        <f t="shared" ref="C52:C76" ca="1" si="7">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D52" s="84" t="str">
@@ -7802,7 +7776,7 @@
       <c r="BO52" s="49"/>
     </row>
     <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53" s="123"/>
+      <c r="A53" s="129"/>
       <c r="B53" s="100" t="s">
         <v>148</v>
       </c>
@@ -7885,7 +7859,7 @@
       <c r="BO53" s="49"/>
     </row>
     <row r="54" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A54" s="123"/>
+      <c r="A54" s="129"/>
       <c r="B54" s="100" t="s">
         <v>149</v>
       </c>
@@ -7968,7 +7942,7 @@
       <c r="BO54" s="49"/>
     </row>
     <row r="55" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A55" s="123"/>
+      <c r="A55" s="129"/>
       <c r="B55" s="100" t="s">
         <v>150</v>
       </c>
@@ -8051,9 +8025,9 @@
       <c r="BO55" s="49"/>
     </row>
     <row r="56" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A56" s="123"/>
+      <c r="A56" s="129"/>
       <c r="B56" s="118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C56" s="119" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -8134,7 +8108,7 @@
       <c r="BO56" s="49"/>
     </row>
     <row r="57" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A57" s="123"/>
+      <c r="A57" s="129"/>
       <c r="B57" s="104" t="s">
         <v>151</v>
       </c>
@@ -8217,78 +8191,78 @@
       <c r="BO57" s="49"/>
     </row>
     <row r="58" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A58" s="123"/>
-      <c r="B58" s="140" t="s">
+      <c r="A58" s="129"/>
+      <c r="B58" s="146" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="141"/>
-      <c r="D58" s="141"/>
-      <c r="E58" s="141"/>
-      <c r="F58" s="141"/>
-      <c r="G58" s="142"/>
-      <c r="H58" s="125"/>
-      <c r="I58" s="126"/>
-      <c r="J58" s="126"/>
-      <c r="K58" s="126"/>
-      <c r="L58" s="126"/>
-      <c r="M58" s="126"/>
-      <c r="N58" s="126"/>
-      <c r="O58" s="126"/>
-      <c r="P58" s="126"/>
-      <c r="Q58" s="126"/>
-      <c r="R58" s="126"/>
-      <c r="S58" s="126"/>
-      <c r="T58" s="126"/>
-      <c r="U58" s="126"/>
-      <c r="V58" s="126"/>
-      <c r="W58" s="126"/>
-      <c r="X58" s="126"/>
-      <c r="Y58" s="126"/>
-      <c r="Z58" s="126"/>
-      <c r="AA58" s="126"/>
-      <c r="AB58" s="126"/>
-      <c r="AC58" s="126"/>
-      <c r="AD58" s="126"/>
-      <c r="AE58" s="126"/>
-      <c r="AF58" s="126"/>
-      <c r="AG58" s="126"/>
-      <c r="AH58" s="126"/>
-      <c r="AI58" s="126"/>
-      <c r="AJ58" s="126"/>
-      <c r="AK58" s="126"/>
-      <c r="AL58" s="126"/>
-      <c r="AM58" s="126"/>
-      <c r="AN58" s="126"/>
-      <c r="AO58" s="126"/>
-      <c r="AP58" s="126"/>
-      <c r="AQ58" s="126"/>
-      <c r="AR58" s="126"/>
-      <c r="AS58" s="126"/>
-      <c r="AT58" s="126"/>
-      <c r="AU58" s="126"/>
-      <c r="AV58" s="126"/>
-      <c r="AW58" s="126"/>
-      <c r="AX58" s="126"/>
-      <c r="AY58" s="126"/>
-      <c r="AZ58" s="126"/>
-      <c r="BA58" s="126"/>
-      <c r="BB58" s="126"/>
-      <c r="BC58" s="126"/>
-      <c r="BD58" s="126"/>
-      <c r="BE58" s="126"/>
-      <c r="BF58" s="126"/>
-      <c r="BG58" s="126"/>
-      <c r="BH58" s="126"/>
-      <c r="BI58" s="126"/>
-      <c r="BJ58" s="126"/>
-      <c r="BK58" s="126"/>
-      <c r="BL58" s="126"/>
-      <c r="BM58" s="126"/>
-      <c r="BN58" s="126"/>
-      <c r="BO58" s="127"/>
+      <c r="C58" s="147"/>
+      <c r="D58" s="147"/>
+      <c r="E58" s="147"/>
+      <c r="F58" s="147"/>
+      <c r="G58" s="148"/>
+      <c r="H58" s="131"/>
+      <c r="I58" s="132"/>
+      <c r="J58" s="132"/>
+      <c r="K58" s="132"/>
+      <c r="L58" s="132"/>
+      <c r="M58" s="132"/>
+      <c r="N58" s="132"/>
+      <c r="O58" s="132"/>
+      <c r="P58" s="132"/>
+      <c r="Q58" s="132"/>
+      <c r="R58" s="132"/>
+      <c r="S58" s="132"/>
+      <c r="T58" s="132"/>
+      <c r="U58" s="132"/>
+      <c r="V58" s="132"/>
+      <c r="W58" s="132"/>
+      <c r="X58" s="132"/>
+      <c r="Y58" s="132"/>
+      <c r="Z58" s="132"/>
+      <c r="AA58" s="132"/>
+      <c r="AB58" s="132"/>
+      <c r="AC58" s="132"/>
+      <c r="AD58" s="132"/>
+      <c r="AE58" s="132"/>
+      <c r="AF58" s="132"/>
+      <c r="AG58" s="132"/>
+      <c r="AH58" s="132"/>
+      <c r="AI58" s="132"/>
+      <c r="AJ58" s="132"/>
+      <c r="AK58" s="132"/>
+      <c r="AL58" s="132"/>
+      <c r="AM58" s="132"/>
+      <c r="AN58" s="132"/>
+      <c r="AO58" s="132"/>
+      <c r="AP58" s="132"/>
+      <c r="AQ58" s="132"/>
+      <c r="AR58" s="132"/>
+      <c r="AS58" s="132"/>
+      <c r="AT58" s="132"/>
+      <c r="AU58" s="132"/>
+      <c r="AV58" s="132"/>
+      <c r="AW58" s="132"/>
+      <c r="AX58" s="132"/>
+      <c r="AY58" s="132"/>
+      <c r="AZ58" s="132"/>
+      <c r="BA58" s="132"/>
+      <c r="BB58" s="132"/>
+      <c r="BC58" s="132"/>
+      <c r="BD58" s="132"/>
+      <c r="BE58" s="132"/>
+      <c r="BF58" s="132"/>
+      <c r="BG58" s="132"/>
+      <c r="BH58" s="132"/>
+      <c r="BI58" s="132"/>
+      <c r="BJ58" s="132"/>
+      <c r="BK58" s="132"/>
+      <c r="BL58" s="132"/>
+      <c r="BM58" s="132"/>
+      <c r="BN58" s="132"/>
+      <c r="BO58" s="133"/>
     </row>
     <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A59" s="123"/>
+      <c r="A59" s="129"/>
       <c r="B59" s="91" t="s">
         <v>132</v>
       </c>
@@ -8371,7 +8345,7 @@
       <c r="BO59" s="49"/>
     </row>
     <row r="60" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A60" s="123"/>
+      <c r="A60" s="129"/>
       <c r="B60" s="108" t="s">
         <v>152</v>
       </c>
@@ -8454,13 +8428,13 @@
       <c r="BO60" s="49"/>
     </row>
     <row r="61" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A61" s="123"/>
+      <c r="A61" s="129"/>
       <c r="B61" s="60" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="32" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>66.7%</v>
+        <v>83.3%</v>
       </c>
       <c r="D61" s="56" t="str">
         <f t="shared" si="0"/>
@@ -8537,16 +8511,16 @@
       <c r="BO61" s="49"/>
     </row>
     <row r="62" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A62" s="123"/>
-      <c r="B62" s="144" t="s">
-        <v>161</v>
+      <c r="A62" s="129"/>
+      <c r="B62" s="124" t="s">
+        <v>160</v>
       </c>
       <c r="C62" s="119" t="str">
         <f ca="1">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D62" s="21" t="str">
-        <f t="shared" ref="D62:D72" si="13">IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D62:D73" si="13">IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
       <c r="E62" s="22">
@@ -8555,7 +8529,7 @@
       <c r="F62" s="22">
         <v>45988</v>
       </c>
-      <c r="G62" s="145" t="s">
+      <c r="G62" s="125" t="s">
         <v>114</v>
       </c>
       <c r="H62" s="48"/>
@@ -8620,8 +8594,8 @@
       <c r="BO62" s="49"/>
     </row>
     <row r="63" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="123"/>
-      <c r="B63" s="146" t="s">
+      <c r="A63" s="129"/>
+      <c r="B63" s="126" t="s">
         <v>120</v>
       </c>
       <c r="C63" s="119" t="str">
@@ -8638,7 +8612,7 @@
       <c r="F63" s="22">
         <v>45988</v>
       </c>
-      <c r="G63" s="145" t="s">
+      <c r="G63" s="125" t="s">
         <v>114</v>
       </c>
       <c r="H63" s="48"/>
@@ -8703,8 +8677,8 @@
       <c r="BO63" s="49"/>
     </row>
     <row r="64" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A64" s="123"/>
-      <c r="B64" s="147" t="s">
+      <c r="A64" s="129"/>
+      <c r="B64" s="127" t="s">
         <v>121</v>
       </c>
       <c r="C64" s="32" t="str">
@@ -8721,7 +8695,7 @@
       <c r="F64" s="22">
         <v>45989</v>
       </c>
-      <c r="G64" s="145" t="s">
+      <c r="G64" s="125" t="s">
         <v>116</v>
       </c>
       <c r="H64" s="48"/>
@@ -8786,9 +8760,9 @@
       <c r="BO64" s="49"/>
     </row>
     <row r="65" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A65" s="123"/>
-      <c r="B65" s="148" t="s">
-        <v>162</v>
+      <c r="A65" s="129"/>
+      <c r="B65" s="128" t="s">
+        <v>161</v>
       </c>
       <c r="C65" s="20" t="str">
         <f ca="1">IF(OR(E65="",F65=""), "0%", IF(F65=E65, IF(TODAY()&gt;F65, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F65) - E65) / (F65 - E65) * 100, 1) &amp; "%"))</f>
@@ -8804,7 +8778,7 @@
       <c r="F65" s="22">
         <v>45992</v>
       </c>
-      <c r="G65" s="145" t="s">
+      <c r="G65" s="125" t="s">
         <v>113</v>
       </c>
       <c r="H65" s="48"/>
@@ -8869,7 +8843,7 @@
       <c r="BO65" s="49"/>
     </row>
     <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="123"/>
+      <c r="A66" s="129"/>
       <c r="B66" s="93" t="s">
         <v>122</v>
       </c>
@@ -8952,13 +8926,13 @@
       <c r="BO66" s="49"/>
     </row>
     <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A67" s="123"/>
+      <c r="A67" s="129"/>
       <c r="B67" s="111" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C67" s="39" t="str">
         <f t="shared" ref="C67" ca="1" si="14">IF(F67=E67, IF(TODAY()&gt;F67, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F67) - E67) / (F67 - E67) * 100, 1) &amp; "%")</f>
-        <v>33.3%</v>
+        <v>66.7%</v>
       </c>
       <c r="D67" s="40" t="str">
         <f t="shared" si="13"/>
@@ -9035,13 +9009,13 @@
       <c r="BO67" s="49"/>
     </row>
     <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A68" s="124"/>
+      <c r="A68" s="130"/>
       <c r="B68" s="111" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C68" s="39" t="str">
         <f ca="1">IF(F68=E68, IF(TODAY()&gt;F68, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F68) - E68) / (F68 - E68) * 100, 1) &amp; "%")</f>
-        <v>53.8%</v>
+        <v>76.9%</v>
       </c>
       <c r="D68" s="40" t="str">
         <f t="shared" si="13"/>
@@ -9118,7 +9092,7 @@
       <c r="BO68" s="49"/>
     </row>
     <row r="69" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A69" s="123" t="s">
+      <c r="A69" s="129" t="s">
         <v>88</v>
       </c>
       <c r="B69" s="57" t="s">
@@ -9203,7 +9177,7 @@
       <c r="BO69" s="53"/>
     </row>
     <row r="70" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A70" s="123"/>
+      <c r="A70" s="129"/>
       <c r="B70" s="113" t="s">
         <v>2</v>
       </c>
@@ -9213,10 +9187,14 @@
       </c>
       <c r="D70" s="40" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
+        <v>10일</v>
+      </c>
+      <c r="E70" s="41">
+        <v>45999</v>
+      </c>
+      <c r="F70" s="41">
+        <v>46008</v>
+      </c>
       <c r="G70" s="114" t="s">
         <v>97</v>
       </c>
@@ -9282,7 +9260,7 @@
       <c r="BO70" s="49"/>
     </row>
     <row r="71" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A71" s="123"/>
+      <c r="A71" s="129"/>
       <c r="B71" s="115" t="s">
         <v>87</v>
       </c>
@@ -9292,10 +9270,14 @@
       </c>
       <c r="D71" s="40" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
+        <v>10일</v>
+      </c>
+      <c r="E71" s="41">
+        <v>45999</v>
+      </c>
+      <c r="F71" s="41">
+        <v>46008</v>
+      </c>
       <c r="G71" s="114" t="s">
         <v>97</v>
       </c>
@@ -9361,9 +9343,9 @@
       <c r="BO71" s="49"/>
     </row>
     <row r="72" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A72" s="123"/>
+      <c r="A72" s="129"/>
       <c r="B72" s="116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C72" s="39" t="str">
         <f ca="1">IF(OR(E72="",F72=""), "0%", IF(F72=E72, IF(TODAY()&gt;F72, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F72) - E72) / (F72 - E72) * 100, 1) &amp; "%"))</f>
@@ -9371,10 +9353,14 @@
       </c>
       <c r="D72" s="40" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
+        <v>10일</v>
+      </c>
+      <c r="E72" s="41">
+        <v>45999</v>
+      </c>
+      <c r="F72" s="41">
+        <v>46008</v>
+      </c>
       <c r="G72" s="114" t="s">
         <v>97</v>
       </c>
@@ -9439,17 +9425,17 @@
       <c r="BN72" s="49"/>
       <c r="BO72" s="49"/>
     </row>
-    <row r="73" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A73" s="123"/>
-      <c r="B73" s="111" t="s">
-        <v>3</v>
+    <row r="73" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A73" s="129"/>
+      <c r="B73" s="149" t="s">
+        <v>163</v>
       </c>
       <c r="C73" s="39" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="C73" ca="1" si="15">IF(F73=E73, IF(TODAY()&gt;F73, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F73) - E73) / (F73 - E73) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
       <c r="D73" s="40" t="str">
-        <f t="shared" ref="D73:D75" si="15">IF(AND(F73&lt;&gt;"", E73&lt;&gt;""), F73 - E73 + 1 &amp; "일", "")</f>
+        <f t="shared" si="13"/>
         <v>10일</v>
       </c>
       <c r="E73" s="41">
@@ -9522,24 +9508,24 @@
       <c r="BN73" s="49"/>
       <c r="BO73" s="49"/>
     </row>
-    <row r="74" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A74" s="123"/>
+    <row r="74" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A74" s="129"/>
       <c r="B74" s="111" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="C74" s="39" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>0%</v>
       </c>
       <c r="D74" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>3일</v>
+        <f t="shared" ref="D74:D76" si="16">IF(AND(F74&lt;&gt;"", E74&lt;&gt;""), F74 - E74 + 1 &amp; "일", "")</f>
+        <v>10일</v>
       </c>
       <c r="E74" s="41">
+        <v>45999</v>
+      </c>
+      <c r="F74" s="41">
         <v>46008</v>
-      </c>
-      <c r="F74" s="41">
-        <v>46010</v>
       </c>
       <c r="G74" s="117" t="s">
         <v>95</v>
@@ -9606,20 +9592,20 @@
       <c r="BO74" s="49"/>
     </row>
     <row r="75" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A75" s="124"/>
+      <c r="A75" s="129"/>
       <c r="B75" s="111" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C75" s="39" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>0%</v>
       </c>
       <c r="D75" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>1일</v>
+        <f t="shared" si="16"/>
+        <v>3일</v>
       </c>
       <c r="E75" s="41">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="F75" s="41">
         <v>46010</v>
@@ -9688,12 +9674,92 @@
       <c r="BN75" s="49"/>
       <c r="BO75" s="49"/>
     </row>
-    <row r="76" spans="1:67">
-      <c r="E76" s="7"/>
-      <c r="F76" s="1"/>
-      <c r="I76" s="3"/>
+    <row r="76" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A76" s="130"/>
+      <c r="B76" s="111" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="39" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>0%</v>
+      </c>
+      <c r="D76" s="40" t="str">
+        <f t="shared" si="16"/>
+        <v>1일</v>
+      </c>
+      <c r="E76" s="41">
+        <v>46010</v>
+      </c>
+      <c r="F76" s="41">
+        <v>46010</v>
+      </c>
+      <c r="G76" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H76" s="48"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="50"/>
+      <c r="M76" s="51"/>
+      <c r="N76" s="49"/>
+      <c r="O76" s="49"/>
+      <c r="P76" s="49"/>
+      <c r="Q76" s="49"/>
+      <c r="R76" s="49"/>
+      <c r="S76" s="50"/>
+      <c r="T76" s="51"/>
+      <c r="U76" s="49"/>
+      <c r="V76" s="49"/>
+      <c r="W76" s="49"/>
+      <c r="X76" s="49"/>
+      <c r="Y76" s="49"/>
+      <c r="Z76" s="50"/>
+      <c r="AA76" s="51"/>
+      <c r="AB76" s="49"/>
+      <c r="AC76" s="49"/>
+      <c r="AD76" s="49"/>
+      <c r="AE76" s="49"/>
+      <c r="AF76" s="49"/>
+      <c r="AG76" s="50"/>
+      <c r="AH76" s="51"/>
+      <c r="AI76" s="49"/>
+      <c r="AJ76" s="49"/>
+      <c r="AK76" s="49"/>
+      <c r="AL76" s="49"/>
+      <c r="AM76" s="49"/>
+      <c r="AN76" s="50"/>
+      <c r="AO76" s="51"/>
+      <c r="AP76" s="49"/>
+      <c r="AQ76" s="49"/>
+      <c r="AR76" s="49"/>
+      <c r="AS76" s="49"/>
+      <c r="AT76" s="49"/>
+      <c r="AU76" s="50"/>
+      <c r="AV76" s="51"/>
+      <c r="AW76" s="49"/>
+      <c r="AX76" s="49"/>
+      <c r="AY76" s="49"/>
+      <c r="AZ76" s="49"/>
+      <c r="BA76" s="49"/>
+      <c r="BB76" s="50"/>
+      <c r="BC76" s="51"/>
+      <c r="BD76" s="49"/>
+      <c r="BE76" s="49"/>
+      <c r="BF76" s="49"/>
+      <c r="BG76" s="49"/>
+      <c r="BH76" s="49"/>
+      <c r="BI76" s="50"/>
+      <c r="BJ76" s="51"/>
+      <c r="BK76" s="49"/>
+      <c r="BL76" s="49"/>
+      <c r="BM76" s="49"/>
+      <c r="BN76" s="49"/>
+      <c r="BO76" s="49"/>
     </row>
     <row r="77" spans="1:67">
+      <c r="E77" s="7"/>
+      <c r="F77" s="1"/>
       <c r="I77" s="3"/>
     </row>
     <row r="78" spans="1:67">
@@ -9705,69 +9771,72 @@
     <row r="80" spans="1:67">
       <c r="I80" s="3"/>
     </row>
-    <row r="81" spans="2:8">
-      <c r="B81" s="8" t="s">
+    <row r="81" spans="2:9">
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" spans="2:9">
+      <c r="B82" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="16.5">
-      <c r="B82" s="9" t="s">
+    <row r="83" spans="2:9" ht="16.5">
+      <c r="B83" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="3"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="3"/>
     </row>
-    <row r="83" spans="2:8">
-      <c r="B83" s="10" t="s">
+    <row r="84" spans="2:9">
+      <c r="B84" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
-      <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="2:8">
+    <row r="85" spans="2:9">
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="2:8"/>
-    <row r="87" spans="2:8"/>
-    <row r="88" spans="2:8" ht="16.5">
-      <c r="B88" s="2"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
+    <row r="86" spans="2:9">
+      <c r="C86" s="3"/>
     </row>
-    <row r="89" spans="2:8">
+    <row r="87" spans="2:9"/>
+    <row r="88" spans="2:9"/>
+    <row r="89" spans="2:9" ht="16.5">
+      <c r="B89" s="2"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="2:8" ht="16.5">
-      <c r="B90" s="2"/>
+    <row r="90" spans="2:9">
+      <c r="C90" s="3"/>
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="2:8">
-      <c r="C91" s="3"/>
+    <row r="91" spans="2:9" ht="16.5">
+      <c r="B91" s="2"/>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:9">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="2:8">
+    <row r="93" spans="2:9">
+      <c r="C93" s="3"/>
       <c r="D93" s="3"/>
     </row>
-    <row r="94" spans="2:8">
+    <row r="94" spans="2:9">
       <c r="D94" s="3"/>
-      <c r="H94" s="11"/>
     </row>
-    <row r="95" spans="2:8" ht="15" customHeight="1">
+    <row r="95" spans="2:9">
       <c r="D95" s="3"/>
+      <c r="H95" s="11"/>
     </row>
-    <row r="96" spans="2:8" ht="15" customHeight="1">
-      <c r="C96" s="3"/>
+    <row r="96" spans="2:9" ht="15" customHeight="1">
       <c r="D96" s="3"/>
+    </row>
+    <row r="97" spans="3:4" ht="15" customHeight="1">
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A69:A75"/>
+    <mergeCell ref="A69:A76"/>
     <mergeCell ref="H51:BO51"/>
     <mergeCell ref="H42:BO42"/>
     <mergeCell ref="C1:E1"/>

--- a/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2. WBS/5조_WBS_현대이지웰_최종프로젝트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\related_Re_View\Re_View_Doc\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53B347F-14BB-4C06-84C9-37176FBF9446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E591CDDA-8563-4497-BD7C-A289787953BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="166">
   <si>
     <t>팀명</t>
   </si>
@@ -450,10 +450,6 @@
   </si>
   <si>
     <t>마이페이지 배송지 UI</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>이미지 업로드 기능</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1623,6 +1619,10 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
+    <t>이미지 업로드 기능( 로컬 기준 )</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">MinIO </t>
     </r>
@@ -1634,7 +1634,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>연결 및 코드 전반적인 수정</t>
+      <t>연결</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1642,10 +1642,71 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김석현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이재빈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정윤성</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배포용 코드 수정</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">AWS </t>
     </r>
     <r>
@@ -1656,7 +1717,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>및 배포용 코드 수정, 테스트</t>
+      <t>연결 및 테스트</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -2602,7 +2663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2793,9 +2854,6 @@
     <xf numFmtId="0" fontId="25" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2970,9 +3028,6 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2988,6 +3043,9 @@
     <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3048,8 +3106,8 @@
     <xf numFmtId="0" fontId="23" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3276,7 +3334,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BO97"/>
+  <dimension ref="A1:BO98"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="60.5703125" customWidth="1"/>
@@ -3291,31 +3349,31 @@
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="134" t="s">
+      <c r="C1" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="136" t="s">
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
@@ -3379,7 +3437,7 @@
       <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="137" t="s">
+      <c r="G2" s="136" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="15" t="s">
@@ -3570,7 +3628,7 @@
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="138"/>
+      <c r="G3" s="137"/>
       <c r="H3" s="24">
         <v>45951</v>
       </c>
@@ -3753,10 +3811,10 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="65" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="20" t="str">
@@ -3838,8 +3896,8 @@
       <c r="BO4" s="44"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A5" s="140"/>
-      <c r="B5" s="66" t="s">
+      <c r="A5" s="139"/>
+      <c r="B5" s="65" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="20" t="str">
@@ -3921,8 +3979,8 @@
       <c r="BO5" s="49"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="140"/>
-      <c r="B6" s="66" t="s">
+      <c r="A6" s="139"/>
+      <c r="B6" s="65" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="20" t="str">
@@ -4004,8 +4062,8 @@
       <c r="BO6" s="49"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="140"/>
-      <c r="B7" s="70" t="s">
+      <c r="A7" s="139"/>
+      <c r="B7" s="69" t="s">
         <v>75</v>
       </c>
       <c r="C7" s="20" t="str">
@@ -4087,8 +4145,8 @@
       <c r="BO7" s="49"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="140"/>
-      <c r="B8" s="71" t="s">
+      <c r="A8" s="139"/>
+      <c r="B8" s="70" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="20" t="str">
@@ -4105,7 +4163,7 @@
       <c r="F8" s="22">
         <v>45966</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="71" t="s">
         <v>96</v>
       </c>
       <c r="H8" s="48"/>
@@ -4170,8 +4228,8 @@
       <c r="BO8" s="49"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="140"/>
-      <c r="B9" s="66" t="s">
+      <c r="A9" s="139"/>
+      <c r="B9" s="65" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="20" t="str">
@@ -4253,8 +4311,8 @@
       <c r="BO9" s="49"/>
     </row>
     <row r="10" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="140"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="139"/>
+      <c r="B10" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="20" t="str">
@@ -4336,8 +4394,8 @@
       <c r="BO10" s="49"/>
     </row>
     <row r="11" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="140"/>
-      <c r="B11" s="73" t="s">
+      <c r="A11" s="139"/>
+      <c r="B11" s="72" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="31" t="str">
@@ -4348,13 +4406,13 @@
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="73">
         <v>45957</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F11" s="73">
         <v>45958</v>
       </c>
-      <c r="G11" s="75" t="s">
+      <c r="G11" s="74" t="s">
         <v>105</v>
       </c>
       <c r="H11" s="48"/>
@@ -4419,7 +4477,7 @@
       <c r="BO11" s="49"/>
     </row>
     <row r="12" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="144" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="57" t="s">
@@ -4504,8 +4562,8 @@
       <c r="BO12" s="49"/>
     </row>
     <row r="13" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A13" s="129"/>
-      <c r="B13" s="69" t="s">
+      <c r="A13" s="128"/>
+      <c r="B13" s="68" t="s">
         <v>82</v>
       </c>
       <c r="C13" s="32" t="str">
@@ -4587,8 +4645,8 @@
       <c r="BO13" s="49"/>
     </row>
     <row r="14" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="129"/>
-      <c r="B14" s="76" t="s">
+      <c r="A14" s="128"/>
+      <c r="B14" s="75" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="31" t="str">
@@ -4599,13 +4657,13 @@
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E14" s="73">
         <v>45959</v>
       </c>
-      <c r="F14" s="74">
+      <c r="F14" s="73">
         <v>45959</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="G14" s="76" t="s">
         <v>95</v>
       </c>
       <c r="H14" s="48"/>
@@ -4670,7 +4728,7 @@
       <c r="BO14" s="49"/>
     </row>
     <row r="15" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A15" s="129"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="57" t="s">
         <v>84</v>
       </c>
@@ -4753,9 +4811,9 @@
       <c r="BO15" s="38"/>
     </row>
     <row r="16" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="129"/>
-      <c r="B16" s="78" t="s">
-        <v>136</v>
+      <c r="A16" s="128"/>
+      <c r="B16" s="77" t="s">
+        <v>135</v>
       </c>
       <c r="C16" s="32" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4771,7 +4829,7 @@
       <c r="F16" s="33">
         <v>45966</v>
       </c>
-      <c r="G16" s="79" t="s">
+      <c r="G16" s="78" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="48"/>
@@ -4836,80 +4894,80 @@
       <c r="BO16" s="42"/>
     </row>
     <row r="17" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="129"/>
-      <c r="B17" s="143" t="s">
+      <c r="A17" s="128"/>
+      <c r="B17" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="132"/>
-      <c r="R17" s="132"/>
-      <c r="S17" s="132"/>
-      <c r="T17" s="132"/>
-      <c r="U17" s="132"/>
-      <c r="V17" s="132"/>
-      <c r="W17" s="132"/>
-      <c r="X17" s="132"/>
-      <c r="Y17" s="132"/>
-      <c r="Z17" s="132"/>
-      <c r="AA17" s="132"/>
-      <c r="AB17" s="132"/>
-      <c r="AC17" s="132"/>
-      <c r="AD17" s="132"/>
-      <c r="AE17" s="132"/>
-      <c r="AF17" s="132"/>
-      <c r="AG17" s="132"/>
-      <c r="AH17" s="132"/>
-      <c r="AI17" s="132"/>
-      <c r="AJ17" s="132"/>
-      <c r="AK17" s="132"/>
-      <c r="AL17" s="132"/>
-      <c r="AM17" s="132"/>
-      <c r="AN17" s="132"/>
-      <c r="AO17" s="132"/>
-      <c r="AP17" s="132"/>
-      <c r="AQ17" s="132"/>
-      <c r="AR17" s="132"/>
-      <c r="AS17" s="132"/>
-      <c r="AT17" s="132"/>
-      <c r="AU17" s="132"/>
-      <c r="AV17" s="132"/>
-      <c r="AW17" s="132"/>
-      <c r="AX17" s="132"/>
-      <c r="AY17" s="132"/>
-      <c r="AZ17" s="132"/>
-      <c r="BA17" s="132"/>
-      <c r="BB17" s="132"/>
-      <c r="BC17" s="132"/>
-      <c r="BD17" s="132"/>
-      <c r="BE17" s="132"/>
-      <c r="BF17" s="132"/>
-      <c r="BG17" s="132"/>
-      <c r="BH17" s="132"/>
-      <c r="BI17" s="132"/>
-      <c r="BJ17" s="132"/>
-      <c r="BK17" s="132"/>
-      <c r="BL17" s="132"/>
-      <c r="BM17" s="132"/>
-      <c r="BN17" s="132"/>
-      <c r="BO17" s="133"/>
+      <c r="C17" s="142"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="131"/>
+      <c r="N17" s="131"/>
+      <c r="O17" s="131"/>
+      <c r="P17" s="131"/>
+      <c r="Q17" s="131"/>
+      <c r="R17" s="131"/>
+      <c r="S17" s="131"/>
+      <c r="T17" s="131"/>
+      <c r="U17" s="131"/>
+      <c r="V17" s="131"/>
+      <c r="W17" s="131"/>
+      <c r="X17" s="131"/>
+      <c r="Y17" s="131"/>
+      <c r="Z17" s="131"/>
+      <c r="AA17" s="131"/>
+      <c r="AB17" s="131"/>
+      <c r="AC17" s="131"/>
+      <c r="AD17" s="131"/>
+      <c r="AE17" s="131"/>
+      <c r="AF17" s="131"/>
+      <c r="AG17" s="131"/>
+      <c r="AH17" s="131"/>
+      <c r="AI17" s="131"/>
+      <c r="AJ17" s="131"/>
+      <c r="AK17" s="131"/>
+      <c r="AL17" s="131"/>
+      <c r="AM17" s="131"/>
+      <c r="AN17" s="131"/>
+      <c r="AO17" s="131"/>
+      <c r="AP17" s="131"/>
+      <c r="AQ17" s="131"/>
+      <c r="AR17" s="131"/>
+      <c r="AS17" s="131"/>
+      <c r="AT17" s="131"/>
+      <c r="AU17" s="131"/>
+      <c r="AV17" s="131"/>
+      <c r="AW17" s="131"/>
+      <c r="AX17" s="131"/>
+      <c r="AY17" s="131"/>
+      <c r="AZ17" s="131"/>
+      <c r="BA17" s="131"/>
+      <c r="BB17" s="131"/>
+      <c r="BC17" s="131"/>
+      <c r="BD17" s="131"/>
+      <c r="BE17" s="131"/>
+      <c r="BF17" s="131"/>
+      <c r="BG17" s="131"/>
+      <c r="BH17" s="131"/>
+      <c r="BI17" s="131"/>
+      <c r="BJ17" s="131"/>
+      <c r="BK17" s="131"/>
+      <c r="BL17" s="131"/>
+      <c r="BM17" s="131"/>
+      <c r="BN17" s="131"/>
+      <c r="BO17" s="132"/>
     </row>
     <row r="18" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="129"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="20" t="str">
         <f ca="1">IF(F18=E18, IF(TODAY()&gt;F18, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F18) - E18) / (F18 - E18) * 100, 1) &amp; "%")</f>
@@ -4990,8 +5048,8 @@
       <c r="BO18" s="44"/>
     </row>
     <row r="19" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="129"/>
-      <c r="B19" s="67" t="s">
+      <c r="A19" s="128"/>
+      <c r="B19" s="66" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="20" t="str">
@@ -5073,8 +5131,8 @@
       <c r="BO19" s="49"/>
     </row>
     <row r="20" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A20" s="129"/>
-      <c r="B20" s="80" t="s">
+      <c r="A20" s="128"/>
+      <c r="B20" s="79" t="s">
         <v>110</v>
       </c>
       <c r="C20" s="20" t="str">
@@ -5091,7 +5149,7 @@
       <c r="F20" s="22">
         <v>45967</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="71" t="s">
         <v>104</v>
       </c>
       <c r="H20" s="48"/>
@@ -5156,80 +5214,80 @@
       <c r="BO20" s="49"/>
     </row>
     <row r="21" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="129"/>
-      <c r="B21" s="141" t="s">
+      <c r="A21" s="128"/>
+      <c r="B21" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="132"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="132"/>
-      <c r="T21" s="132"/>
-      <c r="U21" s="132"/>
-      <c r="V21" s="132"/>
-      <c r="W21" s="132"/>
-      <c r="X21" s="132"/>
-      <c r="Y21" s="132"/>
-      <c r="Z21" s="132"/>
-      <c r="AA21" s="132"/>
-      <c r="AB21" s="132"/>
-      <c r="AC21" s="132"/>
-      <c r="AD21" s="132"/>
-      <c r="AE21" s="132"/>
-      <c r="AF21" s="132"/>
-      <c r="AG21" s="132"/>
-      <c r="AH21" s="132"/>
-      <c r="AI21" s="132"/>
-      <c r="AJ21" s="132"/>
-      <c r="AK21" s="132"/>
-      <c r="AL21" s="132"/>
-      <c r="AM21" s="132"/>
-      <c r="AN21" s="132"/>
-      <c r="AO21" s="132"/>
-      <c r="AP21" s="132"/>
-      <c r="AQ21" s="132"/>
-      <c r="AR21" s="132"/>
-      <c r="AS21" s="132"/>
-      <c r="AT21" s="132"/>
-      <c r="AU21" s="132"/>
-      <c r="AV21" s="132"/>
-      <c r="AW21" s="132"/>
-      <c r="AX21" s="132"/>
-      <c r="AY21" s="132"/>
-      <c r="AZ21" s="132"/>
-      <c r="BA21" s="132"/>
-      <c r="BB21" s="132"/>
-      <c r="BC21" s="132"/>
-      <c r="BD21" s="132"/>
-      <c r="BE21" s="132"/>
-      <c r="BF21" s="132"/>
-      <c r="BG21" s="132"/>
-      <c r="BH21" s="132"/>
-      <c r="BI21" s="132"/>
-      <c r="BJ21" s="132"/>
-      <c r="BK21" s="132"/>
-      <c r="BL21" s="132"/>
-      <c r="BM21" s="132"/>
-      <c r="BN21" s="132"/>
-      <c r="BO21" s="133"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="131"/>
+      <c r="U21" s="131"/>
+      <c r="V21" s="131"/>
+      <c r="W21" s="131"/>
+      <c r="X21" s="131"/>
+      <c r="Y21" s="131"/>
+      <c r="Z21" s="131"/>
+      <c r="AA21" s="131"/>
+      <c r="AB21" s="131"/>
+      <c r="AC21" s="131"/>
+      <c r="AD21" s="131"/>
+      <c r="AE21" s="131"/>
+      <c r="AF21" s="131"/>
+      <c r="AG21" s="131"/>
+      <c r="AH21" s="131"/>
+      <c r="AI21" s="131"/>
+      <c r="AJ21" s="131"/>
+      <c r="AK21" s="131"/>
+      <c r="AL21" s="131"/>
+      <c r="AM21" s="131"/>
+      <c r="AN21" s="131"/>
+      <c r="AO21" s="131"/>
+      <c r="AP21" s="131"/>
+      <c r="AQ21" s="131"/>
+      <c r="AR21" s="131"/>
+      <c r="AS21" s="131"/>
+      <c r="AT21" s="131"/>
+      <c r="AU21" s="131"/>
+      <c r="AV21" s="131"/>
+      <c r="AW21" s="131"/>
+      <c r="AX21" s="131"/>
+      <c r="AY21" s="131"/>
+      <c r="AZ21" s="131"/>
+      <c r="BA21" s="131"/>
+      <c r="BB21" s="131"/>
+      <c r="BC21" s="131"/>
+      <c r="BD21" s="131"/>
+      <c r="BE21" s="131"/>
+      <c r="BF21" s="131"/>
+      <c r="BG21" s="131"/>
+      <c r="BH21" s="131"/>
+      <c r="BI21" s="131"/>
+      <c r="BJ21" s="131"/>
+      <c r="BK21" s="131"/>
+      <c r="BL21" s="131"/>
+      <c r="BM21" s="131"/>
+      <c r="BN21" s="131"/>
+      <c r="BO21" s="132"/>
     </row>
     <row r="22" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="129"/>
-      <c r="B22" s="81" t="s">
-        <v>138</v>
+      <c r="A22" s="128"/>
+      <c r="B22" s="80" t="s">
+        <v>137</v>
       </c>
       <c r="C22" s="20" t="str">
         <f t="shared" ref="C22:C40" ca="1" si="2">IF(F22=E22, IF(TODAY()&gt;F22, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F22) - E22) / (F22 - E22) * 100, 1) &amp; "%")</f>
@@ -5245,7 +5303,7 @@
       <c r="F22" s="22">
         <v>45969</v>
       </c>
-      <c r="G22" s="72" t="s">
+      <c r="G22" s="71" t="s">
         <v>113</v>
       </c>
       <c r="H22" s="43"/>
@@ -5310,8 +5368,8 @@
       <c r="BO22" s="49"/>
     </row>
     <row r="23" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="129"/>
-      <c r="B23" s="68" t="s">
+      <c r="A23" s="128"/>
+      <c r="B23" s="67" t="s">
         <v>85</v>
       </c>
       <c r="C23" s="20" t="str">
@@ -5393,8 +5451,8 @@
       <c r="BO23" s="49"/>
     </row>
     <row r="24" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="129"/>
-      <c r="B24" s="82" t="s">
+      <c r="A24" s="128"/>
+      <c r="B24" s="81" t="s">
         <v>128</v>
       </c>
       <c r="C24" s="20" t="str">
@@ -5476,8 +5534,8 @@
       <c r="BO24" s="49"/>
     </row>
     <row r="25" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="129"/>
-      <c r="B25" s="82" t="s">
+      <c r="A25" s="128"/>
+      <c r="B25" s="81" t="s">
         <v>127</v>
       </c>
       <c r="C25" s="20" t="str">
@@ -5559,9 +5617,9 @@
       <c r="BO25" s="49"/>
     </row>
     <row r="26" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="129"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5642,9 +5700,9 @@
       <c r="BO26" s="49"/>
     </row>
     <row r="27" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="129"/>
+      <c r="A27" s="128"/>
       <c r="B27" s="63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5725,25 +5783,25 @@
       <c r="BO27" s="49"/>
     </row>
     <row r="28" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A28" s="129"/>
-      <c r="B28" s="65" t="s">
+      <c r="A28" s="128"/>
+      <c r="B28" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="83" t="str">
+      <c r="C28" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D28" s="84" t="str">
+      <c r="D28" s="83" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E28" s="85">
+      <c r="E28" s="84">
         <v>45980</v>
       </c>
-      <c r="F28" s="85">
+      <c r="F28" s="84">
         <v>45982</v>
       </c>
-      <c r="G28" s="86" t="s">
+      <c r="G28" s="85" t="s">
         <v>130</v>
       </c>
       <c r="H28" s="48"/>
@@ -5808,9 +5866,9 @@
       <c r="BO28" s="49"/>
     </row>
     <row r="29" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="129"/>
-      <c r="B29" s="122" t="s">
-        <v>135</v>
+      <c r="A29" s="128"/>
+      <c r="B29" s="121" t="s">
+        <v>134</v>
       </c>
       <c r="C29" s="20" t="str">
         <f t="shared" ref="C29" ca="1" si="4">IF(F29=E29, IF(TODAY()&gt;F29, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F29) - E29) / (F29 - E29) * 100, 1) &amp; "%")</f>
@@ -5891,25 +5949,25 @@
       <c r="BO29" s="49"/>
     </row>
     <row r="30" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="129"/>
+      <c r="A30" s="128"/>
       <c r="B30" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="39" t="str">
+      <c r="C30" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D30" s="40" t="str">
+      <c r="D30" s="83" t="str">
         <f t="shared" si="0"/>
         <v>9일</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="84">
         <v>45980</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="84">
         <v>45988</v>
       </c>
-      <c r="G30" s="123" t="s">
+      <c r="G30" s="85" t="s">
         <v>130</v>
       </c>
       <c r="H30" s="48"/>
@@ -5974,25 +6032,25 @@
       <c r="BO30" s="49"/>
     </row>
     <row r="31" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A31" s="129"/>
-      <c r="B31" s="65" t="s">
+      <c r="A31" s="128"/>
+      <c r="B31" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="83" t="str">
+      <c r="C31" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D31" s="84" t="str">
+      <c r="D31" s="83" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E31" s="85">
+      <c r="E31" s="84">
         <v>45980</v>
       </c>
-      <c r="F31" s="85">
+      <c r="F31" s="84">
         <v>45982</v>
       </c>
-      <c r="G31" s="86" t="s">
+      <c r="G31" s="85" t="s">
         <v>99</v>
       </c>
       <c r="H31" s="48"/>
@@ -6057,25 +6115,25 @@
       <c r="BO31" s="49"/>
     </row>
     <row r="32" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A32" s="129"/>
-      <c r="B32" s="87" t="s">
+      <c r="A32" s="128"/>
+      <c r="B32" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="83" t="str">
+      <c r="C32" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D32" s="84" t="str">
+      <c r="D32" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E32" s="85">
+      <c r="E32" s="84">
         <v>45965</v>
       </c>
-      <c r="F32" s="85">
+      <c r="F32" s="84">
         <v>45971</v>
       </c>
-      <c r="G32" s="86" t="s">
+      <c r="G32" s="85" t="s">
         <v>100</v>
       </c>
       <c r="H32" s="48"/>
@@ -6140,25 +6198,25 @@
       <c r="BO32" s="28"/>
     </row>
     <row r="33" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A33" s="129"/>
-      <c r="B33" s="88" t="s">
+      <c r="A33" s="128"/>
+      <c r="B33" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="83" t="str">
+      <c r="C33" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D33" s="84" t="str">
+      <c r="D33" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E33" s="85">
+      <c r="E33" s="84">
         <v>45971</v>
       </c>
-      <c r="F33" s="85">
+      <c r="F33" s="84">
         <v>45977</v>
       </c>
-      <c r="G33" s="89" t="s">
+      <c r="G33" s="88" t="s">
         <v>114</v>
       </c>
       <c r="H33" s="48"/>
@@ -6223,25 +6281,25 @@
       <c r="BO33" s="49"/>
     </row>
     <row r="34" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A34" s="129"/>
-      <c r="B34" s="90" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="83" t="str">
+      <c r="A34" s="128"/>
+      <c r="B34" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="82" t="str">
         <f ca="1">IF(F34=E34, IF(TODAY()&gt;F34, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F34) - E34) / (F34 - E34) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D34" s="84" t="str">
+      <c r="D34" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E34" s="85">
+      <c r="E34" s="84">
         <v>45971</v>
       </c>
-      <c r="F34" s="85">
+      <c r="F34" s="84">
         <v>45977</v>
       </c>
-      <c r="G34" s="89" t="s">
+      <c r="G34" s="88" t="s">
         <v>114</v>
       </c>
       <c r="H34" s="48"/>
@@ -6306,25 +6364,25 @@
       <c r="BO34" s="49"/>
     </row>
     <row r="35" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="129"/>
-      <c r="B35" s="88" t="s">
+      <c r="A35" s="128"/>
+      <c r="B35" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="83" t="str">
+      <c r="C35" s="82" t="str">
         <f ca="1">IF(F35=E35, IF(TODAY()&gt;F35, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F35) - E35) / (F35 - E35) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D35" s="84" t="str">
+      <c r="D35" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E35" s="85">
+      <c r="E35" s="84">
         <v>45971</v>
       </c>
-      <c r="F35" s="85">
+      <c r="F35" s="84">
         <v>45977</v>
       </c>
-      <c r="G35" s="89" t="s">
+      <c r="G35" s="88" t="s">
         <v>114</v>
       </c>
       <c r="H35" s="48"/>
@@ -6389,25 +6447,25 @@
       <c r="BO35" s="49"/>
     </row>
     <row r="36" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A36" s="129"/>
-      <c r="B36" s="91" t="s">
+      <c r="A36" s="128"/>
+      <c r="B36" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="83" t="str">
+      <c r="C36" s="82" t="str">
         <f ca="1">IF(F36=E36, IF(TODAY()&gt;F36, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F36) - E36) / (F36 - E36) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D36" s="84" t="str">
+      <c r="D36" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E36" s="85">
+      <c r="E36" s="84">
         <v>45980</v>
       </c>
-      <c r="F36" s="85">
+      <c r="F36" s="84">
         <v>45980</v>
       </c>
-      <c r="G36" s="89" t="s">
+      <c r="G36" s="88" t="s">
         <v>114</v>
       </c>
       <c r="H36" s="48"/>
@@ -6472,25 +6530,25 @@
       <c r="BO36" s="49"/>
     </row>
     <row r="37" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="129"/>
-      <c r="B37" s="91" t="s">
+      <c r="A37" s="128"/>
+      <c r="B37" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="83" t="str">
+      <c r="C37" s="82" t="str">
         <f ca="1">IF(F37=E37, IF(TODAY()&gt;F37, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F37) - E37) / (F37 - E37) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D37" s="84" t="str">
+      <c r="D37" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E37" s="85">
+      <c r="E37" s="84">
         <v>45980</v>
       </c>
-      <c r="F37" s="85">
+      <c r="F37" s="84">
         <v>45980</v>
       </c>
-      <c r="G37" s="89" t="s">
+      <c r="G37" s="88" t="s">
         <v>116</v>
       </c>
       <c r="H37" s="48"/>
@@ -6555,25 +6613,25 @@
       <c r="BO37" s="49"/>
     </row>
     <row r="38" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="129"/>
-      <c r="B38" s="92" t="s">
+      <c r="A38" s="128"/>
+      <c r="B38" s="91" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="83" t="str">
+      <c r="C38" s="82" t="str">
         <f ca="1">IF(F38=E38, IF(TODAY()&gt;F38, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F38) - E38) / (F38 - E38) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D38" s="84" t="str">
+      <c r="D38" s="83" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E38" s="85">
+      <c r="E38" s="84">
         <v>45977</v>
       </c>
-      <c r="F38" s="85">
+      <c r="F38" s="84">
         <v>45980</v>
       </c>
-      <c r="G38" s="89" t="s">
+      <c r="G38" s="88" t="s">
         <v>113</v>
       </c>
       <c r="H38" s="48"/>
@@ -6638,25 +6696,25 @@
       <c r="BO38" s="49"/>
     </row>
     <row r="39" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="129"/>
-      <c r="B39" s="93" t="s">
+      <c r="A39" s="128"/>
+      <c r="B39" s="92" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="83" t="str">
+      <c r="C39" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D39" s="84" t="str">
+      <c r="D39" s="83" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E39" s="85">
+      <c r="E39" s="84">
         <v>45977</v>
       </c>
-      <c r="F39" s="85">
+      <c r="F39" s="84">
         <v>45980</v>
       </c>
-      <c r="G39" s="89" t="s">
+      <c r="G39" s="88" t="s">
         <v>114</v>
       </c>
       <c r="H39" s="48"/>
@@ -6721,25 +6779,25 @@
       <c r="BO39" s="49"/>
     </row>
     <row r="40" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A40" s="129"/>
-      <c r="B40" s="93" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="83" t="str">
+      <c r="A40" s="128"/>
+      <c r="B40" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="82" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>100%</v>
       </c>
-      <c r="D40" s="84" t="str">
+      <c r="D40" s="83" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E40" s="85">
+      <c r="E40" s="84">
         <v>45977</v>
       </c>
-      <c r="F40" s="85">
+      <c r="F40" s="84">
         <v>45980</v>
       </c>
-      <c r="G40" s="89" t="s">
+      <c r="G40" s="88" t="s">
         <v>116</v>
       </c>
       <c r="H40" s="43"/>
@@ -6804,25 +6862,25 @@
       <c r="BO40" s="49"/>
     </row>
     <row r="41" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="129"/>
-      <c r="B41" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="83" t="str">
+      <c r="A41" s="128"/>
+      <c r="B41" s="89" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="82" t="str">
         <f t="shared" ref="C41" ca="1" si="5">IF(F41=E41, IF(TODAY()&gt;F41, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F41) - E41) / (F41 - E41) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D41" s="84" t="str">
+      <c r="D41" s="83" t="str">
         <f t="shared" si="0"/>
         <v>4일</v>
       </c>
-      <c r="E41" s="85">
+      <c r="E41" s="84">
         <v>45977</v>
       </c>
-      <c r="F41" s="85">
+      <c r="F41" s="84">
         <v>45980</v>
       </c>
-      <c r="G41" s="89" t="s">
+      <c r="G41" s="88" t="s">
         <v>113</v>
       </c>
       <c r="H41" s="48"/>
@@ -6887,96 +6945,96 @@
       <c r="BO41" s="49"/>
     </row>
     <row r="42" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="129"/>
-      <c r="B42" s="142" t="s">
+      <c r="A42" s="128"/>
+      <c r="B42" s="141" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="142"/>
-      <c r="D42" s="142"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="131"/>
-      <c r="I42" s="132"/>
-      <c r="J42" s="132"/>
-      <c r="K42" s="132"/>
-      <c r="L42" s="132"/>
-      <c r="M42" s="132"/>
-      <c r="N42" s="132"/>
-      <c r="O42" s="132"/>
-      <c r="P42" s="132"/>
-      <c r="Q42" s="132"/>
-      <c r="R42" s="132"/>
-      <c r="S42" s="132"/>
-      <c r="T42" s="132"/>
-      <c r="U42" s="132"/>
-      <c r="V42" s="132"/>
-      <c r="W42" s="132"/>
-      <c r="X42" s="132"/>
-      <c r="Y42" s="132"/>
-      <c r="Z42" s="132"/>
-      <c r="AA42" s="132"/>
-      <c r="AB42" s="132"/>
-      <c r="AC42" s="132"/>
-      <c r="AD42" s="132"/>
-      <c r="AE42" s="132"/>
-      <c r="AF42" s="132"/>
-      <c r="AG42" s="132"/>
-      <c r="AH42" s="132"/>
-      <c r="AI42" s="132"/>
-      <c r="AJ42" s="132"/>
-      <c r="AK42" s="132"/>
-      <c r="AL42" s="132"/>
-      <c r="AM42" s="132"/>
-      <c r="AN42" s="132"/>
-      <c r="AO42" s="132"/>
-      <c r="AP42" s="132"/>
-      <c r="AQ42" s="132"/>
-      <c r="AR42" s="132"/>
-      <c r="AS42" s="132"/>
-      <c r="AT42" s="132"/>
-      <c r="AU42" s="132"/>
-      <c r="AV42" s="132"/>
-      <c r="AW42" s="132"/>
-      <c r="AX42" s="132"/>
-      <c r="AY42" s="132"/>
-      <c r="AZ42" s="132"/>
-      <c r="BA42" s="132"/>
-      <c r="BB42" s="132"/>
-      <c r="BC42" s="132"/>
-      <c r="BD42" s="132"/>
-      <c r="BE42" s="132"/>
-      <c r="BF42" s="132"/>
-      <c r="BG42" s="132"/>
-      <c r="BH42" s="132"/>
-      <c r="BI42" s="132"/>
-      <c r="BJ42" s="132"/>
-      <c r="BK42" s="132"/>
-      <c r="BL42" s="132"/>
-      <c r="BM42" s="132"/>
-      <c r="BN42" s="132"/>
-      <c r="BO42" s="133"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="131"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="131"/>
+      <c r="L42" s="131"/>
+      <c r="M42" s="131"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="131"/>
+      <c r="P42" s="131"/>
+      <c r="Q42" s="131"/>
+      <c r="R42" s="131"/>
+      <c r="S42" s="131"/>
+      <c r="T42" s="131"/>
+      <c r="U42" s="131"/>
+      <c r="V42" s="131"/>
+      <c r="W42" s="131"/>
+      <c r="X42" s="131"/>
+      <c r="Y42" s="131"/>
+      <c r="Z42" s="131"/>
+      <c r="AA42" s="131"/>
+      <c r="AB42" s="131"/>
+      <c r="AC42" s="131"/>
+      <c r="AD42" s="131"/>
+      <c r="AE42" s="131"/>
+      <c r="AF42" s="131"/>
+      <c r="AG42" s="131"/>
+      <c r="AH42" s="131"/>
+      <c r="AI42" s="131"/>
+      <c r="AJ42" s="131"/>
+      <c r="AK42" s="131"/>
+      <c r="AL42" s="131"/>
+      <c r="AM42" s="131"/>
+      <c r="AN42" s="131"/>
+      <c r="AO42" s="131"/>
+      <c r="AP42" s="131"/>
+      <c r="AQ42" s="131"/>
+      <c r="AR42" s="131"/>
+      <c r="AS42" s="131"/>
+      <c r="AT42" s="131"/>
+      <c r="AU42" s="131"/>
+      <c r="AV42" s="131"/>
+      <c r="AW42" s="131"/>
+      <c r="AX42" s="131"/>
+      <c r="AY42" s="131"/>
+      <c r="AZ42" s="131"/>
+      <c r="BA42" s="131"/>
+      <c r="BB42" s="131"/>
+      <c r="BC42" s="131"/>
+      <c r="BD42" s="131"/>
+      <c r="BE42" s="131"/>
+      <c r="BF42" s="131"/>
+      <c r="BG42" s="131"/>
+      <c r="BH42" s="131"/>
+      <c r="BI42" s="131"/>
+      <c r="BJ42" s="131"/>
+      <c r="BK42" s="131"/>
+      <c r="BL42" s="131"/>
+      <c r="BM42" s="131"/>
+      <c r="BN42" s="131"/>
+      <c r="BO42" s="132"/>
     </row>
     <row r="43" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A43" s="129"/>
-      <c r="B43" s="88" t="s">
+      <c r="A43" s="128"/>
+      <c r="B43" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="83" t="str">
+      <c r="C43" s="82" t="str">
         <f t="shared" ref="C43:C50" ca="1" si="6">IF(F43=E43, IF(TODAY()&gt;F43, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F43) - E43) / (F43 - E43) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D43" s="84" t="str">
+      <c r="D43" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E43" s="85">
+      <c r="E43" s="84">
         <v>45971</v>
       </c>
-      <c r="F43" s="85">
+      <c r="F43" s="84">
         <v>45977</v>
       </c>
-      <c r="G43" s="89" t="s">
+      <c r="G43" s="88" t="s">
         <v>116</v>
       </c>
       <c r="H43" s="48"/>
@@ -7041,25 +7099,25 @@
       <c r="BO43" s="49"/>
     </row>
     <row r="44" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A44" s="129"/>
-      <c r="B44" s="90" t="s">
-        <v>143</v>
-      </c>
-      <c r="C44" s="83" t="str">
+      <c r="A44" s="128"/>
+      <c r="B44" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="82" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D44" s="84" t="str">
+      <c r="D44" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E44" s="85">
+      <c r="E44" s="84">
         <v>45971</v>
       </c>
-      <c r="F44" s="85">
+      <c r="F44" s="84">
         <v>45977</v>
       </c>
-      <c r="G44" s="89" t="s">
+      <c r="G44" s="88" t="s">
         <v>116</v>
       </c>
       <c r="H44" s="48"/>
@@ -7124,25 +7182,25 @@
       <c r="BO44" s="49"/>
     </row>
     <row r="45" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A45" s="129"/>
-      <c r="B45" s="90" t="s">
-        <v>144</v>
-      </c>
-      <c r="C45" s="83" t="str">
+      <c r="A45" s="128"/>
+      <c r="B45" s="89" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="82" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D45" s="84" t="str">
+      <c r="D45" s="83" t="str">
         <f t="shared" si="0"/>
         <v>10일</v>
       </c>
-      <c r="E45" s="85">
+      <c r="E45" s="84">
         <v>45971</v>
       </c>
-      <c r="F45" s="85">
+      <c r="F45" s="84">
         <v>45980</v>
       </c>
-      <c r="G45" s="89" t="s">
+      <c r="G45" s="88" t="s">
         <v>116</v>
       </c>
       <c r="H45" s="48"/>
@@ -7207,26 +7265,26 @@
       <c r="BO45" s="49"/>
     </row>
     <row r="46" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="129"/>
-      <c r="B46" s="94" t="s">
-        <v>145</v>
-      </c>
-      <c r="C46" s="83" t="str">
+      <c r="A46" s="128"/>
+      <c r="B46" s="93" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="82" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D46" s="84" t="str">
+      <c r="D46" s="83" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E46" s="85">
+      <c r="E46" s="84">
         <v>45979</v>
       </c>
-      <c r="F46" s="85">
+      <c r="F46" s="84">
         <v>45981</v>
       </c>
-      <c r="G46" s="86" t="s">
-        <v>133</v>
+      <c r="G46" s="85" t="s">
+        <v>132</v>
       </c>
       <c r="H46" s="48"/>
       <c r="I46" s="49"/>
@@ -7290,25 +7348,25 @@
       <c r="BO46" s="49"/>
     </row>
     <row r="47" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="129"/>
-      <c r="B47" s="95" t="s">
-        <v>154</v>
-      </c>
-      <c r="C47" s="83" t="str">
+      <c r="A47" s="128"/>
+      <c r="B47" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="82" t="str">
         <f ca="1">IF(F47=E47, IF(TODAY()&gt;F47, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F47) - E47) / (F47 - E47) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D47" s="84" t="str">
+      <c r="D47" s="83" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E47" s="85">
+      <c r="E47" s="84">
         <v>45980</v>
       </c>
-      <c r="F47" s="85">
+      <c r="F47" s="84">
         <v>45982</v>
       </c>
-      <c r="G47" s="86" t="s">
+      <c r="G47" s="85" t="s">
         <v>102</v>
       </c>
       <c r="H47" s="48"/>
@@ -7373,25 +7431,25 @@
       <c r="BO47" s="49"/>
     </row>
     <row r="48" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="129"/>
-      <c r="B48" s="95" t="s">
-        <v>153</v>
-      </c>
-      <c r="C48" s="83" t="str">
+      <c r="A48" s="128"/>
+      <c r="B48" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="82" t="str">
         <f ca="1">IF(F48=E48, IF(TODAY()&gt;F48, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F48) - E48) / (F48 - E48) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D48" s="84" t="str">
+      <c r="D48" s="83" t="str">
         <f t="shared" si="0"/>
         <v>3일</v>
       </c>
-      <c r="E48" s="85">
+      <c r="E48" s="84">
         <v>45980</v>
       </c>
-      <c r="F48" s="85">
+      <c r="F48" s="84">
         <v>45982</v>
       </c>
-      <c r="G48" s="86" t="s">
+      <c r="G48" s="85" t="s">
         <v>102</v>
       </c>
       <c r="H48" s="48"/>
@@ -7456,26 +7514,26 @@
       <c r="BO48" s="49"/>
     </row>
     <row r="49" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="129"/>
-      <c r="B49" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" s="83" t="str">
+      <c r="A49" s="128"/>
+      <c r="B49" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="82" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D49" s="84" t="str">
+      <c r="D49" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E49" s="85">
+      <c r="E49" s="84">
         <v>45981</v>
       </c>
-      <c r="F49" s="85">
+      <c r="F49" s="84">
         <v>45981</v>
       </c>
-      <c r="G49" s="86" t="s">
-        <v>133</v>
+      <c r="G49" s="85" t="s">
+        <v>132</v>
       </c>
       <c r="H49" s="48"/>
       <c r="I49" s="49"/>
@@ -7539,26 +7597,26 @@
       <c r="BO49" s="49"/>
     </row>
     <row r="50" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A50" s="129"/>
-      <c r="B50" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="83" t="str">
+      <c r="A50" s="128"/>
+      <c r="B50" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="82" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>100%</v>
       </c>
-      <c r="D50" s="84" t="str">
+      <c r="D50" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E50" s="85">
+      <c r="E50" s="84">
         <v>45987</v>
       </c>
-      <c r="F50" s="85">
+      <c r="F50" s="84">
         <v>45987</v>
       </c>
-      <c r="G50" s="86" t="s">
-        <v>133</v>
+      <c r="G50" s="85" t="s">
+        <v>132</v>
       </c>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
@@ -7622,96 +7680,96 @@
       <c r="BO50" s="29"/>
     </row>
     <row r="51" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51" s="129"/>
-      <c r="B51" s="142" t="s">
+      <c r="A51" s="128"/>
+      <c r="B51" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="142"/>
-      <c r="D51" s="142"/>
-      <c r="E51" s="142"/>
-      <c r="F51" s="142"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="131"/>
-      <c r="I51" s="132"/>
-      <c r="J51" s="132"/>
-      <c r="K51" s="132"/>
-      <c r="L51" s="132"/>
-      <c r="M51" s="132"/>
-      <c r="N51" s="132"/>
-      <c r="O51" s="132"/>
-      <c r="P51" s="132"/>
-      <c r="Q51" s="132"/>
-      <c r="R51" s="132"/>
-      <c r="S51" s="132"/>
-      <c r="T51" s="132"/>
-      <c r="U51" s="132"/>
-      <c r="V51" s="132"/>
-      <c r="W51" s="132"/>
-      <c r="X51" s="132"/>
-      <c r="Y51" s="132"/>
-      <c r="Z51" s="132"/>
-      <c r="AA51" s="132"/>
-      <c r="AB51" s="132"/>
-      <c r="AC51" s="132"/>
-      <c r="AD51" s="132"/>
-      <c r="AE51" s="132"/>
-      <c r="AF51" s="132"/>
-      <c r="AG51" s="132"/>
-      <c r="AH51" s="132"/>
-      <c r="AI51" s="132"/>
-      <c r="AJ51" s="132"/>
-      <c r="AK51" s="132"/>
-      <c r="AL51" s="132"/>
-      <c r="AM51" s="132"/>
-      <c r="AN51" s="132"/>
-      <c r="AO51" s="132"/>
-      <c r="AP51" s="132"/>
-      <c r="AQ51" s="132"/>
-      <c r="AR51" s="132"/>
-      <c r="AS51" s="132"/>
-      <c r="AT51" s="132"/>
-      <c r="AU51" s="132"/>
-      <c r="AV51" s="132"/>
-      <c r="AW51" s="132"/>
-      <c r="AX51" s="132"/>
-      <c r="AY51" s="132"/>
-      <c r="AZ51" s="132"/>
-      <c r="BA51" s="132"/>
-      <c r="BB51" s="132"/>
-      <c r="BC51" s="132"/>
-      <c r="BD51" s="132"/>
-      <c r="BE51" s="132"/>
-      <c r="BF51" s="132"/>
-      <c r="BG51" s="132"/>
-      <c r="BH51" s="132"/>
-      <c r="BI51" s="132"/>
-      <c r="BJ51" s="132"/>
-      <c r="BK51" s="132"/>
-      <c r="BL51" s="132"/>
-      <c r="BM51" s="132"/>
-      <c r="BN51" s="132"/>
-      <c r="BO51" s="133"/>
+      <c r="C51" s="141"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="141"/>
+      <c r="F51" s="141"/>
+      <c r="G51" s="141"/>
+      <c r="H51" s="130"/>
+      <c r="I51" s="131"/>
+      <c r="J51" s="131"/>
+      <c r="K51" s="131"/>
+      <c r="L51" s="131"/>
+      <c r="M51" s="131"/>
+      <c r="N51" s="131"/>
+      <c r="O51" s="131"/>
+      <c r="P51" s="131"/>
+      <c r="Q51" s="131"/>
+      <c r="R51" s="131"/>
+      <c r="S51" s="131"/>
+      <c r="T51" s="131"/>
+      <c r="U51" s="131"/>
+      <c r="V51" s="131"/>
+      <c r="W51" s="131"/>
+      <c r="X51" s="131"/>
+      <c r="Y51" s="131"/>
+      <c r="Z51" s="131"/>
+      <c r="AA51" s="131"/>
+      <c r="AB51" s="131"/>
+      <c r="AC51" s="131"/>
+      <c r="AD51" s="131"/>
+      <c r="AE51" s="131"/>
+      <c r="AF51" s="131"/>
+      <c r="AG51" s="131"/>
+      <c r="AH51" s="131"/>
+      <c r="AI51" s="131"/>
+      <c r="AJ51" s="131"/>
+      <c r="AK51" s="131"/>
+      <c r="AL51" s="131"/>
+      <c r="AM51" s="131"/>
+      <c r="AN51" s="131"/>
+      <c r="AO51" s="131"/>
+      <c r="AP51" s="131"/>
+      <c r="AQ51" s="131"/>
+      <c r="AR51" s="131"/>
+      <c r="AS51" s="131"/>
+      <c r="AT51" s="131"/>
+      <c r="AU51" s="131"/>
+      <c r="AV51" s="131"/>
+      <c r="AW51" s="131"/>
+      <c r="AX51" s="131"/>
+      <c r="AY51" s="131"/>
+      <c r="AZ51" s="131"/>
+      <c r="BA51" s="131"/>
+      <c r="BB51" s="131"/>
+      <c r="BC51" s="131"/>
+      <c r="BD51" s="131"/>
+      <c r="BE51" s="131"/>
+      <c r="BF51" s="131"/>
+      <c r="BG51" s="131"/>
+      <c r="BH51" s="131"/>
+      <c r="BI51" s="131"/>
+      <c r="BJ51" s="131"/>
+      <c r="BK51" s="131"/>
+      <c r="BL51" s="131"/>
+      <c r="BM51" s="131"/>
+      <c r="BN51" s="131"/>
+      <c r="BO51" s="132"/>
     </row>
     <row r="52" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52" s="129"/>
-      <c r="B52" s="96" t="s">
-        <v>147</v>
-      </c>
-      <c r="C52" s="97" t="str">
-        <f t="shared" ref="C52:C76" ca="1" si="7">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
+      <c r="A52" s="128"/>
+      <c r="B52" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="96" t="str">
+        <f t="shared" ref="C52:C77" ca="1" si="7">IF(F52=E52, IF(TODAY()&gt;F52, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F52) - E52) / (F52 - E52) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D52" s="84" t="str">
+      <c r="D52" s="83" t="str">
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E52" s="98">
+      <c r="E52" s="97">
         <v>45971</v>
       </c>
-      <c r="F52" s="98">
+      <c r="F52" s="97">
         <v>45977</v>
       </c>
-      <c r="G52" s="99" t="s">
+      <c r="G52" s="98" t="s">
         <v>98</v>
       </c>
       <c r="H52" s="48"/>
@@ -7776,25 +7834,25 @@
       <c r="BO52" s="49"/>
     </row>
     <row r="53" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53" s="129"/>
-      <c r="B53" s="100" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="101" t="str">
+      <c r="A53" s="128"/>
+      <c r="B53" s="99" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" s="100" t="str">
         <f t="shared" ref="C53" ca="1" si="8">IF(F53=E53, IF(TODAY()&gt;F53, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F53) - E53) / (F53 - E53) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D53" s="84" t="str">
+      <c r="D53" s="83" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E53" s="102">
+      <c r="E53" s="101">
         <v>45982</v>
       </c>
-      <c r="F53" s="102">
+      <c r="F53" s="101">
         <v>45983</v>
       </c>
-      <c r="G53" s="103" t="s">
+      <c r="G53" s="102" t="s">
         <v>100</v>
       </c>
       <c r="H53" s="59"/>
@@ -7859,25 +7917,25 @@
       <c r="BO53" s="49"/>
     </row>
     <row r="54" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A54" s="129"/>
-      <c r="B54" s="100" t="s">
-        <v>149</v>
-      </c>
-      <c r="C54" s="101" t="str">
+      <c r="A54" s="128"/>
+      <c r="B54" s="99" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="100" t="str">
         <f t="shared" ref="C54" ca="1" si="9">IF(F54=E54, IF(TODAY()&gt;F54, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F54) - E54) / (F54 - E54) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D54" s="84" t="str">
+      <c r="D54" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E54" s="102">
+      <c r="E54" s="101">
         <v>45982</v>
       </c>
-      <c r="F54" s="102">
+      <c r="F54" s="101">
         <v>45982</v>
       </c>
-      <c r="G54" s="103" t="s">
+      <c r="G54" s="102" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="59"/>
@@ -7942,25 +8000,25 @@
       <c r="BO54" s="49"/>
     </row>
     <row r="55" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A55" s="129"/>
-      <c r="B55" s="100" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="101" t="str">
+      <c r="A55" s="128"/>
+      <c r="B55" s="99" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="100" t="str">
         <f t="shared" ref="C55" ca="1" si="10">IF(F55=E55, IF(TODAY()&gt;F55, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F55) - E55) / (F55 - E55) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D55" s="84" t="str">
+      <c r="D55" s="83" t="str">
         <f t="shared" si="0"/>
         <v>1일</v>
       </c>
-      <c r="E55" s="102">
+      <c r="E55" s="101">
         <v>45983</v>
       </c>
-      <c r="F55" s="102">
+      <c r="F55" s="101">
         <v>45983</v>
       </c>
-      <c r="G55" s="103" t="s">
+      <c r="G55" s="102" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="59"/>
@@ -8025,11 +8083,11 @@
       <c r="BO55" s="49"/>
     </row>
     <row r="56" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A56" s="129"/>
-      <c r="B56" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="C56" s="119" t="str">
+      <c r="A56" s="128"/>
+      <c r="B56" s="117" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="118" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>100%</v>
       </c>
@@ -8037,13 +8095,13 @@
         <f t="shared" si="0"/>
         <v>7일</v>
       </c>
-      <c r="E56" s="120">
+      <c r="E56" s="119">
         <v>45983</v>
       </c>
-      <c r="F56" s="120">
+      <c r="F56" s="119">
         <v>45989</v>
       </c>
-      <c r="G56" s="121" t="s">
+      <c r="G56" s="120" t="s">
         <v>100</v>
       </c>
       <c r="H56" s="59"/>
@@ -8108,25 +8166,25 @@
       <c r="BO56" s="49"/>
     </row>
     <row r="57" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A57" s="129"/>
-      <c r="B57" s="104" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" s="101" t="str">
+      <c r="A57" s="128"/>
+      <c r="B57" s="103" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="100" t="str">
         <f t="shared" ref="C57" ca="1" si="11">IF(F57=E57, IF(TODAY()&gt;F57, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F57) - E57) / (F57 - E57) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D57" s="84" t="str">
+      <c r="D57" s="83" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E57" s="102">
+      <c r="E57" s="101">
         <v>45986</v>
       </c>
-      <c r="F57" s="102">
+      <c r="F57" s="101">
         <v>45987</v>
       </c>
-      <c r="G57" s="103" t="s">
+      <c r="G57" s="102" t="s">
         <v>100</v>
       </c>
       <c r="H57" s="59"/>
@@ -8191,96 +8249,96 @@
       <c r="BO57" s="49"/>
     </row>
     <row r="58" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A58" s="129"/>
-      <c r="B58" s="146" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" s="147"/>
-      <c r="D58" s="147"/>
-      <c r="E58" s="147"/>
-      <c r="F58" s="147"/>
-      <c r="G58" s="148"/>
-      <c r="H58" s="131"/>
-      <c r="I58" s="132"/>
-      <c r="J58" s="132"/>
-      <c r="K58" s="132"/>
-      <c r="L58" s="132"/>
-      <c r="M58" s="132"/>
-      <c r="N58" s="132"/>
-      <c r="O58" s="132"/>
-      <c r="P58" s="132"/>
-      <c r="Q58" s="132"/>
-      <c r="R58" s="132"/>
-      <c r="S58" s="132"/>
-      <c r="T58" s="132"/>
-      <c r="U58" s="132"/>
-      <c r="V58" s="132"/>
-      <c r="W58" s="132"/>
-      <c r="X58" s="132"/>
-      <c r="Y58" s="132"/>
-      <c r="Z58" s="132"/>
-      <c r="AA58" s="132"/>
-      <c r="AB58" s="132"/>
-      <c r="AC58" s="132"/>
-      <c r="AD58" s="132"/>
-      <c r="AE58" s="132"/>
-      <c r="AF58" s="132"/>
-      <c r="AG58" s="132"/>
-      <c r="AH58" s="132"/>
-      <c r="AI58" s="132"/>
-      <c r="AJ58" s="132"/>
-      <c r="AK58" s="132"/>
-      <c r="AL58" s="132"/>
-      <c r="AM58" s="132"/>
-      <c r="AN58" s="132"/>
-      <c r="AO58" s="132"/>
-      <c r="AP58" s="132"/>
-      <c r="AQ58" s="132"/>
-      <c r="AR58" s="132"/>
-      <c r="AS58" s="132"/>
-      <c r="AT58" s="132"/>
-      <c r="AU58" s="132"/>
-      <c r="AV58" s="132"/>
-      <c r="AW58" s="132"/>
-      <c r="AX58" s="132"/>
-      <c r="AY58" s="132"/>
-      <c r="AZ58" s="132"/>
-      <c r="BA58" s="132"/>
-      <c r="BB58" s="132"/>
-      <c r="BC58" s="132"/>
-      <c r="BD58" s="132"/>
-      <c r="BE58" s="132"/>
-      <c r="BF58" s="132"/>
-      <c r="BG58" s="132"/>
-      <c r="BH58" s="132"/>
-      <c r="BI58" s="132"/>
-      <c r="BJ58" s="132"/>
-      <c r="BK58" s="132"/>
-      <c r="BL58" s="132"/>
-      <c r="BM58" s="132"/>
-      <c r="BN58" s="132"/>
-      <c r="BO58" s="133"/>
+      <c r="A58" s="128"/>
+      <c r="B58" s="145" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="146"/>
+      <c r="D58" s="146"/>
+      <c r="E58" s="146"/>
+      <c r="F58" s="146"/>
+      <c r="G58" s="147"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="131"/>
+      <c r="J58" s="131"/>
+      <c r="K58" s="131"/>
+      <c r="L58" s="131"/>
+      <c r="M58" s="131"/>
+      <c r="N58" s="131"/>
+      <c r="O58" s="131"/>
+      <c r="P58" s="131"/>
+      <c r="Q58" s="131"/>
+      <c r="R58" s="131"/>
+      <c r="S58" s="131"/>
+      <c r="T58" s="131"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="131"/>
+      <c r="W58" s="131"/>
+      <c r="X58" s="131"/>
+      <c r="Y58" s="131"/>
+      <c r="Z58" s="131"/>
+      <c r="AA58" s="131"/>
+      <c r="AB58" s="131"/>
+      <c r="AC58" s="131"/>
+      <c r="AD58" s="131"/>
+      <c r="AE58" s="131"/>
+      <c r="AF58" s="131"/>
+      <c r="AG58" s="131"/>
+      <c r="AH58" s="131"/>
+      <c r="AI58" s="131"/>
+      <c r="AJ58" s="131"/>
+      <c r="AK58" s="131"/>
+      <c r="AL58" s="131"/>
+      <c r="AM58" s="131"/>
+      <c r="AN58" s="131"/>
+      <c r="AO58" s="131"/>
+      <c r="AP58" s="131"/>
+      <c r="AQ58" s="131"/>
+      <c r="AR58" s="131"/>
+      <c r="AS58" s="131"/>
+      <c r="AT58" s="131"/>
+      <c r="AU58" s="131"/>
+      <c r="AV58" s="131"/>
+      <c r="AW58" s="131"/>
+      <c r="AX58" s="131"/>
+      <c r="AY58" s="131"/>
+      <c r="AZ58" s="131"/>
+      <c r="BA58" s="131"/>
+      <c r="BB58" s="131"/>
+      <c r="BC58" s="131"/>
+      <c r="BD58" s="131"/>
+      <c r="BE58" s="131"/>
+      <c r="BF58" s="131"/>
+      <c r="BG58" s="131"/>
+      <c r="BH58" s="131"/>
+      <c r="BI58" s="131"/>
+      <c r="BJ58" s="131"/>
+      <c r="BK58" s="131"/>
+      <c r="BL58" s="131"/>
+      <c r="BM58" s="131"/>
+      <c r="BN58" s="131"/>
+      <c r="BO58" s="132"/>
     </row>
     <row r="59" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A59" s="129"/>
-      <c r="B59" s="91" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="105" t="str">
+      <c r="A59" s="128"/>
+      <c r="B59" s="90" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" s="104" t="str">
         <f t="shared" ref="C59" ca="1" si="12">IF(F59=E59, IF(TODAY()&gt;F59, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F59) - E59) / (F59 - E59) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D59" s="84" t="str">
+      <c r="D59" s="83" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E59" s="106">
+      <c r="E59" s="105">
         <v>45980</v>
       </c>
-      <c r="F59" s="106">
+      <c r="F59" s="105">
         <v>45981</v>
       </c>
-      <c r="G59" s="107" t="s">
+      <c r="G59" s="106" t="s">
         <v>114</v>
       </c>
       <c r="H59" s="48"/>
@@ -8345,25 +8403,25 @@
       <c r="BO59" s="49"/>
     </row>
     <row r="60" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A60" s="129"/>
-      <c r="B60" s="108" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" s="101" t="str">
+      <c r="A60" s="128"/>
+      <c r="B60" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" s="100" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>100%</v>
       </c>
-      <c r="D60" s="84" t="str">
+      <c r="D60" s="83" t="str">
         <f t="shared" si="0"/>
         <v>2일</v>
       </c>
-      <c r="E60" s="102">
+      <c r="E60" s="101">
         <v>45979</v>
       </c>
-      <c r="F60" s="102">
+      <c r="F60" s="101">
         <v>45980</v>
       </c>
-      <c r="G60" s="109" t="s">
+      <c r="G60" s="108" t="s">
         <v>114</v>
       </c>
       <c r="H60" s="59"/>
@@ -8428,13 +8486,13 @@
       <c r="BO60" s="49"/>
     </row>
     <row r="61" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A61" s="129"/>
+      <c r="A61" s="128"/>
       <c r="B61" s="60" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="32" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>83.3%</v>
+        <v>88.9%</v>
       </c>
       <c r="D61" s="56" t="str">
         <f t="shared" si="0"/>
@@ -8511,16 +8569,16 @@
       <c r="BO61" s="49"/>
     </row>
     <row r="62" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A62" s="129"/>
-      <c r="B62" s="124" t="s">
-        <v>160</v>
-      </c>
-      <c r="C62" s="119" t="str">
+      <c r="A62" s="128"/>
+      <c r="B62" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="118" t="str">
         <f ca="1">IF(F62=E62, IF(TODAY()&gt;F62, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F62) - E62) / (F62 - E62) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
       <c r="D62" s="21" t="str">
-        <f t="shared" ref="D62:D73" si="13">IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
+        <f t="shared" ref="D62:D74" si="13">IF(AND(F62&lt;&gt;"", E62&lt;&gt;""), F62 - E62 + 1 &amp; "일", "")</f>
         <v>9일</v>
       </c>
       <c r="E62" s="22">
@@ -8529,7 +8587,7 @@
       <c r="F62" s="22">
         <v>45988</v>
       </c>
-      <c r="G62" s="125" t="s">
+      <c r="G62" s="123" t="s">
         <v>114</v>
       </c>
       <c r="H62" s="48"/>
@@ -8594,11 +8652,11 @@
       <c r="BO62" s="49"/>
     </row>
     <row r="63" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="129"/>
-      <c r="B63" s="126" t="s">
+      <c r="A63" s="128"/>
+      <c r="B63" s="124" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="119" t="str">
+      <c r="C63" s="118" t="str">
         <f ca="1">IF(F63=E63, IF(TODAY()&gt;F63, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F63) - E63) / (F63 - E63) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
@@ -8612,7 +8670,7 @@
       <c r="F63" s="22">
         <v>45988</v>
       </c>
-      <c r="G63" s="125" t="s">
+      <c r="G63" s="123" t="s">
         <v>114</v>
       </c>
       <c r="H63" s="48"/>
@@ -8677,8 +8735,8 @@
       <c r="BO63" s="49"/>
     </row>
     <row r="64" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A64" s="129"/>
-      <c r="B64" s="127" t="s">
+      <c r="A64" s="128"/>
+      <c r="B64" s="125" t="s">
         <v>121</v>
       </c>
       <c r="C64" s="32" t="str">
@@ -8695,7 +8753,7 @@
       <c r="F64" s="22">
         <v>45989</v>
       </c>
-      <c r="G64" s="125" t="s">
+      <c r="G64" s="123" t="s">
         <v>116</v>
       </c>
       <c r="H64" s="48"/>
@@ -8760,9 +8818,9 @@
       <c r="BO64" s="49"/>
     </row>
     <row r="65" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A65" s="129"/>
-      <c r="B65" s="128" t="s">
-        <v>161</v>
+      <c r="A65" s="128"/>
+      <c r="B65" s="126" t="s">
+        <v>160</v>
       </c>
       <c r="C65" s="20" t="str">
         <f ca="1">IF(OR(E65="",F65=""), "0%", IF(F65=E65, IF(TODAY()&gt;F65, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F65) - E65) / (F65 - E65) * 100, 1) &amp; "%"))</f>
@@ -8778,7 +8836,7 @@
       <c r="F65" s="22">
         <v>45992</v>
       </c>
-      <c r="G65" s="125" t="s">
+      <c r="G65" s="123" t="s">
         <v>113</v>
       </c>
       <c r="H65" s="48"/>
@@ -8843,25 +8901,25 @@
       <c r="BO65" s="49"/>
     </row>
     <row r="66" spans="1:67" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="129"/>
-      <c r="B66" s="93" t="s">
+      <c r="A66" s="128"/>
+      <c r="B66" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="83" t="str">
+      <c r="C66" s="82" t="str">
         <f ca="1">IF(F66=E66, IF(TODAY()&gt;F66, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F66) - E66) / (F66 - E66) * 100, 1) &amp; "%")</f>
         <v>100%</v>
       </c>
-      <c r="D66" s="84" t="str">
+      <c r="D66" s="83" t="str">
         <f t="shared" si="13"/>
         <v>2일</v>
       </c>
-      <c r="E66" s="85">
+      <c r="E66" s="84">
         <v>45985</v>
       </c>
-      <c r="F66" s="85">
+      <c r="F66" s="84">
         <v>45986</v>
       </c>
-      <c r="G66" s="110" t="s">
+      <c r="G66" s="109" t="s">
         <v>113</v>
       </c>
       <c r="H66" s="48"/>
@@ -8926,13 +8984,13 @@
       <c r="BO66" s="49"/>
     </row>
     <row r="67" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A67" s="129"/>
-      <c r="B67" s="111" t="s">
+      <c r="A67" s="128"/>
+      <c r="B67" s="110" t="s">
         <v>162</v>
       </c>
       <c r="C67" s="39" t="str">
-        <f t="shared" ref="C67" ca="1" si="14">IF(F67=E67, IF(TODAY()&gt;F67, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F67) - E67) / (F67 - E67) * 100, 1) &amp; "%")</f>
-        <v>66.7%</v>
+        <f t="shared" ref="C67:C68" ca="1" si="14">IF(F67=E67, IF(TODAY()&gt;F67, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F67) - E67) / (F67 - E67) * 100, 1) &amp; "%")</f>
+        <v>77.8%</v>
       </c>
       <c r="D67" s="40" t="str">
         <f t="shared" si="13"/>
@@ -8944,7 +9002,7 @@
       <c r="F67" s="41">
         <v>45998</v>
       </c>
-      <c r="G67" s="112" t="s">
+      <c r="G67" s="111" t="s">
         <v>114</v>
       </c>
       <c r="H67" s="48"/>
@@ -9009,13 +9067,13 @@
       <c r="BO67" s="49"/>
     </row>
     <row r="68" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A68" s="130"/>
-      <c r="B68" s="111" t="s">
-        <v>156</v>
+      <c r="A68" s="128"/>
+      <c r="B68" s="125" t="s">
+        <v>164</v>
       </c>
       <c r="C68" s="39" t="str">
-        <f ca="1">IF(F68=E68, IF(TODAY()&gt;F68, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F68) - E68) / (F68 - E68) * 100, 1) &amp; "%")</f>
-        <v>76.9%</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>84.6%</v>
       </c>
       <c r="D68" s="40" t="str">
         <f t="shared" si="13"/>
@@ -9027,8 +9085,8 @@
       <c r="F68" s="41">
         <v>45998</v>
       </c>
-      <c r="G68" s="112" t="s">
-        <v>123</v>
+      <c r="G68" s="148" t="s">
+        <v>163</v>
       </c>
       <c r="H68" s="48"/>
       <c r="I68" s="49"/>
@@ -9092,28 +9150,26 @@
       <c r="BO68" s="49"/>
     </row>
     <row r="69" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A69" s="129" t="s">
-        <v>88</v>
-      </c>
-      <c r="B69" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="35" t="str">
+      <c r="A69" s="129"/>
+      <c r="B69" s="110" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="39" t="str">
         <f ca="1">IF(F69=E69, IF(TODAY()&gt;F69, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F69) - E69) / (F69 - E69) * 100, 1) &amp; "%")</f>
-        <v>0%</v>
-      </c>
-      <c r="D69" s="56" t="str">
+        <v>84.6%</v>
+      </c>
+      <c r="D69" s="40" t="str">
         <f t="shared" si="13"/>
-        <v>12일</v>
-      </c>
-      <c r="E69" s="36">
-        <v>45999</v>
-      </c>
-      <c r="F69" s="36">
-        <v>46010</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>95</v>
+        <v>14일</v>
+      </c>
+      <c r="E69" s="41">
+        <v>45985</v>
+      </c>
+      <c r="F69" s="41">
+        <v>45998</v>
+      </c>
+      <c r="G69" s="111" t="s">
+        <v>123</v>
       </c>
       <c r="H69" s="48"/>
       <c r="I69" s="49"/>
@@ -9163,40 +9219,42 @@
       <c r="BA69" s="49"/>
       <c r="BB69" s="50"/>
       <c r="BC69" s="51"/>
-      <c r="BD69" s="53"/>
-      <c r="BE69" s="53"/>
-      <c r="BF69" s="53"/>
-      <c r="BG69" s="53"/>
-      <c r="BH69" s="53"/>
-      <c r="BI69" s="53"/>
-      <c r="BJ69" s="53"/>
-      <c r="BK69" s="53"/>
-      <c r="BL69" s="53"/>
-      <c r="BM69" s="53"/>
-      <c r="BN69" s="53"/>
-      <c r="BO69" s="53"/>
+      <c r="BD69" s="49"/>
+      <c r="BE69" s="49"/>
+      <c r="BF69" s="49"/>
+      <c r="BG69" s="49"/>
+      <c r="BH69" s="49"/>
+      <c r="BI69" s="50"/>
+      <c r="BJ69" s="51"/>
+      <c r="BK69" s="49"/>
+      <c r="BL69" s="49"/>
+      <c r="BM69" s="49"/>
+      <c r="BN69" s="49"/>
+      <c r="BO69" s="49"/>
     </row>
-    <row r="70" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A70" s="129"/>
-      <c r="B70" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="C70" s="39" t="str">
-        <f ca="1">IF(OR(E70="",F70=""), "0%", IF(F70=E70, IF(TODAY()&gt;F70, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F70) - E70) / (F70 - E70) * 100, 1) &amp; "%"))</f>
+    <row r="70" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A70" s="128" t="s">
+        <v>88</v>
+      </c>
+      <c r="B70" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="35" t="str">
+        <f ca="1">IF(F70=E70, IF(TODAY()&gt;F70, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F70) - E70) / (F70 - E70) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
-      <c r="D70" s="40" t="str">
+      <c r="D70" s="56" t="str">
         <f t="shared" si="13"/>
-        <v>10일</v>
-      </c>
-      <c r="E70" s="41">
+        <v>12일</v>
+      </c>
+      <c r="E70" s="36">
         <v>45999</v>
       </c>
-      <c r="F70" s="41">
-        <v>46008</v>
-      </c>
-      <c r="G70" s="114" t="s">
-        <v>97</v>
+      <c r="F70" s="36">
+        <v>46010</v>
+      </c>
+      <c r="G70" s="37" t="s">
+        <v>95</v>
       </c>
       <c r="H70" s="48"/>
       <c r="I70" s="49"/>
@@ -9246,23 +9304,23 @@
       <c r="BA70" s="49"/>
       <c r="BB70" s="50"/>
       <c r="BC70" s="51"/>
-      <c r="BD70" s="49"/>
-      <c r="BE70" s="49"/>
-      <c r="BF70" s="49"/>
-      <c r="BG70" s="49"/>
-      <c r="BH70" s="49"/>
-      <c r="BI70" s="50"/>
-      <c r="BJ70" s="51"/>
-      <c r="BK70" s="49"/>
-      <c r="BL70" s="49"/>
-      <c r="BM70" s="49"/>
-      <c r="BN70" s="49"/>
-      <c r="BO70" s="49"/>
+      <c r="BD70" s="53"/>
+      <c r="BE70" s="53"/>
+      <c r="BF70" s="53"/>
+      <c r="BG70" s="53"/>
+      <c r="BH70" s="53"/>
+      <c r="BI70" s="53"/>
+      <c r="BJ70" s="53"/>
+      <c r="BK70" s="53"/>
+      <c r="BL70" s="53"/>
+      <c r="BM70" s="53"/>
+      <c r="BN70" s="53"/>
+      <c r="BO70" s="53"/>
     </row>
     <row r="71" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A71" s="129"/>
-      <c r="B71" s="115" t="s">
-        <v>87</v>
+      <c r="A71" s="128"/>
+      <c r="B71" s="112" t="s">
+        <v>2</v>
       </c>
       <c r="C71" s="39" t="str">
         <f ca="1">IF(OR(E71="",F71=""), "0%", IF(F71=E71, IF(TODAY()&gt;F71, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F71) - E71) / (F71 - E71) * 100, 1) &amp; "%"))</f>
@@ -9278,7 +9336,7 @@
       <c r="F71" s="41">
         <v>46008</v>
       </c>
-      <c r="G71" s="114" t="s">
+      <c r="G71" s="113" t="s">
         <v>97</v>
       </c>
       <c r="H71" s="48"/>
@@ -9343,9 +9401,9 @@
       <c r="BO71" s="49"/>
     </row>
     <row r="72" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A72" s="129"/>
-      <c r="B72" s="116" t="s">
-        <v>157</v>
+      <c r="A72" s="128"/>
+      <c r="B72" s="114" t="s">
+        <v>87</v>
       </c>
       <c r="C72" s="39" t="str">
         <f ca="1">IF(OR(E72="",F72=""), "0%", IF(F72=E72, IF(TODAY()&gt;F72, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F72) - E72) / (F72 - E72) * 100, 1) &amp; "%"))</f>
@@ -9361,7 +9419,7 @@
       <c r="F72" s="41">
         <v>46008</v>
       </c>
-      <c r="G72" s="114" t="s">
+      <c r="G72" s="113" t="s">
         <v>97</v>
       </c>
       <c r="H72" s="48"/>
@@ -9426,12 +9484,12 @@
       <c r="BO72" s="49"/>
     </row>
     <row r="73" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A73" s="129"/>
-      <c r="B73" s="149" t="s">
-        <v>163</v>
+      <c r="A73" s="128"/>
+      <c r="B73" s="115" t="s">
+        <v>156</v>
       </c>
       <c r="C73" s="39" t="str">
-        <f t="shared" ref="C73" ca="1" si="15">IF(F73=E73, IF(TODAY()&gt;F73, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F73) - E73) / (F73 - E73) * 100, 1) &amp; "%")</f>
+        <f ca="1">IF(OR(E73="",F73=""), "0%", IF(F73=E73, IF(TODAY()&gt;F73, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F73) - E73) / (F73 - E73) * 100, 1) &amp; "%"))</f>
         <v>0%</v>
       </c>
       <c r="D73" s="40" t="str">
@@ -9444,8 +9502,8 @@
       <c r="F73" s="41">
         <v>46008</v>
       </c>
-      <c r="G73" s="117" t="s">
-        <v>95</v>
+      <c r="G73" s="113" t="s">
+        <v>97</v>
       </c>
       <c r="H73" s="48"/>
       <c r="I73" s="49"/>
@@ -9508,17 +9566,17 @@
       <c r="BN73" s="49"/>
       <c r="BO73" s="49"/>
     </row>
-    <row r="74" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A74" s="129"/>
-      <c r="B74" s="111" t="s">
-        <v>3</v>
+    <row r="74" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A74" s="128"/>
+      <c r="B74" s="127" t="s">
+        <v>165</v>
       </c>
       <c r="C74" s="39" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="C74" ca="1" si="15">IF(F74=E74, IF(TODAY()&gt;F74, "100%", "0%"), ROUND(MAX(0, MIN(TODAY(), F74) - E74) / (F74 - E74) * 100, 1) &amp; "%")</f>
         <v>0%</v>
       </c>
       <c r="D74" s="40" t="str">
-        <f t="shared" ref="D74:D76" si="16">IF(AND(F74&lt;&gt;"", E74&lt;&gt;""), F74 - E74 + 1 &amp; "일", "")</f>
+        <f t="shared" si="13"/>
         <v>10일</v>
       </c>
       <c r="E74" s="41">
@@ -9527,7 +9585,7 @@
       <c r="F74" s="41">
         <v>46008</v>
       </c>
-      <c r="G74" s="117" t="s">
+      <c r="G74" s="116" t="s">
         <v>95</v>
       </c>
       <c r="H74" s="48"/>
@@ -9591,26 +9649,26 @@
       <c r="BN74" s="49"/>
       <c r="BO74" s="49"/>
     </row>
-    <row r="75" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A75" s="129"/>
-      <c r="B75" s="111" t="s">
-        <v>89</v>
+    <row r="75" spans="1:67" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A75" s="128"/>
+      <c r="B75" s="110" t="s">
+        <v>3</v>
       </c>
       <c r="C75" s="39" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>0%</v>
       </c>
       <c r="D75" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>3일</v>
+        <f t="shared" ref="D75:D77" si="16">IF(AND(F75&lt;&gt;"", E75&lt;&gt;""), F75 - E75 + 1 &amp; "일", "")</f>
+        <v>10일</v>
       </c>
       <c r="E75" s="41">
+        <v>45999</v>
+      </c>
+      <c r="F75" s="41">
         <v>46008</v>
       </c>
-      <c r="F75" s="41">
-        <v>46010</v>
-      </c>
-      <c r="G75" s="117" t="s">
+      <c r="G75" s="116" t="s">
         <v>95</v>
       </c>
       <c r="H75" s="48"/>
@@ -9675,9 +9733,9 @@
       <c r="BO75" s="49"/>
     </row>
     <row r="76" spans="1:67" ht="15.75" thickBot="1">
-      <c r="A76" s="130"/>
-      <c r="B76" s="111" t="s">
-        <v>90</v>
+      <c r="A76" s="128"/>
+      <c r="B76" s="110" t="s">
+        <v>89</v>
       </c>
       <c r="C76" s="39" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -9685,15 +9743,15 @@
       </c>
       <c r="D76" s="40" t="str">
         <f t="shared" si="16"/>
-        <v>1일</v>
+        <v>3일</v>
       </c>
       <c r="E76" s="41">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="F76" s="41">
         <v>46010</v>
       </c>
-      <c r="G76" s="117" t="s">
+      <c r="G76" s="116" t="s">
         <v>95</v>
       </c>
       <c r="H76" s="48"/>
@@ -9757,12 +9815,92 @@
       <c r="BN76" s="49"/>
       <c r="BO76" s="49"/>
     </row>
-    <row r="77" spans="1:67">
-      <c r="E77" s="7"/>
-      <c r="F77" s="1"/>
-      <c r="I77" s="3"/>
+    <row r="77" spans="1:67" ht="15.75" thickBot="1">
+      <c r="A77" s="129"/>
+      <c r="B77" s="110" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="39" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>0%</v>
+      </c>
+      <c r="D77" s="40" t="str">
+        <f t="shared" si="16"/>
+        <v>1일</v>
+      </c>
+      <c r="E77" s="41">
+        <v>46010</v>
+      </c>
+      <c r="F77" s="41">
+        <v>46010</v>
+      </c>
+      <c r="G77" s="116" t="s">
+        <v>95</v>
+      </c>
+      <c r="H77" s="48"/>
+      <c r="I77" s="49"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
+      <c r="L77" s="50"/>
+      <c r="M77" s="51"/>
+      <c r="N77" s="49"/>
+      <c r="O77" s="49"/>
+      <c r="P77" s="49"/>
+      <c r="Q77" s="49"/>
+      <c r="R77" s="49"/>
+      <c r="S77" s="50"/>
+      <c r="T77" s="51"/>
+      <c r="U77" s="49"/>
+      <c r="V77" s="49"/>
+      <c r="W77" s="49"/>
+      <c r="X77" s="49"/>
+      <c r="Y77" s="49"/>
+      <c r="Z77" s="50"/>
+      <c r="AA77" s="51"/>
+      <c r="AB77" s="49"/>
+      <c r="AC77" s="49"/>
+      <c r="AD77" s="49"/>
+      <c r="AE77" s="49"/>
+      <c r="AF77" s="49"/>
+      <c r="AG77" s="50"/>
+      <c r="AH77" s="51"/>
+      <c r="AI77" s="49"/>
+      <c r="AJ77" s="49"/>
+      <c r="AK77" s="49"/>
+      <c r="AL77" s="49"/>
+      <c r="AM77" s="49"/>
+      <c r="AN77" s="50"/>
+      <c r="AO77" s="51"/>
+      <c r="AP77" s="49"/>
+      <c r="AQ77" s="49"/>
+      <c r="AR77" s="49"/>
+      <c r="AS77" s="49"/>
+      <c r="AT77" s="49"/>
+      <c r="AU77" s="50"/>
+      <c r="AV77" s="51"/>
+      <c r="AW77" s="49"/>
+      <c r="AX77" s="49"/>
+      <c r="AY77" s="49"/>
+      <c r="AZ77" s="49"/>
+      <c r="BA77" s="49"/>
+      <c r="BB77" s="50"/>
+      <c r="BC77" s="51"/>
+      <c r="BD77" s="49"/>
+      <c r="BE77" s="49"/>
+      <c r="BF77" s="49"/>
+      <c r="BG77" s="49"/>
+      <c r="BH77" s="49"/>
+      <c r="BI77" s="50"/>
+      <c r="BJ77" s="51"/>
+      <c r="BK77" s="49"/>
+      <c r="BL77" s="49"/>
+      <c r="BM77" s="49"/>
+      <c r="BN77" s="49"/>
+      <c r="BO77" s="49"/>
     </row>
     <row r="78" spans="1:67">
+      <c r="E78" s="7"/>
+      <c r="F78" s="1"/>
       <c r="I78" s="3"/>
     </row>
     <row r="79" spans="1:67">
@@ -9775,45 +9913,44 @@
       <c r="I81" s="3"/>
     </row>
     <row r="82" spans="2:9">
-      <c r="B82" s="8" t="s">
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" spans="2:9">
+      <c r="B83" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="2:9" ht="16.5">
-      <c r="B83" s="9" t="s">
+    <row r="84" spans="2:9" ht="16.5">
+      <c r="B84" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" spans="2:9">
-      <c r="B84" s="10" t="s">
-        <v>93</v>
-      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" spans="2:9">
-      <c r="C85" s="3"/>
+      <c r="B85" s="10" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="86" spans="2:9">
       <c r="C86" s="3"/>
     </row>
-    <row r="87" spans="2:9"/>
+    <row r="87" spans="2:9">
+      <c r="C87" s="3"/>
+    </row>
     <row r="88" spans="2:9"/>
-    <row r="89" spans="2:9" ht="16.5">
-      <c r="B89" s="2"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-    </row>
-    <row r="90" spans="2:9">
+    <row r="89" spans="2:9"/>
+    <row r="90" spans="2:9" ht="16.5">
+      <c r="B90" s="2"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="2:9" ht="16.5">
-      <c r="B91" s="2"/>
+    <row r="91" spans="2:9">
+      <c r="C91" s="3"/>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="2:9">
-      <c r="C92" s="3"/>
+    <row r="92" spans="2:9" ht="16.5">
+      <c r="B92" s="2"/>
       <c r="D92" s="3"/>
     </row>
     <row r="93" spans="2:9">
@@ -9821,22 +9958,26 @@
       <c r="D93" s="3"/>
     </row>
     <row r="94" spans="2:9">
+      <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="3"/>
-      <c r="H95" s="11"/>
     </row>
-    <row r="96" spans="2:9" ht="15" customHeight="1">
+    <row r="96" spans="2:9">
       <c r="D96" s="3"/>
+      <c r="H96" s="11"/>
     </row>
     <row r="97" spans="3:4" ht="15" customHeight="1">
-      <c r="C97" s="3"/>
       <c r="D97" s="3"/>
+    </row>
+    <row r="98" spans="3:4" ht="15" customHeight="1">
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A69:A76"/>
+    <mergeCell ref="A70:A77"/>
     <mergeCell ref="H51:BO51"/>
     <mergeCell ref="H42:BO42"/>
     <mergeCell ref="C1:E1"/>
@@ -9847,7 +9988,7 @@
     <mergeCell ref="B42:G42"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A12:A68"/>
+    <mergeCell ref="A12:A69"/>
     <mergeCell ref="H17:BO17"/>
     <mergeCell ref="H21:BO21"/>
     <mergeCell ref="B58:G58"/>
